--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{143E446D-C230-4A80-8DE4-E4FD442E7D72}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="333">
   <si>
     <t>Nome account</t>
   </si>
@@ -995,6 +995,30 @@
   </si>
   <si>
     <t>VIA FABIO FILZI 7</t>
+  </si>
+  <si>
+    <t>VEN.SAR. SRL</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>VIA ALGHERO 33</t>
+  </si>
+  <si>
+    <t>CAGLIARI</t>
+  </si>
+  <si>
+    <t>09127</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
+    <t>STM26 SRL</t>
+  </si>
+  <si>
+    <t>VIA PIETRO NENNI 6/E</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1069,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1068,11 +1092,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD5D3D1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD5D3D1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1084,6 +1119,10 @@
     <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1398,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" customWidth="1"/>
@@ -3871,6 +3910,52 @@
         <v>38</v>
       </c>
     </row>
+    <row r="108" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>325</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D108" t="s">
+        <v>327</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>331</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" t="s">
+        <v>332</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F109" s="6">
+        <v>40026</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="A2:G107">
     <sortCondition ref="A1"/>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{143E446D-C230-4A80-8DE4-E4FD442E7D72}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{E781357D-F26A-4A91-B56E-73EDE6F04AC1}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="340">
   <si>
     <t>Nome account</t>
   </si>
@@ -1019,6 +1019,27 @@
   </si>
   <si>
     <t>VIA PIETRO NENNI 6/E</t>
+  </si>
+  <si>
+    <t>MENINAS SRL</t>
+  </si>
+  <si>
+    <t>DS ITALIA 56 SRL</t>
+  </si>
+  <si>
+    <t>VIA DEL PLEBISCITO 112</t>
+  </si>
+  <si>
+    <t>FLYSUN 10 SRL</t>
+  </si>
+  <si>
+    <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+  </si>
+  <si>
+    <t>AUKERA ITALY 9 SRL</t>
+  </si>
+  <si>
+    <t>LARGO GUIDO DONEGANI 2</t>
   </si>
 </sst>
 </file>
@@ -1437,7 +1458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" customWidth="1"/>
@@ -3914,22 +3935,22 @@
       <c r="A108" t="s">
         <v>325</v>
       </c>
-      <c r="B108" s="5" t="s">
+      <c r="B108" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C108" s="5" t="s">
+      <c r="C108" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D108" t="s">
         <v>327</v>
       </c>
-      <c r="E108" s="5" t="s">
+      <c r="E108" s="3" t="s">
         <v>328</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="G108" s="5" t="s">
+      <c r="G108" s="2" t="s">
         <v>330</v>
       </c>
     </row>
@@ -3937,24 +3958,129 @@
       <c r="A109" t="s">
         <v>331</v>
       </c>
-      <c r="B109" s="5" t="s">
+      <c r="B109" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C109" s="5" t="s">
+      <c r="C109" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D109" t="s">
         <v>332</v>
       </c>
-      <c r="E109" s="5" t="s">
+      <c r="E109" s="3" t="s">
         <v>318</v>
       </c>
       <c r="F109" s="6">
         <v>40026</v>
       </c>
-      <c r="G109" s="5" t="s">
+      <c r="G109" s="2" t="s">
         <v>26</v>
       </c>
+    </row>
+    <row r="110" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>333</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" t="s">
+        <v>189</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F110" s="6">
+        <v>20158</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>334</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D111" t="s">
+        <v>335</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>336</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" t="s">
+        <v>337</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F112" s="6">
+        <v>10153</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>338</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D113" t="s">
+        <v>339</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F113" s="6">
+        <v>20121</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E114" s="3"/>
+      <c r="G114" s="2"/>
+    </row>
+    <row r="115" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E115" s="3"/>
+    </row>
+    <row r="116" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E116" s="3"/>
+    </row>
+    <row r="117" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E117" s="3"/>
     </row>
   </sheetData>
   <sortState ref="A2:G107">

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{E781357D-F26A-4A91-B56E-73EDE6F04AC1}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D156B79F-0EFF-4528-955C-CBA90DCDAA55}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="345">
   <si>
     <t>Nome account</t>
   </si>
@@ -1040,6 +1040,21 @@
   </si>
   <si>
     <t>LARGO GUIDO DONEGANI 2</t>
+  </si>
+  <si>
+    <t>REN UP SRL</t>
+  </si>
+  <si>
+    <t>VR</t>
+  </si>
+  <si>
+    <t>VIA GOITO 4</t>
+  </si>
+  <si>
+    <t>LEGNANO</t>
+  </si>
+  <si>
+    <t>Verona</t>
   </si>
 </sst>
 </file>
@@ -4070,8 +4085,27 @@
       </c>
     </row>
     <row r="114" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="E114" s="3"/>
-      <c r="G114" s="2"/>
+      <c r="A114" t="s">
+        <v>340</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" t="s">
+        <v>342</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="F114" s="6">
+        <v>37045</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="115" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="E115" s="3"/>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D156B79F-0EFF-4528-955C-CBA90DCDAA55}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{CC9BD2AF-A053-4A68-A7EC-62983E05E8F4}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="346">
   <si>
     <t>Nome account</t>
   </si>
@@ -1055,6 +1055,9 @@
   </si>
   <si>
     <t>Verona</t>
+  </si>
+  <si>
+    <t>ABEI ENERGY GREEN ITALY VI SRL</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1108,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1128,22 +1131,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD5D3D1"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD5D3D1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1153,9 +1145,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1473,7 +1462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" customWidth="1"/>
@@ -3962,7 +3951,7 @@
       <c r="E108" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="6" t="s">
+      <c r="F108" s="5" t="s">
         <v>329</v>
       </c>
       <c r="G108" s="2" t="s">
@@ -3985,7 +3974,7 @@
       <c r="E109" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="F109" s="6">
+      <c r="F109" s="5">
         <v>40026</v>
       </c>
       <c r="G109" s="2" t="s">
@@ -4008,7 +3997,7 @@
       <c r="E110" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F110" s="6">
+      <c r="F110" s="5">
         <v>20158</v>
       </c>
       <c r="G110" s="2" t="s">
@@ -4054,7 +4043,7 @@
       <c r="E112" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F112" s="6">
+      <c r="F112" s="5">
         <v>10153</v>
       </c>
       <c r="G112" s="3" t="s">
@@ -4068,7 +4057,7 @@
       <c r="B113" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C113" s="5" t="s">
+      <c r="C113" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D113" t="s">
@@ -4077,7 +4066,7 @@
       <c r="E113" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F113" s="6">
+      <c r="F113" s="5">
         <v>20121</v>
       </c>
       <c r="G113" s="3" t="s">
@@ -4088,10 +4077,10 @@
       <c r="A114" t="s">
         <v>340</v>
       </c>
-      <c r="B114" s="5" t="s">
+      <c r="B114" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="C114" s="5" t="s">
+      <c r="C114" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D114" t="s">
@@ -4100,7 +4089,7 @@
       <c r="E114" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="F114" s="6">
+      <c r="F114" s="5">
         <v>37045</v>
       </c>
       <c r="G114" s="3" t="s">
@@ -4108,13 +4097,45 @@
       </c>
     </row>
     <row r="115" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="E115" s="3"/>
+      <c r="A115" t="s">
+        <v>345</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D115" t="s">
+        <v>222</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="116" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
       <c r="E116" s="3"/>
+      <c r="G116" s="3"/>
     </row>
     <row r="117" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
       <c r="E117" s="3"/>
+      <c r="G117" s="3"/>
+    </row>
+    <row r="118" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B118" s="3"/>
+    </row>
+    <row r="119" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B119" s="3"/>
     </row>
   </sheetData>
   <sortState ref="A2:G107">

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{CC9BD2AF-A053-4A68-A7EC-62983E05E8F4}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{6DBE207D-EA07-4B0D-90BB-C4AC469064AF}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="358">
   <si>
     <t>Nome account</t>
   </si>
@@ -1058,6 +1058,42 @@
   </si>
   <si>
     <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+  </si>
+  <si>
+    <t>HF SOLAR 4 SRL</t>
+  </si>
+  <si>
+    <t>MAXIMA PV 1 SRL</t>
+  </si>
+  <si>
+    <t>VIA MARCO PARTIPILO 48</t>
+  </si>
+  <si>
+    <t>BARI</t>
+  </si>
+  <si>
+    <t>ARNG SOLAR XI SRL</t>
+  </si>
+  <si>
+    <t>CORSO EUROPA 13</t>
+  </si>
+  <si>
+    <t>FIMENERGIA SRL</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>VIA LUIGI BUZZI 6</t>
+  </si>
+  <si>
+    <t>CASALE MONFERRATO</t>
+  </si>
+  <si>
+    <t>OPEN SOLAR 3 SRL</t>
+  </si>
+  <si>
+    <t>PIAZZA CARLO MIRABELLO 2</t>
   </si>
 </sst>
 </file>
@@ -1108,7 +1144,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1131,11 +1167,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD5D3D1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD5D3D1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1148,6 +1195,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1462,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" customWidth="1"/>
@@ -4120,22 +4170,119 @@
       </c>
     </row>
     <row r="116" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
-      <c r="E116" s="3"/>
-      <c r="G116" s="3"/>
+      <c r="A116" t="s">
+        <v>346</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D116" t="s">
+        <v>195</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F116" s="5">
+        <v>20123</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="117" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
-      <c r="E117" s="3"/>
-      <c r="G117" s="3"/>
+      <c r="A117" t="s">
+        <v>347</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D117" t="s">
+        <v>348</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F117" s="5">
+        <v>70124</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="118" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B118" s="3"/>
+      <c r="A118" t="s">
+        <v>350</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D118" t="s">
+        <v>351</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F118" s="5">
+        <v>20122</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="119" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B119" s="3"/>
+      <c r="A119" t="s">
+        <v>352</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D119" t="s">
+        <v>354</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="F119" s="5">
+        <v>15033</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>356</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D120" t="s">
+        <v>357</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F120" s="5">
+        <v>20121</v>
+      </c>
+      <c r="G120" s="6" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <sortState ref="A2:G107">

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{6DBE207D-EA07-4B0D-90BB-C4AC469064AF}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{BC317B22-60D5-4449-AA95-74F15B8295B0}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="370">
   <si>
     <t>Nome account</t>
   </si>
@@ -1094,6 +1094,42 @@
   </si>
   <si>
     <t>PIAZZA CARLO MIRABELLO 2</t>
+  </si>
+  <si>
+    <t>MGM SOLAR SRL</t>
+  </si>
+  <si>
+    <t>STRADA STATALE 28 SUD 14</t>
+  </si>
+  <si>
+    <t>MONDOVI</t>
+  </si>
+  <si>
+    <t>HF SOLAR 18 SRL</t>
+  </si>
+  <si>
+    <t>PIAZZA FRANCESCO CRISPI 1</t>
+  </si>
+  <si>
+    <t>ELIOS SRL</t>
+  </si>
+  <si>
+    <t>BT</t>
+  </si>
+  <si>
+    <t>VIA VINCENZO GIOBERTI 11</t>
+  </si>
+  <si>
+    <t>ANDRIA</t>
+  </si>
+  <si>
+    <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+  </si>
+  <si>
+    <t>SANTA BARBARA ENERGIA SRL</t>
+  </si>
+  <si>
+    <t>VIA LANZONE 31</t>
   </si>
 </sst>
 </file>
@@ -1512,7 +1548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" customWidth="1"/>
@@ -4222,7 +4258,7 @@
       <c r="B118" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C118" s="6" t="s">
+      <c r="C118" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D118" t="s">
@@ -4234,7 +4270,7 @@
       <c r="F118" s="5">
         <v>20122</v>
       </c>
-      <c r="G118" s="6" t="s">
+      <c r="G118" s="3" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4245,7 +4281,7 @@
       <c r="B119" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="C119" s="6" t="s">
+      <c r="C119" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D119" t="s">
@@ -4257,7 +4293,7 @@
       <c r="F119" s="5">
         <v>15033</v>
       </c>
-      <c r="G119" s="6" t="s">
+      <c r="G119" s="3" t="s">
         <v>83</v>
       </c>
     </row>
@@ -4265,10 +4301,10 @@
       <c r="A120" t="s">
         <v>356</v>
       </c>
-      <c r="B120" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C120" s="6" t="s">
+      <c r="B120" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C120" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D120" t="s">
@@ -4280,9 +4316,160 @@
       <c r="F120" s="5">
         <v>20121</v>
       </c>
-      <c r="G120" s="6" t="s">
+      <c r="G120" s="3" t="s">
         <v>38</v>
       </c>
+    </row>
+    <row r="121" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>358</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D121" t="s">
+        <v>359</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="F121" s="5">
+        <v>12084</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>361</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D122" t="s">
+        <v>362</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F122" s="5">
+        <v>90139</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>363</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D123" t="s">
+        <v>365</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="F123" s="5">
+        <v>76123</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>367</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" t="s">
+        <v>60</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F124" s="5">
+        <v>20123</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>368</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125" t="s">
+        <v>369</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F125" s="5">
+        <v>20123</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="G126" s="3"/>
+    </row>
+    <row r="127" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="G127" s="3"/>
+    </row>
+    <row r="128" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="G128" s="3"/>
+    </row>
+    <row r="129" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="G129" s="3"/>
+    </row>
+    <row r="130" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="G130" s="3"/>
+    </row>
+    <row r="131" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="G131" s="3"/>
+    </row>
+    <row r="132" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B132" s="3"/>
+    </row>
+    <row r="133" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B133" s="3"/>
     </row>
   </sheetData>
   <sortState ref="A2:G107">

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{BC317B22-60D5-4449-AA95-74F15B8295B0}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D52810F1-AF21-48B1-A804-5F9E06E48BBF}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="385">
   <si>
     <t>Nome account</t>
   </si>
@@ -1130,6 +1130,51 @@
   </si>
   <si>
     <t>VIA LANZONE 31</t>
+  </si>
+  <si>
+    <t>HERGO RENEWABLES SPA</t>
+  </si>
+  <si>
+    <t>VIA PRIVATA MARIA TERESA 8</t>
+  </si>
+  <si>
+    <t>EOR POWER SRL</t>
+  </si>
+  <si>
+    <t>PU</t>
+  </si>
+  <si>
+    <t>VIA DELLE GALIGARIE 6</t>
+  </si>
+  <si>
+    <t>PESARO</t>
+  </si>
+  <si>
+    <t>ECOPIEDMONT 1 SRL</t>
+  </si>
+  <si>
+    <t>VIA SENATO 28</t>
+  </si>
+  <si>
+    <t>R.M. SOLAR SRL</t>
+  </si>
+  <si>
+    <t>TE</t>
+  </si>
+  <si>
+    <t>CONTRADA SANT'ARCANGELO 93</t>
+  </si>
+  <si>
+    <t>BELLANTE</t>
+  </si>
+  <si>
+    <t>SOLE PV SOLAR 3 SRL</t>
+  </si>
+  <si>
+    <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
+  </si>
+  <si>
+    <t>ROZZANO</t>
   </si>
 </sst>
 </file>
@@ -1180,7 +1225,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1203,22 +1248,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD5D3D1"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD5D3D1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1231,9 +1265,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1548,7 +1579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" customWidth="1"/>
@@ -4264,7 +4295,7 @@
       <c r="D118" t="s">
         <v>351</v>
       </c>
-      <c r="E118" s="6" t="s">
+      <c r="E118" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F118" s="5">
@@ -4287,7 +4318,7 @@
       <c r="D119" t="s">
         <v>354</v>
       </c>
-      <c r="E119" s="6" t="s">
+      <c r="E119" s="3" t="s">
         <v>355</v>
       </c>
       <c r="F119" s="5">
@@ -4310,7 +4341,7 @@
       <c r="D120" t="s">
         <v>357</v>
       </c>
-      <c r="E120" s="6" t="s">
+      <c r="E120" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F120" s="5">
@@ -4333,7 +4364,7 @@
       <c r="D121" t="s">
         <v>359</v>
       </c>
-      <c r="E121" s="6" t="s">
+      <c r="E121" s="3" t="s">
         <v>360</v>
       </c>
       <c r="F121" s="5">
@@ -4356,7 +4387,7 @@
       <c r="D122" t="s">
         <v>362</v>
       </c>
-      <c r="E122" s="6" t="s">
+      <c r="E122" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F122" s="5">
@@ -4379,7 +4410,7 @@
       <c r="D123" t="s">
         <v>365</v>
       </c>
-      <c r="E123" s="6" t="s">
+      <c r="E123" s="3" t="s">
         <v>366</v>
       </c>
       <c r="F123" s="5">
@@ -4402,7 +4433,7 @@
       <c r="D124" t="s">
         <v>60</v>
       </c>
-      <c r="E124" s="6" t="s">
+      <c r="E124" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F124" s="5">
@@ -4425,7 +4456,7 @@
       <c r="D125" t="s">
         <v>369</v>
       </c>
-      <c r="E125" s="6" t="s">
+      <c r="E125" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F125" s="5">
@@ -4436,40 +4467,151 @@
       </c>
     </row>
     <row r="126" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B126" s="3"/>
-      <c r="C126" s="3"/>
-      <c r="G126" s="3"/>
+      <c r="A126" t="s">
+        <v>370</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" t="s">
+        <v>371</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F126" s="5">
+        <v>20123</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="127" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B127" s="3"/>
-      <c r="C127" s="3"/>
-      <c r="G127" s="3"/>
+      <c r="A127" t="s">
+        <v>372</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D127" t="s">
+        <v>374</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="F127" s="5">
+        <v>61121</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="128" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B128" s="3"/>
-      <c r="C128" s="3"/>
-      <c r="G128" s="3"/>
-    </row>
-    <row r="129" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B129" s="3"/>
-      <c r="C129" s="3"/>
-      <c r="G129" s="3"/>
-    </row>
-    <row r="130" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B130" s="3"/>
-      <c r="C130" s="3"/>
-      <c r="G130" s="3"/>
-    </row>
-    <row r="131" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>376</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D128" t="s">
+        <v>377</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F128" s="5">
+        <v>20121</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>378</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D129" t="s">
+        <v>380</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="F129" s="5">
+        <v>64020</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>382</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D130" t="s">
+        <v>383</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="F130" s="5">
+        <v>20089</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
+      <c r="E131" s="3"/>
       <c r="G131" s="3"/>
     </row>
-    <row r="132" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B132" s="3"/>
-    </row>
-    <row r="133" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E132" s="3"/>
+    </row>
+    <row r="133" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B133" s="3"/>
+      <c r="E133" s="3"/>
+    </row>
+    <row r="134" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E134" s="3"/>
+    </row>
+    <row r="135" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E135" s="3"/>
+    </row>
+    <row r="136" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E136" s="3"/>
+    </row>
+    <row r="137" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E137" s="3"/>
+    </row>
+    <row r="138" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E138" s="3"/>
+    </row>
+    <row r="139" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E139" s="3"/>
     </row>
   </sheetData>
   <sortState ref="A2:G107">

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D52810F1-AF21-48B1-A804-5F9E06E48BBF}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{6248BB91-1CC2-4613-B312-022B0278FFE5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="387">
   <si>
     <t>Nome account</t>
   </si>
@@ -1175,6 +1175,12 @@
   </si>
   <si>
     <t>ROZZANO</t>
+  </si>
+  <si>
+    <t>LIO ENERGY BUBO SRL</t>
+  </si>
+  <si>
+    <t>VIA ARRIGO BOITO 8</t>
   </si>
 </sst>
 </file>
@@ -4582,10 +4588,27 @@
       </c>
     </row>
     <row r="131" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B131" s="3"/>
-      <c r="C131" s="3"/>
-      <c r="E131" s="3"/>
-      <c r="G131" s="3"/>
+      <c r="A131" t="s">
+        <v>385</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D131" t="s">
+        <v>386</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F131" s="5">
+        <v>20121</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="132" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B132" s="3"/>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{6248BB91-1CC2-4613-B312-022B0278FFE5}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{393B3E21-5EED-4D72-A028-73DC6F2A67FA}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="390">
   <si>
     <t>Nome account</t>
   </si>
@@ -1181,6 +1181,15 @@
   </si>
   <si>
     <t>VIA ARRIGO BOITO 8</t>
+  </si>
+  <si>
+    <t>LIO ENERGY TAURUS SRL</t>
+  </si>
+  <si>
+    <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+  </si>
+  <si>
+    <t>VIA BENEDETTO CROCE 19</t>
   </si>
 </sst>
 </file>
@@ -1231,7 +1240,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1254,11 +1263,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD5D3D1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD5D3D1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1271,6 +1291,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -4611,12 +4634,50 @@
       </c>
     </row>
     <row r="132" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B132" s="3"/>
-      <c r="E132" s="3"/>
+      <c r="A132" t="s">
+        <v>387</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D132" t="s">
+        <v>386</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F132" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="133" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B133" s="3"/>
-      <c r="E133" s="3"/>
+      <c r="A133" t="s">
+        <v>388</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D133" t="s">
+        <v>389</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F133" s="5">
+        <v>142</v>
+      </c>
+      <c r="G133" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="134" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="E134" s="3"/>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{393B3E21-5EED-4D72-A028-73DC6F2A67FA}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{2D94519B-72F6-42DD-8F56-B2CC8BAD82F0}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="392">
   <si>
     <t>Nome account</t>
   </si>
@@ -1190,6 +1190,12 @@
   </si>
   <si>
     <t>VIA BENEDETTO CROCE 19</t>
+  </si>
+  <si>
+    <t>CONTOURGLOBAL AUGIA SRL</t>
+  </si>
+  <si>
+    <t>00142</t>
   </si>
 </sst>
 </file>
@@ -1240,7 +1246,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1263,22 +1269,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD5D3D1"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD5D3D1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1291,9 +1286,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -4640,7 +4632,7 @@
       <c r="B132" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C132" s="6" t="s">
+      <c r="C132" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D132" t="s">
@@ -4663,7 +4655,7 @@
       <c r="B133" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C133" s="6" t="s">
+      <c r="C133" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D133" t="s">
@@ -4672,29 +4664,62 @@
       <c r="E133" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F133" s="5">
-        <v>142</v>
-      </c>
-      <c r="G133" s="6" t="s">
+      <c r="F133" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="G133" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="E134" s="3"/>
+      <c r="A134" t="s">
+        <v>390</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D134" t="s">
+        <v>270</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F134" s="5">
+        <v>20123</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="135" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
       <c r="E135" s="3"/>
+      <c r="G135" s="3"/>
     </row>
     <row r="136" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
       <c r="E136" s="3"/>
+      <c r="G136" s="3"/>
     </row>
     <row r="137" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
       <c r="E137" s="3"/>
+      <c r="G137" s="3"/>
     </row>
     <row r="138" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
       <c r="E138" s="3"/>
+      <c r="G138" s="3"/>
     </row>
     <row r="139" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B139" s="3"/>
       <c r="E139" s="3"/>
     </row>
   </sheetData>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{2D94519B-72F6-42DD-8F56-B2CC8BAD82F0}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{535DC2EC-74E0-42D9-941B-96B6DFD09BF7}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="402">
   <si>
     <t>Nome account</t>
   </si>
@@ -1196,6 +1196,36 @@
   </si>
   <si>
     <t>00142</t>
+  </si>
+  <si>
+    <t>ENERGETICA SALENTINA SRL</t>
+  </si>
+  <si>
+    <t>VIA BAIONE 200</t>
+  </si>
+  <si>
+    <t>TRINA SOLAR PAPIRO SRL</t>
+  </si>
+  <si>
+    <t>PIAZZA BORROMEO 14</t>
+  </si>
+  <si>
+    <t>OPDENERGY SALENTO 3 SRL</t>
+  </si>
+  <si>
+    <t>X ELIO ITALIA 6 SRL</t>
+  </si>
+  <si>
+    <t>CONTOURGLOBAL LERNA SRL</t>
+  </si>
+  <si>
+    <t>ASJA NURRA SRL</t>
+  </si>
+  <si>
+    <t>APOLLOSA SOLAR PARK SRL</t>
+  </si>
+  <si>
+    <t>VIALE FRANCESCO RESTELLI 3/7</t>
   </si>
 </sst>
 </file>
@@ -1246,7 +1276,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1269,11 +1299,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD5D3D1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD5D3D1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1286,6 +1327,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1600,7 +1644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" customWidth="1"/>
@@ -4695,32 +4739,183 @@
       </c>
     </row>
     <row r="135" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B135" s="3"/>
-      <c r="C135" s="3"/>
-      <c r="E135" s="3"/>
-      <c r="G135" s="3"/>
+      <c r="A135" t="s">
+        <v>392</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D135" t="s">
+        <v>393</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F135" s="5">
+        <v>70043</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="136" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B136" s="3"/>
-      <c r="C136" s="3"/>
-      <c r="E136" s="3"/>
-      <c r="G136" s="3"/>
+      <c r="A136" t="s">
+        <v>394</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D136" t="s">
+        <v>395</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F136" s="5">
+        <v>20123</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="137" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B137" s="3"/>
-      <c r="C137" s="3"/>
-      <c r="E137" s="3"/>
-      <c r="G137" s="3"/>
+      <c r="A137" t="s">
+        <v>396</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D137" t="s">
+        <v>23</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F137" s="5">
+        <v>40127</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="138" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B138" s="3"/>
-      <c r="C138" s="3"/>
-      <c r="E138" s="3"/>
-      <c r="G138" s="3"/>
+      <c r="A138" t="s">
+        <v>397</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D138" t="s">
+        <v>217</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="139" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B139" s="3"/>
-      <c r="E139" s="3"/>
+      <c r="A139" t="s">
+        <v>398</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D139" t="s">
+        <v>270</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F139" s="5">
+        <v>20123</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>399</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D140" t="s">
+        <v>80</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F140" s="5">
+        <v>10123</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>400</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D141" t="s">
+        <v>401</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F141" s="5">
+        <v>20124</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B142" s="3"/>
+      <c r="E142" s="3"/>
+      <c r="G142" s="3"/>
+    </row>
+    <row r="143" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B143" s="3"/>
+      <c r="E143" s="3"/>
+      <c r="G143" s="3"/>
+    </row>
+    <row r="144" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="G144" s="3"/>
+    </row>
+    <row r="145" spans="2:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B145" s="3"/>
     </row>
   </sheetData>
   <sortState ref="A2:G107">

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{535DC2EC-74E0-42D9-941B-96B6DFD09BF7}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{6D3024FC-FAC0-41E4-B8EF-313567C83AC8}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="404">
   <si>
     <t>Nome account</t>
   </si>
@@ -1226,6 +1226,12 @@
   </si>
   <si>
     <t>VIALE FRANCESCO RESTELLI 3/7</t>
+  </si>
+  <si>
+    <t>AG 31 SRL</t>
+  </si>
+  <si>
+    <t>PIAZZALE LUIGI CADORNA 6</t>
   </si>
 </sst>
 </file>
@@ -4900,9 +4906,27 @@
       </c>
     </row>
     <row r="142" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B142" s="3"/>
-      <c r="E142" s="3"/>
-      <c r="G142" s="3"/>
+      <c r="A142" t="s">
+        <v>402</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D142" t="s">
+        <v>403</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F142" s="5">
+        <v>20123</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="143" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B143" s="3"/>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{6D3024FC-FAC0-41E4-B8EF-313567C83AC8}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{8860DA08-5610-4E10-8C16-2503EAB4D620}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="406">
   <si>
     <t>Nome account</t>
   </si>
@@ -1232,6 +1232,12 @@
   </si>
   <si>
     <t>PIAZZALE LUIGI CADORNA 6</t>
+  </si>
+  <si>
+    <t>APOLLO FOGGIA SRL</t>
+  </si>
+  <si>
+    <t>VIALE DELLA STAZIONE 8</t>
   </si>
 </sst>
 </file>
@@ -4929,9 +4935,27 @@
       </c>
     </row>
     <row r="143" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B143" s="3"/>
-      <c r="E143" s="3"/>
-      <c r="G143" s="3"/>
+      <c r="A143" t="s">
+        <v>404</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D143" t="s">
+        <v>405</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F143" s="5">
+        <v>39100</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="144" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B144" s="3"/>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{8860DA08-5610-4E10-8C16-2503EAB4D620}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{88DF3B35-447D-4DDF-886B-BEB480BB216B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="411">
   <si>
     <t>Nome account</t>
   </si>
@@ -1238,6 +1238,21 @@
   </si>
   <si>
     <t>VIALE DELLA STAZIONE 8</t>
+  </si>
+  <si>
+    <t>REVALUE PV 8 SRL</t>
+  </si>
+  <si>
+    <t>HEPV12 SRL</t>
+  </si>
+  <si>
+    <t>VIA ALTO ADIGE 160/A</t>
+  </si>
+  <si>
+    <t>TRENTO</t>
+  </si>
+  <si>
+    <t>CUBICO NORA SRL</t>
   </si>
 </sst>
 </file>
@@ -1656,7 +1671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" customWidth="1"/>
@@ -4958,12 +4973,73 @@
       </c>
     </row>
     <row r="144" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B144" s="3"/>
-      <c r="E144" s="3"/>
-      <c r="G144" s="3"/>
-    </row>
-    <row r="145" spans="2:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B145" s="3"/>
+      <c r="A144" t="s">
+        <v>406</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D144" t="s">
+        <v>260</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F144" s="5">
+        <v>20135</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>407</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D145" t="s">
+        <v>408</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="F145" s="5">
+        <v>38121</v>
+      </c>
+      <c r="G145" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>410</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D146" t="s">
+        <v>122</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F146" s="5">
+        <v>20121</v>
+      </c>
+      <c r="G146" s="6" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <sortState ref="A2:G107">

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{88DF3B35-447D-4DDF-886B-BEB480BB216B}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{7790D114-10A0-40E8-B981-5A57421918F1}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Report!$A$1:$G$147</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="415">
   <si>
     <t>Nome account</t>
   </si>
@@ -1253,6 +1256,18 @@
   </si>
   <si>
     <t>CUBICO NORA SRL</t>
+  </si>
+  <si>
+    <t>RAMACCA AGRISOLAR SRL</t>
+  </si>
+  <si>
+    <t>JUWI ENERGIE RINNOVABILI SRL</t>
+  </si>
+  <si>
+    <t>VIA SOMMACAMPAGNA 59/D</t>
+  </si>
+  <si>
+    <t>VERONA</t>
   </si>
 </sst>
 </file>
@@ -1671,7 +1686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G194"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" customWidth="1"/>
@@ -4864,7 +4879,7 @@
       <c r="B139" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C139" s="6" t="s">
+      <c r="C139" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D139" t="s">
@@ -4887,7 +4902,7 @@
       <c r="B140" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C140" s="6" t="s">
+      <c r="C140" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D140" t="s">
@@ -4910,7 +4925,7 @@
       <c r="B141" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C141" s="6" t="s">
+      <c r="C141" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D141" t="s">
@@ -4933,7 +4948,7 @@
       <c r="B142" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C142" s="6" t="s">
+      <c r="C142" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D142" t="s">
@@ -4956,7 +4971,7 @@
       <c r="B143" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C143" s="6" t="s">
+      <c r="C143" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D143" t="s">
@@ -4979,7 +4994,7 @@
       <c r="B144" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C144" s="6" t="s">
+      <c r="C144" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D144" t="s">
@@ -5002,7 +5017,7 @@
       <c r="B145" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="C145" s="6" t="s">
+      <c r="C145" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D145" t="s">
@@ -5022,10 +5037,10 @@
       <c r="A146" t="s">
         <v>410</v>
       </c>
-      <c r="B146" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C146" s="6" t="s">
+      <c r="B146" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C146" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D146" t="s">
@@ -5041,7 +5056,214 @@
         <v>38</v>
       </c>
     </row>
+    <row r="147" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>411</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D147" t="s">
+        <v>211</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F147" s="5">
+        <v>20121</v>
+      </c>
+      <c r="G147" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>412</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D148" t="s">
+        <v>413</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="F148" s="5">
+        <v>37137</v>
+      </c>
+      <c r="G148" s="6" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>256</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D149" t="s">
+        <v>230</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F149" s="5">
+        <v>20148</v>
+      </c>
+      <c r="G149" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B150" s="3"/>
+      <c r="C150" s="3"/>
+    </row>
+    <row r="151" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+    </row>
+    <row r="152" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C152" s="3"/>
+    </row>
+    <row r="153" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C153" s="3"/>
+    </row>
+    <row r="154" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C154" s="3"/>
+    </row>
+    <row r="155" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C155" s="3"/>
+    </row>
+    <row r="156" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C156" s="3"/>
+    </row>
+    <row r="157" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C157" s="3"/>
+    </row>
+    <row r="158" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C158" s="3"/>
+    </row>
+    <row r="159" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C159" s="3"/>
+    </row>
+    <row r="160" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C160" s="3"/>
+    </row>
+    <row r="161" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C161" s="3"/>
+    </row>
+    <row r="162" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C162" s="3"/>
+    </row>
+    <row r="163" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C163" s="3"/>
+    </row>
+    <row r="164" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C164" s="3"/>
+    </row>
+    <row r="165" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C165" s="3"/>
+    </row>
+    <row r="166" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C166" s="3"/>
+    </row>
+    <row r="167" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C167" s="3"/>
+    </row>
+    <row r="168" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C168" s="3"/>
+    </row>
+    <row r="169" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C169" s="3"/>
+    </row>
+    <row r="170" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C170" s="3"/>
+    </row>
+    <row r="171" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C171" s="3"/>
+    </row>
+    <row r="172" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C172" s="3"/>
+    </row>
+    <row r="173" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C173" s="3"/>
+    </row>
+    <row r="174" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C174" s="3"/>
+    </row>
+    <row r="175" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C175" s="3"/>
+    </row>
+    <row r="176" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C176" s="3"/>
+    </row>
+    <row r="177" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C177" s="3"/>
+    </row>
+    <row r="178" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C178" s="3"/>
+    </row>
+    <row r="179" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C179" s="3"/>
+    </row>
+    <row r="180" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C180" s="3"/>
+    </row>
+    <row r="181" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C181" s="3"/>
+    </row>
+    <row r="182" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C182" s="3"/>
+    </row>
+    <row r="183" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C183" s="3"/>
+    </row>
+    <row r="184" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C184" s="3"/>
+    </row>
+    <row r="185" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C185" s="3"/>
+    </row>
+    <row r="186" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C186" s="3"/>
+    </row>
+    <row r="187" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C187" s="3"/>
+    </row>
+    <row r="188" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C188" s="3"/>
+    </row>
+    <row r="189" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C189" s="3"/>
+    </row>
+    <row r="190" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C190" s="3"/>
+    </row>
+    <row r="191" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C191" s="3"/>
+    </row>
+    <row r="192" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C192" s="3"/>
+    </row>
+    <row r="193" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C193" s="3"/>
+    </row>
+    <row r="194" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C194" s="3"/>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:G147" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}"/>
   <sortState ref="A2:G107">
     <sortCondition ref="A1"/>
   </sortState>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{E544A8E8-7A93-4241-BFC7-ACAB607FD2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{7790D114-10A0-40E8-B981-5A57421918F1}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="113_{2EFB4B30-93F9-4B06-8E68-756D72557CE1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{E5E4E98C-CB04-4B75-8A77-F57E65A54998}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="422">
   <si>
     <t>Nome account</t>
   </si>
@@ -1268,6 +1268,27 @@
   </si>
   <si>
     <t>VERONA</t>
+  </si>
+  <si>
+    <t>FRV ITALIA SRL</t>
+  </si>
+  <si>
+    <t>VIA RUBICONE 11</t>
+  </si>
+  <si>
+    <t>TROINA SOLAR SRL</t>
+  </si>
+  <si>
+    <t>VIA DON FELICE CANELLI 21</t>
+  </si>
+  <si>
+    <t>SAN SEVERO</t>
+  </si>
+  <si>
+    <t>TEAGRI SOLARE 1 SRL</t>
+  </si>
+  <si>
+    <t>PIAZZALE LUIGI CADORNA 9</t>
   </si>
 </sst>
 </file>
@@ -1318,7 +1339,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1341,22 +1362,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD5D3D1"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD5D3D1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1369,9 +1379,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -5023,13 +5030,13 @@
       <c r="D145" t="s">
         <v>408</v>
       </c>
-      <c r="E145" s="6" t="s">
+      <c r="E145" s="3" t="s">
         <v>409</v>
       </c>
       <c r="F145" s="5">
         <v>38121</v>
       </c>
-      <c r="G145" s="6" t="s">
+      <c r="G145" s="3" t="s">
         <v>268</v>
       </c>
     </row>
@@ -5046,13 +5053,13 @@
       <c r="D146" t="s">
         <v>122</v>
       </c>
-      <c r="E146" s="6" t="s">
+      <c r="E146" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F146" s="5">
         <v>20121</v>
       </c>
-      <c r="G146" s="6" t="s">
+      <c r="G146" s="3" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5069,13 +5076,13 @@
       <c r="D147" t="s">
         <v>211</v>
       </c>
-      <c r="E147" s="6" t="s">
+      <c r="E147" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F147" s="5">
         <v>20121</v>
       </c>
-      <c r="G147" s="6" t="s">
+      <c r="G147" s="3" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5092,13 +5099,13 @@
       <c r="D148" t="s">
         <v>413</v>
       </c>
-      <c r="E148" s="6" t="s">
+      <c r="E148" s="3" t="s">
         <v>414</v>
       </c>
       <c r="F148" s="5">
         <v>37137</v>
       </c>
-      <c r="G148" s="6" t="s">
+      <c r="G148" s="3" t="s">
         <v>344</v>
       </c>
     </row>
@@ -5115,44 +5122,119 @@
       <c r="D149" t="s">
         <v>230</v>
       </c>
-      <c r="E149" s="6" t="s">
+      <c r="E149" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F149" s="5">
         <v>20148</v>
       </c>
-      <c r="G149" s="6" t="s">
+      <c r="G149" s="3" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B150" s="3"/>
-      <c r="C150" s="3"/>
+      <c r="A150" t="s">
+        <v>415</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D150" t="s">
+        <v>416</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="151" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B151" s="3"/>
-      <c r="C151" s="3"/>
+      <c r="A151" t="s">
+        <v>417</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D151" t="s">
+        <v>418</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="F151" s="5">
+        <v>71016</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="152" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="C152" s="3"/>
+      <c r="A152" t="s">
+        <v>420</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" t="s">
+        <v>421</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F152" s="5">
+        <v>20123</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="153" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B153" s="3"/>
       <c r="C153" s="3"/>
+      <c r="E153" s="3"/>
+      <c r="G153" s="3"/>
     </row>
     <row r="154" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B154" s="3"/>
       <c r="C154" s="3"/>
+      <c r="E154" s="3"/>
+      <c r="G154" s="3"/>
     </row>
     <row r="155" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B155" s="3"/>
       <c r="C155" s="3"/>
+      <c r="E155" s="3"/>
+      <c r="G155" s="3"/>
     </row>
     <row r="156" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B156" s="3"/>
       <c r="C156" s="3"/>
+      <c r="E156" s="3"/>
+      <c r="G156" s="3"/>
     </row>
     <row r="157" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B157" s="3"/>
       <c r="C157" s="3"/>
+      <c r="E157" s="3"/>
+      <c r="G157" s="3"/>
     </row>
     <row r="158" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B158" s="3"/>
       <c r="C158" s="3"/>
+      <c r="G158" s="3"/>
     </row>
     <row r="159" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C159" s="3"/>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="113_{2EFB4B30-93F9-4B06-8E68-756D72557CE1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{E5E4E98C-CB04-4B75-8A77-F57E65A54998}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="113_{2EFB4B30-93F9-4B06-8E68-756D72557CE1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{E8D34D0C-8BD4-45F0-9C5E-ADED382AE5FF}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="432">
   <si>
     <t>Nome account</t>
   </si>
@@ -1289,6 +1289,36 @@
   </si>
   <si>
     <t>PIAZZALE LUIGI CADORNA 9</t>
+  </si>
+  <si>
+    <t>SEGNALETICA NOVARESE SRL</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>VIA VARALLO POMBIA 44</t>
+  </si>
+  <si>
+    <t>CASTELLETTO SOPRA TICINO</t>
+  </si>
+  <si>
+    <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+  </si>
+  <si>
+    <t>PV ICHNOSOLAR SRL</t>
+  </si>
+  <si>
+    <t>TRAIANO SRL</t>
+  </si>
+  <si>
+    <t>VIA VOLTA 13</t>
+  </si>
+  <si>
+    <t>SAN ZENO NAVIGLIO</t>
+  </si>
+  <si>
+    <t>FLYSUN 5 SRL</t>
   </si>
 </sst>
 </file>
@@ -5202,34 +5232,119 @@
       </c>
     </row>
     <row r="153" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B153" s="3"/>
-      <c r="C153" s="3"/>
-      <c r="E153" s="3"/>
-      <c r="G153" s="3"/>
+      <c r="A153" t="s">
+        <v>422</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D153" t="s">
+        <v>424</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="F153" s="5">
+        <v>28053</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="154" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B154" s="3"/>
-      <c r="C154" s="3"/>
-      <c r="E154" s="3"/>
-      <c r="G154" s="3"/>
+      <c r="A154" t="s">
+        <v>426</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D154" t="s">
+        <v>132</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F154" s="5">
+        <v>39100</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="155" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B155" s="3"/>
-      <c r="C155" s="3"/>
-      <c r="E155" s="3"/>
-      <c r="G155" s="3"/>
+      <c r="A155" t="s">
+        <v>427</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D155" t="s">
+        <v>236</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F155" s="5">
+        <v>10121</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="156" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B156" s="3"/>
-      <c r="C156" s="3"/>
-      <c r="E156" s="3"/>
-      <c r="G156" s="3"/>
+      <c r="A156" t="s">
+        <v>428</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" t="s">
+        <v>429</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F156" s="5">
+        <v>25010</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="157" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B157" s="3"/>
-      <c r="C157" s="3"/>
-      <c r="E157" s="3"/>
-      <c r="G157" s="3"/>
+      <c r="A157" t="s">
+        <v>431</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D157" t="s">
+        <v>337</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F157" s="5">
+        <v>10153</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="158" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B158" s="3"/>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="113_{2EFB4B30-93F9-4B06-8E68-756D72557CE1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{E8D34D0C-8BD4-45F0-9C5E-ADED382AE5FF}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{BEDAFBF4-E166-49E1-A534-F5ED8E94E97D}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="436">
   <si>
     <t>Nome account</t>
   </si>
@@ -1319,6 +1319,18 @@
   </si>
   <si>
     <t>FLYSUN 5 SRL</t>
+  </si>
+  <si>
+    <t>OGR SRL</t>
+  </si>
+  <si>
+    <t>CORSO GIOVANNI GIOLITTI 2</t>
+  </si>
+  <si>
+    <t>CUNEO</t>
+  </si>
+  <si>
+    <t>XELIO ANTARES SRL</t>
   </si>
 </sst>
 </file>
@@ -1369,7 +1381,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1392,11 +1404,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD5D3D1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD5D3D1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1409,6 +1432,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -5347,12 +5373,50 @@
       </c>
     </row>
     <row r="158" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B158" s="3"/>
-      <c r="C158" s="3"/>
-      <c r="G158" s="3"/>
+      <c r="A158" t="s">
+        <v>432</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D158" t="s">
+        <v>433</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="F158" s="5">
+        <v>12100</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="159" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="C159" s="3"/>
+      <c r="A159" t="s">
+        <v>435</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D159" t="s">
+        <v>217</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="G159" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="160" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C160" s="3"/>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{BEDAFBF4-E166-49E1-A534-F5ED8E94E97D}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{DA9C20B5-694C-4E31-BFEB-40D0133F5D37}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="437">
   <si>
     <t>Nome account</t>
   </si>
@@ -1331,6 +1331,9 @@
   </si>
   <si>
     <t>XELIO ANTARES SRL</t>
+  </si>
+  <si>
+    <t>GREEN ENERGY SARDEGNA 2 SRL</t>
   </si>
 </sst>
 </file>
@@ -1381,7 +1384,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1404,22 +1407,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD5D3D1"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD5D3D1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1432,9 +1424,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -5385,7 +5374,7 @@
       <c r="D158" t="s">
         <v>433</v>
       </c>
-      <c r="E158" s="6" t="s">
+      <c r="E158" s="3" t="s">
         <v>434</v>
       </c>
       <c r="F158" s="5">
@@ -5399,7 +5388,7 @@
       <c r="A159" t="s">
         <v>435</v>
       </c>
-      <c r="B159" s="6" t="s">
+      <c r="B159" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C159" s="3" t="s">
@@ -5408,65 +5397,107 @@
       <c r="D159" t="s">
         <v>217</v>
       </c>
-      <c r="E159" s="6" t="s">
+      <c r="E159" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="G159" s="6" t="s">
+      <c r="G159" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="C160" s="3"/>
-    </row>
-    <row r="161" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>436</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D160" t="s">
+        <v>129</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F160" s="5">
+        <v>39100</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="161" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B161" s="3"/>
       <c r="C161" s="3"/>
-    </row>
-    <row r="162" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E161" s="3"/>
+      <c r="G161" s="3"/>
+    </row>
+    <row r="162" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B162" s="3"/>
       <c r="C162" s="3"/>
-    </row>
-    <row r="163" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E162" s="3"/>
+      <c r="G162" s="3"/>
+    </row>
+    <row r="163" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B163" s="3"/>
       <c r="C163" s="3"/>
-    </row>
-    <row r="164" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E163" s="3"/>
+      <c r="G163" s="3"/>
+    </row>
+    <row r="164" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B164" s="3"/>
       <c r="C164" s="3"/>
-    </row>
-    <row r="165" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E164" s="3"/>
+      <c r="G164" s="3"/>
+    </row>
+    <row r="165" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C165" s="3"/>
-    </row>
-    <row r="166" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E165" s="3"/>
+      <c r="G165" s="3"/>
+    </row>
+    <row r="166" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C166" s="3"/>
-    </row>
-    <row r="167" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="E166" s="3"/>
+      <c r="G166" s="3"/>
+    </row>
+    <row r="167" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C167" s="3"/>
-    </row>
-    <row r="168" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="G167" s="3"/>
+    </row>
+    <row r="168" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C168" s="3"/>
-    </row>
-    <row r="169" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="G168" s="3"/>
+    </row>
+    <row r="169" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C169" s="3"/>
-    </row>
-    <row r="170" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="G169" s="3"/>
+    </row>
+    <row r="170" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C170" s="3"/>
-    </row>
-    <row r="171" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="G170" s="3"/>
+    </row>
+    <row r="171" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C171" s="3"/>
-    </row>
-    <row r="172" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="G171" s="3"/>
+    </row>
+    <row r="172" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C172" s="3"/>
-    </row>
-    <row r="173" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="G172" s="3"/>
+    </row>
+    <row r="173" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C173" s="3"/>
     </row>
-    <row r="174" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C174" s="3"/>
     </row>
-    <row r="175" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C175" s="3"/>
     </row>
-    <row r="176" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C176" s="3"/>
     </row>
     <row r="177" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{DA9C20B5-694C-4E31-BFEB-40D0133F5D37}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{C3329923-A51D-4D31-852D-7D79B4B1AE2B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="438">
   <si>
     <t>Nome account</t>
   </si>
@@ -1334,6 +1334,9 @@
   </si>
   <si>
     <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+  </si>
+  <si>
+    <t>ARIAN SOLAR SRL</t>
   </si>
 </sst>
 </file>
@@ -5430,74 +5433,91 @@
         <v>32</v>
       </c>
     </row>
-    <row r="161" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B161" s="3"/>
-      <c r="C161" s="3"/>
-      <c r="E161" s="3"/>
-      <c r="G161" s="3"/>
-    </row>
-    <row r="162" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>437</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D161" t="s">
+        <v>305</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F161" s="5">
+        <v>20123</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
       <c r="E162" s="3"/>
       <c r="G162" s="3"/>
     </row>
-    <row r="163" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
       <c r="E163" s="3"/>
       <c r="G163" s="3"/>
     </row>
-    <row r="164" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
       <c r="E164" s="3"/>
       <c r="G164" s="3"/>
     </row>
-    <row r="165" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C165" s="3"/>
       <c r="E165" s="3"/>
       <c r="G165" s="3"/>
     </row>
-    <row r="166" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C166" s="3"/>
       <c r="E166" s="3"/>
       <c r="G166" s="3"/>
     </row>
-    <row r="167" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C167" s="3"/>
       <c r="G167" s="3"/>
     </row>
-    <row r="168" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C168" s="3"/>
       <c r="G168" s="3"/>
     </row>
-    <row r="169" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C169" s="3"/>
       <c r="G169" s="3"/>
     </row>
-    <row r="170" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C170" s="3"/>
       <c r="G170" s="3"/>
     </row>
-    <row r="171" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C171" s="3"/>
       <c r="G171" s="3"/>
     </row>
-    <row r="172" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C172" s="3"/>
       <c r="G172" s="3"/>
     </row>
-    <row r="173" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C173" s="3"/>
     </row>
-    <row r="174" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C174" s="3"/>
     </row>
-    <row r="175" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C175" s="3"/>
     </row>
-    <row r="176" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C176" s="3"/>
     </row>
     <row r="177" spans="3:3" ht="15.5" x14ac:dyDescent="0.35">

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{8E9EE1E7-B240-45FB-8A78-1C3F47E369A8}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{AC6C13FE-BE5C-45A0-9A4B-41DFDCEE8C76}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="499">
   <si>
     <t>Nome account</t>
   </si>
@@ -1511,6 +1511,15 @@
   </si>
   <si>
     <t>VIA PAOLO EMILIO 10</t>
+  </si>
+  <si>
+    <t>ALTEA GREEN POWER SPA</t>
+  </si>
+  <si>
+    <t>VIA CHIVASSO 15/A</t>
+  </si>
+  <si>
+    <t>RIVOLI</t>
   </si>
 </sst>
 </file>
@@ -6263,7 +6272,27 @@
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C189" s="1"/>
+      <c r="A189" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="F189" s="7">
+        <v>10098</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C190" s="1"/>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{AC6C13FE-BE5C-45A0-9A4B-41DFDCEE8C76}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00ED886E-FF23-4483-995F-41111347223B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="500">
   <si>
     <t>Nome account</t>
   </si>
@@ -1520,6 +1520,9 @@
   </si>
   <si>
     <t>RIVOLI</t>
+  </si>
+  <si>
+    <t>INE LA CASSETTA SRL</t>
   </si>
 </sst>
 </file>
@@ -1600,7 +1603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1618,6 +1621,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2156,76 +2163,76 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>45</v>
+        <v>496</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>47</v>
+        <v>497</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>49</v>
+        <v>498</v>
+      </c>
+      <c r="F10" s="5">
+        <v>10098</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>9</v>
@@ -2248,7 +2255,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>9</v>
@@ -2271,7 +2278,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>483</v>
+        <v>196</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>9</v>
@@ -2285,7 +2292,7 @@
       <c r="E15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="5" t="s">
         <v>180</v>
       </c>
       <c r="G15" s="4" t="s">
@@ -2294,7 +2301,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>197</v>
+        <v>483</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>9</v>
@@ -2308,7 +2315,7 @@
       <c r="E16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="8" t="s">
         <v>180</v>
       </c>
       <c r="G16" s="4" t="s">
@@ -2317,7 +2324,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>9</v>
@@ -2340,99 +2347,99 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>404</v>
+        <v>183</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>405</v>
+        <v>179</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F19" s="5">
-        <v>20124</v>
+        <v>39100</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>469</v>
+        <v>400</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>470</v>
+        <v>401</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>471</v>
+        <v>36</v>
+      </c>
+      <c r="F20" s="5">
+        <v>20124</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>437</v>
+        <v>469</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>305</v>
+        <v>470</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>471</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>350</v>
+        <v>437</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>34</v>
@@ -2441,13 +2448,13 @@
         <v>8</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>351</v>
+        <v>305</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F22" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>38</v>
@@ -2455,53 +2462,53 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>67</v>
+        <v>350</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>18</v>
+        <v>351</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F23" s="5">
+        <v>20122</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>399</v>
+        <v>67</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F24" s="5">
-        <v>10123</v>
+        <v>19</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>78</v>
+        <v>399</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>79</v>
@@ -2515,8 +2522,8 @@
       <c r="E25" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F25" s="5" t="s">
-        <v>82</v>
+      <c r="F25" s="5">
+        <v>10123</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>83</v>
@@ -2524,53 +2531,53 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>279</v>
+        <v>78</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="F26" s="5">
-        <v>39042</v>
+        <v>81</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>338</v>
+        <v>279</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>339</v>
+        <v>289</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>36</v>
+        <v>290</v>
       </c>
       <c r="F27" s="5">
-        <v>20121</v>
+        <v>39042</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>33</v>
+        <v>338</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>34</v>
@@ -2579,13 +2586,13 @@
         <v>8</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>35</v>
+        <v>339</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>37</v>
+      <c r="F28" s="5">
+        <v>20121</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>38</v>
@@ -2593,45 +2600,45 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>221</v>
+        <v>33</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>221</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>118</v>
+        <v>222</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>77</v>
@@ -2639,7 +2646,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>254</v>
+        <v>116</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>117</v>
@@ -2662,99 +2669,99 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>62</v>
+        <v>254</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>291</v>
+        <v>145</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>292</v>
+        <v>146</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>293</v>
+        <v>147</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="F34" s="5">
-        <v>60035</v>
+        <v>148</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>390</v>
+        <v>291</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>34</v>
+        <v>292</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>36</v>
+        <v>294</v>
       </c>
       <c r="F35" s="5">
-        <v>20123</v>
+        <v>60035</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>438</v>
+        <v>390</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>34</v>
@@ -2777,7 +2784,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>398</v>
+        <v>438</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>34</v>
@@ -2800,7 +2807,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>269</v>
+        <v>398</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>34</v>
@@ -2814,8 +2821,8 @@
       <c r="E38" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F38" s="5" t="s">
-        <v>61</v>
+      <c r="F38" s="5">
+        <v>20123</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>38</v>
@@ -2823,7 +2830,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>34</v>
@@ -2832,13 +2839,13 @@
         <v>8</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>38</v>
@@ -2846,7 +2853,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>410</v>
+        <v>137</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>34</v>
@@ -2860,8 +2867,8 @@
       <c r="E40" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F40" s="5">
-        <v>20121</v>
+      <c r="F40" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>38</v>
@@ -2869,283 +2876,283 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>138</v>
+        <v>410</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>142</v>
+        <v>36</v>
+      </c>
+      <c r="F41" s="5">
+        <v>20121</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>445</v>
+        <v>125</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F43" s="5">
-        <v>20158</v>
+        <v>19</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>225</v>
+        <v>445</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F44" s="5">
+        <v>20158</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>488</v>
+        <v>84</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>489</v>
+        <v>85</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>490</v>
+        <v>86</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="F46" s="5">
-        <v>26015</v>
+        <v>87</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>334</v>
+        <v>488</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>9</v>
+        <v>489</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>335</v>
+        <v>490</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>218</v>
+        <v>491</v>
+      </c>
+      <c r="F47" s="5">
+        <v>26015</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="F48" s="5">
-        <v>56025</v>
+        <v>10</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>9</v>
+        <v>296</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>273</v>
+        <v>302</v>
+      </c>
+      <c r="F49" s="5">
+        <v>56025</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>376</v>
+        <v>271</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>377</v>
+        <v>272</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F50" s="5">
-        <v>20121</v>
+        <v>10</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>280</v>
+        <v>376</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>303</v>
+        <v>377</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>304</v>
+        <v>36</v>
       </c>
       <c r="F51" s="5">
-        <v>24060</v>
+        <v>20121</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>482</v>
+        <v>280</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="F52" s="5">
-        <v>20121</v>
+        <v>24060</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>175</v>
+        <v>482</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>34</v>
@@ -3154,21 +3161,21 @@
         <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F53" s="5" t="s">
-        <v>158</v>
+      <c r="F53" s="5">
+        <v>20121</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>34</v>
@@ -3191,7 +3198,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>253</v>
+        <v>156</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>34</v>
@@ -3200,21 +3207,21 @@
         <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>440</v>
+        <v>253</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>34</v>
@@ -3223,205 +3230,205 @@
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>441</v>
+        <v>230</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F56" s="5">
-        <v>20122</v>
+      <c r="F56" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>245</v>
+        <v>440</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>247</v>
+        <v>441</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>249</v>
+        <v>36</v>
+      </c>
+      <c r="F57" s="5">
+        <v>20122</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>83</v>
+        <v>250</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>363</v>
+        <v>251</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>364</v>
+        <v>79</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>365</v>
+        <v>252</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="F59" s="5">
-        <v>76123</v>
+        <v>81</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>426</v>
+        <v>363</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>28</v>
+        <v>364</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>132</v>
+        <v>365</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>30</v>
+        <v>366</v>
       </c>
       <c r="F60" s="5">
-        <v>39100</v>
+        <v>76123</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>393</v>
+        <v>132</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F61" s="5">
-        <v>70043</v>
+        <v>39100</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>392</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>220</v>
+        <v>393</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="F62" s="5">
+        <v>70043</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>34</v>
@@ -3430,13 +3437,13 @@
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>38</v>
@@ -3444,7 +3451,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>34</v>
@@ -3467,7 +3474,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>34</v>
@@ -3490,53 +3497,53 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>372</v>
+        <v>130</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>373</v>
+        <v>34</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>374</v>
+        <v>122</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="F68" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>201</v>
+        <v>372</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>34</v>
+        <v>373</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>190</v>
+        <v>375</v>
+      </c>
+      <c r="F69" s="5">
+        <v>61121</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>281</v>
+        <v>201</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>34</v>
@@ -3545,90 +3552,90 @@
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>305</v>
+        <v>189</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F70" s="5">
-        <v>20123</v>
+      <c r="F70" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>352</v>
+        <v>281</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>353</v>
+        <v>34</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>355</v>
+        <v>36</v>
       </c>
       <c r="F71" s="5">
-        <v>15033</v>
+        <v>20123</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>59</v>
+        <v>352</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>34</v>
+        <v>353</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>60</v>
+        <v>354</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>61</v>
+        <v>355</v>
+      </c>
+      <c r="F72" s="5">
+        <v>15033</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F73" s="5">
-        <v>10153</v>
+        <v>36</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>431</v>
+        <v>336</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>79</v>
@@ -3651,53 +3658,53 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>282</v>
+        <v>431</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="F75" s="5">
-        <v>183</v>
+        <v>10153</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>211</v>
+        <v>306</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>58</v>
+        <v>10</v>
+      </c>
+      <c r="F76" s="5">
+        <v>183</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>275</v>
+        <v>210</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>34</v>
@@ -3706,44 +3713,44 @@
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>276</v>
+        <v>211</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>128</v>
+        <v>275</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>28</v>
@@ -3766,122 +3773,122 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>415</v>
+        <v>242</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>416</v>
+        <v>129</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>274</v>
+        <v>415</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>29</v>
+        <v>416</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>241</v>
+        <v>31</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>436</v>
+        <v>238</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>129</v>
+        <v>239</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F83" s="5">
-        <v>39100</v>
+        <v>240</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>206</v>
+        <v>436</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>61</v>
+        <v>30</v>
+      </c>
+      <c r="F84" s="5">
+        <v>39100</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>367</v>
+        <v>206</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>34</v>
@@ -3895,8 +3902,8 @@
       <c r="E85" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F85" s="5">
-        <v>20123</v>
+      <c r="F85" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G85" s="4" t="s">
         <v>38</v>
@@ -3904,7 +3911,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>101</v>
+        <v>367</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>34</v>
@@ -3918,8 +3925,8 @@
       <c r="E86" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F86" s="5" t="s">
-        <v>61</v>
+      <c r="F86" s="5">
+        <v>20123</v>
       </c>
       <c r="G86" s="4" t="s">
         <v>38</v>
@@ -3927,214 +3934,214 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>494</v>
+        <v>101</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>495</v>
+        <v>60</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F87" s="8" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>407</v>
+        <v>494</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>408</v>
+        <v>495</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="F88" s="5">
-        <v>38121</v>
+        <v>10</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>36</v>
+        <v>409</v>
       </c>
       <c r="F89" s="5">
-        <v>20123</v>
+        <v>38121</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F90" s="5">
-        <v>90139</v>
+        <v>20123</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>195</v>
+        <v>362</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F91" s="5">
-        <v>20123</v>
+        <v>90139</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>456</v>
+        <v>346</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>457</v>
+        <v>195</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F92" s="5">
+        <v>20123</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>283</v>
+        <v>456</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>309</v>
+        <v>457</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="F93" s="5">
-        <v>12037</v>
+        <v>10</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>13</v>
+        <v>283</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>14</v>
+        <v>309</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>15</v>
+        <v>310</v>
+      </c>
+      <c r="F94" s="5">
+        <v>12037</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>11</v>
+        <v>307</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>28</v>
@@ -4157,467 +4164,467 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>233</v>
+        <v>27</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>218</v>
+        <v>31</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>188</v>
+        <v>499</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C100" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>189</v>
+        <v>29</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>190</v>
+        <v>30</v>
+      </c>
+      <c r="F100" s="5">
+        <v>39100</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>484</v>
+        <v>233</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>485</v>
+        <v>9</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>486</v>
+        <v>234</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="F101" s="5">
-        <v>66020</v>
+        <v>10</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>412</v>
+        <v>188</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>413</v>
+        <v>189</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="F102" s="5">
-        <v>37137</v>
+        <v>36</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>344</v>
+        <v>159</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>9</v>
+        <v>485</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F103" s="8" t="s">
-        <v>218</v>
+        <v>487</v>
+      </c>
+      <c r="F103" s="5">
+        <v>66020</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>295</v>
+        <v>412</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>296</v>
+        <v>341</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>297</v>
+        <v>413</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>298</v>
+        <v>414</v>
       </c>
       <c r="F104" s="5">
-        <v>56010</v>
+        <v>37137</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>299</v>
+        <v>344</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>311</v>
+        <v>461</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>312</v>
+        <v>462</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="F105" s="5">
-        <v>40060</v>
+        <v>10</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>385</v>
+        <v>295</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>386</v>
+        <v>297</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>36</v>
+        <v>298</v>
       </c>
       <c r="F106" s="5">
-        <v>20121</v>
+        <v>56010</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>387</v>
+        <v>311</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>386</v>
+        <v>312</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>58</v>
+        <v>313</v>
+      </c>
+      <c r="F107" s="5">
+        <v>40060</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>213</v>
+        <v>385</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>179</v>
+        <v>386</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F108" s="5">
+        <v>20121</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>68</v>
+        <v>387</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>70</v>
+        <v>386</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>284</v>
+        <v>213</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>314</v>
+        <v>9</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>315</v>
+        <v>179</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="F110" s="5">
-        <v>57021</v>
+        <v>10</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>299</v>
+        <v>77</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>179</v>
+        <v>70</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>463</v>
+        <v>284</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F112" s="8" t="s">
-        <v>180</v>
+        <v>316</v>
+      </c>
+      <c r="F112" s="5">
+        <v>57021</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>347</v>
+        <v>463</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>348</v>
+        <v>179</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="F114" s="5">
-        <v>70124</v>
+        <v>10</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>333</v>
+        <v>89</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F115" s="5">
-        <v>20158</v>
+        <v>92</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>308</v>
+        <v>40</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="F116" s="5">
-        <v>12084</v>
+        <v>70124</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>307</v>
+        <v>44</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>34</v>
@@ -4626,182 +4633,182 @@
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E117" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F117" s="5" t="s">
-        <v>61</v>
+      <c r="F117" s="5">
+        <v>20158</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>227</v>
+        <v>358</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>228</v>
+        <v>359</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>37</v>
+        <v>360</v>
+      </c>
+      <c r="F118" s="5">
+        <v>12084</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>458</v>
+        <v>194</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>459</v>
+        <v>195</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F119" s="8" t="s">
-        <v>460</v>
+        <v>36</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>108</v>
+        <v>227</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="F121" s="5">
-        <v>12100</v>
+        <v>10</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>460</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>396</v>
+        <v>108</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F122" s="5">
-        <v>40127</v>
+        <v>111</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>356</v>
+        <v>432</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>357</v>
+        <v>433</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>36</v>
+        <v>434</v>
       </c>
       <c r="F123" s="5">
-        <v>20121</v>
+        <v>12100</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>232</v>
+        <v>396</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
+      </c>
+      <c r="F124" s="5">
+        <v>40127</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>143</v>
+        <v>356</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>34</v>
@@ -4810,13 +4817,13 @@
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>144</v>
+        <v>357</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F125" s="5" t="s">
-        <v>37</v>
+      <c r="F125" s="5">
+        <v>20121</v>
       </c>
       <c r="G125" s="4" t="s">
         <v>38</v>
@@ -4824,30 +4831,30 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>442</v>
+        <v>143</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>34</v>
@@ -4856,136 +4863,136 @@
         <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>443</v>
+        <v>144</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="F127" s="5">
-        <v>20038</v>
+        <v>36</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>427</v>
+        <v>56</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F128" s="5">
-        <v>10121</v>
+        <v>36</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>95</v>
+        <v>442</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>97</v>
+        <v>443</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>99</v>
+        <v>444</v>
+      </c>
+      <c r="F129" s="5">
+        <v>20038</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>378</v>
+        <v>427</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>379</v>
+        <v>79</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>380</v>
+        <v>236</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>381</v>
+        <v>81</v>
       </c>
       <c r="F130" s="5">
-        <v>64020</v>
+        <v>10121</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>411</v>
+        <v>95</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>211</v>
+        <v>97</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F131" s="5">
-        <v>20121</v>
+        <v>98</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>133</v>
+        <v>378</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>34</v>
+        <v>379</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>134</v>
+        <v>380</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F132" s="5" t="s">
-        <v>135</v>
+        <v>381</v>
+      </c>
+      <c r="F132" s="5">
+        <v>64020</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>257</v>
+        <v>411</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>34</v>
@@ -4994,13 +5001,13 @@
         <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F133" s="5" t="s">
-        <v>58</v>
+      <c r="F133" s="5">
+        <v>20121</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>38</v>
@@ -5008,30 +5015,30 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>340</v>
+        <v>133</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>342</v>
+        <v>134</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="F134" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>344</v>
+        <v>136</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>34</v>
@@ -5040,44 +5047,44 @@
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>167</v>
+        <v>258</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>472</v>
+        <v>340</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>260</v>
+        <v>342</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>36</v>
+        <v>343</v>
       </c>
       <c r="F136" s="5">
-        <v>20135</v>
+        <v>37045</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>262</v>
+        <v>344</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>406</v>
+        <v>166</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>34</v>
@@ -5086,44 +5093,44 @@
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F137" s="5">
-        <v>20135</v>
+      <c r="F137" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>204</v>
+        <v>472</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F138" s="5">
+        <v>20135</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>454</v>
+        <v>406</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>34</v>
@@ -5132,297 +5139,297 @@
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>455</v>
+        <v>260</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F139" s="5">
-        <v>20144</v>
+        <v>20135</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>36</v>
+        <v>186</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>136</v>
+        <v>319</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>285</v>
+        <v>454</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>317</v>
+        <v>455</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F141" s="5">
-        <v>40026</v>
+        <v>20144</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>286</v>
+        <v>223</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>320</v>
+        <v>224</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>323</v>
+        <v>135</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>368</v>
+        <v>285</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>369</v>
+        <v>317</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="F143" s="5">
-        <v>20123</v>
+        <v>40026</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F144" s="5">
-        <v>12020</v>
+        <v>10</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>307</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>39</v>
+        <v>368</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>41</v>
+        <v>369</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
+      </c>
+      <c r="F145" s="5">
+        <v>20123</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>422</v>
+        <v>287</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>423</v>
+        <v>308</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>424</v>
+        <v>321</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>425</v>
+        <v>322</v>
       </c>
       <c r="F146" s="5">
-        <v>28053</v>
+        <v>12020</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>136</v>
+        <v>307</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>172</v>
+        <v>39</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>198</v>
+        <v>422</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>22</v>
+        <v>423</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>199</v>
+        <v>424</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>200</v>
+        <v>425</v>
+      </c>
+      <c r="F148" s="5">
+        <v>28053</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>446</v>
+        <v>207</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>447</v>
+        <v>69</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>448</v>
+        <v>208</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="F151" s="5">
-        <v>53048</v>
+        <v>71</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>450</v>
+        <v>73</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>34</v>
@@ -5445,168 +5452,168 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>131</v>
+        <v>446</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>28</v>
+        <v>447</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>132</v>
+        <v>448</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F153" s="5" t="s">
-        <v>31</v>
+        <v>449</v>
+      </c>
+      <c r="F153" s="5">
+        <v>53048</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>32</v>
+        <v>450</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>382</v>
+        <v>131</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>383</v>
+        <v>132</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="F155" s="5">
-        <v>20089</v>
+        <v>30</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>476</v>
+        <v>21</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>477</v>
+        <v>23</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F156" s="8" t="s">
-        <v>478</v>
+        <v>24</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>212</v>
+        <v>382</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>202</v>
+        <v>383</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>203</v>
+        <v>384</v>
+      </c>
+      <c r="F157" s="5">
+        <v>20089</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>214</v>
+        <v>476</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>215</v>
+        <v>477</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F158" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>478</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>439</v>
+        <v>212</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F159" s="5">
-        <v>20124</v>
+        <v>24</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>34</v>
@@ -5615,21 +5622,21 @@
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E160" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>256</v>
+        <v>439</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>34</v>
@@ -5638,21 +5645,21 @@
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E161" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F161" s="5" t="s">
-        <v>231</v>
+      <c r="F161" s="5">
+        <v>20124</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>473</v>
+        <v>229</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>34</v>
@@ -5661,21 +5668,21 @@
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>465</v>
+        <v>230</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F162" s="5">
-        <v>20129</v>
+      <c r="F162" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>464</v>
+        <v>256</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>34</v>
@@ -5684,21 +5691,21 @@
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>465</v>
+        <v>230</v>
       </c>
       <c r="E163" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F163" s="5">
-        <v>20129</v>
+      <c r="F163" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>34</v>
@@ -5721,7 +5728,7 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>34</v>
@@ -5744,7 +5751,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>176</v>
+        <v>474</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>34</v>
@@ -5753,59 +5760,59 @@
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>177</v>
+        <v>465</v>
       </c>
       <c r="E166" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F166" s="5" t="s">
-        <v>58</v>
+      <c r="F166" s="5">
+        <v>20129</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>331</v>
+        <v>475</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>332</v>
+        <v>465</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F167" s="5">
-        <v>40026</v>
+        <v>20129</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>288</v>
+        <v>176</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>324</v>
+        <v>177</v>
       </c>
       <c r="E168" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F168" s="5">
-        <v>20124</v>
+      <c r="F168" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>38</v>
@@ -5813,398 +5820,398 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>451</v>
+        <v>331</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>452</v>
+        <v>332</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>453</v>
+        <v>318</v>
       </c>
       <c r="F169" s="5">
-        <v>12011</v>
+        <v>40026</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>307</v>
+        <v>26</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>151</v>
+        <v>288</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>153</v>
+        <v>324</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>155</v>
+        <v>36</v>
+      </c>
+      <c r="F170" s="5">
+        <v>20124</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>421</v>
+        <v>452</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>36</v>
+        <v>453</v>
       </c>
       <c r="F171" s="5">
-        <v>20123</v>
+        <v>12011</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>492</v>
+        <v>151</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>493</v>
+        <v>153</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F172" s="5">
-        <v>90141</v>
+        <v>154</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>481</v>
+        <v>420</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>389</v>
+        <v>421</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F173" s="8" t="s">
-        <v>391</v>
+        <v>36</v>
+      </c>
+      <c r="F173" s="5">
+        <v>20123</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>388</v>
+        <v>492</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>389</v>
+        <v>493</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>391</v>
+        <v>19</v>
+      </c>
+      <c r="F174" s="5">
+        <v>90141</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>467</v>
+        <v>389</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="F175" s="5">
-        <v>38055</v>
+        <v>10</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>391</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>429</v>
+        <v>389</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="F176" s="5">
-        <v>25010</v>
+        <v>10</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>391</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>394</v>
+        <v>466</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>395</v>
+        <v>467</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>36</v>
+        <v>468</v>
       </c>
       <c r="F177" s="5">
-        <v>20123</v>
+        <v>38055</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="F178" s="5">
-        <v>71016</v>
+        <v>25010</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>16</v>
+        <v>394</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>18</v>
+        <v>395</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F179" s="5">
+        <v>20123</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>325</v>
+        <v>417</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>327</v>
+        <v>418</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>329</v>
+        <v>419</v>
+      </c>
+      <c r="F180" s="5">
+        <v>71016</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>330</v>
+        <v>44</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>479</v>
+        <v>325</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>480</v>
+        <v>327</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F182" s="5">
-        <v>20123</v>
+        <v>328</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>329</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>38</v>
+        <v>330</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>397</v>
+        <v>277</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>218</v>
+        <v>37</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>216</v>
+        <v>479</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>217</v>
+        <v>480</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F184" s="5">
+        <v>20123</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>160</v>
+        <v>397</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>435</v>
+        <v>216</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>9</v>
@@ -6227,75 +6234,95 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F188" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="G188" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A189" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B189" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D189" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E189" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F189" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G189" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A190" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B188" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C188" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D188" s="4" t="s">
+      <c r="B190" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D190" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E188" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F188" s="5" t="s">
+      <c r="E190" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F190" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G188" s="4" t="s">
+      <c r="G190" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A189" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D189" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="E189" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="F189" s="7">
-        <v>10098</v>
-      </c>
-      <c r="G189" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C190" s="1"/>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C191" s="1"/>
@@ -6308,7 +6335,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G146" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G188">
+    <sortState ref="A2:G190">
       <sortCondition ref="A1:A146"/>
     </sortState>
   </autoFilter>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00ED886E-FF23-4483-995F-41111347223B}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{86012B01-5E68-4376-B503-7A8E76D9B93F}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="502">
   <si>
     <t>Nome account</t>
   </si>
@@ -1523,6 +1523,12 @@
   </si>
   <si>
     <t>INE LA CASSETTA SRL</t>
+  </si>
+  <si>
+    <t>COESA SRL</t>
+  </si>
+  <si>
+    <t>VIA CLAUDIO BEAUMONT 7</t>
   </si>
 </sst>
 </file>
@@ -2761,30 +2767,30 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>390</v>
+        <v>500</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C36" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>270</v>
+        <v>501</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F36" s="5">
-        <v>20123</v>
+        <v>10143</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>438</v>
+        <v>390</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>34</v>
@@ -2807,7 +2813,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>398</v>
+        <v>438</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>34</v>
@@ -2830,7 +2836,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>269</v>
+        <v>398</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>34</v>
@@ -2844,8 +2850,8 @@
       <c r="E39" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F39" s="5" t="s">
-        <v>61</v>
+      <c r="F39" s="5">
+        <v>20123</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>38</v>
@@ -2853,7 +2859,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>34</v>
@@ -2862,13 +2868,13 @@
         <v>8</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>38</v>
@@ -2876,7 +2882,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>410</v>
+        <v>137</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>34</v>
@@ -2890,8 +2896,8 @@
       <c r="E41" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F41" s="5">
-        <v>20121</v>
+      <c r="F41" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>38</v>
@@ -2899,283 +2905,283 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>138</v>
+        <v>410</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>142</v>
+        <v>36</v>
+      </c>
+      <c r="F42" s="5">
+        <v>20121</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>445</v>
+        <v>125</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F44" s="5">
-        <v>20158</v>
+        <v>19</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>225</v>
+        <v>445</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F45" s="5">
+        <v>20158</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>488</v>
+        <v>84</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>489</v>
+        <v>85</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>490</v>
+        <v>86</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="F47" s="5">
-        <v>26015</v>
+        <v>87</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>334</v>
+        <v>488</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>9</v>
+        <v>489</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>335</v>
+        <v>490</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>218</v>
+        <v>491</v>
+      </c>
+      <c r="F48" s="5">
+        <v>26015</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="F49" s="5">
-        <v>56025</v>
+        <v>10</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>9</v>
+        <v>296</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>273</v>
+        <v>302</v>
+      </c>
+      <c r="F50" s="5">
+        <v>56025</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>376</v>
+        <v>271</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>377</v>
+        <v>272</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F51" s="5">
-        <v>20121</v>
+        <v>10</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>280</v>
+        <v>376</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>303</v>
+        <v>377</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>304</v>
+        <v>36</v>
       </c>
       <c r="F52" s="5">
-        <v>24060</v>
+        <v>20121</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>482</v>
+        <v>280</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="F53" s="5">
-        <v>20121</v>
+        <v>24060</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>175</v>
+        <v>482</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>34</v>
@@ -3184,21 +3190,21 @@
         <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F54" s="5" t="s">
-        <v>158</v>
+      <c r="F54" s="5">
+        <v>20121</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>34</v>
@@ -3221,7 +3227,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>253</v>
+        <v>156</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>34</v>
@@ -3230,21 +3236,21 @@
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>440</v>
+        <v>253</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>34</v>
@@ -3253,205 +3259,205 @@
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>441</v>
+        <v>230</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F57" s="5">
-        <v>20122</v>
+      <c r="F57" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>245</v>
+        <v>440</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>247</v>
+        <v>441</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>249</v>
+        <v>36</v>
+      </c>
+      <c r="F58" s="5">
+        <v>20122</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>83</v>
+        <v>250</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>363</v>
+        <v>251</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>364</v>
+        <v>79</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>365</v>
+        <v>252</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="F60" s="5">
-        <v>76123</v>
+        <v>81</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>426</v>
+        <v>363</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>28</v>
+        <v>364</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>132</v>
+        <v>365</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>30</v>
+        <v>366</v>
       </c>
       <c r="F61" s="5">
-        <v>39100</v>
+        <v>76123</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>393</v>
+        <v>132</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F62" s="5">
-        <v>70043</v>
+        <v>39100</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>219</v>
+        <v>392</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>220</v>
+        <v>393</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="F63" s="5">
+        <v>70043</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>34</v>
@@ -3460,13 +3466,13 @@
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>38</v>
@@ -3474,7 +3480,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>34</v>
@@ -3497,7 +3503,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>34</v>
@@ -3520,53 +3526,53 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>372</v>
+        <v>130</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>373</v>
+        <v>34</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>374</v>
+        <v>122</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="F69" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>201</v>
+        <v>372</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>34</v>
+        <v>373</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>190</v>
+        <v>375</v>
+      </c>
+      <c r="F70" s="5">
+        <v>61121</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>281</v>
+        <v>201</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>34</v>
@@ -3575,90 +3581,90 @@
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>305</v>
+        <v>189</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F71" s="5">
-        <v>20123</v>
+      <c r="F71" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>352</v>
+        <v>281</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>353</v>
+        <v>34</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>355</v>
+        <v>36</v>
       </c>
       <c r="F72" s="5">
-        <v>15033</v>
+        <v>20123</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>59</v>
+        <v>352</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>34</v>
+        <v>353</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>60</v>
+        <v>354</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>61</v>
+        <v>355</v>
+      </c>
+      <c r="F73" s="5">
+        <v>15033</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F74" s="5">
-        <v>10153</v>
+        <v>36</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>431</v>
+        <v>336</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>79</v>
@@ -3681,53 +3687,53 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>282</v>
+        <v>431</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="F76" s="5">
-        <v>183</v>
+        <v>10153</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>211</v>
+        <v>306</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>58</v>
+        <v>10</v>
+      </c>
+      <c r="F77" s="5">
+        <v>183</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>275</v>
+        <v>210</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>34</v>
@@ -3736,44 +3742,44 @@
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>276</v>
+        <v>211</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>128</v>
+        <v>275</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>28</v>
@@ -3796,122 +3802,122 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>415</v>
+        <v>242</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>416</v>
+        <v>129</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>274</v>
+        <v>415</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>29</v>
+        <v>416</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>241</v>
+        <v>31</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>436</v>
+        <v>238</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>129</v>
+        <v>239</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F84" s="5">
-        <v>39100</v>
+        <v>240</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>206</v>
+        <v>436</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>61</v>
+        <v>30</v>
+      </c>
+      <c r="F85" s="5">
+        <v>39100</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>367</v>
+        <v>206</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>34</v>
@@ -3925,8 +3931,8 @@
       <c r="E86" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F86" s="5">
-        <v>20123</v>
+      <c r="F86" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G86" s="4" t="s">
         <v>38</v>
@@ -3934,7 +3940,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>101</v>
+        <v>367</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>34</v>
@@ -3948,8 +3954,8 @@
       <c r="E87" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F87" s="5" t="s">
-        <v>61</v>
+      <c r="F87" s="5">
+        <v>20123</v>
       </c>
       <c r="G87" s="4" t="s">
         <v>38</v>
@@ -3957,214 +3963,214 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>494</v>
+        <v>101</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>495</v>
+        <v>60</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>407</v>
+        <v>494</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>408</v>
+        <v>495</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="F89" s="5">
-        <v>38121</v>
+        <v>10</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>36</v>
+        <v>409</v>
       </c>
       <c r="F90" s="5">
-        <v>20123</v>
+        <v>38121</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F91" s="5">
-        <v>90139</v>
+        <v>20123</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>195</v>
+        <v>362</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F92" s="5">
-        <v>20123</v>
+        <v>90139</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>456</v>
+        <v>346</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>457</v>
+        <v>195</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F93" s="8" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F93" s="5">
+        <v>20123</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>283</v>
+        <v>456</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>309</v>
+        <v>457</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="F94" s="5">
-        <v>12037</v>
+        <v>10</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>13</v>
+        <v>283</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>14</v>
+        <v>309</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>15</v>
+        <v>310</v>
+      </c>
+      <c r="F95" s="5">
+        <v>12037</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>11</v>
+        <v>307</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>28</v>
@@ -4187,58 +4193,58 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>499</v>
+        <v>27</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
@@ -4247,8 +4253,8 @@
       <c r="E100" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F100" s="5">
-        <v>39100</v>
+      <c r="F100" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G100" s="4" t="s">
         <v>32</v>
@@ -4256,191 +4262,191 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>233</v>
+        <v>499</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C101" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>218</v>
+        <v>30</v>
+      </c>
+      <c r="F101" s="5">
+        <v>39100</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>188</v>
+        <v>233</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>484</v>
+        <v>188</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>485</v>
+        <v>34</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>486</v>
+        <v>189</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="F103" s="5">
-        <v>66020</v>
+        <v>36</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>412</v>
+        <v>484</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>341</v>
+        <v>485</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>413</v>
+        <v>486</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>414</v>
+        <v>487</v>
       </c>
       <c r="F104" s="5">
-        <v>37137</v>
+        <v>66020</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>344</v>
+        <v>77</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>461</v>
+        <v>412</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>9</v>
+        <v>341</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>462</v>
+        <v>413</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>218</v>
+        <v>414</v>
+      </c>
+      <c r="F105" s="5">
+        <v>37137</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>11</v>
+        <v>344</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>295</v>
+        <v>461</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>297</v>
+        <v>462</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="F106" s="5">
-        <v>56010</v>
+        <v>10</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="F107" s="5">
-        <v>40060</v>
+        <v>56010</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>26</v>
+        <v>299</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>385</v>
+        <v>311</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>386</v>
+        <v>312</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>36</v>
+        <v>313</v>
       </c>
       <c r="F108" s="5">
-        <v>20121</v>
+        <v>40060</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>34</v>
@@ -4454,8 +4460,8 @@
       <c r="E109" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F109" s="5" t="s">
-        <v>58</v>
+      <c r="F109" s="5">
+        <v>20121</v>
       </c>
       <c r="G109" s="4" t="s">
         <v>38</v>
@@ -4463,99 +4469,99 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>213</v>
+        <v>387</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>179</v>
+        <v>386</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>180</v>
+        <v>58</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>68</v>
+        <v>213</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>284</v>
+        <v>68</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>314</v>
+        <v>69</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>315</v>
+        <v>70</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="F112" s="5">
-        <v>57021</v>
+        <v>71</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>299</v>
+        <v>73</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>184</v>
+        <v>284</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>180</v>
+        <v>316</v>
+      </c>
+      <c r="F113" s="5">
+        <v>57021</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>463</v>
+        <v>184</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>9</v>
@@ -4569,7 +4575,7 @@
       <c r="E114" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F114" s="8" t="s">
+      <c r="F114" s="5" t="s">
         <v>180</v>
       </c>
       <c r="G114" s="4" t="s">
@@ -4578,122 +4584,122 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>89</v>
+        <v>463</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F115" s="5" t="s">
-        <v>93</v>
+        <v>10</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>347</v>
+        <v>89</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>348</v>
+        <v>91</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="F116" s="5">
-        <v>70124</v>
+        <v>92</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>189</v>
+        <v>348</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>36</v>
+        <v>349</v>
       </c>
       <c r="F117" s="5">
-        <v>20158</v>
+        <v>70124</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>359</v>
+        <v>189</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>360</v>
+        <v>36</v>
       </c>
       <c r="F118" s="5">
-        <v>12084</v>
+        <v>20158</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>307</v>
+        <v>159</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>194</v>
+        <v>358</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>195</v>
+        <v>359</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F119" s="5" t="s">
-        <v>61</v>
+        <v>360</v>
+      </c>
+      <c r="F119" s="5">
+        <v>12084</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>34</v>
@@ -4702,13 +4708,13 @@
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="E120" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="G120" s="4" t="s">
         <v>38</v>
@@ -4716,168 +4722,168 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>458</v>
+        <v>227</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>459</v>
+        <v>228</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F121" s="8" t="s">
-        <v>460</v>
+        <v>36</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>108</v>
+        <v>458</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>110</v>
+        <v>459</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>112</v>
+        <v>10</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>460</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>432</v>
+        <v>108</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>308</v>
+        <v>109</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>433</v>
+        <v>110</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="F123" s="5">
-        <v>12100</v>
+        <v>111</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>307</v>
+        <v>113</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>22</v>
+        <v>308</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>23</v>
+        <v>433</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>24</v>
+        <v>434</v>
       </c>
       <c r="F124" s="5">
-        <v>40127</v>
+        <v>12100</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>26</v>
+        <v>307</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>356</v>
+        <v>396</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>357</v>
+        <v>23</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F125" s="5">
-        <v>20121</v>
+        <v>40127</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>232</v>
+        <v>356</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>29</v>
+        <v>357</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F126" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F126" s="5">
+        <v>20121</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>34</v>
@@ -4886,13 +4892,13 @@
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G128" s="4" t="s">
         <v>38</v>
@@ -4900,7 +4906,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>442</v>
+        <v>56</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>34</v>
@@ -4909,113 +4915,113 @@
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>443</v>
+        <v>57</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="F129" s="5">
-        <v>20038</v>
+        <v>36</v>
+      </c>
+      <c r="F129" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>236</v>
+        <v>443</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="F130" s="5">
-        <v>10121</v>
+        <v>20038</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>95</v>
+        <v>427</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>99</v>
+        <v>81</v>
+      </c>
+      <c r="F131" s="5">
+        <v>10121</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>378</v>
+        <v>95</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>379</v>
+        <v>96</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>380</v>
+        <v>97</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="F132" s="5">
-        <v>64020</v>
+        <v>98</v>
+      </c>
+      <c r="F132" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>34</v>
+        <v>379</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>211</v>
+        <v>380</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>36</v>
+        <v>381</v>
       </c>
       <c r="F133" s="5">
-        <v>20121</v>
+        <v>64020</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>133</v>
+        <v>411</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>34</v>
@@ -5024,21 +5030,21 @@
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F134" s="5" t="s">
-        <v>135</v>
+      <c r="F134" s="5">
+        <v>20121</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>34</v>
@@ -5047,67 +5053,67 @@
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>258</v>
+        <v>134</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>340</v>
+        <v>257</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>342</v>
+        <v>258</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="F136" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>344</v>
+        <v>38</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>166</v>
+        <v>340</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>167</v>
+        <v>342</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>168</v>
+        <v>343</v>
+      </c>
+      <c r="F137" s="5">
+        <v>37045</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>159</v>
+        <v>344</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>472</v>
+        <v>166</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>34</v>
@@ -5116,21 +5122,21 @@
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F138" s="5">
-        <v>20135</v>
+      <c r="F138" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>406</v>
+        <v>472</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>34</v>
@@ -5153,53 +5159,53 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>204</v>
+        <v>406</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F140" s="5">
+        <v>20135</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>454</v>
+        <v>204</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>455</v>
+        <v>205</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F141" s="5">
-        <v>20144</v>
+        <v>186</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>38</v>
+        <v>319</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>223</v>
+        <v>454</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>34</v>
@@ -5208,435 +5214,435 @@
         <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>224</v>
+        <v>455</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F142" s="5" t="s">
-        <v>135</v>
+      <c r="F142" s="5">
+        <v>20144</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>285</v>
+        <v>223</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>317</v>
+        <v>224</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F143" s="5">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>323</v>
+        <v>318</v>
+      </c>
+      <c r="F144" s="5">
+        <v>40026</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>368</v>
+        <v>286</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>369</v>
+        <v>320</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F145" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>287</v>
+        <v>368</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>322</v>
+        <v>36</v>
       </c>
       <c r="F146" s="5">
-        <v>12020</v>
+        <v>20123</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>39</v>
+        <v>287</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>41</v>
+        <v>321</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>43</v>
+        <v>322</v>
+      </c>
+      <c r="F147" s="5">
+        <v>12020</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>422</v>
+        <v>39</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>423</v>
+        <v>40</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>424</v>
+        <v>41</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="F148" s="5">
-        <v>28053</v>
+        <v>42</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>136</v>
+        <v>44</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>172</v>
+        <v>422</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>34</v>
+        <v>423</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>169</v>
+        <v>424</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>171</v>
+        <v>425</v>
+      </c>
+      <c r="F149" s="5">
+        <v>28053</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>24</v>
+        <v>170</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>446</v>
+        <v>244</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>447</v>
+        <v>34</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>448</v>
+        <v>177</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="F153" s="5">
-        <v>53048</v>
+        <v>36</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>450</v>
+        <v>38</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>243</v>
+        <v>446</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>34</v>
+        <v>447</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>177</v>
+        <v>448</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>58</v>
+        <v>449</v>
+      </c>
+      <c r="F154" s="5">
+        <v>53048</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>38</v>
+        <v>450</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>131</v>
+        <v>243</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>382</v>
+        <v>21</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>383</v>
+        <v>23</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="F157" s="5">
-        <v>20089</v>
+        <v>24</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>476</v>
+        <v>382</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>477</v>
+        <v>383</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F158" s="8" t="s">
-        <v>478</v>
+        <v>384</v>
+      </c>
+      <c r="F158" s="5">
+        <v>20089</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>212</v>
+        <v>476</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>202</v>
+        <v>477</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>203</v>
+        <v>10</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>478</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>439</v>
+        <v>214</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>34</v>
@@ -5650,8 +5656,8 @@
       <c r="E161" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F161" s="5">
-        <v>20124</v>
+      <c r="F161" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>159</v>
@@ -5659,7 +5665,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>229</v>
+        <v>439</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>34</v>
@@ -5668,21 +5674,21 @@
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F162" s="5" t="s">
-        <v>231</v>
+      <c r="F162" s="5">
+        <v>20124</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>34</v>
@@ -5705,7 +5711,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>473</v>
+        <v>256</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>34</v>
@@ -5714,21 +5720,21 @@
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>465</v>
+        <v>230</v>
       </c>
       <c r="E164" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F164" s="5">
-        <v>20129</v>
+      <c r="F164" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>34</v>
@@ -5751,7 +5757,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>34</v>
@@ -5774,7 +5780,7 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>34</v>
@@ -5797,7 +5803,7 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>176</v>
+        <v>475</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>34</v>
@@ -5806,182 +5812,182 @@
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>177</v>
+        <v>465</v>
       </c>
       <c r="E168" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F168" s="5" t="s">
-        <v>58</v>
+      <c r="F168" s="5">
+        <v>20129</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>331</v>
+        <v>176</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>332</v>
+        <v>177</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F169" s="5">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="F170" s="5">
-        <v>20124</v>
+        <v>40026</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>451</v>
+        <v>288</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>452</v>
+        <v>324</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>453</v>
+        <v>36</v>
       </c>
       <c r="F171" s="5">
-        <v>12011</v>
+        <v>20124</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>151</v>
+        <v>451</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>152</v>
+        <v>308</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>153</v>
+        <v>452</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>155</v>
+        <v>453</v>
+      </c>
+      <c r="F172" s="5">
+        <v>12011</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>420</v>
+        <v>151</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>421</v>
+        <v>153</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F173" s="5">
-        <v>20123</v>
+        <v>154</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>492</v>
+        <v>420</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>493</v>
+        <v>421</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F174" s="5">
-        <v>90141</v>
+        <v>20123</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>389</v>
+        <v>493</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F175" s="8" t="s">
-        <v>391</v>
+        <v>19</v>
+      </c>
+      <c r="F175" s="5">
+        <v>90141</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>388</v>
+        <v>481</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>9</v>
@@ -5995,7 +6001,7 @@
       <c r="E176" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F176" s="5" t="s">
+      <c r="F176" s="8" t="s">
         <v>391</v>
       </c>
       <c r="G176" s="4" t="s">
@@ -6004,168 +6010,168 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>466</v>
+        <v>388</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>467</v>
+        <v>389</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="F177" s="5">
-        <v>38055</v>
+        <v>10</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>391</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>428</v>
+        <v>466</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>103</v>
+        <v>264</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>429</v>
+        <v>467</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>430</v>
+        <v>468</v>
       </c>
       <c r="F178" s="5">
-        <v>25010</v>
+        <v>38055</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>107</v>
+        <v>268</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>36</v>
+        <v>430</v>
       </c>
       <c r="F179" s="5">
-        <v>20123</v>
+        <v>25010</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>418</v>
+        <v>395</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>419</v>
+        <v>36</v>
       </c>
       <c r="F180" s="5">
-        <v>71016</v>
+        <v>20123</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>16</v>
+        <v>417</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>18</v>
+        <v>418</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F181" s="5" t="s">
-        <v>20</v>
+        <v>419</v>
+      </c>
+      <c r="F181" s="5">
+        <v>71016</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>325</v>
+        <v>16</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>326</v>
+        <v>17</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>327</v>
+        <v>18</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>328</v>
+        <v>19</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>329</v>
+        <v>20</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>330</v>
+        <v>12</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>277</v>
+        <v>325</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>278</v>
+        <v>327</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>37</v>
+        <v>329</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>38</v>
+        <v>330</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>479</v>
+        <v>277</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>34</v>
@@ -6174,13 +6180,13 @@
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>480</v>
+        <v>278</v>
       </c>
       <c r="E184" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F184" s="5">
-        <v>20123</v>
+      <c r="F184" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G184" s="4" t="s">
         <v>38</v>
@@ -6188,30 +6194,30 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>397</v>
+        <v>479</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>217</v>
+        <v>480</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F185" s="5" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F185" s="5">
+        <v>20123</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>216</v>
+        <v>397</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>9</v>
@@ -6234,53 +6240,53 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>435</v>
+        <v>160</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>255</v>
+        <v>435</v>
       </c>
       <c r="B189" s="9" t="s">
         <v>9</v>
@@ -6303,29 +6309,49 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B190" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D190" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E190" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F190" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G190" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A191" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B190" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D190" s="9" t="s">
+      <c r="B191" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D191" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E190" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F190" s="10" t="s">
+      <c r="E191" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F191" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G190" s="9" t="s">
+      <c r="G191" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C191" s="1"/>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C192" s="1"/>
@@ -6335,7 +6361,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G146" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G190">
+    <sortState ref="A2:G191">
       <sortCondition ref="A1:A146"/>
     </sortState>
   </autoFilter>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{86012B01-5E68-4376-B503-7A8E76D9B93F}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{BFEEF0D2-DA37-407F-8EB2-B587CF0E4CDC}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="511">
   <si>
     <t>Nome account</t>
   </si>
@@ -1529,6 +1529,33 @@
   </si>
   <si>
     <t>VIA CLAUDIO BEAUMONT 7</t>
+  </si>
+  <si>
+    <t>AG 14 SRL</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
+  <si>
+    <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
+  </si>
+  <si>
+    <t>ROVIGO</t>
+  </si>
+  <si>
+    <t>Padova</t>
+  </si>
+  <si>
+    <t>ESPE SRL</t>
+  </si>
+  <si>
+    <t>GRANTORTO</t>
+  </si>
+  <si>
+    <t>VIA DELL'ARTIGIANATO 6</t>
+  </si>
+  <si>
+    <t>PD</t>
   </si>
 </sst>
 </file>
@@ -2054,137 +2081,137 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>402</v>
+        <v>502</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>403</v>
+        <v>504</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>36</v>
+        <v>505</v>
       </c>
       <c r="F5" s="5">
-        <v>20123</v>
+        <v>45100</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>38</v>
+        <v>506</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>181</v>
+        <v>402</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>182</v>
+        <v>403</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F6" s="5">
+        <v>20123</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>259</v>
+        <v>181</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>260</v>
+        <v>182</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>262</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>264</v>
+        <v>34</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>266</v>
+        <v>36</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>83</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>496</v>
+        <v>235</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>497</v>
+        <v>236</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="F10" s="5">
-        <v>10098</v>
+        <v>81</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>83</v>
@@ -2192,76 +2219,76 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>45</v>
+        <v>496</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>47</v>
+        <v>497</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>49</v>
+        <v>498</v>
+      </c>
+      <c r="F11" s="5">
+        <v>10098</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>9</v>
@@ -2284,7 +2311,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>9</v>
@@ -2307,7 +2334,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>483</v>
+        <v>196</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>9</v>
@@ -2321,7 +2348,7 @@
       <c r="E16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="5" t="s">
         <v>180</v>
       </c>
       <c r="G16" s="4" t="s">
@@ -2330,7 +2357,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>197</v>
+        <v>483</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>9</v>
@@ -2344,7 +2371,7 @@
       <c r="E17" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="8" t="s">
         <v>180</v>
       </c>
       <c r="G17" s="4" t="s">
@@ -2353,7 +2380,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>9</v>
@@ -2376,99 +2403,99 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>404</v>
+        <v>183</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>405</v>
+        <v>179</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F20" s="5">
-        <v>20124</v>
+        <v>39100</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>469</v>
+        <v>400</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>470</v>
+        <v>401</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>471</v>
+        <v>36</v>
+      </c>
+      <c r="F21" s="5">
+        <v>20124</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>437</v>
+        <v>469</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>305</v>
+        <v>470</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>471</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>350</v>
+        <v>437</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>34</v>
@@ -2477,13 +2504,13 @@
         <v>8</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>351</v>
+        <v>305</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F23" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>38</v>
@@ -2491,53 +2518,53 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>67</v>
+        <v>350</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>18</v>
+        <v>351</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F24" s="5">
+        <v>20122</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>399</v>
+        <v>67</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F25" s="5">
-        <v>10123</v>
+        <v>19</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>78</v>
+        <v>399</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>79</v>
@@ -2551,8 +2578,8 @@
       <c r="E26" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>82</v>
+      <c r="F26" s="5">
+        <v>10123</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>83</v>
@@ -2560,53 +2587,53 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>279</v>
+        <v>78</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="F27" s="5">
-        <v>39042</v>
+        <v>81</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>338</v>
+        <v>279</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>339</v>
+        <v>289</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>36</v>
+        <v>290</v>
       </c>
       <c r="F28" s="5">
-        <v>20121</v>
+        <v>39042</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>33</v>
+        <v>338</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>34</v>
@@ -2615,13 +2642,13 @@
         <v>8</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>35</v>
+        <v>339</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="5" t="s">
-        <v>37</v>
+      <c r="F29" s="5">
+        <v>20121</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>38</v>
@@ -2629,45 +2656,45 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>221</v>
+        <v>33</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>116</v>
+        <v>221</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>118</v>
+        <v>222</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>77</v>
@@ -2675,7 +2702,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>254</v>
+        <v>116</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>117</v>
@@ -2698,122 +2725,122 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>62</v>
+        <v>254</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>291</v>
+        <v>145</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>292</v>
+        <v>146</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>293</v>
+        <v>147</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="F35" s="5">
-        <v>60035</v>
+        <v>148</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>500</v>
+        <v>291</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>501</v>
+        <v>293</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="F36" s="5">
-        <v>10143</v>
+        <v>60035</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>390</v>
+        <v>500</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>270</v>
+        <v>501</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F37" s="5">
-        <v>20123</v>
+        <v>10143</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>438</v>
+        <v>390</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>34</v>
@@ -2836,7 +2863,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>398</v>
+        <v>438</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>34</v>
@@ -2859,7 +2886,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>269</v>
+        <v>398</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>34</v>
@@ -2873,8 +2900,8 @@
       <c r="E40" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F40" s="5" t="s">
-        <v>61</v>
+      <c r="F40" s="5">
+        <v>20123</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>38</v>
@@ -2882,7 +2909,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>34</v>
@@ -2891,13 +2918,13 @@
         <v>8</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>38</v>
@@ -2905,7 +2932,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>410</v>
+        <v>137</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>34</v>
@@ -2919,8 +2946,8 @@
       <c r="E42" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F42" s="5">
-        <v>20121</v>
+      <c r="F42" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>38</v>
@@ -2928,283 +2955,283 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>138</v>
+        <v>410</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>142</v>
+        <v>36</v>
+      </c>
+      <c r="F43" s="5">
+        <v>20121</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>445</v>
+        <v>125</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F45" s="5">
-        <v>20158</v>
+        <v>19</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>225</v>
+        <v>445</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F46" s="5">
+        <v>20158</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>488</v>
+        <v>84</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>489</v>
+        <v>85</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>490</v>
+        <v>86</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="F48" s="5">
-        <v>26015</v>
+        <v>87</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>334</v>
+        <v>488</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>9</v>
+        <v>489</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>335</v>
+        <v>490</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>218</v>
+        <v>491</v>
+      </c>
+      <c r="F49" s="5">
+        <v>26015</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="F50" s="5">
-        <v>56025</v>
+        <v>10</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>9</v>
+        <v>296</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>273</v>
+        <v>302</v>
+      </c>
+      <c r="F51" s="5">
+        <v>56025</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>376</v>
+        <v>271</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>377</v>
+        <v>272</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F52" s="5">
-        <v>20121</v>
+        <v>10</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>280</v>
+        <v>376</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>303</v>
+        <v>377</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>304</v>
+        <v>36</v>
       </c>
       <c r="F53" s="5">
-        <v>24060</v>
+        <v>20121</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>482</v>
+        <v>280</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="F54" s="5">
-        <v>20121</v>
+        <v>24060</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>175</v>
+        <v>482</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>34</v>
@@ -3213,21 +3240,21 @@
         <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F55" s="5" t="s">
-        <v>158</v>
+      <c r="F55" s="5">
+        <v>20121</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>34</v>
@@ -3250,7 +3277,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>253</v>
+        <v>156</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>34</v>
@@ -3259,21 +3286,21 @@
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>440</v>
+        <v>253</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>34</v>
@@ -3282,205 +3309,205 @@
         <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>441</v>
+        <v>230</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F58" s="5">
-        <v>20122</v>
+      <c r="F58" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>245</v>
+        <v>440</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>247</v>
+        <v>441</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>249</v>
+        <v>36</v>
+      </c>
+      <c r="F59" s="5">
+        <v>20122</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>83</v>
+        <v>250</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>363</v>
+        <v>251</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>364</v>
+        <v>79</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>365</v>
+        <v>252</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="F61" s="5">
-        <v>76123</v>
+        <v>81</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>426</v>
+        <v>363</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>28</v>
+        <v>364</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>132</v>
+        <v>365</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>30</v>
+        <v>366</v>
       </c>
       <c r="F62" s="5">
-        <v>39100</v>
+        <v>76123</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>393</v>
+        <v>132</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F63" s="5">
-        <v>70043</v>
+        <v>39100</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>219</v>
+        <v>392</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>220</v>
+        <v>393</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="F64" s="5">
+        <v>70043</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>34</v>
@@ -3489,13 +3516,13 @@
         <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>38</v>
@@ -3503,7 +3530,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>34</v>
@@ -3526,7 +3553,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>34</v>
@@ -3549,53 +3576,53 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>372</v>
+        <v>130</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>373</v>
+        <v>34</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>374</v>
+        <v>122</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="F70" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>201</v>
+        <v>372</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>34</v>
+        <v>373</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>190</v>
+        <v>375</v>
+      </c>
+      <c r="F71" s="5">
+        <v>61121</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>281</v>
+        <v>201</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>34</v>
@@ -3604,44 +3631,44 @@
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>305</v>
+        <v>189</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F72" s="5">
-        <v>20123</v>
+      <c r="F72" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>352</v>
+        <v>507</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="C73" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>354</v>
+        <v>509</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>355</v>
+        <v>508</v>
       </c>
       <c r="F73" s="5">
-        <v>15033</v>
+        <v>35010</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>83</v>
+        <v>506</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>59</v>
+        <v>281</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>34</v>
@@ -3650,13 +3677,13 @@
         <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>60</v>
+        <v>305</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F74" s="5" t="s">
-        <v>61</v>
+      <c r="F74" s="5">
+        <v>20123</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>38</v>
@@ -3664,22 +3691,22 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>79</v>
+        <v>353</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>81</v>
+        <v>355</v>
       </c>
       <c r="F75" s="5">
-        <v>10153</v>
+        <v>15033</v>
       </c>
       <c r="G75" s="4" t="s">
         <v>83</v>
@@ -3687,168 +3714,168 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>431</v>
+        <v>59</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F76" s="5">
-        <v>10153</v>
+        <v>36</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>282</v>
+        <v>336</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="F77" s="5">
-        <v>183</v>
+        <v>10153</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>210</v>
+        <v>431</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>211</v>
+        <v>337</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>58</v>
+        <v>81</v>
+      </c>
+      <c r="F78" s="5">
+        <v>10153</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
+      </c>
+      <c r="F79" s="5">
+        <v>183</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>159</v>
+        <v>307</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>129</v>
+        <v>211</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>242</v>
+        <v>275</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>415</v>
+        <v>128</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>416</v>
+        <v>129</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>28</v>
@@ -3857,7 +3884,7 @@
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>30</v>
@@ -3871,30 +3898,30 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>238</v>
+        <v>415</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>239</v>
+        <v>416</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>241</v>
+        <v>180</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>436</v>
+        <v>274</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>28</v>
@@ -3903,13 +3930,13 @@
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F85" s="5">
-        <v>39100</v>
+      <c r="F85" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G85" s="4" t="s">
         <v>32</v>
@@ -3917,53 +3944,53 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>60</v>
+        <v>239</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>36</v>
+        <v>240</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>61</v>
+        <v>241</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>367</v>
+        <v>436</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F87" s="5">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>34</v>
@@ -3986,99 +4013,99 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>494</v>
+        <v>367</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>495</v>
+        <v>60</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F89" s="8" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F89" s="5">
+        <v>20123</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>407</v>
+        <v>101</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>264</v>
+        <v>34</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>408</v>
+        <v>60</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="F90" s="5">
-        <v>38121</v>
+        <v>36</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>268</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>370</v>
+        <v>494</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>371</v>
+        <v>495</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F91" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>361</v>
+        <v>407</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>362</v>
+        <v>408</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>19</v>
+        <v>409</v>
       </c>
       <c r="F92" s="5">
-        <v>90139</v>
+        <v>38121</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>12</v>
+        <v>268</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>34</v>
@@ -4087,7 +4114,7 @@
         <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>195</v>
+        <v>371</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>36</v>
@@ -4101,53 +4128,53 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>456</v>
+        <v>361</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>457</v>
+        <v>362</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>180</v>
+        <v>19</v>
+      </c>
+      <c r="F94" s="5">
+        <v>90139</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>283</v>
+        <v>346</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>309</v>
+        <v>195</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>310</v>
+        <v>36</v>
       </c>
       <c r="F95" s="5">
-        <v>12037</v>
+        <v>20123</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>13</v>
+        <v>456</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>9</v>
@@ -4156,90 +4183,90 @@
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>14</v>
+        <v>457</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F96" s="5" t="s">
-        <v>15</v>
+      <c r="F96" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>123</v>
+        <v>283</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>28</v>
+        <v>308</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>55</v>
+        <v>309</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>31</v>
+        <v>310</v>
+      </c>
+      <c r="F97" s="5">
+        <v>12037</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>32</v>
+        <v>307</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>28</v>
@@ -4248,7 +4275,7 @@
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>30</v>
@@ -4262,444 +4289,444 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>499</v>
+        <v>74</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C101" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C101" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F101" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>233</v>
+        <v>27</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>218</v>
+        <v>31</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>188</v>
+        <v>499</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C103" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>189</v>
+        <v>29</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>190</v>
+        <v>30</v>
+      </c>
+      <c r="F103" s="5">
+        <v>39100</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>484</v>
+        <v>233</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>485</v>
+        <v>9</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>486</v>
+        <v>234</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="F104" s="5">
-        <v>66020</v>
+        <v>10</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>412</v>
+        <v>188</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>413</v>
+        <v>189</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="F105" s="5">
-        <v>37137</v>
+        <v>36</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>344</v>
+        <v>159</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>9</v>
+        <v>485</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F106" s="8" t="s">
-        <v>218</v>
+        <v>487</v>
+      </c>
+      <c r="F106" s="5">
+        <v>66020</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>295</v>
+        <v>412</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>296</v>
+        <v>341</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>297</v>
+        <v>413</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>298</v>
+        <v>414</v>
       </c>
       <c r="F107" s="5">
-        <v>56010</v>
+        <v>37137</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>299</v>
+        <v>344</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>311</v>
+        <v>461</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>312</v>
+        <v>462</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="F108" s="5">
-        <v>40060</v>
+        <v>10</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>385</v>
+        <v>295</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>386</v>
+        <v>297</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>36</v>
+        <v>298</v>
       </c>
       <c r="F109" s="5">
-        <v>20121</v>
+        <v>56010</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>387</v>
+        <v>311</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>386</v>
+        <v>312</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>58</v>
+        <v>313</v>
+      </c>
+      <c r="F110" s="5">
+        <v>40060</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>213</v>
+        <v>385</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>179</v>
+        <v>386</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F111" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F111" s="5">
+        <v>20121</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>68</v>
+        <v>387</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>70</v>
+        <v>386</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>284</v>
+        <v>213</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>314</v>
+        <v>9</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>315</v>
+        <v>179</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="F113" s="5">
-        <v>57021</v>
+        <v>10</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>299</v>
+        <v>77</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>179</v>
+        <v>70</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>463</v>
+        <v>284</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F115" s="8" t="s">
-        <v>180</v>
+        <v>316</v>
+      </c>
+      <c r="F115" s="5">
+        <v>57021</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>347</v>
+        <v>463</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>348</v>
+        <v>179</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="F117" s="5">
-        <v>70124</v>
+        <v>10</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>333</v>
+        <v>89</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F118" s="5">
-        <v>20158</v>
+        <v>92</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>308</v>
+        <v>40</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="F119" s="5">
-        <v>12084</v>
+        <v>70124</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>307</v>
+        <v>44</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>34</v>
@@ -4708,182 +4735,182 @@
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E120" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F120" s="5" t="s">
-        <v>61</v>
+      <c r="F120" s="5">
+        <v>20158</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>227</v>
+        <v>358</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>228</v>
+        <v>359</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F121" s="5" t="s">
-        <v>37</v>
+        <v>360</v>
+      </c>
+      <c r="F121" s="5">
+        <v>12084</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>458</v>
+        <v>194</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>459</v>
+        <v>195</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" s="8" t="s">
-        <v>460</v>
+        <v>36</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>108</v>
+        <v>227</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="F124" s="5">
-        <v>12100</v>
+        <v>10</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>460</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>396</v>
+        <v>108</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F125" s="5">
-        <v>40127</v>
+        <v>111</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>356</v>
+        <v>432</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>357</v>
+        <v>433</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>36</v>
+        <v>434</v>
       </c>
       <c r="F126" s="5">
-        <v>20121</v>
+        <v>12100</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>232</v>
+        <v>396</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F127" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
+      </c>
+      <c r="F127" s="5">
+        <v>40127</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>143</v>
+        <v>356</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>34</v>
@@ -4892,13 +4919,13 @@
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>144</v>
+        <v>357</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F128" s="5" t="s">
-        <v>37</v>
+      <c r="F128" s="5">
+        <v>20121</v>
       </c>
       <c r="G128" s="4" t="s">
         <v>38</v>
@@ -4906,30 +4933,30 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>442</v>
+        <v>143</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>34</v>
@@ -4938,136 +4965,136 @@
         <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>443</v>
+        <v>144</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="F130" s="5">
-        <v>20038</v>
+        <v>36</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>427</v>
+        <v>56</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F131" s="5">
-        <v>10121</v>
+        <v>36</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>95</v>
+        <v>442</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>97</v>
+        <v>443</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F132" s="5" t="s">
-        <v>99</v>
+        <v>444</v>
+      </c>
+      <c r="F132" s="5">
+        <v>20038</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>378</v>
+        <v>427</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>379</v>
+        <v>79</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>380</v>
+        <v>236</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>381</v>
+        <v>81</v>
       </c>
       <c r="F133" s="5">
-        <v>64020</v>
+        <v>10121</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>411</v>
+        <v>95</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>211</v>
+        <v>97</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F134" s="5">
-        <v>20121</v>
+        <v>98</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>133</v>
+        <v>378</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>34</v>
+        <v>379</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>134</v>
+        <v>380</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F135" s="5" t="s">
-        <v>135</v>
+        <v>381</v>
+      </c>
+      <c r="F135" s="5">
+        <v>64020</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>257</v>
+        <v>411</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>34</v>
@@ -5076,13 +5103,13 @@
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F136" s="5" t="s">
-        <v>58</v>
+      <c r="F136" s="5">
+        <v>20121</v>
       </c>
       <c r="G136" s="4" t="s">
         <v>38</v>
@@ -5090,30 +5117,30 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>340</v>
+        <v>133</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>342</v>
+        <v>134</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="F137" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>344</v>
+        <v>136</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>34</v>
@@ -5122,44 +5149,44 @@
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>167</v>
+        <v>258</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>472</v>
+        <v>340</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>260</v>
+        <v>342</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>36</v>
+        <v>343</v>
       </c>
       <c r="F139" s="5">
-        <v>20135</v>
+        <v>37045</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>262</v>
+        <v>344</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>406</v>
+        <v>166</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>34</v>
@@ -5168,44 +5195,44 @@
         <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E140" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F140" s="5">
-        <v>20135</v>
+      <c r="F140" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>204</v>
+        <v>472</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F141" s="5">
+        <v>20135</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>454</v>
+        <v>406</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>34</v>
@@ -5214,297 +5241,297 @@
         <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>455</v>
+        <v>260</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F142" s="5">
-        <v>20144</v>
+        <v>20135</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>36</v>
+        <v>186</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>136</v>
+        <v>319</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>285</v>
+        <v>454</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>317</v>
+        <v>455</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F144" s="5">
-        <v>40026</v>
+        <v>20144</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>286</v>
+        <v>223</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>320</v>
+        <v>224</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>323</v>
+        <v>135</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>368</v>
+        <v>285</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>369</v>
+        <v>317</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="F146" s="5">
-        <v>20123</v>
+        <v>40026</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F147" s="5">
-        <v>12020</v>
+        <v>10</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>307</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>39</v>
+        <v>368</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>41</v>
+        <v>369</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
+      </c>
+      <c r="F148" s="5">
+        <v>20123</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>422</v>
+        <v>287</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>423</v>
+        <v>308</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>424</v>
+        <v>321</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>425</v>
+        <v>322</v>
       </c>
       <c r="F149" s="5">
-        <v>28053</v>
+        <v>12020</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>136</v>
+        <v>307</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>172</v>
+        <v>39</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>198</v>
+        <v>422</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>22</v>
+        <v>423</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>199</v>
+        <v>424</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>200</v>
+        <v>425</v>
+      </c>
+      <c r="F151" s="5">
+        <v>28053</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>446</v>
+        <v>207</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>447</v>
+        <v>69</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>448</v>
+        <v>208</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="F154" s="5">
-        <v>53048</v>
+        <v>71</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>450</v>
+        <v>73</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>34</v>
@@ -5527,168 +5554,168 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>131</v>
+        <v>446</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>28</v>
+        <v>447</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>132</v>
+        <v>448</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F156" s="5" t="s">
-        <v>31</v>
+        <v>449</v>
+      </c>
+      <c r="F156" s="5">
+        <v>53048</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>32</v>
+        <v>450</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>382</v>
+        <v>131</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>383</v>
+        <v>132</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="F158" s="5">
-        <v>20089</v>
+        <v>30</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>476</v>
+        <v>21</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>477</v>
+        <v>23</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F159" s="8" t="s">
-        <v>478</v>
+        <v>24</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>212</v>
+        <v>382</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>202</v>
+        <v>383</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F160" s="5" t="s">
-        <v>203</v>
+        <v>384</v>
+      </c>
+      <c r="F160" s="5">
+        <v>20089</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>214</v>
+        <v>476</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>215</v>
+        <v>477</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F161" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>478</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>439</v>
+        <v>212</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F162" s="5">
-        <v>20124</v>
+        <v>24</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>34</v>
@@ -5697,21 +5724,21 @@
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E163" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>256</v>
+        <v>439</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>34</v>
@@ -5720,21 +5747,21 @@
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E164" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F164" s="5" t="s">
-        <v>231</v>
+      <c r="F164" s="5">
+        <v>20124</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>473</v>
+        <v>229</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>34</v>
@@ -5743,21 +5770,21 @@
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>465</v>
+        <v>230</v>
       </c>
       <c r="E165" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F165" s="5">
-        <v>20129</v>
+      <c r="F165" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>464</v>
+        <v>256</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>34</v>
@@ -5766,21 +5793,21 @@
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>465</v>
+        <v>230</v>
       </c>
       <c r="E166" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F166" s="5">
-        <v>20129</v>
+      <c r="F166" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>34</v>
@@ -5803,7 +5830,7 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>34</v>
@@ -5826,7 +5853,7 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>176</v>
+        <v>474</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>34</v>
@@ -5835,59 +5862,59 @@
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>177</v>
+        <v>465</v>
       </c>
       <c r="E169" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F169" s="5" t="s">
-        <v>58</v>
+      <c r="F169" s="5">
+        <v>20129</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>331</v>
+        <v>475</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>332</v>
+        <v>465</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F170" s="5">
-        <v>40026</v>
+        <v>20129</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>288</v>
+        <v>176</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>324</v>
+        <v>177</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F171" s="5">
-        <v>20124</v>
+      <c r="F171" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>38</v>
@@ -5895,398 +5922,398 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>451</v>
+        <v>331</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>452</v>
+        <v>332</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>453</v>
+        <v>318</v>
       </c>
       <c r="F172" s="5">
-        <v>12011</v>
+        <v>40026</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>307</v>
+        <v>26</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>151</v>
+        <v>288</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>153</v>
+        <v>324</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>155</v>
+        <v>36</v>
+      </c>
+      <c r="F173" s="5">
+        <v>20124</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>421</v>
+        <v>452</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>36</v>
+        <v>453</v>
       </c>
       <c r="F174" s="5">
-        <v>20123</v>
+        <v>12011</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>492</v>
+        <v>151</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>493</v>
+        <v>153</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F175" s="5">
-        <v>90141</v>
+        <v>154</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>481</v>
+        <v>420</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>389</v>
+        <v>421</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F176" s="8" t="s">
-        <v>391</v>
+        <v>36</v>
+      </c>
+      <c r="F176" s="5">
+        <v>20123</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>388</v>
+        <v>492</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>389</v>
+        <v>493</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>391</v>
+        <v>19</v>
+      </c>
+      <c r="F177" s="5">
+        <v>90141</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>467</v>
+        <v>389</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="F178" s="5">
-        <v>38055</v>
+        <v>10</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>391</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>429</v>
+        <v>389</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="F179" s="5">
-        <v>25010</v>
+        <v>10</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>391</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>394</v>
+        <v>466</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>395</v>
+        <v>467</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>36</v>
+        <v>468</v>
       </c>
       <c r="F180" s="5">
-        <v>20123</v>
+        <v>38055</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="F181" s="5">
-        <v>71016</v>
+        <v>25010</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>16</v>
+        <v>394</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>18</v>
+        <v>395</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F182" s="5">
+        <v>20123</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>325</v>
+        <v>417</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>327</v>
+        <v>418</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>329</v>
+        <v>419</v>
+      </c>
+      <c r="F183" s="5">
+        <v>71016</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>330</v>
+        <v>44</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>479</v>
+        <v>325</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>480</v>
+        <v>327</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F185" s="5">
-        <v>20123</v>
+        <v>328</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>329</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>38</v>
+        <v>330</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>397</v>
+        <v>277</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>218</v>
+        <v>37</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>216</v>
+        <v>479</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>217</v>
+        <v>480</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F187" s="5" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F187" s="5">
+        <v>20123</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>160</v>
+        <v>397</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>435</v>
+        <v>216</v>
       </c>
       <c r="B189" s="9" t="s">
         <v>9</v>
@@ -6309,59 +6336,99 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="F190" s="10" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B191" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D191" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E191" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F191" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G191" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A192" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B192" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D192" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E192" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F192" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G192" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A193" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B191" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C191" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D191" s="9" t="s">
+      <c r="B193" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D193" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E191" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F191" s="10" t="s">
+      <c r="E193" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F193" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G191" s="9" t="s">
+      <c r="G193" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C192" s="1"/>
-    </row>
-    <row r="193" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C193" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G146" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G191">
+    <sortState ref="A2:G193">
       <sortCondition ref="A1:A146"/>
     </sortState>
   </autoFilter>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{BFEEF0D2-DA37-407F-8EB2-B587CF0E4CDC}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{67FD046E-1047-4CFA-AE54-88ACD702A98D}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="516">
   <si>
     <t>Nome account</t>
   </si>
@@ -1556,6 +1556,21 @@
   </si>
   <si>
     <t>PD</t>
+  </si>
+  <si>
+    <t>ALPENFRUT</t>
+  </si>
+  <si>
+    <t>UD</t>
+  </si>
+  <si>
+    <t>STRADA PROVINCIALE N. 82 DI CHIASIELLIS</t>
+  </si>
+  <si>
+    <t>BICINICCO</t>
+  </si>
+  <si>
+    <t>Udine</t>
   </si>
 </sst>
 </file>
@@ -1974,7 +1989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G193"/>
+  <dimension ref="A1:G194"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -2173,68 +2188,68 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>263</v>
+        <v>511</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>264</v>
+        <v>512</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>265</v>
+        <v>513</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>267</v>
+        <v>514</v>
+      </c>
+      <c r="F9" s="5">
+        <v>33050</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>268</v>
+        <v>515</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>83</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>496</v>
+        <v>235</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>497</v>
+        <v>236</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="F11" s="5">
-        <v>10098</v>
+        <v>81</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>83</v>
@@ -2242,76 +2257,76 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>45</v>
+        <v>496</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>47</v>
+        <v>497</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>49</v>
+        <v>498</v>
+      </c>
+      <c r="F12" s="5">
+        <v>10098</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>9</v>
@@ -2334,7 +2349,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>9</v>
@@ -2357,7 +2372,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>483</v>
+        <v>196</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>9</v>
@@ -2371,7 +2386,7 @@
       <c r="E17" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="5" t="s">
         <v>180</v>
       </c>
       <c r="G17" s="4" t="s">
@@ -2380,7 +2395,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>197</v>
+        <v>483</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>9</v>
@@ -2394,7 +2409,7 @@
       <c r="E18" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="8" t="s">
         <v>180</v>
       </c>
       <c r="G18" s="4" t="s">
@@ -2403,7 +2418,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>9</v>
@@ -2426,99 +2441,99 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>404</v>
+        <v>183</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>405</v>
+        <v>179</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F21" s="5">
-        <v>20124</v>
+        <v>39100</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>469</v>
+        <v>400</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>470</v>
+        <v>401</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>471</v>
+        <v>36</v>
+      </c>
+      <c r="F22" s="5">
+        <v>20124</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>437</v>
+        <v>469</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>305</v>
+        <v>470</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>471</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>350</v>
+        <v>437</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>34</v>
@@ -2527,13 +2542,13 @@
         <v>8</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>351</v>
+        <v>305</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F24" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>38</v>
@@ -2541,53 +2556,53 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>67</v>
+        <v>350</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>18</v>
+        <v>351</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F25" s="5">
+        <v>20122</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>399</v>
+        <v>67</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F26" s="5">
-        <v>10123</v>
+        <v>19</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>78</v>
+        <v>399</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>79</v>
@@ -2601,8 +2616,8 @@
       <c r="E27" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>82</v>
+      <c r="F27" s="5">
+        <v>10123</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>83</v>
@@ -2610,53 +2625,53 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>279</v>
+        <v>78</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="F28" s="5">
-        <v>39042</v>
+        <v>81</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>338</v>
+        <v>279</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>339</v>
+        <v>289</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>36</v>
+        <v>290</v>
       </c>
       <c r="F29" s="5">
-        <v>20121</v>
+        <v>39042</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>33</v>
+        <v>338</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>34</v>
@@ -2665,13 +2680,13 @@
         <v>8</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>35</v>
+        <v>339</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>37</v>
+      <c r="F30" s="5">
+        <v>20121</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>38</v>
@@ -2679,45 +2694,45 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>221</v>
+        <v>33</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>116</v>
+        <v>221</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>118</v>
+        <v>222</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>77</v>
@@ -2725,7 +2740,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>254</v>
+        <v>116</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>117</v>
@@ -2748,122 +2763,122 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>62</v>
+        <v>254</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>291</v>
+        <v>145</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>292</v>
+        <v>146</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>293</v>
+        <v>147</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="F36" s="5">
-        <v>60035</v>
+        <v>148</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>500</v>
+        <v>291</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>501</v>
+        <v>293</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="F37" s="5">
-        <v>10143</v>
+        <v>60035</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>390</v>
+        <v>500</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>270</v>
+        <v>501</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F38" s="5">
-        <v>20123</v>
+        <v>10143</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>438</v>
+        <v>390</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>34</v>
@@ -2886,7 +2901,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>398</v>
+        <v>438</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>34</v>
@@ -2909,7 +2924,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>269</v>
+        <v>398</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>34</v>
@@ -2923,8 +2938,8 @@
       <c r="E41" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F41" s="5" t="s">
-        <v>61</v>
+      <c r="F41" s="5">
+        <v>20123</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>38</v>
@@ -2932,7 +2947,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>34</v>
@@ -2941,13 +2956,13 @@
         <v>8</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>38</v>
@@ -2955,7 +2970,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>410</v>
+        <v>137</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>34</v>
@@ -2969,8 +2984,8 @@
       <c r="E43" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F43" s="5">
-        <v>20121</v>
+      <c r="F43" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>38</v>
@@ -2978,283 +2993,283 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>138</v>
+        <v>410</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>142</v>
+        <v>36</v>
+      </c>
+      <c r="F44" s="5">
+        <v>20121</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>445</v>
+        <v>125</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F46" s="5">
-        <v>20158</v>
+        <v>19</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>225</v>
+        <v>445</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F47" s="5">
+        <v>20158</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>488</v>
+        <v>84</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>489</v>
+        <v>85</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>490</v>
+        <v>86</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="F49" s="5">
-        <v>26015</v>
+        <v>87</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>334</v>
+        <v>488</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>9</v>
+        <v>489</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>335</v>
+        <v>490</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>218</v>
+        <v>491</v>
+      </c>
+      <c r="F50" s="5">
+        <v>26015</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="F51" s="5">
-        <v>56025</v>
+        <v>10</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>9</v>
+        <v>296</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>273</v>
+        <v>302</v>
+      </c>
+      <c r="F52" s="5">
+        <v>56025</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>376</v>
+        <v>271</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>377</v>
+        <v>272</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F53" s="5">
-        <v>20121</v>
+        <v>10</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>280</v>
+        <v>376</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>303</v>
+        <v>377</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>304</v>
+        <v>36</v>
       </c>
       <c r="F54" s="5">
-        <v>24060</v>
+        <v>20121</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>482</v>
+        <v>280</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="F55" s="5">
-        <v>20121</v>
+        <v>24060</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>175</v>
+        <v>482</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>34</v>
@@ -3263,21 +3278,21 @@
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F56" s="5" t="s">
-        <v>158</v>
+      <c r="F56" s="5">
+        <v>20121</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>34</v>
@@ -3300,7 +3315,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>253</v>
+        <v>156</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>34</v>
@@ -3309,21 +3324,21 @@
         <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>440</v>
+        <v>253</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>34</v>
@@ -3332,205 +3347,205 @@
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>441</v>
+        <v>230</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F59" s="5">
-        <v>20122</v>
+      <c r="F59" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>245</v>
+        <v>440</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>247</v>
+        <v>441</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>249</v>
+        <v>36</v>
+      </c>
+      <c r="F60" s="5">
+        <v>20122</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>83</v>
+        <v>250</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>363</v>
+        <v>251</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>364</v>
+        <v>79</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>365</v>
+        <v>252</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="F62" s="5">
-        <v>76123</v>
+        <v>81</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>426</v>
+        <v>363</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>28</v>
+        <v>364</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>132</v>
+        <v>365</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>30</v>
+        <v>366</v>
       </c>
       <c r="F63" s="5">
-        <v>39100</v>
+        <v>76123</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>393</v>
+        <v>132</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F64" s="5">
-        <v>70043</v>
+        <v>39100</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>219</v>
+        <v>392</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>220</v>
+        <v>393</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="F65" s="5">
+        <v>70043</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>34</v>
@@ -3539,13 +3554,13 @@
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>38</v>
@@ -3553,7 +3568,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>34</v>
@@ -3576,7 +3591,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>34</v>
@@ -3599,168 +3614,168 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>372</v>
+        <v>130</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>373</v>
+        <v>34</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>374</v>
+        <v>122</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="F71" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>201</v>
+        <v>372</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>34</v>
+        <v>373</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>190</v>
+        <v>375</v>
+      </c>
+      <c r="F72" s="5">
+        <v>61121</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>507</v>
+        <v>201</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="C73" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>509</v>
+        <v>189</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="F73" s="5">
-        <v>35010</v>
+        <v>36</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>506</v>
+        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>281</v>
+        <v>507</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C74" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>305</v>
+        <v>509</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>36</v>
+        <v>508</v>
       </c>
       <c r="F74" s="5">
-        <v>20123</v>
+        <v>35010</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>38</v>
+        <v>506</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>352</v>
+        <v>281</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>353</v>
+        <v>34</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>355</v>
+        <v>36</v>
       </c>
       <c r="F75" s="5">
-        <v>15033</v>
+        <v>20123</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>59</v>
+        <v>352</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>34</v>
+        <v>353</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>60</v>
+        <v>354</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>61</v>
+        <v>355</v>
+      </c>
+      <c r="F76" s="5">
+        <v>15033</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F77" s="5">
-        <v>10153</v>
+        <v>36</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>431</v>
+        <v>336</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>79</v>
@@ -3783,53 +3798,53 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>282</v>
+        <v>431</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="F79" s="5">
-        <v>183</v>
+        <v>10153</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>211</v>
+        <v>306</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>58</v>
+        <v>10</v>
+      </c>
+      <c r="F80" s="5">
+        <v>183</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>275</v>
+        <v>210</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>34</v>
@@ -3838,44 +3853,44 @@
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>276</v>
+        <v>211</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>128</v>
+        <v>275</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>28</v>
@@ -3898,122 +3913,122 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>415</v>
+        <v>242</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>416</v>
+        <v>129</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>274</v>
+        <v>415</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>29</v>
+        <v>416</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>241</v>
+        <v>31</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>436</v>
+        <v>238</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>129</v>
+        <v>239</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F87" s="5">
-        <v>39100</v>
+        <v>240</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>206</v>
+        <v>436</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>61</v>
+        <v>30</v>
+      </c>
+      <c r="F88" s="5">
+        <v>39100</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>367</v>
+        <v>206</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>34</v>
@@ -4027,8 +4042,8 @@
       <c r="E89" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F89" s="5">
-        <v>20123</v>
+      <c r="F89" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>38</v>
@@ -4036,7 +4051,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>101</v>
+        <v>367</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>34</v>
@@ -4050,8 +4065,8 @@
       <c r="E90" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F90" s="5" t="s">
-        <v>61</v>
+      <c r="F90" s="5">
+        <v>20123</v>
       </c>
       <c r="G90" s="4" t="s">
         <v>38</v>
@@ -4059,214 +4074,214 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>494</v>
+        <v>101</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>495</v>
+        <v>60</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F91" s="8" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>407</v>
+        <v>494</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>408</v>
+        <v>495</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="F92" s="5">
-        <v>38121</v>
+        <v>10</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>36</v>
+        <v>409</v>
       </c>
       <c r="F93" s="5">
-        <v>20123</v>
+        <v>38121</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F94" s="5">
-        <v>90139</v>
+        <v>20123</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>195</v>
+        <v>362</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F95" s="5">
-        <v>20123</v>
+        <v>90139</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>456</v>
+        <v>346</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>457</v>
+        <v>195</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F96" s="5">
+        <v>20123</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>283</v>
+        <v>456</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>309</v>
+        <v>457</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="F97" s="5">
-        <v>12037</v>
+        <v>10</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>13</v>
+        <v>283</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>14</v>
+        <v>309</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>15</v>
+        <v>310</v>
+      </c>
+      <c r="F98" s="5">
+        <v>12037</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>11</v>
+        <v>307</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>28</v>
@@ -4289,58 +4304,58 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>499</v>
+        <v>27</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C103" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
@@ -4349,8 +4364,8 @@
       <c r="E103" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F103" s="5">
-        <v>39100</v>
+      <c r="F103" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>32</v>
@@ -4358,191 +4373,191 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>233</v>
+        <v>499</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C104" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>218</v>
+        <v>30</v>
+      </c>
+      <c r="F104" s="5">
+        <v>39100</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>188</v>
+        <v>233</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>484</v>
+        <v>188</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>485</v>
+        <v>34</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>486</v>
+        <v>189</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="F106" s="5">
-        <v>66020</v>
+        <v>36</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>412</v>
+        <v>484</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>341</v>
+        <v>485</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>413</v>
+        <v>486</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>414</v>
+        <v>487</v>
       </c>
       <c r="F107" s="5">
-        <v>37137</v>
+        <v>66020</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>344</v>
+        <v>77</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>461</v>
+        <v>412</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>9</v>
+        <v>341</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>462</v>
+        <v>413</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F108" s="8" t="s">
-        <v>218</v>
+        <v>414</v>
+      </c>
+      <c r="F108" s="5">
+        <v>37137</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>11</v>
+        <v>344</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>295</v>
+        <v>461</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>297</v>
+        <v>462</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="F109" s="5">
-        <v>56010</v>
+        <v>10</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="F110" s="5">
-        <v>40060</v>
+        <v>56010</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>26</v>
+        <v>299</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>385</v>
+        <v>311</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>386</v>
+        <v>312</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>36</v>
+        <v>313</v>
       </c>
       <c r="F111" s="5">
-        <v>20121</v>
+        <v>40060</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>34</v>
@@ -4556,8 +4571,8 @@
       <c r="E112" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F112" s="5" t="s">
-        <v>58</v>
+      <c r="F112" s="5">
+        <v>20121</v>
       </c>
       <c r="G112" s="4" t="s">
         <v>38</v>
@@ -4565,99 +4580,99 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>213</v>
+        <v>387</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>179</v>
+        <v>386</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>180</v>
+        <v>58</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>68</v>
+        <v>213</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>284</v>
+        <v>68</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>314</v>
+        <v>69</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>315</v>
+        <v>70</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="F115" s="5">
-        <v>57021</v>
+        <v>71</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>299</v>
+        <v>73</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>184</v>
+        <v>284</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>180</v>
+        <v>316</v>
+      </c>
+      <c r="F116" s="5">
+        <v>57021</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>463</v>
+        <v>184</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>9</v>
@@ -4671,7 +4686,7 @@
       <c r="E117" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F117" s="8" t="s">
+      <c r="F117" s="5" t="s">
         <v>180</v>
       </c>
       <c r="G117" s="4" t="s">
@@ -4680,122 +4695,122 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>89</v>
+        <v>463</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>93</v>
+        <v>10</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>347</v>
+        <v>89</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>348</v>
+        <v>91</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="F119" s="5">
-        <v>70124</v>
+        <v>92</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>189</v>
+        <v>348</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>36</v>
+        <v>349</v>
       </c>
       <c r="F120" s="5">
-        <v>20158</v>
+        <v>70124</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>359</v>
+        <v>189</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>360</v>
+        <v>36</v>
       </c>
       <c r="F121" s="5">
-        <v>12084</v>
+        <v>20158</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>307</v>
+        <v>159</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>194</v>
+        <v>358</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>195</v>
+        <v>359</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>61</v>
+        <v>360</v>
+      </c>
+      <c r="F122" s="5">
+        <v>12084</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>34</v>
@@ -4804,13 +4819,13 @@
         <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="E123" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="G123" s="4" t="s">
         <v>38</v>
@@ -4818,168 +4833,168 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>458</v>
+        <v>227</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>459</v>
+        <v>228</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F124" s="8" t="s">
-        <v>460</v>
+        <v>36</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>108</v>
+        <v>458</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>110</v>
+        <v>459</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F125" s="5" t="s">
-        <v>112</v>
+        <v>10</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>460</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>432</v>
+        <v>108</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>308</v>
+        <v>109</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>433</v>
+        <v>110</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="F126" s="5">
-        <v>12100</v>
+        <v>111</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>307</v>
+        <v>113</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>22</v>
+        <v>308</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>23</v>
+        <v>433</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>24</v>
+        <v>434</v>
       </c>
       <c r="F127" s="5">
-        <v>40127</v>
+        <v>12100</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>26</v>
+        <v>307</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>356</v>
+        <v>396</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>357</v>
+        <v>23</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F128" s="5">
-        <v>20121</v>
+        <v>40127</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>232</v>
+        <v>356</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>29</v>
+        <v>357</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F129" s="5">
+        <v>20121</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>34</v>
@@ -4988,13 +5003,13 @@
         <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="E131" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>38</v>
@@ -5002,7 +5017,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>442</v>
+        <v>56</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>34</v>
@@ -5011,113 +5026,113 @@
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>443</v>
+        <v>57</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="F132" s="5">
-        <v>20038</v>
+        <v>36</v>
+      </c>
+      <c r="F132" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>236</v>
+        <v>443</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="F133" s="5">
-        <v>10121</v>
+        <v>20038</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>95</v>
+        <v>427</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F134" s="5" t="s">
-        <v>99</v>
+        <v>81</v>
+      </c>
+      <c r="F134" s="5">
+        <v>10121</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>378</v>
+        <v>95</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>379</v>
+        <v>96</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>380</v>
+        <v>97</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="F135" s="5">
-        <v>64020</v>
+        <v>98</v>
+      </c>
+      <c r="F135" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>34</v>
+        <v>379</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>211</v>
+        <v>380</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>36</v>
+        <v>381</v>
       </c>
       <c r="F136" s="5">
-        <v>20121</v>
+        <v>64020</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>133</v>
+        <v>411</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>34</v>
@@ -5126,21 +5141,21 @@
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F137" s="5" t="s">
-        <v>135</v>
+      <c r="F137" s="5">
+        <v>20121</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>34</v>
@@ -5149,67 +5164,67 @@
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>258</v>
+        <v>134</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>340</v>
+        <v>257</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>342</v>
+        <v>258</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="F139" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>344</v>
+        <v>38</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>166</v>
+        <v>340</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>167</v>
+        <v>342</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>168</v>
+        <v>343</v>
+      </c>
+      <c r="F140" s="5">
+        <v>37045</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>159</v>
+        <v>344</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>472</v>
+        <v>166</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>34</v>
@@ -5218,21 +5233,21 @@
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F141" s="5">
-        <v>20135</v>
+      <c r="F141" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>406</v>
+        <v>472</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>34</v>
@@ -5255,53 +5270,53 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>204</v>
+        <v>406</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F143" s="5">
+        <v>20135</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>454</v>
+        <v>204</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>455</v>
+        <v>205</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F144" s="5">
-        <v>20144</v>
+        <v>186</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>38</v>
+        <v>319</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>223</v>
+        <v>454</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>34</v>
@@ -5310,435 +5325,435 @@
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>224</v>
+        <v>455</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F145" s="5" t="s">
-        <v>135</v>
+      <c r="F145" s="5">
+        <v>20144</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>285</v>
+        <v>223</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>317</v>
+        <v>224</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F146" s="5">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>323</v>
+        <v>318</v>
+      </c>
+      <c r="F147" s="5">
+        <v>40026</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>368</v>
+        <v>286</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>369</v>
+        <v>320</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F148" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>287</v>
+        <v>368</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>322</v>
+        <v>36</v>
       </c>
       <c r="F149" s="5">
-        <v>12020</v>
+        <v>20123</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>39</v>
+        <v>287</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>41</v>
+        <v>321</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>43</v>
+        <v>322</v>
+      </c>
+      <c r="F150" s="5">
+        <v>12020</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>422</v>
+        <v>39</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>423</v>
+        <v>40</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>424</v>
+        <v>41</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="F151" s="5">
-        <v>28053</v>
+        <v>42</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>136</v>
+        <v>44</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>172</v>
+        <v>422</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>34</v>
+        <v>423</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>169</v>
+        <v>424</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F152" s="5" t="s">
-        <v>171</v>
+        <v>425</v>
+      </c>
+      <c r="F152" s="5">
+        <v>28053</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>24</v>
+        <v>170</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>446</v>
+        <v>244</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>447</v>
+        <v>34</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>448</v>
+        <v>177</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="F156" s="5">
-        <v>53048</v>
+        <v>36</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>450</v>
+        <v>38</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>243</v>
+        <v>446</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>34</v>
+        <v>447</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>177</v>
+        <v>448</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>58</v>
+        <v>449</v>
+      </c>
+      <c r="F157" s="5">
+        <v>53048</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>38</v>
+        <v>450</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>131</v>
+        <v>243</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>382</v>
+        <v>21</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>383</v>
+        <v>23</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="F160" s="5">
-        <v>20089</v>
+        <v>24</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>476</v>
+        <v>382</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>477</v>
+        <v>383</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F161" s="8" t="s">
-        <v>478</v>
+        <v>384</v>
+      </c>
+      <c r="F161" s="5">
+        <v>20089</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>212</v>
+        <v>476</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>202</v>
+        <v>477</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F162" s="5" t="s">
-        <v>203</v>
+        <v>10</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>478</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>439</v>
+        <v>214</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>34</v>
@@ -5752,8 +5767,8 @@
       <c r="E164" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F164" s="5">
-        <v>20124</v>
+      <c r="F164" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="G164" s="4" t="s">
         <v>159</v>
@@ -5761,7 +5776,7 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>229</v>
+        <v>439</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>34</v>
@@ -5770,21 +5785,21 @@
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E165" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F165" s="5" t="s">
-        <v>231</v>
+      <c r="F165" s="5">
+        <v>20124</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>34</v>
@@ -5807,7 +5822,7 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>473</v>
+        <v>256</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>34</v>
@@ -5816,21 +5831,21 @@
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>465</v>
+        <v>230</v>
       </c>
       <c r="E167" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F167" s="5">
-        <v>20129</v>
+      <c r="F167" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>34</v>
@@ -5853,7 +5868,7 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>34</v>
@@ -5876,7 +5891,7 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>34</v>
@@ -5899,7 +5914,7 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>176</v>
+        <v>475</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>34</v>
@@ -5908,182 +5923,182 @@
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>177</v>
+        <v>465</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F171" s="5" t="s">
-        <v>58</v>
+      <c r="F171" s="5">
+        <v>20129</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>331</v>
+        <v>176</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>332</v>
+        <v>177</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F172" s="5">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="F173" s="5">
-        <v>20124</v>
+        <v>40026</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>451</v>
+        <v>288</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>452</v>
+        <v>324</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>453</v>
+        <v>36</v>
       </c>
       <c r="F174" s="5">
-        <v>12011</v>
+        <v>20124</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>151</v>
+        <v>451</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>152</v>
+        <v>308</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>153</v>
+        <v>452</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>155</v>
+        <v>453</v>
+      </c>
+      <c r="F175" s="5">
+        <v>12011</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>420</v>
+        <v>151</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>421</v>
+        <v>153</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F176" s="5">
-        <v>20123</v>
+        <v>154</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>492</v>
+        <v>420</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>493</v>
+        <v>421</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F177" s="5">
-        <v>90141</v>
+        <v>20123</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>389</v>
+        <v>493</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F178" s="8" t="s">
-        <v>391</v>
+        <v>19</v>
+      </c>
+      <c r="F178" s="5">
+        <v>90141</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>388</v>
+        <v>481</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>9</v>
@@ -6097,7 +6112,7 @@
       <c r="E179" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F179" s="5" t="s">
+      <c r="F179" s="8" t="s">
         <v>391</v>
       </c>
       <c r="G179" s="4" t="s">
@@ -6106,168 +6121,168 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>466</v>
+        <v>388</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>467</v>
+        <v>389</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="F180" s="5">
-        <v>38055</v>
+        <v>10</v>
+      </c>
+      <c r="F180" s="5" t="s">
+        <v>391</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>428</v>
+        <v>466</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>103</v>
+        <v>264</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>429</v>
+        <v>467</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>430</v>
+        <v>468</v>
       </c>
       <c r="F181" s="5">
-        <v>25010</v>
+        <v>38055</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>107</v>
+        <v>268</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>36</v>
+        <v>430</v>
       </c>
       <c r="F182" s="5">
-        <v>20123</v>
+        <v>25010</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>418</v>
+        <v>395</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>419</v>
+        <v>36</v>
       </c>
       <c r="F183" s="5">
-        <v>71016</v>
+        <v>20123</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>16</v>
+        <v>417</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>18</v>
+        <v>418</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>20</v>
+        <v>419</v>
+      </c>
+      <c r="F184" s="5">
+        <v>71016</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>325</v>
+        <v>16</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>326</v>
+        <v>17</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>327</v>
+        <v>18</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>328</v>
+        <v>19</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>329</v>
+        <v>20</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>330</v>
+        <v>12</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>277</v>
+        <v>325</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>278</v>
+        <v>327</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>37</v>
+        <v>329</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>38</v>
+        <v>330</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>479</v>
+        <v>277</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>34</v>
@@ -6276,13 +6291,13 @@
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>480</v>
+        <v>278</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F187" s="5">
-        <v>20123</v>
+      <c r="F187" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G187" s="4" t="s">
         <v>38</v>
@@ -6290,30 +6305,30 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>397</v>
+        <v>479</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>217</v>
+        <v>480</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F188" s="5" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F188" s="5">
+        <v>20123</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>216</v>
+        <v>397</v>
       </c>
       <c r="B189" s="9" t="s">
         <v>9</v>
@@ -6336,53 +6351,53 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="F190" s="10" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>435</v>
+        <v>160</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="F191" s="10" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>255</v>
+        <v>435</v>
       </c>
       <c r="B192" s="9" t="s">
         <v>9</v>
@@ -6405,30 +6420,53 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B193" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D193" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E193" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F193" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G193" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A194" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B193" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D193" s="9" t="s">
+      <c r="B194" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C194" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D194" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E193" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F193" s="10" t="s">
+      <c r="E194" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F194" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G193" s="9" t="s">
+      <c r="G194" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G146" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G193">
+    <sortState ref="A2:G194">
       <sortCondition ref="A1:A146"/>
     </sortState>
   </autoFilter>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{67FD046E-1047-4CFA-AE54-88ACD702A98D}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{3CF84D38-D8CE-4C6E-A3FF-09511E8F20F3}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="517">
   <si>
     <t>Nome account</t>
   </si>
@@ -1571,6 +1571,9 @@
   </si>
   <si>
     <t>Udine</t>
+  </si>
+  <si>
+    <t>PACIFICO BERILLO SRL</t>
   </si>
 </sst>
 </file>
@@ -1989,7 +1992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G194"/>
+  <dimension ref="A1:G195"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -6464,6 +6467,29 @@
         <v>38</v>
       </c>
     </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A195" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F195" s="7">
+        <v>39100</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G146" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
     <sortState ref="A2:G194">

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{3CF84D38-D8CE-4C6E-A3FF-09511E8F20F3}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{2C224AFA-E473-42E8-964F-E7BF46E04A0B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="524">
   <si>
     <t>Nome account</t>
   </si>
@@ -1574,6 +1574,27 @@
   </si>
   <si>
     <t>PACIFICO BERILLO SRL</t>
+  </si>
+  <si>
+    <t>SOLAR BOREALIS SRL</t>
+  </si>
+  <si>
+    <t>VIA ANTONIANA 220/E</t>
+  </si>
+  <si>
+    <t>CAMPODARSEGO</t>
+  </si>
+  <si>
+    <t>HELIOS ONE SRL</t>
+  </si>
+  <si>
+    <t>VIA VITTORIA COLONNA 14</t>
+  </si>
+  <si>
+    <t>CASTELNOVO SRL</t>
+  </si>
+  <si>
+    <t>VIA VARESE 194</t>
   </si>
 </sst>
 </file>
@@ -1992,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G195"/>
+  <dimension ref="A1:G198"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -6490,6 +6511,75 @@
         <v>32</v>
       </c>
     </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A196" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="F196" s="7">
+        <v>35011</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A197" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F197" s="7">
+        <v>80121</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A198" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F198" s="7">
+        <v>20033</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G146" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
     <sortState ref="A2:G194">

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{2C224AFA-E473-42E8-964F-E7BF46E04A0B}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{2AE3201F-87CD-411B-9FFB-40C9BFC15788}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="527">
   <si>
     <t>Nome account</t>
   </si>
@@ -1595,6 +1595,15 @@
   </si>
   <si>
     <t>VIA VARESE 194</t>
+  </si>
+  <si>
+    <t>AUKERA ITALY 5 SRL</t>
+  </si>
+  <si>
+    <t>OPR SUN 8 SRL</t>
+  </si>
+  <si>
+    <t>VIA CERESIO 7</t>
   </si>
 </sst>
 </file>
@@ -2013,7 +2022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G198"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -2695,7 +2704,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>338</v>
+        <v>524</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>34</v>
@@ -2718,7 +2727,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>33</v>
+        <v>338</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>34</v>
@@ -2727,13 +2736,13 @@
         <v>8</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>35</v>
+        <v>339</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>37</v>
+      <c r="F31" s="5">
+        <v>20121</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>38</v>
@@ -2741,45 +2750,45 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>221</v>
+        <v>33</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>116</v>
+        <v>221</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>118</v>
+        <v>222</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>77</v>
@@ -2787,7 +2796,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>254</v>
+        <v>116</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>117</v>
@@ -2810,145 +2819,145 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>62</v>
+        <v>254</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>291</v>
+        <v>145</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>292</v>
+        <v>146</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>293</v>
+        <v>147</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="F37" s="5">
-        <v>60035</v>
+        <v>148</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>500</v>
+        <v>522</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F38" s="5">
-        <v>10143</v>
+        <v>20033</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>83</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>390</v>
+        <v>291</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>34</v>
+        <v>292</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>36</v>
+        <v>294</v>
       </c>
       <c r="F39" s="5">
-        <v>20123</v>
+        <v>60035</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>438</v>
+        <v>500</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C40" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>270</v>
+        <v>501</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F40" s="5">
-        <v>20123</v>
+        <v>10143</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>34</v>
@@ -2971,7 +2980,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>269</v>
+        <v>438</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>34</v>
@@ -2985,8 +2994,8 @@
       <c r="E42" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>61</v>
+      <c r="F42" s="5">
+        <v>20123</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>38</v>
@@ -2994,7 +3003,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>137</v>
+        <v>398</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>34</v>
@@ -3003,13 +3012,13 @@
         <v>8</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F43" s="5" t="s">
-        <v>58</v>
+      <c r="F43" s="5">
+        <v>20123</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>38</v>
@@ -3017,7 +3026,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>410</v>
+        <v>269</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>34</v>
@@ -3026,13 +3035,13 @@
         <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F44" s="5">
-        <v>20121</v>
+      <c r="F44" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>38</v>
@@ -3040,191 +3049,191 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>125</v>
+        <v>410</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>127</v>
+        <v>36</v>
+      </c>
+      <c r="F46" s="5">
+        <v>20121</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>445</v>
+        <v>138</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>189</v>
+        <v>140</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F47" s="5">
-        <v>20158</v>
+        <v>141</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>142</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>225</v>
+        <v>125</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>226</v>
+        <v>126</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>84</v>
+        <v>445</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>88</v>
+        <v>36</v>
+      </c>
+      <c r="F49" s="5">
+        <v>20158</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>44</v>
+        <v>159</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>488</v>
+        <v>225</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>489</v>
+        <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>490</v>
+        <v>226</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="F50" s="5">
-        <v>26015</v>
+        <v>30</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>334</v>
+        <v>84</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>335</v>
+        <v>86</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>218</v>
+        <v>88</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>300</v>
+        <v>488</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>296</v>
+        <v>489</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>301</v>
+        <v>490</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>302</v>
+        <v>491</v>
       </c>
       <c r="F52" s="5">
-        <v>56025</v>
+        <v>26015</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>299</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>271</v>
+        <v>334</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>9</v>
@@ -3233,13 +3242,13 @@
         <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>272</v>
+        <v>335</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>273</v>
+        <v>218</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>11</v>
@@ -3247,53 +3256,53 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>376</v>
+        <v>300</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>377</v>
+        <v>301</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>36</v>
+        <v>302</v>
       </c>
       <c r="F54" s="5">
-        <v>20121</v>
+        <v>56025</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="F55" s="5">
-        <v>24060</v>
+        <v>10</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>150</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>482</v>
+        <v>376</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>34</v>
@@ -3302,7 +3311,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>258</v>
+        <v>377</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>36</v>
@@ -3316,30 +3325,30 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>157</v>
+        <v>303</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>158</v>
+        <v>304</v>
+      </c>
+      <c r="F57" s="5">
+        <v>24060</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>156</v>
+        <v>482</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>34</v>
@@ -3348,21 +3357,21 @@
         <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F58" s="5" t="s">
-        <v>158</v>
+      <c r="F58" s="5">
+        <v>20121</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>253</v>
+        <v>175</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>34</v>
@@ -3371,21 +3380,21 @@
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>440</v>
+        <v>156</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>34</v>
@@ -3394,128 +3403,128 @@
         <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>441</v>
+        <v>157</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F60" s="5">
-        <v>20122</v>
+      <c r="F60" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>248</v>
+        <v>36</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>250</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>251</v>
+        <v>440</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>252</v>
+        <v>441</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>237</v>
+        <v>36</v>
+      </c>
+      <c r="F62" s="5">
+        <v>20122</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>363</v>
+        <v>245</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>364</v>
+        <v>246</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>365</v>
+        <v>247</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="F63" s="5">
-        <v>76123</v>
+        <v>248</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>44</v>
+        <v>250</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>426</v>
+        <v>251</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>132</v>
+        <v>252</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F64" s="5">
-        <v>39100</v>
+        <v>81</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>40</v>
+        <v>364</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>393</v>
+        <v>365</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>42</v>
+        <v>366</v>
       </c>
       <c r="F65" s="5">
-        <v>70043</v>
+        <v>76123</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>44</v>
@@ -3523,53 +3532,53 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>219</v>
+        <v>426</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>220</v>
+        <v>132</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="F66" s="5">
+        <v>39100</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>50</v>
+        <v>392</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>47</v>
+        <v>393</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
+      </c>
+      <c r="F67" s="5">
+        <v>70043</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>51</v>
+        <v>219</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>34</v>
@@ -3578,13 +3587,13 @@
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>52</v>
+        <v>220</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>38</v>
@@ -3592,30 +3601,30 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>34</v>
@@ -3624,13 +3633,13 @@
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>38</v>
@@ -3638,7 +3647,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>34</v>
@@ -3661,30 +3670,30 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>372</v>
+        <v>124</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>373</v>
+        <v>34</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>374</v>
+        <v>122</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="F72" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>201</v>
+        <v>130</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>34</v>
@@ -3693,44 +3702,44 @@
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>190</v>
+        <v>58</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>507</v>
+        <v>372</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="C74" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>509</v>
+        <v>374</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>508</v>
+        <v>375</v>
       </c>
       <c r="F74" s="5">
-        <v>35010</v>
+        <v>61121</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>506</v>
+        <v>165</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>281</v>
+        <v>201</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>34</v>
@@ -3739,44 +3748,44 @@
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>305</v>
+        <v>189</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F75" s="5">
-        <v>20123</v>
+      <c r="F75" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>352</v>
+        <v>507</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="C76" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>354</v>
+        <v>509</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>355</v>
+        <v>508</v>
       </c>
       <c r="F76" s="5">
-        <v>15033</v>
+        <v>35010</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>83</v>
+        <v>506</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>59</v>
+        <v>281</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>34</v>
@@ -3785,13 +3794,13 @@
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>60</v>
+        <v>305</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F77" s="5" t="s">
-        <v>61</v>
+      <c r="F77" s="5">
+        <v>20123</v>
       </c>
       <c r="G77" s="4" t="s">
         <v>38</v>
@@ -3799,22 +3808,22 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>79</v>
+        <v>353</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>81</v>
+        <v>355</v>
       </c>
       <c r="F78" s="5">
-        <v>10153</v>
+        <v>15033</v>
       </c>
       <c r="G78" s="4" t="s">
         <v>83</v>
@@ -3822,168 +3831,168 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>431</v>
+        <v>59</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F79" s="5">
-        <v>10153</v>
+        <v>36</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>282</v>
+        <v>336</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="F80" s="5">
-        <v>183</v>
+        <v>10153</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>210</v>
+        <v>431</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>211</v>
+        <v>337</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>58</v>
+        <v>81</v>
+      </c>
+      <c r="F81" s="5">
+        <v>10153</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
+      </c>
+      <c r="F82" s="5">
+        <v>183</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>159</v>
+        <v>307</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>129</v>
+        <v>211</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>242</v>
+        <v>275</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>415</v>
+        <v>128</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>416</v>
+        <v>129</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>28</v>
@@ -3992,7 +4001,7 @@
         <v>8</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>30</v>
@@ -4006,30 +4015,30 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>238</v>
+        <v>415</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>239</v>
+        <v>416</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>241</v>
+        <v>180</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>436</v>
+        <v>274</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>28</v>
@@ -4038,13 +4047,13 @@
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F88" s="5">
-        <v>39100</v>
+      <c r="F88" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G88" s="4" t="s">
         <v>32</v>
@@ -4052,53 +4061,53 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>60</v>
+        <v>239</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>36</v>
+        <v>240</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>61</v>
+        <v>241</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>367</v>
+        <v>436</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F90" s="5">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>34</v>
@@ -4121,237 +4130,237 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>494</v>
+        <v>367</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>495</v>
+        <v>60</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F92" s="5">
+        <v>20123</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>407</v>
+        <v>101</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>264</v>
+        <v>34</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>408</v>
+        <v>60</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="F93" s="5">
-        <v>38121</v>
+        <v>36</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>268</v>
+        <v>38</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>370</v>
+        <v>494</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>371</v>
+        <v>495</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F94" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>361</v>
+        <v>520</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>362</v>
+        <v>521</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="F95" s="5">
-        <v>90139</v>
+        <v>80121</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>346</v>
+        <v>407</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>195</v>
+        <v>408</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>36</v>
+        <v>409</v>
       </c>
       <c r="F96" s="5">
-        <v>20123</v>
+        <v>38121</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>456</v>
+        <v>370</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>457</v>
+        <v>371</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F97" s="8" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F97" s="5">
+        <v>20123</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>283</v>
+        <v>361</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>308</v>
+        <v>17</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>309</v>
+        <v>362</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>310</v>
+        <v>19</v>
       </c>
       <c r="F98" s="5">
-        <v>12037</v>
+        <v>90139</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>307</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>13</v>
+        <v>346</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>14</v>
+        <v>195</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="F99" s="5">
+        <v>20123</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>123</v>
+        <v>456</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>55</v>
+        <v>457</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>31</v>
+        <v>10</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>54</v>
+        <v>283</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>28</v>
+        <v>308</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>55</v>
+        <v>309</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>31</v>
+        <v>310</v>
+      </c>
+      <c r="F101" s="5">
+        <v>12037</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>32</v>
+        <v>307</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>9</v>
@@ -4360,21 +4369,21 @@
         <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>28</v>
@@ -4383,7 +4392,7 @@
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>30</v>
@@ -4397,22 +4406,22 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>499</v>
+        <v>54</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C104" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F104" s="5">
-        <v>39100</v>
+      <c r="F104" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G104" s="4" t="s">
         <v>32</v>
@@ -4420,7 +4429,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>233</v>
+        <v>74</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>9</v>
@@ -4429,274 +4438,274 @@
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>234</v>
+        <v>75</v>
       </c>
       <c r="E105" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>218</v>
+        <v>76</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>188</v>
+        <v>27</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>189</v>
+        <v>29</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="C107" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>486</v>
+        <v>29</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>487</v>
+        <v>30</v>
       </c>
       <c r="F107" s="5">
-        <v>66020</v>
+        <v>39100</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>412</v>
+        <v>233</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>341</v>
+        <v>9</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>413</v>
+        <v>234</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="F108" s="5">
-        <v>37137</v>
+        <v>10</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>461</v>
+        <v>188</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>462</v>
+        <v>189</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F109" s="8" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>295</v>
+        <v>484</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>296</v>
+        <v>485</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>297</v>
+        <v>486</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>298</v>
+        <v>487</v>
       </c>
       <c r="F110" s="5">
-        <v>56010</v>
+        <v>66020</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>299</v>
+        <v>77</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>311</v>
+        <v>412</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>22</v>
+        <v>341</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>312</v>
+        <v>413</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>313</v>
+        <v>414</v>
       </c>
       <c r="F111" s="5">
-        <v>40060</v>
+        <v>37137</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>26</v>
+        <v>344</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>385</v>
+        <v>461</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>386</v>
+        <v>462</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F112" s="5">
-        <v>20121</v>
+        <v>10</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>387</v>
+        <v>295</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>386</v>
+        <v>297</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>58</v>
+        <v>298</v>
+      </c>
+      <c r="F113" s="5">
+        <v>56010</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>213</v>
+        <v>311</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>179</v>
+        <v>312</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>180</v>
+        <v>313</v>
+      </c>
+      <c r="F114" s="5">
+        <v>40060</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>68</v>
+        <v>385</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>70</v>
+        <v>386</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F115" s="5" t="s">
-        <v>72</v>
+        <v>36</v>
+      </c>
+      <c r="F115" s="5">
+        <v>20121</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>284</v>
+        <v>387</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>314</v>
+        <v>34</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>315</v>
+        <v>386</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="F116" s="5">
-        <v>57021</v>
+        <v>36</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>299</v>
+        <v>38</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>9</v>
@@ -4719,145 +4728,145 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>463</v>
+        <v>68</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>179</v>
+        <v>70</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F118" s="8" t="s">
-        <v>180</v>
+        <v>71</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>89</v>
+        <v>284</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>90</v>
+        <v>314</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>91</v>
+        <v>315</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F119" s="5" t="s">
-        <v>93</v>
+        <v>316</v>
+      </c>
+      <c r="F119" s="5">
+        <v>57021</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>94</v>
+        <v>299</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>347</v>
+        <v>184</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>348</v>
+        <v>179</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="F120" s="5">
-        <v>70124</v>
+        <v>10</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>333</v>
+        <v>463</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F121" s="5">
-        <v>20158</v>
+        <v>10</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>358</v>
+        <v>89</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>308</v>
+        <v>90</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>359</v>
+        <v>91</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="F122" s="5">
-        <v>12084</v>
+        <v>92</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>307</v>
+        <v>94</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>195</v>
+        <v>348</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F123" s="5" t="s">
-        <v>61</v>
+        <v>349</v>
+      </c>
+      <c r="F123" s="5">
+        <v>70124</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>227</v>
+        <v>333</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>34</v>
@@ -4866,182 +4875,182 @@
         <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="E124" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F124" s="5" t="s">
-        <v>37</v>
+      <c r="F124" s="5">
+        <v>20158</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>458</v>
+        <v>358</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>459</v>
+        <v>359</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F125" s="8" t="s">
-        <v>460</v>
+        <v>360</v>
+      </c>
+      <c r="F125" s="5">
+        <v>12084</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>77</v>
+        <v>307</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>432</v>
+        <v>227</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>433</v>
+        <v>228</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="F127" s="5">
-        <v>12100</v>
+        <v>36</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>396</v>
+        <v>458</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>23</v>
+        <v>459</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F128" s="5">
-        <v>40127</v>
+        <v>10</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>460</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>356</v>
+        <v>108</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>357</v>
+        <v>110</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F129" s="5">
-        <v>20121</v>
+        <v>111</v>
+      </c>
+      <c r="F129" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>232</v>
+        <v>432</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>28</v>
+        <v>308</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>29</v>
+        <v>433</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>31</v>
+        <v>434</v>
+      </c>
+      <c r="F130" s="5">
+        <v>12100</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>32</v>
+        <v>307</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>143</v>
+        <v>396</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>37</v>
+        <v>24</v>
+      </c>
+      <c r="F131" s="5">
+        <v>40127</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>56</v>
+        <v>356</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>34</v>
@@ -5050,13 +5059,13 @@
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>57</v>
+        <v>357</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F132" s="5" t="s">
-        <v>58</v>
+      <c r="F132" s="5">
+        <v>20121</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>38</v>
@@ -5064,7 +5073,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>442</v>
+        <v>525</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>34</v>
@@ -5073,90 +5082,90 @@
         <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>443</v>
+        <v>526</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>444</v>
+        <v>36</v>
       </c>
       <c r="F133" s="5">
-        <v>20038</v>
+        <v>20154</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>427</v>
+        <v>516</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>236</v>
+        <v>29</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="F134" s="5">
-        <v>10121</v>
+        <v>39100</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>95</v>
+        <v>232</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>378</v>
+        <v>143</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>379</v>
+        <v>34</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>380</v>
+        <v>144</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="F136" s="5">
-        <v>64020</v>
+        <v>36</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>411</v>
+        <v>56</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>34</v>
@@ -5165,13 +5174,13 @@
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>211</v>
+        <v>57</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F137" s="5">
-        <v>20121</v>
+      <c r="F137" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G137" s="4" t="s">
         <v>38</v>
@@ -5179,7 +5188,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>133</v>
+        <v>442</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>34</v>
@@ -5188,13 +5197,13 @@
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>134</v>
+        <v>443</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>135</v>
+        <v>444</v>
+      </c>
+      <c r="F138" s="5">
+        <v>20038</v>
       </c>
       <c r="G138" s="4" t="s">
         <v>136</v>
@@ -5202,76 +5211,76 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>257</v>
+        <v>427</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>58</v>
+        <v>81</v>
+      </c>
+      <c r="F139" s="5">
+        <v>10121</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>340</v>
+        <v>95</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>341</v>
+        <v>96</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>342</v>
+        <v>97</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="F140" s="5">
-        <v>37045</v>
+        <v>98</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>344</v>
+        <v>100</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>166</v>
+        <v>378</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>34</v>
+        <v>379</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>167</v>
+        <v>380</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>168</v>
+        <v>381</v>
+      </c>
+      <c r="F141" s="5">
+        <v>64020</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>472</v>
+        <v>411</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>34</v>
@@ -5280,21 +5289,21 @@
         <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>260</v>
+        <v>211</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F142" s="5">
-        <v>20135</v>
+        <v>20121</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>262</v>
+        <v>38</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>406</v>
+        <v>133</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>34</v>
@@ -5303,67 +5312,67 @@
         <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>260</v>
+        <v>134</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F143" s="5">
-        <v>20135</v>
+      <c r="F143" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>204</v>
+        <v>257</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>205</v>
+        <v>258</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>186</v>
+        <v>36</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>187</v>
+        <v>58</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>319</v>
+        <v>38</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>454</v>
+        <v>340</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>455</v>
+        <v>342</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>36</v>
+        <v>343</v>
       </c>
       <c r="F145" s="5">
-        <v>20144</v>
+        <v>37045</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>38</v>
+        <v>344</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>34</v>
@@ -5372,274 +5381,274 @@
         <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>224</v>
+        <v>167</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>285</v>
+        <v>472</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>317</v>
+        <v>260</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F147" s="5">
-        <v>40026</v>
+        <v>20135</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>286</v>
+        <v>406</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>323</v>
+        <v>36</v>
+      </c>
+      <c r="F148" s="5">
+        <v>20135</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>11</v>
+        <v>262</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>368</v>
+        <v>204</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>369</v>
+        <v>205</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F149" s="5">
-        <v>20123</v>
+        <v>186</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>38</v>
+        <v>319</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>287</v>
+        <v>454</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>321</v>
+        <v>455</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>322</v>
+        <v>36</v>
       </c>
       <c r="F150" s="5">
-        <v>12020</v>
+        <v>20144</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>39</v>
+        <v>223</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>41</v>
+        <v>224</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>44</v>
+        <v>136</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>422</v>
+        <v>285</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>423</v>
+        <v>22</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>424</v>
+        <v>317</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>425</v>
+        <v>318</v>
       </c>
       <c r="F152" s="5">
-        <v>28053</v>
+        <v>40026</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>136</v>
+        <v>26</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>172</v>
+        <v>286</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>169</v>
+        <v>320</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>170</v>
+        <v>10</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>171</v>
+        <v>323</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>198</v>
+        <v>368</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>199</v>
+        <v>369</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>200</v>
+        <v>36</v>
+      </c>
+      <c r="F154" s="5">
+        <v>20123</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>207</v>
+        <v>287</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>69</v>
+        <v>308</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>208</v>
+        <v>321</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F155" s="5" t="s">
-        <v>209</v>
+        <v>322</v>
+      </c>
+      <c r="F155" s="5">
+        <v>12020</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>73</v>
+        <v>307</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>244</v>
+        <v>39</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>177</v>
+        <v>41</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>447</v>
+        <v>423</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>449</v>
+        <v>425</v>
       </c>
       <c r="F157" s="5">
-        <v>53048</v>
+        <v>28053</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>450</v>
+        <v>136</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>243</v>
+        <v>172</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>34</v>
@@ -5648,67 +5657,67 @@
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>58</v>
+        <v>171</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>131</v>
+        <v>198</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>132</v>
+        <v>199</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>31</v>
+        <v>200</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>21</v>
+        <v>207</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>25</v>
+        <v>209</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>382</v>
+        <v>244</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>34</v>
@@ -5717,13 +5726,13 @@
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>383</v>
+        <v>177</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="F161" s="5">
-        <v>20089</v>
+        <v>36</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>38</v>
@@ -5731,53 +5740,53 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>476</v>
+        <v>446</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>9</v>
+        <v>447</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>477</v>
+        <v>448</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F162" s="8" t="s">
-        <v>478</v>
+        <v>449</v>
+      </c>
+      <c r="F162" s="5">
+        <v>53048</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>11</v>
+        <v>450</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>212</v>
+        <v>517</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>22</v>
+        <v>510</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>202</v>
+        <v>518</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>203</v>
+        <v>519</v>
+      </c>
+      <c r="F163" s="5">
+        <v>35011</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>26</v>
+        <v>506</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>34</v>
@@ -5786,67 +5795,67 @@
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="E164" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>439</v>
+        <v>131</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>215</v>
+        <v>132</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F165" s="5">
-        <v>20124</v>
+        <v>30</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>229</v>
+        <v>21</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>230</v>
+        <v>23</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>231</v>
+        <v>25</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>136</v>
+        <v>26</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>256</v>
+        <v>382</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>34</v>
@@ -5855,67 +5864,67 @@
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>230</v>
+        <v>383</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>231</v>
+        <v>384</v>
+      </c>
+      <c r="F167" s="5">
+        <v>20089</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F168" s="5">
-        <v>20129</v>
+        <v>10</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>478</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>262</v>
+        <v>11</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>464</v>
+        <v>212</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>465</v>
+        <v>202</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F169" s="5">
-        <v>20129</v>
+        <v>24</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>262</v>
+        <v>26</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>474</v>
+        <v>214</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>34</v>
@@ -5924,21 +5933,21 @@
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>465</v>
+        <v>215</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F170" s="5">
-        <v>20129</v>
+      <c r="F170" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>34</v>
@@ -5947,21 +5956,21 @@
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>465</v>
+        <v>215</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F171" s="5">
-        <v>20129</v>
+        <v>20124</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>176</v>
+        <v>229</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>34</v>
@@ -5970,113 +5979,113 @@
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>177</v>
+        <v>230</v>
       </c>
       <c r="E172" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>58</v>
+        <v>231</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>331</v>
+        <v>256</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>332</v>
+        <v>230</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F173" s="5">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>288</v>
+        <v>473</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>324</v>
+        <v>465</v>
       </c>
       <c r="E174" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F174" s="5">
-        <v>20124</v>
+        <v>20129</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>453</v>
+        <v>36</v>
       </c>
       <c r="F175" s="5">
-        <v>12011</v>
+        <v>20129</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>307</v>
+        <v>262</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>151</v>
+        <v>474</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>153</v>
+        <v>465</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>155</v>
+        <v>36</v>
+      </c>
+      <c r="F176" s="5">
+        <v>20129</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>44</v>
+        <v>262</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>420</v>
+        <v>475</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>34</v>
@@ -6085,136 +6094,136 @@
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="E177" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F177" s="5">
-        <v>20123</v>
+        <v>20129</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>492</v>
+        <v>176</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>493</v>
+        <v>177</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F178" s="5">
-        <v>90141</v>
+        <v>36</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>481</v>
+        <v>331</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>389</v>
+        <v>332</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F179" s="8" t="s">
-        <v>391</v>
+        <v>318</v>
+      </c>
+      <c r="F179" s="5">
+        <v>40026</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>388</v>
+        <v>288</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>389</v>
+        <v>324</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>391</v>
+        <v>36</v>
+      </c>
+      <c r="F180" s="5">
+        <v>20124</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>264</v>
+        <v>308</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="F181" s="5">
-        <v>38055</v>
+        <v>12011</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>268</v>
+        <v>307</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>428</v>
+        <v>151</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>429</v>
+        <v>153</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="F182" s="5">
-        <v>25010</v>
+        <v>154</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>34</v>
@@ -6223,7 +6232,7 @@
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>36</v>
@@ -6237,237 +6246,237 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>417</v>
+        <v>492</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>418</v>
+        <v>493</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>419</v>
+        <v>19</v>
       </c>
       <c r="F184" s="5">
-        <v>71016</v>
+        <v>90141</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>16</v>
+        <v>481</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>18</v>
+        <v>389</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F185" s="5" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>391</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>325</v>
+        <v>388</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>326</v>
+        <v>9</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>327</v>
+        <v>389</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>328</v>
+        <v>10</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>329</v>
+        <v>391</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>330</v>
+        <v>11</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>277</v>
+        <v>466</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>278</v>
+        <v>467</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F187" s="5" t="s">
-        <v>37</v>
+        <v>468</v>
+      </c>
+      <c r="F187" s="5">
+        <v>38055</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>479</v>
+        <v>428</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>480</v>
+        <v>429</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>36</v>
+        <v>430</v>
       </c>
       <c r="F188" s="5">
-        <v>20123</v>
+        <v>25010</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>217</v>
+        <v>395</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F189" s="10" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F189" s="10">
+        <v>20123</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>216</v>
+        <v>417</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>217</v>
+        <v>418</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F190" s="10" t="s">
-        <v>218</v>
+        <v>419</v>
+      </c>
+      <c r="F190" s="10">
+        <v>71016</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>161</v>
+        <v>17</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>163</v>
+        <v>19</v>
       </c>
       <c r="F191" s="10" t="s">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>9</v>
+        <v>326</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>217</v>
+        <v>327</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>10</v>
+        <v>328</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>218</v>
+        <v>329</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>11</v>
+        <v>330</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F193" s="10" t="s">
-        <v>218</v>
+        <v>37</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>173</v>
+        <v>479</v>
       </c>
       <c r="B194" s="9" t="s">
         <v>34</v>
@@ -6476,113 +6485,159 @@
         <v>8</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>174</v>
+        <v>480</v>
       </c>
       <c r="E194" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F194" s="10" t="s">
-        <v>37</v>
+      <c r="F194" s="10">
+        <v>20123</v>
       </c>
       <c r="G194" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A195" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="B195" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C195" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D195" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E195" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F195" s="7">
-        <v>39100</v>
-      </c>
-      <c r="G195" s="3" t="s">
-        <v>32</v>
+      <c r="A195" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="B195" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C195" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D195" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E195" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F195" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G195" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A196" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="B196" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="C196" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D196" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="E196" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="F196" s="7">
-        <v>35011</v>
-      </c>
-      <c r="G196" s="3" t="s">
-        <v>506</v>
+      <c r="A196" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B196" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C196" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D196" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E196" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F196" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G196" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A197" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="B197" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C197" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="E197" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F197" s="7">
-        <v>80121</v>
-      </c>
-      <c r="G197" s="3" t="s">
-        <v>73</v>
+      <c r="A197" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C197" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D197" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E197" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F197" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G197" s="9" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A198" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="B198" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C198" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D198" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="E198" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F198" s="7">
-        <v>20033</v>
-      </c>
-      <c r="G198" s="3" t="s">
-        <v>159</v>
+      <c r="A198" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B198" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C198" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D198" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E198" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F198" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G198" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A199" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B199" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C199" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D199" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E199" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F199" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G199" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A200" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B200" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C200" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D200" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="E200" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F200" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G200" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G146" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G194">
+    <sortState ref="A2:G200">
       <sortCondition ref="A1:A146"/>
     </sortState>
   </autoFilter>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgtedilizia-my.sharepoint.com/personal/emanuele_anzilotti_alayanrentals_it/Documents/Documenti/GitHub/pv_echarts/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="113_{A90B88B8-F94A-4EC7-B849-139E88F30812}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{2AE3201F-87CD-411B-9FFB-40C9BFC15788}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="529">
   <si>
     <t>Nome account</t>
   </si>
@@ -1604,6 +1604,12 @@
   </si>
   <si>
     <t>VIA CERESIO 7</t>
+  </si>
+  <si>
+    <t>OPR SUN 55 SRL</t>
+  </si>
+  <si>
+    <t>BLUSOLAR GROTTOLE 1 SRL</t>
   </si>
 </sst>
 </file>
@@ -2022,7 +2028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:G202"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -2819,7 +2825,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>254</v>
+        <v>528</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>117</v>
@@ -2833,8 +2839,8 @@
       <c r="E35" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F35" s="5" t="s">
-        <v>120</v>
+      <c r="F35" s="5">
+        <v>65125</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>77</v>
@@ -2842,145 +2848,145 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>62</v>
+        <v>254</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>522</v>
+        <v>145</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>523</v>
+        <v>147</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F38" s="5">
-        <v>20033</v>
+        <v>148</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>291</v>
+        <v>522</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>292</v>
+        <v>34</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>293</v>
+        <v>523</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>294</v>
+        <v>36</v>
       </c>
       <c r="F39" s="5">
-        <v>60035</v>
+        <v>20033</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>500</v>
+        <v>291</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>501</v>
+        <v>293</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="F40" s="5">
-        <v>10143</v>
+        <v>60035</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>390</v>
+        <v>500</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C41" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>270</v>
+        <v>501</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F41" s="5">
-        <v>20123</v>
+        <v>10143</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>438</v>
+        <v>390</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>34</v>
@@ -3003,7 +3009,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>398</v>
+        <v>438</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>34</v>
@@ -3026,7 +3032,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>269</v>
+        <v>398</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>34</v>
@@ -3040,8 +3046,8 @@
       <c r="E44" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>61</v>
+      <c r="F44" s="5">
+        <v>20123</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>38</v>
@@ -3049,7 +3055,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>34</v>
@@ -3058,13 +3064,13 @@
         <v>8</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>38</v>
@@ -3072,7 +3078,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>410</v>
+        <v>137</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>34</v>
@@ -3086,8 +3092,8 @@
       <c r="E46" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F46" s="5">
-        <v>20121</v>
+      <c r="F46" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>38</v>
@@ -3095,283 +3101,283 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>138</v>
+        <v>410</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>142</v>
+        <v>36</v>
+      </c>
+      <c r="F47" s="5">
+        <v>20121</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>445</v>
+        <v>125</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F49" s="5">
-        <v>20158</v>
+        <v>19</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>225</v>
+        <v>445</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F50" s="5">
+        <v>20158</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>488</v>
+        <v>84</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>489</v>
+        <v>85</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>490</v>
+        <v>86</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="F52" s="5">
-        <v>26015</v>
+        <v>87</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>334</v>
+        <v>488</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>9</v>
+        <v>489</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>335</v>
+        <v>490</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>218</v>
+        <v>491</v>
+      </c>
+      <c r="F53" s="5">
+        <v>26015</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="F54" s="5">
-        <v>56025</v>
+        <v>10</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>9</v>
+        <v>296</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>273</v>
+        <v>302</v>
+      </c>
+      <c r="F55" s="5">
+        <v>56025</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>376</v>
+        <v>271</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>377</v>
+        <v>272</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F56" s="5">
-        <v>20121</v>
+        <v>10</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>280</v>
+        <v>376</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>303</v>
+        <v>377</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>304</v>
+        <v>36</v>
       </c>
       <c r="F57" s="5">
-        <v>24060</v>
+        <v>20121</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>482</v>
+        <v>280</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="F58" s="5">
-        <v>20121</v>
+        <v>24060</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>175</v>
+        <v>482</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>34</v>
@@ -3380,21 +3386,21 @@
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F59" s="5" t="s">
-        <v>158</v>
+      <c r="F59" s="5">
+        <v>20121</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>34</v>
@@ -3417,7 +3423,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>253</v>
+        <v>156</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>34</v>
@@ -3426,21 +3432,21 @@
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>440</v>
+        <v>253</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>34</v>
@@ -3449,205 +3455,205 @@
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>441</v>
+        <v>230</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F62" s="5">
-        <v>20122</v>
+      <c r="F62" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>245</v>
+        <v>440</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>247</v>
+        <v>441</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>249</v>
+        <v>36</v>
+      </c>
+      <c r="F63" s="5">
+        <v>20122</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>83</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>363</v>
+        <v>251</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>364</v>
+        <v>79</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>365</v>
+        <v>252</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="F65" s="5">
-        <v>76123</v>
+        <v>81</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>426</v>
+        <v>363</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>28</v>
+        <v>364</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>132</v>
+        <v>365</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>30</v>
+        <v>366</v>
       </c>
       <c r="F66" s="5">
-        <v>39100</v>
+        <v>76123</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>393</v>
+        <v>132</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F67" s="5">
-        <v>70043</v>
+        <v>39100</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>219</v>
+        <v>392</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>220</v>
+        <v>393</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="F68" s="5">
+        <v>70043</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>34</v>
@@ -3656,13 +3662,13 @@
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>38</v>
@@ -3670,7 +3676,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>34</v>
@@ -3693,7 +3699,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>34</v>
@@ -3716,168 +3722,168 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>372</v>
+        <v>130</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>373</v>
+        <v>34</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>374</v>
+        <v>122</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="F74" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>201</v>
+        <v>372</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>34</v>
+        <v>373</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>190</v>
+        <v>375</v>
+      </c>
+      <c r="F75" s="5">
+        <v>61121</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>507</v>
+        <v>201</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="C76" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C76" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>509</v>
+        <v>189</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="F76" s="5">
-        <v>35010</v>
+        <v>36</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>506</v>
+        <v>159</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>281</v>
+        <v>507</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C77" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>305</v>
+        <v>509</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>36</v>
+        <v>508</v>
       </c>
       <c r="F77" s="5">
-        <v>20123</v>
+        <v>35010</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>38</v>
+        <v>506</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>352</v>
+        <v>281</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>353</v>
+        <v>34</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>355</v>
+        <v>36</v>
       </c>
       <c r="F78" s="5">
-        <v>15033</v>
+        <v>20123</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>59</v>
+        <v>352</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>34</v>
+        <v>353</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>60</v>
+        <v>354</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>61</v>
+        <v>355</v>
+      </c>
+      <c r="F79" s="5">
+        <v>15033</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F80" s="5">
-        <v>10153</v>
+        <v>36</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>431</v>
+        <v>336</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>79</v>
@@ -3900,53 +3906,53 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>282</v>
+        <v>431</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="F82" s="5">
-        <v>183</v>
+        <v>10153</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>211</v>
+        <v>306</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>58</v>
+        <v>10</v>
+      </c>
+      <c r="F83" s="5">
+        <v>183</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>275</v>
+        <v>210</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>34</v>
@@ -3955,44 +3961,44 @@
         <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>276</v>
+        <v>211</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>128</v>
+        <v>275</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>28</v>
@@ -4015,122 +4021,122 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>415</v>
+        <v>242</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>416</v>
+        <v>129</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>274</v>
+        <v>415</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>29</v>
+        <v>416</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>241</v>
+        <v>31</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>436</v>
+        <v>238</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>129</v>
+        <v>239</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F90" s="5">
-        <v>39100</v>
+        <v>240</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>206</v>
+        <v>436</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>61</v>
+        <v>30</v>
+      </c>
+      <c r="F91" s="5">
+        <v>39100</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>367</v>
+        <v>206</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>34</v>
@@ -4144,8 +4150,8 @@
       <c r="E92" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F92" s="5">
-        <v>20123</v>
+      <c r="F92" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>38</v>
@@ -4153,7 +4159,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>101</v>
+        <v>367</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>34</v>
@@ -4167,8 +4173,8 @@
       <c r="E93" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F93" s="5" t="s">
-        <v>61</v>
+      <c r="F93" s="5">
+        <v>20123</v>
       </c>
       <c r="G93" s="4" t="s">
         <v>38</v>
@@ -4176,237 +4182,237 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>494</v>
+        <v>101</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>495</v>
+        <v>60</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>521</v>
+        <v>495</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F95" s="5">
-        <v>80121</v>
+        <v>10</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>264</v>
+        <v>69</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>408</v>
+        <v>521</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>409</v>
+        <v>71</v>
       </c>
       <c r="F96" s="5">
-        <v>38121</v>
+        <v>80121</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>268</v>
+        <v>73</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>36</v>
+        <v>409</v>
       </c>
       <c r="F97" s="5">
-        <v>20123</v>
+        <v>38121</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F98" s="5">
-        <v>90139</v>
+        <v>20123</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>195</v>
+        <v>362</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F99" s="5">
-        <v>20123</v>
+        <v>90139</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>456</v>
+        <v>346</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>457</v>
+        <v>195</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F100" s="8" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F100" s="5">
+        <v>20123</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>283</v>
+        <v>456</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>309</v>
+        <v>457</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="F101" s="5">
-        <v>12037</v>
+        <v>10</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>13</v>
+        <v>283</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>14</v>
+        <v>309</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>15</v>
+        <v>310</v>
+      </c>
+      <c r="F102" s="5">
+        <v>12037</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>11</v>
+        <v>307</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>28</v>
@@ -4429,58 +4435,58 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>499</v>
+        <v>27</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C107" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
@@ -4489,8 +4495,8 @@
       <c r="E107" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F107" s="5">
-        <v>39100</v>
+      <c r="F107" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G107" s="4" t="s">
         <v>32</v>
@@ -4498,191 +4504,191 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>233</v>
+        <v>499</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C108" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>218</v>
+        <v>30</v>
+      </c>
+      <c r="F108" s="5">
+        <v>39100</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>188</v>
+        <v>233</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>484</v>
+        <v>188</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>485</v>
+        <v>34</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>486</v>
+        <v>189</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="F110" s="5">
-        <v>66020</v>
+        <v>36</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>412</v>
+        <v>484</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>341</v>
+        <v>485</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>413</v>
+        <v>486</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>414</v>
+        <v>487</v>
       </c>
       <c r="F111" s="5">
-        <v>37137</v>
+        <v>66020</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>344</v>
+        <v>77</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>461</v>
+        <v>412</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>9</v>
+        <v>341</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>462</v>
+        <v>413</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F112" s="8" t="s">
-        <v>218</v>
+        <v>414</v>
+      </c>
+      <c r="F112" s="5">
+        <v>37137</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>11</v>
+        <v>344</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>295</v>
+        <v>461</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>297</v>
+        <v>462</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="F113" s="5">
-        <v>56010</v>
+        <v>10</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="F114" s="5">
-        <v>40060</v>
+        <v>56010</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>26</v>
+        <v>299</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>385</v>
+        <v>311</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>386</v>
+        <v>312</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>36</v>
+        <v>313</v>
       </c>
       <c r="F115" s="5">
-        <v>20121</v>
+        <v>40060</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>34</v>
@@ -4696,8 +4702,8 @@
       <c r="E116" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F116" s="5" t="s">
-        <v>58</v>
+      <c r="F116" s="5">
+        <v>20121</v>
       </c>
       <c r="G116" s="4" t="s">
         <v>38</v>
@@ -4705,99 +4711,99 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>213</v>
+        <v>387</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>179</v>
+        <v>386</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>180</v>
+        <v>58</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>68</v>
+        <v>213</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>284</v>
+        <v>68</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>314</v>
+        <v>69</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>315</v>
+        <v>70</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="F119" s="5">
-        <v>57021</v>
+        <v>71</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>299</v>
+        <v>73</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>184</v>
+        <v>284</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F120" s="5" t="s">
-        <v>180</v>
+        <v>316</v>
+      </c>
+      <c r="F120" s="5">
+        <v>57021</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>463</v>
+        <v>184</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>9</v>
@@ -4811,7 +4817,7 @@
       <c r="E121" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F121" s="8" t="s">
+      <c r="F121" s="5" t="s">
         <v>180</v>
       </c>
       <c r="G121" s="4" t="s">
@@ -4820,122 +4826,122 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>89</v>
+        <v>463</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>93</v>
+        <v>10</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>347</v>
+        <v>89</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>348</v>
+        <v>91</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="F123" s="5">
-        <v>70124</v>
+        <v>92</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>189</v>
+        <v>348</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>36</v>
+        <v>349</v>
       </c>
       <c r="F124" s="5">
-        <v>20158</v>
+        <v>70124</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>359</v>
+        <v>189</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>360</v>
+        <v>36</v>
       </c>
       <c r="F125" s="5">
-        <v>12084</v>
+        <v>20158</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>307</v>
+        <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>194</v>
+        <v>358</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>195</v>
+        <v>359</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F126" s="5" t="s">
-        <v>61</v>
+        <v>360</v>
+      </c>
+      <c r="F126" s="5">
+        <v>12084</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>34</v>
@@ -4944,13 +4950,13 @@
         <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="G127" s="4" t="s">
         <v>38</v>
@@ -4958,122 +4964,122 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>458</v>
+        <v>227</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>459</v>
+        <v>228</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F128" s="8" t="s">
-        <v>460</v>
+        <v>36</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>108</v>
+        <v>458</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>110</v>
+        <v>459</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>112</v>
+        <v>10</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>460</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>432</v>
+        <v>108</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>308</v>
+        <v>109</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>433</v>
+        <v>110</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="F130" s="5">
-        <v>12100</v>
+        <v>111</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>307</v>
+        <v>113</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>22</v>
+        <v>308</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>23</v>
+        <v>433</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>24</v>
+        <v>434</v>
       </c>
       <c r="F131" s="5">
-        <v>40127</v>
+        <v>12100</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>26</v>
+        <v>307</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>356</v>
+        <v>396</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>357</v>
+        <v>23</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F132" s="5">
-        <v>20121</v>
+        <v>40127</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>525</v>
+        <v>356</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>34</v>
@@ -5082,113 +5088,113 @@
         <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>526</v>
+        <v>357</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F133" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>29</v>
+        <v>526</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F134" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>232</v>
+        <v>525</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>29</v>
+        <v>526</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F135" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F135" s="5">
+        <v>20154</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>143</v>
+        <v>516</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F136" s="5" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="F136" s="5">
+        <v>39100</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>442</v>
+        <v>143</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>34</v>
@@ -5197,136 +5203,136 @@
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>443</v>
+        <v>144</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="F138" s="5">
-        <v>20038</v>
+        <v>36</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>427</v>
+        <v>56</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F139" s="5">
-        <v>10121</v>
+        <v>36</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>95</v>
+        <v>442</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>97</v>
+        <v>443</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>99</v>
+        <v>444</v>
+      </c>
+      <c r="F140" s="5">
+        <v>20038</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>378</v>
+        <v>427</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>379</v>
+        <v>79</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>380</v>
+        <v>236</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>381</v>
+        <v>81</v>
       </c>
       <c r="F141" s="5">
-        <v>64020</v>
+        <v>10121</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>411</v>
+        <v>95</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>211</v>
+        <v>97</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F142" s="5">
-        <v>20121</v>
+        <v>98</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>133</v>
+        <v>378</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>34</v>
+        <v>379</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>134</v>
+        <v>380</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>135</v>
+        <v>381</v>
+      </c>
+      <c r="F143" s="5">
+        <v>64020</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>257</v>
+        <v>411</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>34</v>
@@ -5335,13 +5341,13 @@
         <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F144" s="5" t="s">
-        <v>58</v>
+      <c r="F144" s="5">
+        <v>20121</v>
       </c>
       <c r="G144" s="4" t="s">
         <v>38</v>
@@ -5349,30 +5355,30 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>340</v>
+        <v>133</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>342</v>
+        <v>134</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="F145" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>344</v>
+        <v>136</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>34</v>
@@ -5381,44 +5387,44 @@
         <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>167</v>
+        <v>258</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>472</v>
+        <v>340</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>260</v>
+        <v>342</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>36</v>
+        <v>343</v>
       </c>
       <c r="F147" s="5">
-        <v>20135</v>
+        <v>37045</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>262</v>
+        <v>344</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>406</v>
+        <v>166</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>34</v>
@@ -5427,44 +5433,44 @@
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F148" s="5">
-        <v>20135</v>
+      <c r="F148" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>204</v>
+        <v>472</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F149" s="5">
+        <v>20135</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>454</v>
+        <v>406</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>34</v>
@@ -5473,504 +5479,504 @@
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>455</v>
+        <v>260</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F150" s="5">
-        <v>20144</v>
+        <v>20135</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>36</v>
+        <v>186</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>136</v>
+        <v>319</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>285</v>
+        <v>454</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>317</v>
+        <v>455</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F152" s="5">
-        <v>40026</v>
+        <v>20144</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>286</v>
+        <v>223</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>320</v>
+        <v>224</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>323</v>
+        <v>135</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>368</v>
+        <v>285</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>369</v>
+        <v>317</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="F154" s="5">
-        <v>20123</v>
+        <v>40026</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F155" s="5">
-        <v>12020</v>
+        <v>10</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>307</v>
+        <v>11</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>39</v>
+        <v>368</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>41</v>
+        <v>369</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F156" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
+      </c>
+      <c r="F156" s="5">
+        <v>20123</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>422</v>
+        <v>287</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>423</v>
+        <v>308</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>424</v>
+        <v>321</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>425</v>
+        <v>322</v>
       </c>
       <c r="F157" s="5">
-        <v>28053</v>
+        <v>12020</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>136</v>
+        <v>307</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>172</v>
+        <v>39</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>198</v>
+        <v>422</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>22</v>
+        <v>423</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>199</v>
+        <v>424</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>200</v>
+        <v>425</v>
+      </c>
+      <c r="F159" s="5">
+        <v>28053</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>446</v>
+        <v>207</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>447</v>
+        <v>69</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>448</v>
+        <v>208</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="F162" s="5">
-        <v>53048</v>
+        <v>71</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>450</v>
+        <v>73</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>517</v>
+        <v>244</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>510</v>
+        <v>34</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>518</v>
+        <v>177</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="F163" s="5">
-        <v>35011</v>
+        <v>36</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>506</v>
+        <v>38</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>243</v>
+        <v>446</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>34</v>
+        <v>447</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>177</v>
+        <v>448</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>58</v>
+        <v>449</v>
+      </c>
+      <c r="F164" s="5">
+        <v>53048</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>38</v>
+        <v>450</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>131</v>
+        <v>517</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>28</v>
+        <v>510</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>132</v>
+        <v>518</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>31</v>
+        <v>519</v>
+      </c>
+      <c r="F165" s="5">
+        <v>35011</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>382</v>
+        <v>131</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>383</v>
+        <v>132</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="F167" s="5">
-        <v>20089</v>
+        <v>30</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>476</v>
+        <v>21</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>477</v>
+        <v>23</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F168" s="8" t="s">
-        <v>478</v>
+        <v>24</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>212</v>
+        <v>382</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>202</v>
+        <v>383</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>203</v>
+        <v>384</v>
+      </c>
+      <c r="F169" s="5">
+        <v>20089</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>214</v>
+        <v>476</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>215</v>
+        <v>477</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>478</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>439</v>
+        <v>212</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F171" s="5">
-        <v>20124</v>
+        <v>24</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>34</v>
@@ -5979,21 +5985,21 @@
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E172" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>256</v>
+        <v>439</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>34</v>
@@ -6002,21 +6008,21 @@
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E173" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F173" s="5" t="s">
-        <v>231</v>
+      <c r="F173" s="5">
+        <v>20124</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>473</v>
+        <v>229</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>34</v>
@@ -6025,21 +6031,21 @@
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>465</v>
+        <v>230</v>
       </c>
       <c r="E174" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F174" s="5">
-        <v>20129</v>
+      <c r="F174" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>464</v>
+        <v>256</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>34</v>
@@ -6048,21 +6054,21 @@
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>465</v>
+        <v>230</v>
       </c>
       <c r="E175" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F175" s="5">
-        <v>20129</v>
+      <c r="F175" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>34</v>
@@ -6085,7 +6091,7 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>34</v>
@@ -6108,7 +6114,7 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>176</v>
+        <v>474</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>34</v>
@@ -6117,59 +6123,59 @@
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>177</v>
+        <v>465</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F178" s="5" t="s">
-        <v>58</v>
+      <c r="F178" s="5">
+        <v>20129</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>331</v>
+        <v>475</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>332</v>
+        <v>465</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F179" s="5">
-        <v>40026</v>
+        <v>20129</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>288</v>
+        <v>176</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>324</v>
+        <v>177</v>
       </c>
       <c r="E180" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F180" s="5">
-        <v>20124</v>
+      <c r="F180" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G180" s="4" t="s">
         <v>38</v>
@@ -6177,398 +6183,398 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>451</v>
+        <v>331</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>452</v>
+        <v>332</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>453</v>
+        <v>318</v>
       </c>
       <c r="F181" s="5">
-        <v>12011</v>
+        <v>40026</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>307</v>
+        <v>26</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>151</v>
+        <v>288</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>153</v>
+        <v>324</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>155</v>
+        <v>36</v>
+      </c>
+      <c r="F182" s="5">
+        <v>20124</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>421</v>
+        <v>452</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>36</v>
+        <v>453</v>
       </c>
       <c r="F183" s="5">
-        <v>20123</v>
+        <v>12011</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>492</v>
+        <v>151</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>493</v>
+        <v>153</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F184" s="5">
-        <v>90141</v>
+        <v>154</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>481</v>
+        <v>420</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>389</v>
+        <v>421</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F185" s="8" t="s">
-        <v>391</v>
+        <v>36</v>
+      </c>
+      <c r="F185" s="5">
+        <v>20123</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>388</v>
+        <v>492</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>389</v>
+        <v>493</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>391</v>
+        <v>19</v>
+      </c>
+      <c r="F186" s="5">
+        <v>90141</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>467</v>
+        <v>389</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="F187" s="5">
-        <v>38055</v>
+        <v>10</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>391</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>429</v>
+        <v>389</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="F188" s="5">
-        <v>25010</v>
+        <v>10</v>
+      </c>
+      <c r="F188" s="5" t="s">
+        <v>391</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>394</v>
+        <v>466</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>395</v>
+        <v>467</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>36</v>
+        <v>468</v>
       </c>
       <c r="F189" s="10">
-        <v>20123</v>
+        <v>38055</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="F190" s="10">
-        <v>71016</v>
+        <v>25010</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>16</v>
+        <v>394</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>18</v>
+        <v>395</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F191" s="10" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F191" s="10">
+        <v>20123</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>325</v>
+        <v>417</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>327</v>
+        <v>418</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="F192" s="10" t="s">
-        <v>329</v>
+        <v>419</v>
+      </c>
+      <c r="F192" s="10">
+        <v>71016</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>330</v>
+        <v>44</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F193" s="10" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>479</v>
+        <v>325</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="C194" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>480</v>
+        <v>327</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F194" s="10">
-        <v>20123</v>
+        <v>328</v>
+      </c>
+      <c r="F194" s="10" t="s">
+        <v>329</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>38</v>
+        <v>330</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>397</v>
+        <v>277</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C195" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F195" s="10" t="s">
-        <v>218</v>
+        <v>37</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>216</v>
+        <v>479</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C196" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>217</v>
+        <v>480</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F196" s="10" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F196" s="10">
+        <v>20123</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>160</v>
+        <v>397</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="C197" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="F197" s="10" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>435</v>
+        <v>216</v>
       </c>
       <c r="B198" s="9" t="s">
         <v>9</v>
@@ -6591,53 +6597,99 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="C199" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="F199" s="10" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B200" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C200" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D200" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E200" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F200" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G200" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A201" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C201" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D201" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E201" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F201" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G201" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A202" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B200" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C200" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D200" s="9" t="s">
+      <c r="B202" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C202" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D202" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E200" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F200" s="10" t="s">
+      <c r="E202" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F202" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G200" s="9" t="s">
+      <c r="G202" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G146" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G200">
+    <sortState ref="A2:G202">
       <sortCondition ref="A1:A146"/>
     </sortState>
   </autoFilter>
@@ -6647,4 +6699,298 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F040406D9EE34E48977C379A242BB45D" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ab2d492e43f6bec9a26aa4599c840e9">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="877b7d34-4df7-40bf-9eb1-208952470e96" xmlns:ns4="05fc27dd-4454-4248-9c78-3d72b2b155c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc604e5d4aadf5a992ba83f8d4fb519" ns3:_="" ns4:_="">
+    <xsd:import namespace="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <xsd:import namespace="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns4:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns4:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns4:SharingHintHash" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="877b7d34-4df7-40bf-9eb1-208952470e96" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSystemTags" ma:index="15" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="16" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="21" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="22" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="05fc27dd-4454-4248-9c78-3d72b2b155c8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Condiviso con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Condiviso con dettagli" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="SharingHintHash" ma:index="20" nillable="true" ma:displayName="Hash suggerimento condivisione" ma:hidden="true" ma:internalName="SharingHintHash" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo di contenuto"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titolo"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC6436E-C4E7-4E8D-94E8-64DAEC05792B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgtedilizia-my.sharepoint.com/personal/emanuele_anzilotti_alayanrentals_it/Documents/Documenti/GitHub/pv_echarts/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{E924F1C0-78DE-42CC-AD31-ABD991370929}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="531">
   <si>
     <t>Nome account</t>
   </si>
@@ -1054,9 +1054,6 @@
     <t>VIA GOITO 4</t>
   </si>
   <si>
-    <t>LEGNANO</t>
-  </si>
-  <si>
     <t>Verona</t>
   </si>
   <si>
@@ -1610,6 +1607,15 @@
   </si>
   <si>
     <t>BLUSOLAR GROTTOLE 1 SRL</t>
+  </si>
+  <si>
+    <t>LEGNAGO</t>
+  </si>
+  <si>
+    <t>RENANTIS SICILIA SRL</t>
+  </si>
+  <si>
+    <t>TEP RENEWABLES (CARLENTINI PV) SRL</t>
   </si>
 </sst>
 </file>
@@ -1690,7 +1696,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1712,6 +1718,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2028,7 +2037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G202"/>
+  <dimension ref="A1:G204"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -2089,7 +2098,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>9</v>
@@ -2135,39 +2144,39 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>504</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>505</v>
       </c>
       <c r="F5" s="5">
         <v>45100</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>402</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>403</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>36</v>
@@ -2227,25 +2236,25 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>513</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>514</v>
       </c>
       <c r="F9" s="5">
         <v>33050</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -2296,7 +2305,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>79</v>
@@ -2305,10 +2314,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>497</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>498</v>
       </c>
       <c r="F12" s="5">
         <v>10098</v>
@@ -2434,7 +2443,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>9</v>
@@ -2503,7 +2512,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>28</v>
@@ -2512,7 +2521,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>30</v>
@@ -2526,16 +2535,16 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>401</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>36</v>
@@ -2549,7 +2558,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>9</v>
@@ -2558,13 +2567,13 @@
         <v>8</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>11</v>
@@ -2572,7 +2581,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>34</v>
@@ -2595,16 +2604,16 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>351</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>36</v>
@@ -2641,7 +2650,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>79</v>
@@ -2710,7 +2719,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>34</v>
@@ -2825,7 +2834,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>117</v>
@@ -2917,16 +2926,16 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>522</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>523</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>36</v>
@@ -2963,7 +2972,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>79</v>
@@ -2972,7 +2981,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>81</v>
@@ -2986,7 +2995,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>34</v>
@@ -3009,7 +3018,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>34</v>
@@ -3032,7 +3041,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>34</v>
@@ -3101,7 +3110,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>34</v>
@@ -3170,7 +3179,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>34</v>
@@ -3239,19 +3248,19 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="C53" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="C53" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="4" t="s">
+      <c r="E53" s="4" t="s">
         <v>490</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>491</v>
       </c>
       <c r="F53" s="5">
         <v>26015</v>
@@ -3331,16 +3340,16 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>376</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>377</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>36</v>
@@ -3377,7 +3386,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>34</v>
@@ -3469,16 +3478,16 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>440</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>441</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>36</v>
@@ -3538,19 +3547,19 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B66" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="C66" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="4" t="s">
+      <c r="E66" s="4" t="s">
         <v>365</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>366</v>
       </c>
       <c r="F66" s="5">
         <v>76123</v>
@@ -3561,7 +3570,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>28</v>
@@ -3584,7 +3593,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>40</v>
@@ -3593,7 +3602,7 @@
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>42</v>
@@ -3745,19 +3754,19 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="C75" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="C75" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="4" t="s">
+      <c r="E75" s="4" t="s">
         <v>374</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>375</v>
       </c>
       <c r="F75" s="5">
         <v>61121</v>
@@ -3791,25 +3800,25 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="E77" s="4" t="s">
         <v>507</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>508</v>
       </c>
       <c r="F77" s="5">
         <v>35010</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
@@ -3837,19 +3846,19 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B79" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="C79" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="C79" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="4" t="s">
+      <c r="E79" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>355</v>
       </c>
       <c r="F79" s="5">
         <v>15033</v>
@@ -3906,7 +3915,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>79</v>
@@ -4044,7 +4053,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>9</v>
@@ -4053,7 +4062,7 @@
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>10</v>
@@ -4113,7 +4122,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>28</v>
@@ -4159,7 +4168,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>34</v>
@@ -4205,7 +4214,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>9</v>
@@ -4214,7 +4223,7 @@
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>10</v>
@@ -4228,7 +4237,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>69</v>
@@ -4237,7 +4246,7 @@
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>71</v>
@@ -4251,7 +4260,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>264</v>
@@ -4260,10 +4269,10 @@
         <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="E97" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="E97" s="4" t="s">
-        <v>409</v>
       </c>
       <c r="F97" s="5">
         <v>38121</v>
@@ -4274,16 +4283,16 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>370</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>371</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>36</v>
@@ -4297,7 +4306,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>17</v>
@@ -4306,7 +4315,7 @@
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>19</v>
@@ -4320,7 +4329,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>34</v>
@@ -4343,7 +4352,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>9</v>
@@ -4352,7 +4361,7 @@
         <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>10</v>
@@ -4504,7 +4513,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>28</v>
@@ -4573,19 +4582,19 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B111" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="C111" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D111" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="C111" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D111" s="4" t="s">
+      <c r="E111" s="4" t="s">
         <v>486</v>
-      </c>
-      <c r="E111" s="4" t="s">
-        <v>487</v>
       </c>
       <c r="F111" s="5">
         <v>66020</v>
@@ -4596,7 +4605,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>341</v>
@@ -4605,21 +4614,21 @@
         <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="E112" s="4" t="s">
         <v>413</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>414</v>
       </c>
       <c r="F112" s="5">
         <v>37137</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>9</v>
@@ -4628,7 +4637,7 @@
         <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E113" s="4" t="s">
         <v>10</v>
@@ -4688,16 +4697,16 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D116" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>386</v>
       </c>
       <c r="E116" s="4" t="s">
         <v>36</v>
@@ -4711,7 +4720,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>34</v>
@@ -4720,7 +4729,7 @@
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E117" s="4" t="s">
         <v>36</v>
@@ -4826,7 +4835,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>9</v>
@@ -4872,7 +4881,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>40</v>
@@ -4881,10 +4890,10 @@
         <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="E124" s="4" t="s">
         <v>348</v>
-      </c>
-      <c r="E124" s="4" t="s">
-        <v>349</v>
       </c>
       <c r="F124" s="5">
         <v>70124</v>
@@ -4918,7 +4927,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>308</v>
@@ -4927,10 +4936,10 @@
         <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="E126" s="4" t="s">
         <v>359</v>
-      </c>
-      <c r="E126" s="4" t="s">
-        <v>360</v>
       </c>
       <c r="F126" s="5">
         <v>12084</v>
@@ -4987,7 +4996,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>9</v>
@@ -4996,13 +5005,13 @@
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G129" s="4" t="s">
         <v>77</v>
@@ -5033,7 +5042,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>308</v>
@@ -5042,10 +5051,10 @@
         <v>7</v>
       </c>
       <c r="D131" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="E131" s="4" t="s">
         <v>433</v>
-      </c>
-      <c r="E131" s="4" t="s">
-        <v>434</v>
       </c>
       <c r="F131" s="5">
         <v>12100</v>
@@ -5056,7 +5065,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>22</v>
@@ -5079,16 +5088,16 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D133" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>357</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>36</v>
@@ -5102,7 +5111,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>34</v>
@@ -5111,7 +5120,7 @@
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>36</v>
@@ -5125,16 +5134,16 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D135" s="4" t="s">
         <v>525</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>526</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>36</v>
@@ -5148,7 +5157,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>28</v>
@@ -5240,19 +5249,19 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D140" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="B140" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D140" s="4" t="s">
+      <c r="E140" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="E140" s="4" t="s">
-        <v>444</v>
       </c>
       <c r="F140" s="5">
         <v>20038</v>
@@ -5263,7 +5272,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>79</v>
@@ -5309,19 +5318,19 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B143" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="B143" s="4" t="s">
+      <c r="C143" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D143" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="C143" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D143" s="4" t="s">
+      <c r="E143" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="E143" s="4" t="s">
-        <v>381</v>
       </c>
       <c r="F143" s="5">
         <v>64020</v>
@@ -5332,7 +5341,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>34</v>
@@ -5413,13 +5422,13 @@
         <v>342</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>343</v>
+        <v>528</v>
       </c>
       <c r="F147" s="5">
         <v>37045</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
@@ -5447,7 +5456,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>472</v>
+        <v>529</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>34</v>
@@ -5456,21 +5465,21 @@
         <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F149" s="5">
-        <v>20135</v>
+        <v>20126</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>406</v>
+        <v>471</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>34</v>
@@ -5493,53 +5502,53 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>204</v>
+        <v>405</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F151" s="5">
+        <v>20135</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>454</v>
+        <v>204</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>455</v>
+        <v>205</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F152" s="5">
-        <v>20144</v>
+        <v>186</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>38</v>
+        <v>319</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>223</v>
+        <v>453</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>34</v>
@@ -5548,458 +5557,458 @@
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>224</v>
+        <v>454</v>
       </c>
       <c r="E153" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F153" s="5" t="s">
-        <v>135</v>
+      <c r="F153" s="5">
+        <v>20144</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>285</v>
+        <v>223</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>317</v>
+        <v>224</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F154" s="5">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F155" s="5" t="s">
-        <v>323</v>
+        <v>318</v>
+      </c>
+      <c r="F155" s="5">
+        <v>40026</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>368</v>
+        <v>286</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>369</v>
+        <v>320</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F156" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>321</v>
+        <v>368</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>322</v>
+        <v>36</v>
       </c>
       <c r="F157" s="5">
-        <v>12020</v>
+        <v>20123</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>39</v>
+        <v>287</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>41</v>
+        <v>321</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F158" s="5" t="s">
-        <v>43</v>
+        <v>322</v>
+      </c>
+      <c r="F158" s="5">
+        <v>12020</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>422</v>
+        <v>39</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>423</v>
+        <v>40</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>424</v>
+        <v>41</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="F159" s="5">
-        <v>28053</v>
+        <v>42</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>136</v>
+        <v>44</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>172</v>
+        <v>421</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>34</v>
+        <v>422</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>169</v>
+        <v>423</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F160" s="5" t="s">
-        <v>171</v>
+        <v>424</v>
+      </c>
+      <c r="F160" s="5">
+        <v>28053</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>24</v>
+        <v>170</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>446</v>
+        <v>244</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>447</v>
+        <v>34</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>448</v>
+        <v>177</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="F164" s="5">
-        <v>53048</v>
+        <v>36</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>450</v>
+        <v>38</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>517</v>
+        <v>445</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>510</v>
+        <v>446</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>518</v>
+        <v>447</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>519</v>
+        <v>448</v>
       </c>
       <c r="F165" s="5">
-        <v>35011</v>
+        <v>53048</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>506</v>
+        <v>449</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>243</v>
+        <v>516</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>34</v>
+        <v>509</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>177</v>
+        <v>517</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>58</v>
+        <v>518</v>
+      </c>
+      <c r="F166" s="5">
+        <v>35011</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>131</v>
+        <v>243</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>382</v>
+        <v>21</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>383</v>
+        <v>23</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="F169" s="5">
-        <v>20089</v>
+        <v>24</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>476</v>
+        <v>381</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>477</v>
+        <v>382</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F170" s="8" t="s">
-        <v>478</v>
+        <v>383</v>
+      </c>
+      <c r="F170" s="5">
+        <v>20089</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>212</v>
+        <v>475</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>202</v>
+        <v>476</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>203</v>
+        <v>10</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>439</v>
+        <v>214</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>34</v>
@@ -6013,8 +6022,8 @@
       <c r="E173" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F173" s="5">
-        <v>20124</v>
+      <c r="F173" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>159</v>
@@ -6022,7 +6031,7 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>229</v>
+        <v>438</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>34</v>
@@ -6031,21 +6040,21 @@
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E174" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F174" s="5" t="s">
-        <v>231</v>
+      <c r="F174" s="5">
+        <v>20124</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>34</v>
@@ -6068,7 +6077,7 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>473</v>
+        <v>256</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>34</v>
@@ -6077,30 +6086,30 @@
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>465</v>
+        <v>230</v>
       </c>
       <c r="E176" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F176" s="5">
-        <v>20129</v>
+      <c r="F176" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D177" s="4" t="s">
         <v>464</v>
-      </c>
-      <c r="B177" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C177" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D177" s="4" t="s">
-        <v>465</v>
       </c>
       <c r="E177" s="4" t="s">
         <v>36</v>
@@ -6114,7 +6123,7 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>34</v>
@@ -6123,7 +6132,7 @@
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>36</v>
@@ -6137,7 +6146,7 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>34</v>
@@ -6146,7 +6155,7 @@
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E179" s="4" t="s">
         <v>36</v>
@@ -6160,7 +6169,7 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>176</v>
+        <v>474</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>34</v>
@@ -6169,182 +6178,182 @@
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="E180" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F180" s="5" t="s">
-        <v>58</v>
+      <c r="F180" s="5">
+        <v>20129</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>331</v>
+        <v>176</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>332</v>
+        <v>177</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F181" s="5">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="F182" s="5">
-        <v>20124</v>
+        <v>40026</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>451</v>
+        <v>288</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>452</v>
+        <v>324</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>453</v>
+        <v>36</v>
       </c>
       <c r="F183" s="5">
-        <v>12011</v>
+        <v>20124</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>151</v>
+        <v>450</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>152</v>
+        <v>308</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>153</v>
+        <v>451</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>155</v>
+        <v>452</v>
+      </c>
+      <c r="F184" s="5">
+        <v>12011</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>420</v>
+        <v>151</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>421</v>
+        <v>153</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F185" s="5">
-        <v>20123</v>
+        <v>154</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>492</v>
+        <v>419</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>493</v>
+        <v>420</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F186" s="5">
-        <v>90141</v>
+        <v>20123</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>389</v>
+        <v>492</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F187" s="8" t="s">
-        <v>391</v>
+        <v>19</v>
+      </c>
+      <c r="F187" s="5">
+        <v>90141</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>388</v>
+        <v>480</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>9</v>
@@ -6353,274 +6362,274 @@
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F188" s="5" t="s">
-        <v>391</v>
+      <c r="F188" s="8" t="s">
+        <v>390</v>
       </c>
       <c r="G188" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A189" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="B189" s="9" t="s">
-        <v>264</v>
+      <c r="A189" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D189" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="E189" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="F189" s="10">
-        <v>38055</v>
-      </c>
-      <c r="G189" s="9" t="s">
-        <v>268</v>
+      <c r="D189" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F189" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>428</v>
+        <v>387</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>429</v>
+        <v>388</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="F190" s="10">
-        <v>25010</v>
+        <v>10</v>
+      </c>
+      <c r="F190" s="10" t="s">
+        <v>390</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>394</v>
+        <v>465</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>395</v>
+        <v>466</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>36</v>
+        <v>467</v>
       </c>
       <c r="F191" s="10">
-        <v>20123</v>
+        <v>38055</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="F192" s="10">
-        <v>71016</v>
+        <v>25010</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>16</v>
+        <v>393</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>18</v>
+        <v>394</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F193" s="10" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F193" s="10">
+        <v>20123</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>325</v>
+        <v>416</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="C194" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>327</v>
+        <v>417</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="F194" s="10" t="s">
-        <v>329</v>
+        <v>418</v>
+      </c>
+      <c r="F194" s="10">
+        <v>71016</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>330</v>
+        <v>44</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C195" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F195" s="10" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>479</v>
+        <v>325</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="C196" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>480</v>
+        <v>327</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F196" s="10">
-        <v>20123</v>
+        <v>328</v>
+      </c>
+      <c r="F196" s="10" t="s">
+        <v>329</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>38</v>
+        <v>330</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>397</v>
+        <v>277</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C197" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F197" s="10" t="s">
-        <v>218</v>
+        <v>37</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>216</v>
+        <v>478</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C198" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>217</v>
+        <v>479</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F198" s="10" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F198" s="10">
+        <v>20123</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>160</v>
+        <v>396</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="C199" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="F199" s="10" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>435</v>
+        <v>216</v>
       </c>
       <c r="B200" s="9" t="s">
         <v>9</v>
@@ -6643,53 +6652,99 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="C201" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="F201" s="10" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B202" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C202" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D202" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E202" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F202" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G202" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A203" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B203" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C203" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D203" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E203" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F203" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G203" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A204" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B202" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C202" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D202" s="9" t="s">
+      <c r="B204" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C204" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D204" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E202" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F202" s="10" t="s">
+      <c r="E204" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F204" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G202" s="9" t="s">
+      <c r="G204" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G146" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G202">
+    <sortState ref="A2:G204">
       <sortCondition ref="A1:A146"/>
     </sortState>
   </autoFilter>
@@ -6981,16 +7036,16 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{E924F1C0-78DE-42CC-AD31-ABD991370929}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{40EB34CA-AD85-40AA-B01C-F93882E3CCF5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="535">
   <si>
     <t>Nome account</t>
   </si>
@@ -1616,6 +1616,18 @@
   </si>
   <si>
     <t>TEP RENEWABLES (CARLENTINI PV) SRL</t>
+  </si>
+  <si>
+    <t>SOLAR PV 39 SRL</t>
+  </si>
+  <si>
+    <t>PIAZZA CASTELLO 19</t>
+  </si>
+  <si>
+    <t>SAN GIORGIO JONICO SRL</t>
+  </si>
+  <si>
+    <t>SKI 09 SRL</t>
   </si>
 </sst>
 </file>
@@ -1696,7 +1708,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1721,6 +1733,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2037,7 +2052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G204"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -5640,352 +5655,352 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>367</v>
+        <v>533</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>368</v>
+        <v>29</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F157" s="5">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>321</v>
+        <v>368</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>322</v>
+        <v>36</v>
       </c>
       <c r="F158" s="5">
-        <v>12020</v>
+        <v>20123</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>39</v>
+        <v>287</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>41</v>
+        <v>321</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>43</v>
+        <v>322</v>
+      </c>
+      <c r="F159" s="5">
+        <v>12020</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>421</v>
+        <v>39</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>422</v>
+        <v>40</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>423</v>
+        <v>41</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="F160" s="5">
-        <v>28053</v>
+        <v>42</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>136</v>
+        <v>44</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>172</v>
+        <v>421</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>34</v>
+        <v>422</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>169</v>
+        <v>423</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F161" s="5" t="s">
-        <v>171</v>
+        <v>424</v>
+      </c>
+      <c r="F161" s="5">
+        <v>28053</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>24</v>
+        <v>170</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>445</v>
+        <v>244</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>447</v>
+        <v>177</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="F165" s="5">
-        <v>53048</v>
+        <v>36</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>449</v>
+        <v>38</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>509</v>
+        <v>34</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>517</v>
+        <v>177</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>518</v>
+        <v>36</v>
       </c>
       <c r="F166" s="5">
-        <v>35011</v>
+        <v>20121</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>505</v>
+        <v>38</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>243</v>
+        <v>445</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>34</v>
+        <v>446</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>177</v>
+        <v>447</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>58</v>
+        <v>448</v>
+      </c>
+      <c r="F167" s="5">
+        <v>53048</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>38</v>
+        <v>449</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>131</v>
+        <v>516</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>28</v>
+        <v>509</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>132</v>
+        <v>517</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>31</v>
+        <v>518</v>
+      </c>
+      <c r="F168" s="5">
+        <v>35011</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>32</v>
+        <v>505</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>381</v>
+        <v>131</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>382</v>
+        <v>132</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="F170" s="5">
-        <v>20089</v>
+        <v>30</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>475</v>
+        <v>531</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>476</v>
+        <v>532</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F171" s="8" t="s">
-        <v>477</v>
+        <v>36</v>
+      </c>
+      <c r="F171" s="5">
+        <v>20121</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>22</v>
@@ -5994,13 +6009,13 @@
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>202</v>
+        <v>23</v>
       </c>
       <c r="E172" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>203</v>
+        <v>25</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>26</v>
@@ -6008,7 +6023,7 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>214</v>
+        <v>381</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>34</v>
@@ -6017,67 +6032,67 @@
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>215</v>
+        <v>382</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>158</v>
+        <v>383</v>
+      </c>
+      <c r="F173" s="5">
+        <v>20089</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>215</v>
+        <v>476</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F174" s="5">
-        <v>20124</v>
+        <v>10</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>136</v>
+        <v>26</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>34</v>
@@ -6086,21 +6101,21 @@
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E176" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>472</v>
+        <v>438</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>34</v>
@@ -6109,21 +6124,21 @@
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>464</v>
+        <v>215</v>
       </c>
       <c r="E177" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F177" s="5">
-        <v>20129</v>
+        <v>20124</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>463</v>
+        <v>229</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>34</v>
@@ -6132,21 +6147,21 @@
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F178" s="5">
-        <v>20129</v>
+      <c r="F178" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>473</v>
+        <v>256</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>34</v>
@@ -6155,21 +6170,21 @@
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E179" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F179" s="5">
-        <v>20129</v>
+      <c r="F179" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>34</v>
@@ -6192,7 +6207,7 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>176</v>
+        <v>463</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>34</v>
@@ -6201,128 +6216,128 @@
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="E181" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F181" s="5" t="s">
-        <v>58</v>
+      <c r="F181" s="5">
+        <v>20129</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>331</v>
+        <v>473</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>332</v>
+        <v>464</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F182" s="5">
-        <v>40026</v>
+        <v>20129</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>288</v>
+        <v>474</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>324</v>
+        <v>464</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F183" s="5">
-        <v>20124</v>
+        <v>20129</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>450</v>
+        <v>176</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>451</v>
+        <v>177</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="F184" s="5">
-        <v>12011</v>
+        <v>36</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>151</v>
+        <v>331</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>152</v>
+        <v>22</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>153</v>
+        <v>332</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F185" s="5" t="s">
-        <v>155</v>
+        <v>318</v>
+      </c>
+      <c r="F185" s="5">
+        <v>40026</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>419</v>
+        <v>288</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>420</v>
+        <v>324</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F186" s="5">
-        <v>20123</v>
+        <v>20124</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>38</v>
@@ -6330,352 +6345,352 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>491</v>
+        <v>450</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>492</v>
+        <v>451</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>19</v>
+        <v>452</v>
       </c>
       <c r="F187" s="5">
-        <v>90141</v>
+        <v>12011</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>12</v>
+        <v>307</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>480</v>
+        <v>151</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>9</v>
+        <v>152</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>388</v>
+        <v>153</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F188" s="8" t="s">
-        <v>390</v>
+        <v>154</v>
+      </c>
+      <c r="F188" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A189" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>9</v>
+      <c r="A189" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="B189" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D189" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E189" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F189" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="G189" s="3" t="s">
-        <v>11</v>
+      <c r="D189" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E189" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F189" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G189" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>387</v>
+        <v>491</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>388</v>
+        <v>492</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F190" s="10" t="s">
-        <v>390</v>
+        <v>19</v>
+      </c>
+      <c r="F190" s="10">
+        <v>90141</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>466</v>
+        <v>388</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="F191" s="10">
-        <v>38055</v>
+        <v>10</v>
+      </c>
+      <c r="F191" s="12" t="s">
+        <v>390</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A192" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="B192" s="9" t="s">
-        <v>103</v>
+      <c r="A192" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D192" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="E192" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="F192" s="10">
-        <v>25010</v>
-      </c>
-      <c r="G192" s="9" t="s">
-        <v>107</v>
+      <c r="D192" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F192" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F193" s="10">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F193" s="10" t="s">
+        <v>390</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>416</v>
+        <v>465</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>85</v>
+        <v>264</v>
       </c>
       <c r="C194" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>417</v>
+        <v>466</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>418</v>
+        <v>467</v>
       </c>
       <c r="F194" s="10">
-        <v>71016</v>
+        <v>38055</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>44</v>
+        <v>268</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>16</v>
+        <v>427</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="C195" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>18</v>
+        <v>428</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F195" s="10" t="s">
-        <v>20</v>
+        <v>429</v>
+      </c>
+      <c r="F195" s="10">
+        <v>25010</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>326</v>
+        <v>34</v>
       </c>
       <c r="C196" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>327</v>
+        <v>394</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="F196" s="10" t="s">
-        <v>329</v>
+        <v>36</v>
+      </c>
+      <c r="F196" s="10">
+        <v>20123</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>330</v>
+        <v>38</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>277</v>
+        <v>416</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="C197" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>278</v>
+        <v>417</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F197" s="10" t="s">
-        <v>37</v>
+        <v>418</v>
+      </c>
+      <c r="F197" s="10">
+        <v>71016</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>478</v>
+        <v>16</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C198" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>479</v>
+        <v>18</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F198" s="10">
-        <v>20123</v>
+        <v>19</v>
+      </c>
+      <c r="F198" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>396</v>
+        <v>325</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>9</v>
+        <v>326</v>
       </c>
       <c r="C199" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>217</v>
+        <v>327</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>10</v>
+        <v>328</v>
       </c>
       <c r="F199" s="10" t="s">
-        <v>218</v>
+        <v>329</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>11</v>
+        <v>330</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>216</v>
+        <v>277</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C200" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F200" s="10" t="s">
-        <v>218</v>
+        <v>37</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>160</v>
+        <v>478</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>161</v>
+        <v>34</v>
       </c>
       <c r="C201" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>162</v>
+        <v>479</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F201" s="10" t="s">
-        <v>164</v>
+        <v>36</v>
+      </c>
+      <c r="F201" s="10">
+        <v>20123</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>434</v>
+        <v>396</v>
       </c>
       <c r="B202" s="9" t="s">
         <v>9</v>
@@ -6698,7 +6713,7 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>255</v>
+        <v>216</v>
       </c>
       <c r="B203" s="9" t="s">
         <v>9</v>
@@ -6721,30 +6736,99 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B204" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C204" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D204" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E204" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F204" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G204" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A205" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B205" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C205" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D205" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E205" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F205" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G205" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A206" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B206" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C206" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D206" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E206" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F206" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G206" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A207" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B204" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C204" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D204" s="9" t="s">
+      <c r="B207" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C207" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D207" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E204" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F204" s="10" t="s">
+      <c r="E207" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F207" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G204" s="9" t="s">
+      <c r="G207" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G146" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G204">
+    <sortState ref="A2:G207">
       <sortCondition ref="A1:A146"/>
     </sortState>
   </autoFilter>
@@ -6757,6 +6841,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F040406D9EE34E48977C379A242BB45D" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ab2d492e43f6bec9a26aa4599c840e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="877b7d34-4df7-40bf-9eb1-208952470e96" xmlns:ns4="05fc27dd-4454-4248-9c78-3d72b2b155c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc604e5d4aadf5a992ba83f8d4fb519" ns3:_="" ns4:_="">
     <xsd:import namespace="877b7d34-4df7-40bf-9eb1-208952470e96"/>
@@ -6989,24 +7090,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC6436E-C4E7-4E8D-94E8-64DAEC05792B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7023,29 +7132,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{40EB34CA-AD85-40AA-B01C-F93882E3CCF5}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{2C790D21-B0A2-4EAB-A64E-C79CA24C7465}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="541">
   <si>
     <t>Nome account</t>
   </si>
@@ -1628,6 +1628,24 @@
   </si>
   <si>
     <t>SKI 09 SRL</t>
+  </si>
+  <si>
+    <t>FISCAGLIA AGRI-SOLARE SRL</t>
+  </si>
+  <si>
+    <t>PIAZZA ETTORE TROILO 27</t>
+  </si>
+  <si>
+    <t>GRANDE RINNOVABILI SRL</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>VIA GIOSUE' CARDUCCI 8</t>
+  </si>
+  <si>
+    <t>TRIESTE</t>
   </si>
 </sst>
 </file>
@@ -2052,7 +2070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G207"/>
+  <dimension ref="A1:G209"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -3884,53 +3902,53 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>59</v>
+        <v>535</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>60</v>
+        <v>536</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>61</v>
+        <v>119</v>
+      </c>
+      <c r="F80" s="5">
+        <v>65127</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F81" s="5">
-        <v>10153</v>
+        <v>36</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>430</v>
+        <v>336</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>79</v>
@@ -3953,53 +3971,53 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>282</v>
+        <v>430</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="F83" s="5">
-        <v>183</v>
+        <v>10153</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>211</v>
+        <v>306</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>58</v>
+        <v>10</v>
+      </c>
+      <c r="F84" s="5">
+        <v>183</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>275</v>
+        <v>210</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>34</v>
@@ -4008,44 +4026,44 @@
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>276</v>
+        <v>211</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>128</v>
+        <v>275</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>28</v>
@@ -4068,145 +4086,145 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>414</v>
+        <v>242</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>415</v>
+        <v>129</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>274</v>
+        <v>414</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>29</v>
+        <v>415</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>241</v>
+        <v>31</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>435</v>
+        <v>238</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>129</v>
+        <v>239</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F91" s="5">
-        <v>39100</v>
+        <v>240</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>206</v>
+        <v>537</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>34</v>
+        <v>538</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>60</v>
+        <v>539</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>61</v>
+        <v>540</v>
+      </c>
+      <c r="F92" s="5">
+        <v>34133</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>38</v>
+        <v>514</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>366</v>
+        <v>435</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F93" s="5">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>34</v>
@@ -4229,122 +4247,122 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>493</v>
+        <v>366</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>494</v>
+        <v>60</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" s="8" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F95" s="5">
+        <v>20123</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>519</v>
+        <v>101</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>520</v>
+        <v>60</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F96" s="5">
-        <v>80121</v>
+        <v>36</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>406</v>
+        <v>493</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>407</v>
+        <v>494</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="F97" s="5">
-        <v>38121</v>
+        <v>10</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>369</v>
+        <v>519</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>370</v>
+        <v>520</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F98" s="5">
-        <v>20123</v>
+        <v>80121</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>360</v>
+        <v>406</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>361</v>
+        <v>407</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>19</v>
+        <v>408</v>
       </c>
       <c r="F99" s="5">
-        <v>90139</v>
+        <v>38121</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>12</v>
+        <v>268</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>34</v>
@@ -4353,7 +4371,7 @@
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>195</v>
+        <v>370</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>36</v>
@@ -4367,53 +4385,53 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>455</v>
+        <v>360</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>456</v>
+        <v>361</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>180</v>
+        <v>19</v>
+      </c>
+      <c r="F101" s="5">
+        <v>90139</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>283</v>
+        <v>345</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>309</v>
+        <v>195</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>310</v>
+        <v>36</v>
       </c>
       <c r="F102" s="5">
-        <v>12037</v>
+        <v>20123</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>13</v>
+        <v>455</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>9</v>
@@ -4422,90 +4440,90 @@
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>14</v>
+        <v>456</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F103" s="5" t="s">
-        <v>15</v>
+      <c r="F103" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>123</v>
+        <v>283</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>28</v>
+        <v>308</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>55</v>
+        <v>309</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>31</v>
+        <v>310</v>
+      </c>
+      <c r="F104" s="5">
+        <v>12037</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>32</v>
+        <v>307</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>28</v>
@@ -4514,7 +4532,7 @@
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>30</v>
@@ -4528,444 +4546,444 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>498</v>
+        <v>74</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C108" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F108" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>233</v>
+        <v>27</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>218</v>
+        <v>31</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>188</v>
+        <v>498</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C110" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>189</v>
+        <v>29</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>190</v>
+        <v>30</v>
+      </c>
+      <c r="F110" s="5">
+        <v>39100</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>483</v>
+        <v>233</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>484</v>
+        <v>9</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>485</v>
+        <v>234</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="F111" s="5">
-        <v>66020</v>
+        <v>10</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>411</v>
+        <v>188</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>412</v>
+        <v>189</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="F112" s="5">
-        <v>37137</v>
+        <v>36</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>343</v>
+        <v>159</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>9</v>
+        <v>484</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113" s="8" t="s">
-        <v>218</v>
+        <v>486</v>
+      </c>
+      <c r="F113" s="5">
+        <v>66020</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>295</v>
+        <v>411</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>296</v>
+        <v>341</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>297</v>
+        <v>412</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>298</v>
+        <v>413</v>
       </c>
       <c r="F114" s="5">
-        <v>56010</v>
+        <v>37137</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>299</v>
+        <v>343</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>311</v>
+        <v>460</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>312</v>
+        <v>461</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="F115" s="5">
-        <v>40060</v>
+        <v>10</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>384</v>
+        <v>295</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>36</v>
+        <v>298</v>
       </c>
       <c r="F116" s="5">
-        <v>20121</v>
+        <v>56010</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>386</v>
+        <v>311</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>385</v>
+        <v>312</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F117" s="5" t="s">
-        <v>58</v>
+        <v>313</v>
+      </c>
+      <c r="F117" s="5">
+        <v>40060</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>213</v>
+        <v>384</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>179</v>
+        <v>385</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F118" s="5">
+        <v>20121</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>68</v>
+        <v>386</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>70</v>
+        <v>385</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>284</v>
+        <v>213</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>314</v>
+        <v>9</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>315</v>
+        <v>179</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="F120" s="5">
-        <v>57021</v>
+        <v>10</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>299</v>
+        <v>77</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>179</v>
+        <v>70</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>462</v>
+        <v>284</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" s="8" t="s">
-        <v>180</v>
+        <v>316</v>
+      </c>
+      <c r="F122" s="5">
+        <v>57021</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>346</v>
+        <v>462</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>347</v>
+        <v>179</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F124" s="5">
-        <v>70124</v>
+        <v>10</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>333</v>
+        <v>89</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F125" s="5">
-        <v>20158</v>
+        <v>92</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>308</v>
+        <v>40</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="F126" s="5">
-        <v>12084</v>
+        <v>70124</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>307</v>
+        <v>44</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>34</v>
@@ -4974,182 +4992,182 @@
         <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F127" s="5" t="s">
-        <v>61</v>
+      <c r="F127" s="5">
+        <v>20158</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>227</v>
+        <v>357</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>228</v>
+        <v>358</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F128" s="5" t="s">
-        <v>37</v>
+        <v>359</v>
+      </c>
+      <c r="F128" s="5">
+        <v>12084</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>457</v>
+        <v>194</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>458</v>
+        <v>195</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F129" s="8" t="s">
-        <v>459</v>
+        <v>36</v>
+      </c>
+      <c r="F129" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>108</v>
+        <v>227</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F131" s="5">
-        <v>12100</v>
+        <v>10</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>459</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>395</v>
+        <v>108</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F132" s="5">
-        <v>40127</v>
+        <v>111</v>
+      </c>
+      <c r="F132" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>355</v>
+        <v>431</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>356</v>
+        <v>432</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>36</v>
+        <v>433</v>
       </c>
       <c r="F133" s="5">
-        <v>20121</v>
+        <v>12100</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>526</v>
+        <v>395</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>525</v>
+        <v>23</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F134" s="5">
-        <v>20154</v>
+        <v>40127</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>524</v>
+        <v>355</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>34</v>
@@ -5158,113 +5176,113 @@
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>525</v>
+        <v>356</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F135" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F136" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>232</v>
+        <v>524</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F137" s="5">
+        <v>20154</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>143</v>
+        <v>515</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="F138" s="5">
+        <v>39100</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>441</v>
+        <v>143</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>34</v>
@@ -5273,136 +5291,136 @@
         <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>442</v>
+        <v>144</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="F140" s="5">
-        <v>20038</v>
+        <v>36</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>426</v>
+        <v>56</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F141" s="5">
-        <v>10121</v>
+        <v>36</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>95</v>
+        <v>441</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>97</v>
+        <v>442</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>99</v>
+        <v>443</v>
+      </c>
+      <c r="F142" s="5">
+        <v>20038</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>377</v>
+        <v>426</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>379</v>
+        <v>236</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>380</v>
+        <v>81</v>
       </c>
       <c r="F143" s="5">
-        <v>64020</v>
+        <v>10121</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>410</v>
+        <v>95</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>211</v>
+        <v>97</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F144" s="5">
-        <v>20121</v>
+        <v>98</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>133</v>
+        <v>377</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>34</v>
+        <v>378</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>134</v>
+        <v>379</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>135</v>
+        <v>380</v>
+      </c>
+      <c r="F145" s="5">
+        <v>64020</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>257</v>
+        <v>410</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>34</v>
@@ -5411,13 +5429,13 @@
         <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F146" s="5" t="s">
-        <v>58</v>
+      <c r="F146" s="5">
+        <v>20121</v>
       </c>
       <c r="G146" s="4" t="s">
         <v>38</v>
@@ -5425,30 +5443,30 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>340</v>
+        <v>133</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>342</v>
+        <v>134</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="F147" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>343</v>
+        <v>136</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>34</v>
@@ -5457,44 +5475,44 @@
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>167</v>
+        <v>258</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>529</v>
+        <v>340</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>167</v>
+        <v>342</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>36</v>
+        <v>528</v>
       </c>
       <c r="F149" s="5">
-        <v>20126</v>
+        <v>37045</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>159</v>
+        <v>343</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>471</v>
+        <v>166</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>34</v>
@@ -5503,21 +5521,21 @@
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F150" s="5">
-        <v>20135</v>
+      <c r="F150" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>405</v>
+        <v>529</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>34</v>
@@ -5526,44 +5544,44 @@
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F151" s="5">
-        <v>20135</v>
+        <v>20126</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>204</v>
+        <v>471</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F152" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F152" s="5">
+        <v>20135</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>453</v>
+        <v>405</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>34</v>
@@ -5572,412 +5590,412 @@
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>454</v>
+        <v>260</v>
       </c>
       <c r="E153" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F153" s="5">
-        <v>20144</v>
+        <v>20135</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>36</v>
+        <v>186</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>136</v>
+        <v>319</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>285</v>
+        <v>453</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>317</v>
+        <v>454</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F155" s="5">
-        <v>40026</v>
+        <v>20144</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>286</v>
+        <v>223</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>320</v>
+        <v>224</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>323</v>
+        <v>135</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>533</v>
+        <v>285</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>29</v>
+        <v>317</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>30</v>
+        <v>318</v>
       </c>
       <c r="F157" s="5">
-        <v>39100</v>
+        <v>40026</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>367</v>
+        <v>286</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>368</v>
+        <v>320</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F158" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>287</v>
+        <v>533</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>321</v>
+        <v>29</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>322</v>
+        <v>30</v>
       </c>
       <c r="F159" s="5">
-        <v>12020</v>
+        <v>39100</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>307</v>
+        <v>32</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>39</v>
+        <v>367</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>41</v>
+        <v>368</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F160" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
+      </c>
+      <c r="F160" s="5">
+        <v>20123</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>421</v>
+        <v>287</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>422</v>
+        <v>308</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>423</v>
+        <v>321</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>424</v>
+        <v>322</v>
       </c>
       <c r="F161" s="5">
-        <v>28053</v>
+        <v>12020</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>136</v>
+        <v>307</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>172</v>
+        <v>39</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>198</v>
+        <v>421</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>22</v>
+        <v>422</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>199</v>
+        <v>423</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>200</v>
+        <v>424</v>
+      </c>
+      <c r="F163" s="5">
+        <v>28053</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>534</v>
+        <v>207</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F166" s="5">
-        <v>20121</v>
+        <v>71</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>445</v>
+        <v>244</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>447</v>
+        <v>177</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="F167" s="5">
-        <v>53048</v>
+        <v>36</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>449</v>
+        <v>38</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>509</v>
+        <v>34</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>517</v>
+        <v>177</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>518</v>
+        <v>36</v>
       </c>
       <c r="F168" s="5">
-        <v>35011</v>
+        <v>20121</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>505</v>
+        <v>38</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>243</v>
+        <v>445</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>34</v>
+        <v>446</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>177</v>
+        <v>447</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>58</v>
+        <v>448</v>
+      </c>
+      <c r="F169" s="5">
+        <v>53048</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>38</v>
+        <v>449</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>131</v>
+        <v>516</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>28</v>
+        <v>509</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>132</v>
+        <v>517</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>31</v>
+        <v>518</v>
+      </c>
+      <c r="F170" s="5">
+        <v>35011</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>32</v>
+        <v>505</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>531</v>
+        <v>243</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>34</v>
@@ -5986,13 +6004,13 @@
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>532</v>
+        <v>177</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F171" s="5">
-        <v>20121</v>
+      <c r="F171" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>38</v>
@@ -6000,30 +6018,30 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>381</v>
+        <v>531</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>34</v>
@@ -6032,13 +6050,13 @@
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>382</v>
+        <v>532</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>383</v>
+        <v>36</v>
       </c>
       <c r="F173" s="5">
-        <v>20089</v>
+        <v>20121</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>38</v>
@@ -6046,99 +6064,99 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>476</v>
+        <v>23</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F174" s="8" t="s">
-        <v>477</v>
+        <v>24</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>212</v>
+        <v>381</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>202</v>
+        <v>382</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>203</v>
+        <v>383</v>
+      </c>
+      <c r="F175" s="5">
+        <v>20089</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>214</v>
+        <v>475</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>215</v>
+        <v>476</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>438</v>
+        <v>212</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F177" s="5">
-        <v>20124</v>
+        <v>24</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>34</v>
@@ -6147,21 +6165,21 @@
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>256</v>
+        <v>438</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>34</v>
@@ -6170,21 +6188,21 @@
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E179" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F179" s="5" t="s">
-        <v>231</v>
+      <c r="F179" s="5">
+        <v>20124</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>472</v>
+        <v>229</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>34</v>
@@ -6193,21 +6211,21 @@
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E180" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F180" s="5">
-        <v>20129</v>
+      <c r="F180" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>463</v>
+        <v>256</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>34</v>
@@ -6216,21 +6234,21 @@
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E181" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F181" s="5">
-        <v>20129</v>
+      <c r="F181" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>34</v>
@@ -6253,7 +6271,7 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>34</v>
@@ -6276,7 +6294,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>176</v>
+        <v>473</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>34</v>
@@ -6285,59 +6303,59 @@
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="E184" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F184" s="5" t="s">
-        <v>58</v>
+      <c r="F184" s="5">
+        <v>20129</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>331</v>
+        <v>474</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>332</v>
+        <v>464</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F185" s="5">
-        <v>40026</v>
+        <v>20129</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>288</v>
+        <v>176</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>324</v>
+        <v>177</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F186" s="5">
-        <v>20124</v>
+      <c r="F186" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>38</v>
@@ -6345,145 +6363,145 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>450</v>
+        <v>331</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>451</v>
+        <v>332</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>452</v>
+        <v>318</v>
       </c>
       <c r="F187" s="5">
-        <v>12011</v>
+        <v>40026</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>307</v>
+        <v>26</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>151</v>
+        <v>288</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>153</v>
+        <v>324</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F188" s="5" t="s">
-        <v>155</v>
+        <v>36</v>
+      </c>
+      <c r="F188" s="5">
+        <v>20124</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>419</v>
+        <v>450</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>36</v>
+        <v>452</v>
       </c>
       <c r="F189" s="10">
-        <v>20123</v>
+        <v>12011</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>491</v>
+        <v>151</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>492</v>
+        <v>153</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F190" s="10">
-        <v>90141</v>
+        <v>154</v>
+      </c>
+      <c r="F190" s="10" t="s">
+        <v>155</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>480</v>
+        <v>419</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F191" s="12" t="s">
-        <v>390</v>
+        <v>36</v>
+      </c>
+      <c r="F191" s="10">
+        <v>20123</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A192" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="B192" s="3" t="s">
-        <v>9</v>
+      <c r="A192" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="B192" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D192" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E192" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F192" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="G192" s="3" t="s">
-        <v>11</v>
+      <c r="D192" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="E192" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F192" s="10">
+        <v>90141</v>
+      </c>
+      <c r="G192" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>387</v>
+        <v>480</v>
       </c>
       <c r="B193" s="9" t="s">
         <v>9</v>
@@ -6497,7 +6515,7 @@
       <c r="E193" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F193" s="10" t="s">
+      <c r="F193" s="12" t="s">
         <v>390</v>
       </c>
       <c r="G193" s="9" t="s">
@@ -6505,261 +6523,261 @@
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A194" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="B194" s="9" t="s">
-        <v>264</v>
+      <c r="A194" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C194" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D194" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="E194" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="F194" s="10">
-        <v>38055</v>
-      </c>
-      <c r="G194" s="9" t="s">
-        <v>268</v>
+      <c r="D194" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F194" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="C195" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="F195" s="10">
-        <v>25010</v>
+        <v>10</v>
+      </c>
+      <c r="F195" s="10" t="s">
+        <v>390</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>393</v>
+        <v>465</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C196" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>394</v>
+        <v>466</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>36</v>
+        <v>467</v>
       </c>
       <c r="F196" s="10">
-        <v>20123</v>
+        <v>38055</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C197" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="F197" s="10">
-        <v>71016</v>
+        <v>25010</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>16</v>
+        <v>393</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C198" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>18</v>
+        <v>394</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F198" s="10" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F198" s="10">
+        <v>20123</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>325</v>
+        <v>416</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="C199" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>327</v>
+        <v>417</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="F199" s="10" t="s">
-        <v>329</v>
+        <v>418</v>
+      </c>
+      <c r="F199" s="10">
+        <v>71016</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>330</v>
+        <v>44</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C200" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F200" s="10" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>478</v>
+        <v>325</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="C201" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>479</v>
+        <v>327</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F201" s="10">
-        <v>20123</v>
+        <v>328</v>
+      </c>
+      <c r="F201" s="10" t="s">
+        <v>329</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>38</v>
+        <v>330</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>396</v>
+        <v>277</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C202" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F202" s="10" t="s">
-        <v>218</v>
+        <v>37</v>
       </c>
       <c r="G202" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>216</v>
+        <v>478</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C203" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>217</v>
+        <v>479</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F203" s="10" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F203" s="10">
+        <v>20123</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>160</v>
+        <v>396</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="C204" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="E204" s="9" t="s">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="F204" s="10" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="G204" s="9" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
-        <v>434</v>
+        <v>216</v>
       </c>
       <c r="B205" s="9" t="s">
         <v>9</v>
@@ -6782,53 +6800,99 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="C206" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="E206" s="9" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="F206" s="10" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="G206" s="9" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B207" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C207" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D207" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E207" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F207" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G207" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A208" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B208" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C208" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D208" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E208" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F208" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G208" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A209" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B207" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C207" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D207" s="9" t="s">
+      <c r="B209" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C209" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D209" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E207" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F207" s="10" t="s">
+      <c r="E209" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F209" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G207" s="9" t="s">
+      <c r="G209" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G146" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G207">
+    <sortState ref="A2:G209">
       <sortCondition ref="A1:A146"/>
     </sortState>
   </autoFilter>
@@ -6841,23 +6905,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F040406D9EE34E48977C379A242BB45D" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ab2d492e43f6bec9a26aa4599c840e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="877b7d34-4df7-40bf-9eb1-208952470e96" xmlns:ns4="05fc27dd-4454-4248-9c78-3d72b2b155c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc604e5d4aadf5a992ba83f8d4fb519" ns3:_="" ns4:_="">
     <xsd:import namespace="877b7d34-4df7-40bf-9eb1-208952470e96"/>
@@ -7090,32 +7137,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC6436E-C4E7-4E8D-94E8-64DAEC05792B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7132,4 +7171,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{2C790D21-B0A2-4EAB-A64E-C79CA24C7465}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{31BC6D89-A8E8-4247-B2AA-AE375F97C3A3}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="544">
   <si>
     <t>Nome account</t>
   </si>
@@ -1646,6 +1646,15 @@
   </si>
   <si>
     <t>TRIESTE</t>
+  </si>
+  <si>
+    <t>CHIRON ENERGY SPV 05 SRL</t>
+  </si>
+  <si>
+    <t>VIA BIGLI 2</t>
+  </si>
+  <si>
+    <t>CHIRON ENERGY SPV 07 SRL</t>
   </si>
 </sst>
 </file>
@@ -2070,7 +2079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G209"/>
+  <dimension ref="A1:G211"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -3005,30 +3014,30 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>499</v>
+        <v>541</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C41" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>500</v>
+        <v>542</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F41" s="5">
-        <v>10143</v>
+        <v>20121</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>389</v>
+        <v>543</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>34</v>
@@ -3037,13 +3046,13 @@
         <v>8</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>270</v>
+        <v>542</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F42" s="5">
-        <v>20123</v>
+        <v>20121</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>38</v>
@@ -3051,30 +3060,30 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>437</v>
+        <v>499</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C43" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F43" s="5">
-        <v>20123</v>
+        <v>10143</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>34</v>
@@ -3097,7 +3106,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>269</v>
+        <v>437</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>34</v>
@@ -3111,8 +3120,8 @@
       <c r="E45" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>61</v>
+      <c r="F45" s="5">
+        <v>20123</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>38</v>
@@ -3120,7 +3129,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>137</v>
+        <v>397</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>34</v>
@@ -3129,13 +3138,13 @@
         <v>8</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F46" s="5" t="s">
-        <v>58</v>
+      <c r="F46" s="5">
+        <v>20123</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>38</v>
@@ -3143,7 +3152,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>409</v>
+        <v>269</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>34</v>
@@ -3152,13 +3161,13 @@
         <v>8</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F47" s="5">
-        <v>20121</v>
+      <c r="F47" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>38</v>
@@ -3166,191 +3175,191 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>125</v>
+        <v>409</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>127</v>
+        <v>36</v>
+      </c>
+      <c r="F49" s="5">
+        <v>20121</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>444</v>
+        <v>138</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>189</v>
+        <v>140</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F50" s="5">
-        <v>20158</v>
+        <v>141</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>142</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>225</v>
+        <v>125</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>226</v>
+        <v>126</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>84</v>
+        <v>444</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>88</v>
+        <v>36</v>
+      </c>
+      <c r="F52" s="5">
+        <v>20158</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>44</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>487</v>
+        <v>225</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>488</v>
+        <v>28</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>489</v>
+        <v>226</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="F53" s="5">
-        <v>26015</v>
+        <v>30</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>334</v>
+        <v>84</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>335</v>
+        <v>86</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>218</v>
+        <v>88</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>300</v>
+        <v>487</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>296</v>
+        <v>488</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>301</v>
+        <v>489</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>302</v>
+        <v>490</v>
       </c>
       <c r="F55" s="5">
-        <v>56025</v>
+        <v>26015</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>299</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>271</v>
+        <v>334</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>9</v>
@@ -3359,13 +3368,13 @@
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>272</v>
+        <v>335</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>273</v>
+        <v>218</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>11</v>
@@ -3373,53 +3382,53 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>376</v>
+        <v>301</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>36</v>
+        <v>302</v>
       </c>
       <c r="F57" s="5">
-        <v>20121</v>
+        <v>56025</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="F58" s="5">
-        <v>24060</v>
+        <v>10</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>150</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>481</v>
+        <v>375</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>34</v>
@@ -3428,7 +3437,7 @@
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>258</v>
+        <v>376</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>36</v>
@@ -3442,30 +3451,30 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>157</v>
+        <v>303</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>158</v>
+        <v>304</v>
+      </c>
+      <c r="F60" s="5">
+        <v>24060</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>156</v>
+        <v>481</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>34</v>
@@ -3474,21 +3483,21 @@
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F61" s="5" t="s">
-        <v>158</v>
+      <c r="F61" s="5">
+        <v>20121</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>253</v>
+        <v>175</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>34</v>
@@ -3497,21 +3506,21 @@
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>439</v>
+        <v>156</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>34</v>
@@ -3520,128 +3529,128 @@
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>440</v>
+        <v>157</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F63" s="5">
-        <v>20122</v>
+      <c r="F63" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>248</v>
+        <v>36</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>250</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>251</v>
+        <v>439</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>252</v>
+        <v>440</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>237</v>
+        <v>36</v>
+      </c>
+      <c r="F65" s="5">
+        <v>20122</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>362</v>
+        <v>245</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>363</v>
+        <v>246</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>364</v>
+        <v>247</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="F66" s="5">
-        <v>76123</v>
+        <v>248</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>44</v>
+        <v>250</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>425</v>
+        <v>251</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>132</v>
+        <v>252</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F67" s="5">
-        <v>39100</v>
+        <v>81</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>391</v>
+        <v>362</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>40</v>
+        <v>363</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>42</v>
+        <v>365</v>
       </c>
       <c r="F68" s="5">
-        <v>70043</v>
+        <v>76123</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>44</v>
@@ -3649,53 +3658,53 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>219</v>
+        <v>425</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>220</v>
+        <v>132</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="F69" s="5">
+        <v>39100</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>50</v>
+        <v>391</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>47</v>
+        <v>392</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
+      </c>
+      <c r="F70" s="5">
+        <v>70043</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>51</v>
+        <v>219</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>34</v>
@@ -3704,13 +3713,13 @@
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>52</v>
+        <v>220</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>38</v>
@@ -3718,30 +3727,30 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>34</v>
@@ -3750,13 +3759,13 @@
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G73" s="4" t="s">
         <v>38</v>
@@ -3764,7 +3773,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>34</v>
@@ -3787,30 +3796,30 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>371</v>
+        <v>124</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>372</v>
+        <v>34</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>373</v>
+        <v>122</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="F75" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>201</v>
+        <v>130</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>34</v>
@@ -3819,44 +3828,44 @@
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>190</v>
+        <v>58</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>506</v>
+        <v>371</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="C77" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>508</v>
+        <v>373</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>507</v>
+        <v>374</v>
       </c>
       <c r="F77" s="5">
-        <v>35010</v>
+        <v>61121</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>505</v>
+        <v>165</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>281</v>
+        <v>201</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>34</v>
@@ -3865,274 +3874,274 @@
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>305</v>
+        <v>189</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F78" s="5">
-        <v>20123</v>
+      <c r="F78" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>351</v>
+        <v>506</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="C79" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>353</v>
+        <v>508</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>354</v>
+        <v>507</v>
       </c>
       <c r="F79" s="5">
-        <v>15033</v>
+        <v>35010</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>83</v>
+        <v>505</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>535</v>
+        <v>281</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>117</v>
+        <v>34</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>536</v>
+        <v>305</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="F80" s="5">
-        <v>65127</v>
+        <v>20123</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>59</v>
+        <v>351</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>34</v>
+        <v>352</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>60</v>
+        <v>353</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>61</v>
+        <v>354</v>
+      </c>
+      <c r="F81" s="5">
+        <v>15033</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>336</v>
+        <v>535</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>337</v>
+        <v>536</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="F82" s="5">
-        <v>10153</v>
+        <v>65127</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>430</v>
+        <v>59</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F83" s="5">
-        <v>10153</v>
+        <v>36</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>282</v>
+        <v>336</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="F84" s="5">
-        <v>183</v>
+        <v>10153</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>210</v>
+        <v>430</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>211</v>
+        <v>337</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>58</v>
+        <v>81</v>
+      </c>
+      <c r="F85" s="5">
+        <v>10153</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
+      </c>
+      <c r="F86" s="5">
+        <v>183</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>159</v>
+        <v>307</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>129</v>
+        <v>211</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>242</v>
+        <v>275</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>414</v>
+        <v>128</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>415</v>
+        <v>129</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>28</v>
@@ -4141,7 +4150,7 @@
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>30</v>
@@ -4155,122 +4164,122 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>238</v>
+        <v>414</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>239</v>
+        <v>415</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>241</v>
+        <v>180</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>537</v>
+        <v>274</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>538</v>
+        <v>28</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>539</v>
+        <v>29</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="F92" s="5">
-        <v>34133</v>
+        <v>30</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>514</v>
+        <v>32</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>435</v>
+        <v>238</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>129</v>
+        <v>239</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F93" s="5">
-        <v>39100</v>
+        <v>240</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>206</v>
+        <v>537</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>34</v>
+        <v>538</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>60</v>
+        <v>539</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>61</v>
+        <v>540</v>
+      </c>
+      <c r="F94" s="5">
+        <v>34133</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>38</v>
+        <v>514</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>366</v>
+        <v>435</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F95" s="5">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>34</v>
@@ -4293,122 +4302,122 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>493</v>
+        <v>366</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>494</v>
+        <v>60</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F97" s="8" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F97" s="5">
+        <v>20123</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>519</v>
+        <v>101</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>520</v>
+        <v>60</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F98" s="5">
-        <v>80121</v>
+        <v>36</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>406</v>
+        <v>493</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>407</v>
+        <v>494</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="F99" s="5">
-        <v>38121</v>
+        <v>10</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>369</v>
+        <v>519</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>370</v>
+        <v>520</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F100" s="5">
-        <v>20123</v>
+        <v>80121</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>360</v>
+        <v>406</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>361</v>
+        <v>407</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>19</v>
+        <v>408</v>
       </c>
       <c r="F101" s="5">
-        <v>90139</v>
+        <v>38121</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>12</v>
+        <v>268</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>34</v>
@@ -4417,7 +4426,7 @@
         <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>195</v>
+        <v>370</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>36</v>
@@ -4431,53 +4440,53 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>455</v>
+        <v>360</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>456</v>
+        <v>361</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F103" s="8" t="s">
-        <v>180</v>
+        <v>19</v>
+      </c>
+      <c r="F103" s="5">
+        <v>90139</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>283</v>
+        <v>345</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>309</v>
+        <v>195</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>310</v>
+        <v>36</v>
       </c>
       <c r="F104" s="5">
-        <v>12037</v>
+        <v>20123</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>13</v>
+        <v>455</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>9</v>
@@ -4486,90 +4495,90 @@
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>14</v>
+        <v>456</v>
       </c>
       <c r="E105" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F105" s="5" t="s">
-        <v>15</v>
+      <c r="F105" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>123</v>
+        <v>283</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>28</v>
+        <v>308</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>55</v>
+        <v>309</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>31</v>
+        <v>310</v>
+      </c>
+      <c r="F106" s="5">
+        <v>12037</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>32</v>
+        <v>307</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>28</v>
@@ -4578,7 +4587,7 @@
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>30</v>
@@ -4592,444 +4601,444 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>498</v>
+        <v>74</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C110" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C110" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F110" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>233</v>
+        <v>27</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>218</v>
+        <v>31</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>188</v>
+        <v>498</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C112" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>189</v>
+        <v>29</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>190</v>
+        <v>30</v>
+      </c>
+      <c r="F112" s="5">
+        <v>39100</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>483</v>
+        <v>233</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>484</v>
+        <v>9</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>485</v>
+        <v>234</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="F113" s="5">
-        <v>66020</v>
+        <v>10</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>411</v>
+        <v>188</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>412</v>
+        <v>189</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="F114" s="5">
-        <v>37137</v>
+        <v>36</v>
+      </c>
+      <c r="F114" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>343</v>
+        <v>159</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>9</v>
+        <v>484</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F115" s="8" t="s">
-        <v>218</v>
+        <v>486</v>
+      </c>
+      <c r="F115" s="5">
+        <v>66020</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>295</v>
+        <v>411</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>296</v>
+        <v>341</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>297</v>
+        <v>412</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>298</v>
+        <v>413</v>
       </c>
       <c r="F116" s="5">
-        <v>56010</v>
+        <v>37137</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>299</v>
+        <v>343</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>311</v>
+        <v>460</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>312</v>
+        <v>461</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="F117" s="5">
-        <v>40060</v>
+        <v>10</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>384</v>
+        <v>295</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>36</v>
+        <v>298</v>
       </c>
       <c r="F118" s="5">
-        <v>20121</v>
+        <v>56010</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>386</v>
+        <v>311</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>385</v>
+        <v>312</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F119" s="5" t="s">
-        <v>58</v>
+        <v>313</v>
+      </c>
+      <c r="F119" s="5">
+        <v>40060</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>213</v>
+        <v>384</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>179</v>
+        <v>385</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F120" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F120" s="5">
+        <v>20121</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>68</v>
+        <v>386</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>70</v>
+        <v>385</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>284</v>
+        <v>213</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>314</v>
+        <v>9</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>315</v>
+        <v>179</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="F122" s="5">
-        <v>57021</v>
+        <v>10</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>299</v>
+        <v>77</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>179</v>
+        <v>70</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>462</v>
+        <v>284</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F124" s="8" t="s">
-        <v>180</v>
+        <v>316</v>
+      </c>
+      <c r="F124" s="5">
+        <v>57021</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>346</v>
+        <v>462</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>347</v>
+        <v>179</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F126" s="5">
-        <v>70124</v>
+        <v>10</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>333</v>
+        <v>89</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F127" s="5">
-        <v>20158</v>
+        <v>92</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>308</v>
+        <v>40</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="F128" s="5">
-        <v>12084</v>
+        <v>70124</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>307</v>
+        <v>44</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>34</v>
@@ -5038,182 +5047,182 @@
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F129" s="5" t="s">
-        <v>61</v>
+      <c r="F129" s="5">
+        <v>20158</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>227</v>
+        <v>357</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>228</v>
+        <v>358</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>37</v>
+        <v>359</v>
+      </c>
+      <c r="F130" s="5">
+        <v>12084</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>457</v>
+        <v>194</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>458</v>
+        <v>195</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F131" s="8" t="s">
-        <v>459</v>
+        <v>36</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>108</v>
+        <v>227</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F133" s="5">
-        <v>12100</v>
+        <v>10</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>459</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>395</v>
+        <v>108</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F134" s="5">
-        <v>40127</v>
+        <v>111</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>355</v>
+        <v>431</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>356</v>
+        <v>432</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>36</v>
+        <v>433</v>
       </c>
       <c r="F135" s="5">
-        <v>20121</v>
+        <v>12100</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>526</v>
+        <v>395</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>525</v>
+        <v>23</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F136" s="5">
-        <v>20154</v>
+        <v>40127</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>524</v>
+        <v>355</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>34</v>
@@ -5222,113 +5231,113 @@
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>525</v>
+        <v>356</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F137" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F138" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>232</v>
+        <v>524</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F139" s="5">
+        <v>20154</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>143</v>
+        <v>515</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="F140" s="5">
+        <v>39100</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>441</v>
+        <v>143</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>34</v>
@@ -5337,136 +5346,136 @@
         <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>442</v>
+        <v>144</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="F142" s="5">
-        <v>20038</v>
+        <v>36</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>426</v>
+        <v>56</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F143" s="5">
-        <v>10121</v>
+        <v>36</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>95</v>
+        <v>441</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>97</v>
+        <v>442</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>99</v>
+        <v>443</v>
+      </c>
+      <c r="F144" s="5">
+        <v>20038</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>377</v>
+        <v>426</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>379</v>
+        <v>236</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>380</v>
+        <v>81</v>
       </c>
       <c r="F145" s="5">
-        <v>64020</v>
+        <v>10121</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>410</v>
+        <v>95</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>211</v>
+        <v>97</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F146" s="5">
-        <v>20121</v>
+        <v>98</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>133</v>
+        <v>377</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>34</v>
+        <v>378</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>134</v>
+        <v>379</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>135</v>
+        <v>380</v>
+      </c>
+      <c r="F147" s="5">
+        <v>64020</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>257</v>
+        <v>410</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>34</v>
@@ -5475,13 +5484,13 @@
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F148" s="5" t="s">
-        <v>58</v>
+      <c r="F148" s="5">
+        <v>20121</v>
       </c>
       <c r="G148" s="4" t="s">
         <v>38</v>
@@ -5489,30 +5498,30 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>340</v>
+        <v>133</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>342</v>
+        <v>134</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="F149" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>343</v>
+        <v>136</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>34</v>
@@ -5521,44 +5530,44 @@
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>167</v>
+        <v>258</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>529</v>
+        <v>340</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>167</v>
+        <v>342</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>36</v>
+        <v>528</v>
       </c>
       <c r="F151" s="5">
-        <v>20126</v>
+        <v>37045</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>159</v>
+        <v>343</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>471</v>
+        <v>166</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>34</v>
@@ -5567,21 +5576,21 @@
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E152" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F152" s="5">
-        <v>20135</v>
+      <c r="F152" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>405</v>
+        <v>529</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>34</v>
@@ -5590,44 +5599,44 @@
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E153" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F153" s="5">
-        <v>20135</v>
+        <v>20126</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>204</v>
+        <v>471</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F154" s="5">
+        <v>20135</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>453</v>
+        <v>405</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>34</v>
@@ -5636,412 +5645,412 @@
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>454</v>
+        <v>260</v>
       </c>
       <c r="E155" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F155" s="5">
-        <v>20144</v>
+        <v>20135</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>36</v>
+        <v>186</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>136</v>
+        <v>319</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>285</v>
+        <v>453</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>317</v>
+        <v>454</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F157" s="5">
-        <v>40026</v>
+        <v>20144</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>286</v>
+        <v>223</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>320</v>
+        <v>224</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>323</v>
+        <v>135</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>533</v>
+        <v>285</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>29</v>
+        <v>317</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>30</v>
+        <v>318</v>
       </c>
       <c r="F159" s="5">
-        <v>39100</v>
+        <v>40026</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>367</v>
+        <v>286</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>368</v>
+        <v>320</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F160" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>287</v>
+        <v>533</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>321</v>
+        <v>29</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>322</v>
+        <v>30</v>
       </c>
       <c r="F161" s="5">
-        <v>12020</v>
+        <v>39100</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>307</v>
+        <v>32</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>39</v>
+        <v>367</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>41</v>
+        <v>368</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F162" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
+      </c>
+      <c r="F162" s="5">
+        <v>20123</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>421</v>
+        <v>287</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>422</v>
+        <v>308</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>423</v>
+        <v>321</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>424</v>
+        <v>322</v>
       </c>
       <c r="F163" s="5">
-        <v>28053</v>
+        <v>12020</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>136</v>
+        <v>307</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>172</v>
+        <v>39</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>198</v>
+        <v>421</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>22</v>
+        <v>422</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>199</v>
+        <v>423</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>200</v>
+        <v>424</v>
+      </c>
+      <c r="F165" s="5">
+        <v>28053</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>534</v>
+        <v>207</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F168" s="5">
-        <v>20121</v>
+        <v>71</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>445</v>
+        <v>244</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>447</v>
+        <v>177</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="F169" s="5">
-        <v>53048</v>
+        <v>36</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>449</v>
+        <v>38</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>509</v>
+        <v>34</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>517</v>
+        <v>177</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>518</v>
+        <v>36</v>
       </c>
       <c r="F170" s="5">
-        <v>35011</v>
+        <v>20121</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>505</v>
+        <v>38</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>243</v>
+        <v>445</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>34</v>
+        <v>446</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>177</v>
+        <v>447</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>58</v>
+        <v>448</v>
+      </c>
+      <c r="F171" s="5">
+        <v>53048</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>38</v>
+        <v>449</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>131</v>
+        <v>516</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>28</v>
+        <v>509</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>132</v>
+        <v>517</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>31</v>
+        <v>518</v>
+      </c>
+      <c r="F172" s="5">
+        <v>35011</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>32</v>
+        <v>505</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>531</v>
+        <v>243</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>34</v>
@@ -6050,13 +6059,13 @@
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>532</v>
+        <v>177</v>
       </c>
       <c r="E173" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F173" s="5">
-        <v>20121</v>
+      <c r="F173" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>38</v>
@@ -6064,30 +6073,30 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>381</v>
+        <v>531</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>34</v>
@@ -6096,13 +6105,13 @@
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>382</v>
+        <v>532</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>383</v>
+        <v>36</v>
       </c>
       <c r="F175" s="5">
-        <v>20089</v>
+        <v>20121</v>
       </c>
       <c r="G175" s="4" t="s">
         <v>38</v>
@@ -6110,99 +6119,99 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>476</v>
+        <v>23</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F176" s="8" t="s">
-        <v>477</v>
+        <v>24</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>212</v>
+        <v>381</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>202</v>
+        <v>382</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>203</v>
+        <v>383</v>
+      </c>
+      <c r="F177" s="5">
+        <v>20089</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>214</v>
+        <v>475</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>215</v>
+        <v>476</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>438</v>
+        <v>212</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F179" s="5">
-        <v>20124</v>
+        <v>24</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>34</v>
@@ -6211,21 +6220,21 @@
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E180" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>256</v>
+        <v>438</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>34</v>
@@ -6234,21 +6243,21 @@
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E181" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F181" s="5" t="s">
-        <v>231</v>
+      <c r="F181" s="5">
+        <v>20124</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>472</v>
+        <v>229</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>34</v>
@@ -6257,21 +6266,21 @@
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E182" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F182" s="5">
-        <v>20129</v>
+      <c r="F182" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>463</v>
+        <v>256</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>34</v>
@@ -6280,21 +6289,21 @@
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F183" s="5">
-        <v>20129</v>
+      <c r="F183" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>34</v>
@@ -6317,7 +6326,7 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>34</v>
@@ -6340,7 +6349,7 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>176</v>
+        <v>473</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>34</v>
@@ -6349,59 +6358,59 @@
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F186" s="5" t="s">
-        <v>58</v>
+      <c r="F186" s="5">
+        <v>20129</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>331</v>
+        <v>474</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>332</v>
+        <v>464</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F187" s="5">
-        <v>40026</v>
+        <v>20129</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>288</v>
+        <v>176</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>324</v>
+        <v>177</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F188" s="5">
-        <v>20124</v>
+      <c r="F188" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G188" s="4" t="s">
         <v>38</v>
@@ -6409,145 +6418,145 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>450</v>
+        <v>331</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>451</v>
+        <v>332</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>452</v>
+        <v>318</v>
       </c>
       <c r="F189" s="10">
-        <v>12011</v>
+        <v>40026</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>307</v>
+        <v>26</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>151</v>
+        <v>288</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>153</v>
+        <v>324</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F190" s="10" t="s">
-        <v>155</v>
+        <v>36</v>
+      </c>
+      <c r="F190" s="10">
+        <v>20124</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>419</v>
+        <v>450</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>36</v>
+        <v>452</v>
       </c>
       <c r="F191" s="10">
-        <v>20123</v>
+        <v>12011</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>491</v>
+        <v>151</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>492</v>
+        <v>153</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F192" s="10">
-        <v>90141</v>
+        <v>154</v>
+      </c>
+      <c r="F192" s="10" t="s">
+        <v>155</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>480</v>
+        <v>419</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F193" s="12" t="s">
-        <v>390</v>
+        <v>36</v>
+      </c>
+      <c r="F193" s="10">
+        <v>20123</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A194" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="B194" s="3" t="s">
-        <v>9</v>
+      <c r="A194" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="B194" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="C194" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D194" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E194" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F194" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="G194" s="3" t="s">
-        <v>11</v>
+      <c r="D194" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="E194" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F194" s="10">
+        <v>90141</v>
+      </c>
+      <c r="G194" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>387</v>
+        <v>480</v>
       </c>
       <c r="B195" s="9" t="s">
         <v>9</v>
@@ -6561,7 +6570,7 @@
       <c r="E195" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F195" s="10" t="s">
+      <c r="F195" s="12" t="s">
         <v>390</v>
       </c>
       <c r="G195" s="9" t="s">
@@ -6569,261 +6578,261 @@
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A196" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="B196" s="9" t="s">
-        <v>264</v>
+      <c r="A196" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C196" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D196" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="E196" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="F196" s="10">
-        <v>38055</v>
-      </c>
-      <c r="G196" s="9" t="s">
-        <v>268</v>
+      <c r="D196" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F196" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="C197" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="F197" s="10">
-        <v>25010</v>
+        <v>10</v>
+      </c>
+      <c r="F197" s="10" t="s">
+        <v>390</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>393</v>
+        <v>465</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C198" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>394</v>
+        <v>466</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>36</v>
+        <v>467</v>
       </c>
       <c r="F198" s="10">
-        <v>20123</v>
+        <v>38055</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C199" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="F199" s="10">
-        <v>71016</v>
+        <v>25010</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>16</v>
+        <v>393</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C200" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>18</v>
+        <v>394</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F200" s="10" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F200" s="10">
+        <v>20123</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>325</v>
+        <v>416</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="C201" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>327</v>
+        <v>417</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="F201" s="10" t="s">
-        <v>329</v>
+        <v>418</v>
+      </c>
+      <c r="F201" s="10">
+        <v>71016</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>330</v>
+        <v>44</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C202" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F202" s="10" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G202" s="9" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>478</v>
+        <v>325</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="C203" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>479</v>
+        <v>327</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F203" s="10">
-        <v>20123</v>
+        <v>328</v>
+      </c>
+      <c r="F203" s="10" t="s">
+        <v>329</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>38</v>
+        <v>330</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>396</v>
+        <v>277</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C204" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="E204" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F204" s="10" t="s">
-        <v>218</v>
+        <v>37</v>
       </c>
       <c r="G204" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
-        <v>216</v>
+        <v>478</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C205" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>217</v>
+        <v>479</v>
       </c>
       <c r="E205" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F205" s="10" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F205" s="10">
+        <v>20123</v>
       </c>
       <c r="G205" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
-        <v>160</v>
+        <v>396</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="C206" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="E206" s="9" t="s">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="F206" s="10" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="G206" s="9" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
-        <v>434</v>
+        <v>216</v>
       </c>
       <c r="B207" s="9" t="s">
         <v>9</v>
@@ -6846,53 +6855,99 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="C208" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="E208" s="9" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="F208" s="10" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="G208" s="9" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B209" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C209" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D209" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E209" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F209" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G209" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A210" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B210" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C210" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D210" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E210" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F210" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G210" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A211" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B209" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C209" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D209" s="9" t="s">
+      <c r="B211" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C211" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D211" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E209" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F209" s="10" t="s">
+      <c r="E211" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F211" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G209" s="9" t="s">
+      <c r="G211" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G146" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G209">
+    <sortState ref="A2:G211">
       <sortCondition ref="A1:A146"/>
     </sortState>
   </autoFilter>
@@ -6905,6 +6960,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F040406D9EE34E48977C379A242BB45D" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ab2d492e43f6bec9a26aa4599c840e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="877b7d34-4df7-40bf-9eb1-208952470e96" xmlns:ns4="05fc27dd-4454-4248-9c78-3d72b2b155c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc604e5d4aadf5a992ba83f8d4fb519" ns3:_="" ns4:_="">
     <xsd:import namespace="877b7d34-4df7-40bf-9eb1-208952470e96"/>
@@ -7137,15 +7201,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7155,6 +7210,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC6436E-C4E7-4E8D-94E8-64DAEC05792B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7173,27 +7236,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{31BC6D89-A8E8-4247-B2AA-AE375F97C3A3}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{5975B458-2E39-4590-8F92-57ADF6CB2684}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="557">
   <si>
     <t>Nome account</t>
   </si>
@@ -1655,6 +1655,45 @@
   </si>
   <si>
     <t>CHIRON ENERGY SPV 07 SRL</t>
+  </si>
+  <si>
+    <t>DOMUSNOVAS SRL</t>
+  </si>
+  <si>
+    <t>VIA NICOLO' PORPORA 12</t>
+  </si>
+  <si>
+    <t>ATLAS SOLAR 13 SRL</t>
+  </si>
+  <si>
+    <t>VIA ANTONIO ANDREUZZI 12</t>
+  </si>
+  <si>
+    <t>UDINE</t>
+  </si>
+  <si>
+    <t>FRANCOFONTE SRL</t>
+  </si>
+  <si>
+    <t>PIAZZA GAE AULENTI 1</t>
+  </si>
+  <si>
+    <t>ELPI SRL</t>
+  </si>
+  <si>
+    <t>RI</t>
+  </si>
+  <si>
+    <t>VIA FUNDANIA 2</t>
+  </si>
+  <si>
+    <t>RIETI</t>
+  </si>
+  <si>
+    <t>02100</t>
+  </si>
+  <si>
+    <t>OPR SUN 30 SRL</t>
   </si>
 </sst>
 </file>
@@ -2079,7 +2118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G211"/>
+  <dimension ref="A1:G216"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -2738,53 +2777,53 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>279</v>
+        <v>546</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>28</v>
+        <v>511</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>289</v>
+        <v>547</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>290</v>
+        <v>548</v>
       </c>
       <c r="F29" s="5">
-        <v>39042</v>
+        <v>33100</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>32</v>
+        <v>514</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>523</v>
+        <v>279</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>339</v>
+        <v>289</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>36</v>
+        <v>290</v>
       </c>
       <c r="F30" s="5">
-        <v>20121</v>
+        <v>39042</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>338</v>
+        <v>523</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>34</v>
@@ -2807,7 +2846,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>33</v>
+        <v>338</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>34</v>
@@ -2816,13 +2855,13 @@
         <v>8</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>35</v>
+        <v>339</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="5" t="s">
-        <v>37</v>
+      <c r="F32" s="5">
+        <v>20121</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>38</v>
@@ -2830,45 +2869,45 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>221</v>
+        <v>33</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>116</v>
+        <v>221</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>118</v>
+        <v>222</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>77</v>
@@ -2876,7 +2915,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>527</v>
+        <v>116</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>117</v>
@@ -2890,8 +2929,8 @@
       <c r="E35" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F35" s="5">
-        <v>65125</v>
+      <c r="F35" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>77</v>
@@ -2899,7 +2938,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>254</v>
+        <v>527</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>117</v>
@@ -2913,8 +2952,8 @@
       <c r="E36" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F36" s="5" t="s">
-        <v>120</v>
+      <c r="F36" s="5">
+        <v>65125</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>77</v>
@@ -2922,122 +2961,122 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>62</v>
+        <v>254</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>521</v>
+        <v>145</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>522</v>
+        <v>147</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F39" s="5">
-        <v>20033</v>
+        <v>148</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>291</v>
+        <v>521</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>292</v>
+        <v>34</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>293</v>
+        <v>522</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>294</v>
+        <v>36</v>
       </c>
       <c r="F40" s="5">
-        <v>60035</v>
+        <v>20033</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>541</v>
+        <v>291</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>34</v>
+        <v>292</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>542</v>
+        <v>293</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>36</v>
+        <v>294</v>
       </c>
       <c r="F41" s="5">
-        <v>20121</v>
+        <v>60035</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>34</v>
@@ -3060,53 +3099,53 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>499</v>
+        <v>543</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C43" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>500</v>
+        <v>542</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F43" s="5">
-        <v>10143</v>
+        <v>20121</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>389</v>
+        <v>499</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C44" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F44" s="5">
-        <v>20123</v>
+        <v>10143</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>437</v>
+        <v>389</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>34</v>
@@ -3129,7 +3168,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>397</v>
+        <v>437</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>34</v>
@@ -3152,7 +3191,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>269</v>
+        <v>397</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>34</v>
@@ -3166,8 +3205,8 @@
       <c r="E47" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F47" s="5" t="s">
-        <v>61</v>
+      <c r="F47" s="5">
+        <v>20123</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>38</v>
@@ -3175,7 +3214,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>34</v>
@@ -3184,13 +3223,13 @@
         <v>8</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>38</v>
@@ -3198,7 +3237,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>409</v>
+        <v>137</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>34</v>
@@ -3212,8 +3251,8 @@
       <c r="E49" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F49" s="5">
-        <v>20121</v>
+      <c r="F49" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>38</v>
@@ -3221,145 +3260,145 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>138</v>
+        <v>409</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>142</v>
+        <v>36</v>
+      </c>
+      <c r="F50" s="5">
+        <v>20121</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>444</v>
+        <v>125</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F52" s="5">
-        <v>20158</v>
+        <v>19</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>225</v>
+        <v>444</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F53" s="5">
+        <v>20158</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>487</v>
+        <v>84</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>488</v>
+        <v>85</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>489</v>
+        <v>86</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="F55" s="5">
-        <v>26015</v>
+        <v>87</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>334</v>
+        <v>544</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>9</v>
@@ -3368,44 +3407,44 @@
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>335</v>
+        <v>545</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F56" s="5" t="s">
-        <v>218</v>
+      <c r="F56" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>300</v>
+        <v>487</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>296</v>
+        <v>488</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>301</v>
+        <v>489</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>302</v>
+        <v>490</v>
       </c>
       <c r="F57" s="5">
-        <v>56025</v>
+        <v>26015</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>299</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>271</v>
+        <v>334</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>9</v>
@@ -3414,13 +3453,13 @@
         <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>272</v>
+        <v>335</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>273</v>
+        <v>218</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>11</v>
@@ -3428,53 +3467,53 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>376</v>
+        <v>301</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>36</v>
+        <v>302</v>
       </c>
       <c r="F59" s="5">
-        <v>20121</v>
+        <v>56025</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="F60" s="5">
-        <v>24060</v>
+        <v>10</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>150</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>481</v>
+        <v>375</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>34</v>
@@ -3483,7 +3522,7 @@
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>258</v>
+        <v>376</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>36</v>
@@ -3497,30 +3536,30 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>157</v>
+        <v>303</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>158</v>
+        <v>304</v>
+      </c>
+      <c r="F62" s="5">
+        <v>24060</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>156</v>
+        <v>481</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>34</v>
@@ -3529,21 +3568,21 @@
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F63" s="5" t="s">
-        <v>158</v>
+      <c r="F63" s="5">
+        <v>20121</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>253</v>
+        <v>175</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>34</v>
@@ -3552,21 +3591,21 @@
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>439</v>
+        <v>156</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>34</v>
@@ -3575,128 +3614,128 @@
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>440</v>
+        <v>157</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F65" s="5">
-        <v>20122</v>
+      <c r="F65" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>248</v>
+        <v>36</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>250</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>251</v>
+        <v>439</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>252</v>
+        <v>440</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>237</v>
+        <v>36</v>
+      </c>
+      <c r="F67" s="5">
+        <v>20122</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>362</v>
+        <v>245</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>363</v>
+        <v>246</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>364</v>
+        <v>247</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="F68" s="5">
-        <v>76123</v>
+        <v>248</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>44</v>
+        <v>250</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>425</v>
+        <v>251</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>132</v>
+        <v>252</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F69" s="5">
-        <v>39100</v>
+        <v>81</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>391</v>
+        <v>362</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>40</v>
+        <v>363</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>42</v>
+        <v>365</v>
       </c>
       <c r="F70" s="5">
-        <v>70043</v>
+        <v>76123</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>44</v>
@@ -3704,76 +3743,76 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>219</v>
+        <v>425</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>220</v>
+        <v>132</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="F71" s="5">
+        <v>39100</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>50</v>
+        <v>551</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>46</v>
+        <v>552</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>47</v>
+        <v>553</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>49</v>
+        <v>554</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>555</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>51</v>
+        <v>391</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>52</v>
+        <v>392</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
+      </c>
+      <c r="F73" s="5">
+        <v>70043</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>121</v>
+        <v>219</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>34</v>
@@ -3782,13 +3821,13 @@
         <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>122</v>
+        <v>220</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>38</v>
@@ -3796,30 +3835,30 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>34</v>
@@ -3828,13 +3867,13 @@
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>38</v>
@@ -3842,30 +3881,30 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>371</v>
+        <v>121</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>372</v>
+        <v>34</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>373</v>
+        <v>122</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="F77" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>201</v>
+        <v>124</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>34</v>
@@ -3874,113 +3913,113 @@
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>190</v>
+        <v>58</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>506</v>
+        <v>130</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="C79" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>508</v>
+        <v>122</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="F79" s="5">
-        <v>35010</v>
+        <v>36</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>505</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>281</v>
+        <v>371</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>34</v>
+        <v>372</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>305</v>
+        <v>373</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>36</v>
+        <v>374</v>
       </c>
       <c r="F80" s="5">
-        <v>20123</v>
+        <v>61121</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>351</v>
+        <v>201</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>353</v>
+        <v>189</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="F81" s="5">
-        <v>15033</v>
+        <v>36</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>83</v>
+        <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>535</v>
+        <v>506</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C82" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>536</v>
+        <v>508</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>119</v>
+        <v>507</v>
       </c>
       <c r="F82" s="5">
-        <v>65127</v>
+        <v>35010</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>77</v>
+        <v>505</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>59</v>
+        <v>281</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>34</v>
@@ -3989,13 +4028,13 @@
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>60</v>
+        <v>305</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F83" s="5" t="s">
-        <v>61</v>
+      <c r="F83" s="5">
+        <v>20123</v>
       </c>
       <c r="G83" s="4" t="s">
         <v>38</v>
@@ -4003,22 +4042,22 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>81</v>
+        <v>354</v>
       </c>
       <c r="F84" s="5">
-        <v>10153</v>
+        <v>15033</v>
       </c>
       <c r="G84" s="4" t="s">
         <v>83</v>
@@ -4026,398 +4065,398 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>430</v>
+        <v>535</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>337</v>
+        <v>536</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="F85" s="5">
-        <v>10153</v>
+        <v>65127</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>282</v>
+        <v>59</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>306</v>
+        <v>60</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" s="5">
-        <v>183</v>
+        <v>36</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>210</v>
+        <v>336</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>211</v>
+        <v>337</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>58</v>
+        <v>81</v>
+      </c>
+      <c r="F87" s="5">
+        <v>10153</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>275</v>
+        <v>430</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>158</v>
+        <v>81</v>
+      </c>
+      <c r="F88" s="5">
+        <v>10153</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>128</v>
+        <v>282</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>129</v>
+        <v>306</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>31</v>
+        <v>10</v>
+      </c>
+      <c r="F89" s="5">
+        <v>183</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>32</v>
+        <v>307</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>129</v>
+        <v>211</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>414</v>
+        <v>549</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>415</v>
+        <v>550</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F91" s="5">
+        <v>20154</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>29</v>
+        <v>276</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>238</v>
+        <v>128</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>239</v>
+        <v>129</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>241</v>
+        <v>31</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>537</v>
+        <v>242</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>538</v>
+        <v>28</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>539</v>
+        <v>129</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="F94" s="5">
-        <v>34133</v>
+        <v>30</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>514</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>435</v>
+        <v>414</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>129</v>
+        <v>415</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F95" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>206</v>
+        <v>274</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>366</v>
+        <v>238</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>60</v>
+        <v>239</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F97" s="5">
-        <v>20123</v>
+        <v>240</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>101</v>
+        <v>537</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>34</v>
+        <v>538</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>60</v>
+        <v>539</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>61</v>
+        <v>540</v>
+      </c>
+      <c r="F98" s="5">
+        <v>34133</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>38</v>
+        <v>514</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>493</v>
+        <v>435</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>494</v>
+        <v>129</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>273</v>
+        <v>30</v>
+      </c>
+      <c r="F99" s="5">
+        <v>39100</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>519</v>
+        <v>206</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>520</v>
+        <v>60</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F100" s="5">
-        <v>80121</v>
+        <v>36</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>406</v>
+        <v>366</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>264</v>
+        <v>34</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>407</v>
+        <v>60</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>408</v>
+        <v>36</v>
       </c>
       <c r="F101" s="5">
-        <v>38121</v>
+        <v>20123</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>268</v>
+        <v>38</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>369</v>
+        <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>34</v>
@@ -4426,13 +4465,13 @@
         <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>370</v>
+        <v>60</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F102" s="5">
-        <v>20123</v>
+      <c r="F102" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>38</v>
@@ -4440,229 +4479,229 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>360</v>
+        <v>493</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>361</v>
+        <v>494</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F103" s="5">
-        <v>90139</v>
+        <v>10</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>345</v>
+        <v>519</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>195</v>
+        <v>520</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F104" s="5">
-        <v>20123</v>
+        <v>80121</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>455</v>
+        <v>406</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>456</v>
+        <v>407</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>180</v>
+        <v>408</v>
+      </c>
+      <c r="F105" s="5">
+        <v>38121</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>77</v>
+        <v>268</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>283</v>
+        <v>369</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>309</v>
+        <v>370</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>310</v>
+        <v>36</v>
       </c>
       <c r="F106" s="5">
-        <v>12037</v>
+        <v>20123</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>13</v>
+        <v>360</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>14</v>
+        <v>361</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
+      </c>
+      <c r="F107" s="5">
+        <v>90139</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>123</v>
+        <v>345</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F108" s="5">
+        <v>20123</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>54</v>
+        <v>455</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>55</v>
+        <v>456</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F109" s="5" t="s">
-        <v>31</v>
+        <v>10</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>74</v>
+        <v>283</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>75</v>
+        <v>309</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>76</v>
+        <v>310</v>
+      </c>
+      <c r="F110" s="5">
+        <v>12037</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>77</v>
+        <v>307</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>498</v>
+        <v>123</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C112" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F112" s="5">
-        <v>39100</v>
+      <c r="F112" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G112" s="4" t="s">
         <v>32</v>
@@ -4670,99 +4709,99 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>233</v>
+        <v>54</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>234</v>
+        <v>55</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>218</v>
+        <v>31</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>188</v>
+        <v>74</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>190</v>
+        <v>76</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>483</v>
+        <v>27</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>484</v>
+        <v>28</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>485</v>
+        <v>29</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="F115" s="5">
-        <v>66020</v>
+        <v>30</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>411</v>
+        <v>498</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="C116" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>412</v>
+        <v>29</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>413</v>
+        <v>30</v>
       </c>
       <c r="F116" s="5">
-        <v>37137</v>
+        <v>39100</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>343</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>460</v>
+        <v>233</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>9</v>
@@ -4771,12 +4810,12 @@
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>461</v>
+        <v>234</v>
       </c>
       <c r="E117" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F117" s="8" t="s">
+      <c r="F117" s="5" t="s">
         <v>218</v>
       </c>
       <c r="G117" s="4" t="s">
@@ -4785,191 +4824,191 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>295</v>
+        <v>188</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>296</v>
+        <v>34</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>297</v>
+        <v>189</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="F118" s="5">
-        <v>56010</v>
+        <v>36</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>299</v>
+        <v>159</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>311</v>
+        <v>483</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>22</v>
+        <v>484</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>312</v>
+        <v>485</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>313</v>
+        <v>486</v>
       </c>
       <c r="F119" s="5">
-        <v>40060</v>
+        <v>66020</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>36</v>
+        <v>413</v>
       </c>
       <c r="F120" s="5">
-        <v>20121</v>
+        <v>37137</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>38</v>
+        <v>343</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>386</v>
+        <v>460</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>385</v>
+        <v>461</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F121" s="5" t="s">
-        <v>58</v>
+        <v>10</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>213</v>
+        <v>295</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>9</v>
+        <v>296</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>179</v>
+        <v>297</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>180</v>
+        <v>298</v>
+      </c>
+      <c r="F122" s="5">
+        <v>56010</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>68</v>
+        <v>311</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>70</v>
+        <v>312</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F123" s="5" t="s">
-        <v>72</v>
+        <v>313</v>
+      </c>
+      <c r="F123" s="5">
+        <v>40060</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>284</v>
+        <v>384</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>314</v>
+        <v>34</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>315</v>
+        <v>385</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>316</v>
+        <v>36</v>
       </c>
       <c r="F124" s="5">
-        <v>57021</v>
+        <v>20121</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>299</v>
+        <v>38</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>184</v>
+        <v>386</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>179</v>
+        <v>385</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>180</v>
+        <v>58</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>462</v>
+        <v>213</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>9</v>
@@ -4983,7 +5022,7 @@
       <c r="E126" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F126" s="8" t="s">
+      <c r="F126" s="5" t="s">
         <v>180</v>
       </c>
       <c r="G126" s="4" t="s">
@@ -4992,352 +5031,352 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>346</v>
+        <v>284</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>40</v>
+        <v>314</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="F128" s="5">
-        <v>70124</v>
+        <v>57021</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>44</v>
+        <v>299</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>333</v>
+        <v>184</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F129" s="5">
-        <v>20158</v>
+        <v>10</v>
+      </c>
+      <c r="F129" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>357</v>
+        <v>462</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>358</v>
+        <v>179</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="F130" s="5">
-        <v>12084</v>
+        <v>10</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>194</v>
+        <v>89</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>195</v>
+        <v>91</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>227</v>
+        <v>346</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>228</v>
+        <v>347</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F132" s="5" t="s">
-        <v>37</v>
+        <v>348</v>
+      </c>
+      <c r="F132" s="5">
+        <v>70124</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>457</v>
+        <v>333</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>458</v>
+        <v>189</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F133" s="8" t="s">
-        <v>459</v>
+        <v>36</v>
+      </c>
+      <c r="F133" s="5">
+        <v>20158</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>108</v>
+        <v>357</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>109</v>
+        <v>308</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>110</v>
+        <v>358</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F134" s="5" t="s">
-        <v>112</v>
+        <v>359</v>
+      </c>
+      <c r="F134" s="5">
+        <v>12084</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>113</v>
+        <v>307</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>431</v>
+        <v>194</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>432</v>
+        <v>195</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F135" s="5">
-        <v>12100</v>
+        <v>36</v>
+      </c>
+      <c r="F135" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>395</v>
+        <v>227</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>23</v>
+        <v>228</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F136" s="5">
-        <v>40127</v>
+        <v>36</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>355</v>
+        <v>457</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>356</v>
+        <v>458</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F137" s="5">
-        <v>20121</v>
+        <v>10</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>459</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>526</v>
+        <v>108</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>525</v>
+        <v>110</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F138" s="5">
-        <v>20154</v>
+        <v>111</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>524</v>
+        <v>431</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>525</v>
+        <v>432</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>36</v>
+        <v>433</v>
       </c>
       <c r="F139" s="5">
-        <v>20154</v>
+        <v>12100</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>159</v>
+        <v>307</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>515</v>
+        <v>395</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F140" s="5">
-        <v>39100</v>
+        <v>40127</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>232</v>
+        <v>355</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>29</v>
+        <v>356</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F141" s="5">
+        <v>20121</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>143</v>
+        <v>556</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>34</v>
@@ -5346,21 +5385,21 @@
         <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>144</v>
+        <v>525</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F142" s="5" t="s">
-        <v>37</v>
+      <c r="F142" s="5">
+        <v>20154</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>56</v>
+        <v>526</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>34</v>
@@ -5369,21 +5408,21 @@
         <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>57</v>
+        <v>525</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F143" s="5" t="s">
-        <v>58</v>
+      <c r="F143" s="5">
+        <v>20154</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>441</v>
+        <v>524</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>34</v>
@@ -5392,90 +5431,90 @@
         <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>442</v>
+        <v>525</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>443</v>
+        <v>36</v>
       </c>
       <c r="F144" s="5">
-        <v>20038</v>
+        <v>20154</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>426</v>
+        <v>515</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>236</v>
+        <v>29</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="F145" s="5">
-        <v>10121</v>
+        <v>39100</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>95</v>
+        <v>232</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>377</v>
+        <v>143</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>378</v>
+        <v>34</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>379</v>
+        <v>144</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="F147" s="5">
-        <v>64020</v>
+        <v>36</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>410</v>
+        <v>56</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>34</v>
@@ -5484,13 +5523,13 @@
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>211</v>
+        <v>57</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F148" s="5">
-        <v>20121</v>
+      <c r="F148" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G148" s="4" t="s">
         <v>38</v>
@@ -5498,7 +5537,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>133</v>
+        <v>441</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>34</v>
@@ -5507,13 +5546,13 @@
         <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>134</v>
+        <v>442</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>135</v>
+        <v>443</v>
+      </c>
+      <c r="F149" s="5">
+        <v>20038</v>
       </c>
       <c r="G149" s="4" t="s">
         <v>136</v>
@@ -5521,76 +5560,76 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>257</v>
+        <v>426</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>58</v>
+        <v>81</v>
+      </c>
+      <c r="F150" s="5">
+        <v>10121</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>340</v>
+        <v>95</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>341</v>
+        <v>96</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>342</v>
+        <v>97</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="F151" s="5">
-        <v>37045</v>
+        <v>98</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>343</v>
+        <v>100</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>166</v>
+        <v>377</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>34</v>
+        <v>378</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>167</v>
+        <v>379</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F152" s="5" t="s">
-        <v>168</v>
+        <v>380</v>
+      </c>
+      <c r="F152" s="5">
+        <v>64020</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>529</v>
+        <v>410</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>34</v>
@@ -5599,21 +5638,21 @@
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>167</v>
+        <v>211</v>
       </c>
       <c r="E153" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F153" s="5">
-        <v>20126</v>
+        <v>20121</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>471</v>
+        <v>133</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>34</v>
@@ -5622,21 +5661,21 @@
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>260</v>
+        <v>134</v>
       </c>
       <c r="E154" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F154" s="5">
-        <v>20135</v>
+      <c r="F154" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>405</v>
+        <v>257</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>34</v>
@@ -5645,44 +5684,44 @@
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E155" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F155" s="5">
-        <v>20135</v>
+      <c r="F155" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>262</v>
+        <v>38</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>204</v>
+        <v>340</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>185</v>
+        <v>341</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>205</v>
+        <v>342</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F156" s="5" t="s">
-        <v>187</v>
+        <v>528</v>
+      </c>
+      <c r="F156" s="5">
+        <v>37045</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>453</v>
+        <v>166</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>34</v>
@@ -5691,21 +5730,21 @@
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>454</v>
+        <v>167</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F157" s="5">
-        <v>20144</v>
+      <c r="F157" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>223</v>
+        <v>529</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>34</v>
@@ -5714,90 +5753,90 @@
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>224</v>
+        <v>167</v>
       </c>
       <c r="E158" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F158" s="5" t="s">
-        <v>135</v>
+      <c r="F158" s="5">
+        <v>20126</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>285</v>
+        <v>471</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>317</v>
+        <v>260</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F159" s="5">
-        <v>40026</v>
+        <v>20135</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>286</v>
+        <v>405</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F160" s="5" t="s">
-        <v>323</v>
+        <v>36</v>
+      </c>
+      <c r="F160" s="5">
+        <v>20135</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>11</v>
+        <v>262</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>533</v>
+        <v>204</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>29</v>
+        <v>205</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F161" s="5">
-        <v>39100</v>
+        <v>186</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>32</v>
+        <v>319</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>367</v>
+        <v>453</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>34</v>
@@ -5806,13 +5845,13 @@
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>368</v>
+        <v>454</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F162" s="5">
-        <v>20123</v>
+        <v>20144</v>
       </c>
       <c r="G162" s="4" t="s">
         <v>38</v>
@@ -5820,283 +5859,283 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>287</v>
+        <v>223</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>321</v>
+        <v>224</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F163" s="5">
-        <v>12020</v>
+        <v>36</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>307</v>
+        <v>136</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>39</v>
+        <v>285</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>41</v>
+        <v>317</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>43</v>
+        <v>318</v>
+      </c>
+      <c r="F164" s="5">
+        <v>40026</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>421</v>
+        <v>286</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>422</v>
+        <v>9</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>423</v>
+        <v>320</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="F165" s="5">
-        <v>28053</v>
+        <v>10</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>172</v>
+        <v>533</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>169</v>
+        <v>29</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>171</v>
+        <v>30</v>
+      </c>
+      <c r="F166" s="5">
+        <v>39100</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>198</v>
+        <v>367</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>199</v>
+        <v>368</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>200</v>
+        <v>36</v>
+      </c>
+      <c r="F167" s="5">
+        <v>20123</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>207</v>
+        <v>287</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>69</v>
+        <v>308</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>208</v>
+        <v>321</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>209</v>
+        <v>322</v>
+      </c>
+      <c r="F168" s="5">
+        <v>12020</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>73</v>
+        <v>307</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>244</v>
+        <v>39</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>177</v>
+        <v>41</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>534</v>
+        <v>421</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>34</v>
+        <v>422</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>177</v>
+        <v>423</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>36</v>
+        <v>424</v>
       </c>
       <c r="F170" s="5">
-        <v>20121</v>
+        <v>28053</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>445</v>
+        <v>172</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>447</v>
+        <v>169</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="F171" s="5">
-        <v>53048</v>
+        <v>170</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>449</v>
+        <v>159</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>516</v>
+        <v>198</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>509</v>
+        <v>22</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>517</v>
+        <v>199</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="F172" s="5">
-        <v>35011</v>
+        <v>24</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>505</v>
+        <v>26</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>131</v>
+        <v>244</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>34</v>
@@ -6105,7 +6144,7 @@
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>532</v>
+        <v>177</v>
       </c>
       <c r="E175" s="4" t="s">
         <v>36</v>
@@ -6119,99 +6158,99 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>21</v>
+        <v>445</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>22</v>
+        <v>446</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>23</v>
+        <v>447</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>25</v>
+        <v>448</v>
+      </c>
+      <c r="F176" s="5">
+        <v>53048</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>26</v>
+        <v>449</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>381</v>
+        <v>516</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>34</v>
+        <v>509</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>382</v>
+        <v>517</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>383</v>
+        <v>518</v>
       </c>
       <c r="F177" s="5">
-        <v>20089</v>
+        <v>35011</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>475</v>
+        <v>243</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>476</v>
+        <v>177</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F178" s="8" t="s">
-        <v>477</v>
+        <v>36</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>212</v>
+        <v>131</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>202</v>
+        <v>132</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>203</v>
+        <v>31</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>214</v>
+        <v>531</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>34</v>
@@ -6220,44 +6259,44 @@
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>215</v>
+        <v>532</v>
       </c>
       <c r="E180" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F180" s="5" t="s">
-        <v>158</v>
+      <c r="F180" s="5">
+        <v>20121</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F181" s="5">
-        <v>20124</v>
+        <v>24</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>229</v>
+        <v>381</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>34</v>
@@ -6266,67 +6305,67 @@
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>230</v>
+        <v>382</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>231</v>
+        <v>383</v>
+      </c>
+      <c r="F182" s="5">
+        <v>20089</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>256</v>
+        <v>475</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>230</v>
+        <v>476</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>231</v>
+        <v>10</v>
+      </c>
+      <c r="F183" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>472</v>
+        <v>212</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>464</v>
+        <v>202</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F184" s="5">
-        <v>20129</v>
+        <v>24</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>262</v>
+        <v>26</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>463</v>
+        <v>214</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>34</v>
@@ -6335,21 +6374,21 @@
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>464</v>
+        <v>215</v>
       </c>
       <c r="E185" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F185" s="5">
-        <v>20129</v>
+      <c r="F185" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>473</v>
+        <v>438</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>34</v>
@@ -6358,21 +6397,21 @@
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>464</v>
+        <v>215</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F186" s="5">
-        <v>20129</v>
+        <v>20124</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>474</v>
+        <v>229</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>34</v>
@@ -6381,21 +6420,21 @@
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F187" s="5">
-        <v>20129</v>
+      <c r="F187" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>176</v>
+        <v>256</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>34</v>
@@ -6404,113 +6443,113 @@
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>177</v>
+        <v>230</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>58</v>
+        <v>231</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>331</v>
+        <v>472</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>332</v>
+        <v>464</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F189" s="10">
-        <v>40026</v>
+        <v>20129</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>288</v>
+        <v>463</v>
       </c>
       <c r="B190" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>324</v>
+        <v>464</v>
       </c>
       <c r="E190" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F190" s="10">
-        <v>20124</v>
+        <v>20129</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>452</v>
+        <v>36</v>
       </c>
       <c r="F191" s="10">
-        <v>12011</v>
+        <v>20129</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>307</v>
+        <v>262</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>151</v>
+        <v>474</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>153</v>
+        <v>464</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F192" s="10" t="s">
-        <v>155</v>
+        <v>36</v>
+      </c>
+      <c r="F192" s="10">
+        <v>20129</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>44</v>
+        <v>262</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>419</v>
+        <v>176</v>
       </c>
       <c r="B193" s="9" t="s">
         <v>34</v>
@@ -6519,13 +6558,13 @@
         <v>8</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>420</v>
+        <v>177</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F193" s="10">
-        <v>20123</v>
+      <c r="F193" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G193" s="9" t="s">
         <v>38</v>
@@ -6533,260 +6572,260 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>491</v>
+        <v>331</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C194" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>492</v>
+        <v>332</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>19</v>
+        <v>318</v>
       </c>
       <c r="F194" s="10">
-        <v>90141</v>
+        <v>40026</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>480</v>
+        <v>288</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C195" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>388</v>
+        <v>324</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F195" s="12" t="s">
-        <v>390</v>
+        <v>36</v>
+      </c>
+      <c r="F195" s="10">
+        <v>20124</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A196" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="B196" s="3" t="s">
-        <v>9</v>
+      <c r="A196" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="B196" s="9" t="s">
+        <v>308</v>
       </c>
       <c r="C196" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D196" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E196" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F196" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="G196" s="3" t="s">
-        <v>11</v>
+      <c r="D196" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="E196" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="F196" s="10">
+        <v>12011</v>
+      </c>
+      <c r="G196" s="9" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>387</v>
+        <v>151</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>9</v>
+        <v>152</v>
       </c>
       <c r="C197" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>388</v>
+        <v>153</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="F197" s="10" t="s">
-        <v>390</v>
+        <v>155</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>465</v>
+        <v>419</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>264</v>
+        <v>34</v>
       </c>
       <c r="C198" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>466</v>
+        <v>420</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>467</v>
+        <v>36</v>
       </c>
       <c r="F198" s="10">
-        <v>38055</v>
+        <v>20123</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>268</v>
+        <v>38</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>427</v>
+        <v>491</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="C199" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>428</v>
+        <v>492</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>429</v>
+        <v>19</v>
       </c>
       <c r="F199" s="10">
-        <v>25010</v>
+        <v>90141</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>107</v>
+        <v>12</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>393</v>
+        <v>480</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C200" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F200" s="10">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F200" s="12" t="s">
+        <v>390</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A201" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="B201" s="9" t="s">
-        <v>85</v>
+      <c r="A201" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C201" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D201" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="E201" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="F201" s="10">
-        <v>71016</v>
-      </c>
-      <c r="G201" s="9" t="s">
-        <v>44</v>
+      <c r="D201" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F201" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>16</v>
+        <v>387</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C202" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>18</v>
+        <v>388</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F202" s="10" t="s">
-        <v>20</v>
+        <v>390</v>
       </c>
       <c r="G202" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>325</v>
+        <v>465</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>326</v>
+        <v>264</v>
       </c>
       <c r="C203" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>327</v>
+        <v>466</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="F203" s="10" t="s">
-        <v>329</v>
+        <v>467</v>
+      </c>
+      <c r="F203" s="10">
+        <v>38055</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>330</v>
+        <v>268</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>277</v>
+        <v>427</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="C204" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>278</v>
+        <v>428</v>
       </c>
       <c r="E204" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F204" s="10" t="s">
-        <v>37</v>
+        <v>429</v>
+      </c>
+      <c r="F204" s="10">
+        <v>25010</v>
       </c>
       <c r="G204" s="9" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
-        <v>478</v>
+        <v>393</v>
       </c>
       <c r="B205" s="9" t="s">
         <v>34</v>
@@ -6795,7 +6834,7 @@
         <v>8</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>479</v>
+        <v>394</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>36</v>
@@ -6809,145 +6848,260 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="C206" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>217</v>
+        <v>417</v>
       </c>
       <c r="E206" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F206" s="10" t="s">
-        <v>218</v>
+        <v>418</v>
+      </c>
+      <c r="F206" s="10">
+        <v>71016</v>
       </c>
       <c r="G206" s="9" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C207" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>217</v>
+        <v>18</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F207" s="10" t="s">
-        <v>218</v>
+        <v>20</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
-        <v>160</v>
+        <v>325</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>161</v>
+        <v>326</v>
       </c>
       <c r="C208" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>162</v>
+        <v>327</v>
       </c>
       <c r="E208" s="9" t="s">
-        <v>163</v>
+        <v>328</v>
       </c>
       <c r="F208" s="10" t="s">
-        <v>164</v>
+        <v>329</v>
       </c>
       <c r="G208" s="9" t="s">
-        <v>165</v>
+        <v>330</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
-        <v>434</v>
+        <v>277</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C209" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="E209" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F209" s="10" t="s">
-        <v>218</v>
+        <v>37</v>
       </c>
       <c r="G209" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
-        <v>255</v>
+        <v>478</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C210" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D210" s="9" t="s">
-        <v>217</v>
+        <v>479</v>
       </c>
       <c r="E210" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F210" s="10" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F210" s="10">
+        <v>20123</v>
       </c>
       <c r="G210" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="B211" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C211" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D211" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E211" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F211" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G211" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A212" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B212" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C212" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D212" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E212" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F212" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G212" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A213" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B213" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C213" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D213" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E213" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F213" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G213" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A214" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B214" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C214" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D214" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E214" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F214" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G214" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A215" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C215" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D215" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E215" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F215" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G215" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A216" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B211" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C211" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D211" s="9" t="s">
+      <c r="B216" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C216" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D216" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E211" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F211" s="10" t="s">
+      <c r="E216" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F216" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G211" s="9" t="s">
+      <c r="G216" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G146" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G211">
+    <sortState ref="A2:G216">
       <sortCondition ref="A1:A146"/>
     </sortState>
   </autoFilter>
@@ -6960,12 +7114,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7202,17 +7355,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7237,18 +7400,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{5975B458-2E39-4590-8F92-57ADF6CB2684}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{B5CF236B-803A-4DF5-A97A-DA942647C97A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Report" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Report!$A$1:$G$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Report!$A$1:$G$218</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="559">
   <si>
     <t>Nome account</t>
   </si>
@@ -1694,6 +1694,12 @@
   </si>
   <si>
     <t>OPR SUN 30 SRL</t>
+  </si>
+  <si>
+    <t>CHERRY PICKING SRL</t>
+  </si>
+  <si>
+    <t>DS ITALIA 44 SRL</t>
   </si>
 </sst>
 </file>
@@ -2118,7 +2124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G216"/>
+  <dimension ref="A1:G218"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -3076,7 +3082,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>34</v>
@@ -3085,21 +3091,21 @@
         <v>8</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>542</v>
+        <v>215</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F42" s="5">
-        <v>20121</v>
+        <v>20124</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>34</v>
@@ -3122,53 +3128,53 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>499</v>
+        <v>543</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>500</v>
+        <v>542</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F44" s="5">
-        <v>10143</v>
+        <v>20121</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>389</v>
+        <v>499</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C45" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F45" s="5">
-        <v>20123</v>
+        <v>10143</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>437</v>
+        <v>389</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>34</v>
@@ -3191,7 +3197,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>397</v>
+        <v>437</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>34</v>
@@ -3214,7 +3220,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>269</v>
+        <v>397</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>34</v>
@@ -3228,8 +3234,8 @@
       <c r="E48" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F48" s="5" t="s">
-        <v>61</v>
+      <c r="F48" s="5">
+        <v>20123</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>38</v>
@@ -3237,7 +3243,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>34</v>
@@ -3246,13 +3252,13 @@
         <v>8</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>38</v>
@@ -3260,7 +3266,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>409</v>
+        <v>137</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>34</v>
@@ -3274,8 +3280,8 @@
       <c r="E50" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F50" s="5">
-        <v>20121</v>
+      <c r="F50" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>38</v>
@@ -3283,214 +3289,214 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>138</v>
+        <v>409</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>142</v>
+        <v>36</v>
+      </c>
+      <c r="F51" s="5">
+        <v>20121</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>444</v>
+        <v>125</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F53" s="5">
-        <v>20158</v>
+        <v>19</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>225</v>
+        <v>444</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F54" s="5">
+        <v>20158</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>544</v>
+        <v>84</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>545</v>
+        <v>86</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>180</v>
+        <v>87</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>487</v>
+        <v>544</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>488</v>
+        <v>9</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>489</v>
+        <v>545</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="F57" s="5">
-        <v>26015</v>
+        <v>10</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>334</v>
+        <v>487</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>9</v>
+        <v>488</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>335</v>
+        <v>489</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>218</v>
+        <v>490</v>
+      </c>
+      <c r="F58" s="5">
+        <v>26015</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>300</v>
+        <v>558</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="F59" s="5">
-        <v>56025</v>
+        <v>10</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>271</v>
+        <v>334</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>9</v>
@@ -3499,13 +3505,13 @@
         <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>272</v>
+        <v>335</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>273</v>
+        <v>218</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>11</v>
@@ -3513,53 +3519,53 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>376</v>
+        <v>301</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>36</v>
+        <v>302</v>
       </c>
       <c r="F61" s="5">
-        <v>20121</v>
+        <v>56025</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="F62" s="5">
-        <v>24060</v>
+        <v>10</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>150</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>481</v>
+        <v>375</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>34</v>
@@ -3568,7 +3574,7 @@
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>258</v>
+        <v>376</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>36</v>
@@ -3582,30 +3588,30 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>157</v>
+        <v>303</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>158</v>
+        <v>304</v>
+      </c>
+      <c r="F64" s="5">
+        <v>24060</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>156</v>
+        <v>481</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>34</v>
@@ -3614,21 +3620,21 @@
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F65" s="5" t="s">
-        <v>158</v>
+      <c r="F65" s="5">
+        <v>20121</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>253</v>
+        <v>175</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>34</v>
@@ -3637,21 +3643,21 @@
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>439</v>
+        <v>156</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>34</v>
@@ -3660,205 +3666,205 @@
         <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>440</v>
+        <v>157</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F67" s="5">
-        <v>20122</v>
+      <c r="F67" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>248</v>
+        <v>36</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>250</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>251</v>
+        <v>439</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>252</v>
+        <v>440</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>237</v>
+        <v>36</v>
+      </c>
+      <c r="F69" s="5">
+        <v>20122</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>362</v>
+        <v>245</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>363</v>
+        <v>246</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>364</v>
+        <v>247</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="F70" s="5">
-        <v>76123</v>
+        <v>248</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>44</v>
+        <v>250</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>425</v>
+        <v>251</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>132</v>
+        <v>252</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F71" s="5">
-        <v>39100</v>
+        <v>81</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>551</v>
+        <v>362</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>552</v>
+        <v>363</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>553</v>
+        <v>364</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>555</v>
+        <v>365</v>
+      </c>
+      <c r="F72" s="5">
+        <v>76123</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>392</v>
+        <v>132</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F73" s="5">
-        <v>70043</v>
+        <v>39100</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>219</v>
+        <v>551</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>34</v>
+        <v>552</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>220</v>
+        <v>553</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>37</v>
+        <v>554</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>555</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>50</v>
+        <v>391</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>47</v>
+        <v>392</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
+      </c>
+      <c r="F75" s="5">
+        <v>70043</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>51</v>
+        <v>219</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>34</v>
@@ -3867,13 +3873,13 @@
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>52</v>
+        <v>220</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>38</v>
@@ -3881,30 +3887,30 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>34</v>
@@ -3913,13 +3919,13 @@
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G78" s="4" t="s">
         <v>38</v>
@@ -3927,7 +3933,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>34</v>
@@ -3950,30 +3956,30 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>371</v>
+        <v>124</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>372</v>
+        <v>34</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>373</v>
+        <v>122</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="F80" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>201</v>
+        <v>130</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>34</v>
@@ -3982,44 +3988,44 @@
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>190</v>
+        <v>58</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>506</v>
+        <v>371</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="C82" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>508</v>
+        <v>373</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>507</v>
+        <v>374</v>
       </c>
       <c r="F82" s="5">
-        <v>35010</v>
+        <v>61121</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>505</v>
+        <v>165</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>281</v>
+        <v>201</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>34</v>
@@ -4028,205 +4034,205 @@
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>305</v>
+        <v>189</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F83" s="5">
-        <v>20123</v>
+      <c r="F83" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>351</v>
+        <v>506</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="C84" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>353</v>
+        <v>508</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>354</v>
+        <v>507</v>
       </c>
       <c r="F84" s="5">
-        <v>15033</v>
+        <v>35010</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>83</v>
+        <v>505</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>535</v>
+        <v>281</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>117</v>
+        <v>34</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>536</v>
+        <v>305</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="F85" s="5">
-        <v>65127</v>
+        <v>20123</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>59</v>
+        <v>351</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>34</v>
+        <v>352</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>60</v>
+        <v>353</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>61</v>
+        <v>354</v>
+      </c>
+      <c r="F86" s="5">
+        <v>15033</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>336</v>
+        <v>535</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>337</v>
+        <v>536</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="F87" s="5">
-        <v>10153</v>
+        <v>65127</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>430</v>
+        <v>59</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F88" s="5">
-        <v>10153</v>
+        <v>36</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>282</v>
+        <v>336</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="F89" s="5">
-        <v>183</v>
+        <v>10153</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>210</v>
+        <v>430</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>211</v>
+        <v>337</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>58</v>
+        <v>81</v>
+      </c>
+      <c r="F90" s="5">
+        <v>10153</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>549</v>
+        <v>282</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>550</v>
+        <v>306</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F91" s="5">
-        <v>20154</v>
+        <v>183</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>159</v>
+        <v>307</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>275</v>
+        <v>210</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>34</v>
@@ -4235,90 +4241,90 @@
         <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>276</v>
+        <v>211</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>128</v>
+        <v>549</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>129</v>
+        <v>550</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F93" s="5">
+        <v>20154</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>242</v>
+        <v>275</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>414</v>
+        <v>128</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>415</v>
+        <v>129</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>28</v>
@@ -4327,7 +4333,7 @@
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>30</v>
@@ -4341,122 +4347,122 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>238</v>
+        <v>414</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>239</v>
+        <v>415</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>241</v>
+        <v>180</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>537</v>
+        <v>274</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>538</v>
+        <v>28</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>539</v>
+        <v>29</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="F98" s="5">
-        <v>34133</v>
+        <v>30</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>514</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>435</v>
+        <v>238</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>129</v>
+        <v>239</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F99" s="5">
-        <v>39100</v>
+        <v>240</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>206</v>
+        <v>537</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>34</v>
+        <v>538</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>60</v>
+        <v>539</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>61</v>
+        <v>540</v>
+      </c>
+      <c r="F100" s="5">
+        <v>34133</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>38</v>
+        <v>514</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>366</v>
+        <v>435</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F101" s="5">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>34</v>
@@ -4479,122 +4485,122 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>493</v>
+        <v>366</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>494</v>
+        <v>60</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F103" s="8" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F103" s="5">
+        <v>20123</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>519</v>
+        <v>101</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>520</v>
+        <v>60</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F104" s="5">
-        <v>80121</v>
+        <v>36</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>406</v>
+        <v>493</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>407</v>
+        <v>494</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="F105" s="5">
-        <v>38121</v>
+        <v>10</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>369</v>
+        <v>519</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>370</v>
+        <v>520</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F106" s="5">
-        <v>20123</v>
+        <v>80121</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>360</v>
+        <v>406</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>361</v>
+        <v>407</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>19</v>
+        <v>408</v>
       </c>
       <c r="F107" s="5">
-        <v>90139</v>
+        <v>38121</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>12</v>
+        <v>268</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>34</v>
@@ -4603,7 +4609,7 @@
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>195</v>
+        <v>370</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>36</v>
@@ -4617,53 +4623,53 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>455</v>
+        <v>360</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>456</v>
+        <v>361</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F109" s="8" t="s">
-        <v>180</v>
+        <v>19</v>
+      </c>
+      <c r="F109" s="5">
+        <v>90139</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>283</v>
+        <v>345</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>309</v>
+        <v>195</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>310</v>
+        <v>36</v>
       </c>
       <c r="F110" s="5">
-        <v>12037</v>
+        <v>20123</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>13</v>
+        <v>455</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>9</v>
@@ -4672,90 +4678,90 @@
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>14</v>
+        <v>456</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F111" s="5" t="s">
-        <v>15</v>
+      <c r="F111" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>123</v>
+        <v>283</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>28</v>
+        <v>308</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>55</v>
+        <v>309</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>31</v>
+        <v>310</v>
+      </c>
+      <c r="F112" s="5">
+        <v>12037</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>32</v>
+        <v>307</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>28</v>
@@ -4764,7 +4770,7 @@
         <v>8</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>30</v>
@@ -4778,444 +4784,444 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>498</v>
+        <v>74</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C116" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C116" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F116" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>233</v>
+        <v>27</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>218</v>
+        <v>31</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>188</v>
+        <v>498</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C118" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>189</v>
+        <v>29</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>190</v>
+        <v>30</v>
+      </c>
+      <c r="F118" s="5">
+        <v>39100</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>483</v>
+        <v>233</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>484</v>
+        <v>9</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>485</v>
+        <v>234</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="F119" s="5">
-        <v>66020</v>
+        <v>10</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>411</v>
+        <v>188</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>412</v>
+        <v>189</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="F120" s="5">
-        <v>37137</v>
+        <v>36</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>343</v>
+        <v>159</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>9</v>
+        <v>484</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F121" s="8" t="s">
-        <v>218</v>
+        <v>486</v>
+      </c>
+      <c r="F121" s="5">
+        <v>66020</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>295</v>
+        <v>411</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>296</v>
+        <v>341</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>297</v>
+        <v>412</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>298</v>
+        <v>413</v>
       </c>
       <c r="F122" s="5">
-        <v>56010</v>
+        <v>37137</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>299</v>
+        <v>343</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>311</v>
+        <v>460</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>312</v>
+        <v>461</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="F123" s="5">
-        <v>40060</v>
+        <v>10</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>384</v>
+        <v>295</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>36</v>
+        <v>298</v>
       </c>
       <c r="F124" s="5">
-        <v>20121</v>
+        <v>56010</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>386</v>
+        <v>311</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>385</v>
+        <v>312</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F125" s="5" t="s">
-        <v>58</v>
+        <v>313</v>
+      </c>
+      <c r="F125" s="5">
+        <v>40060</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>213</v>
+        <v>384</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>179</v>
+        <v>385</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F126" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F126" s="5">
+        <v>20121</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>68</v>
+        <v>386</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>70</v>
+        <v>385</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>284</v>
+        <v>213</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>314</v>
+        <v>9</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>315</v>
+        <v>179</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="F128" s="5">
-        <v>57021</v>
+        <v>10</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>299</v>
+        <v>77</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>179</v>
+        <v>70</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>462</v>
+        <v>284</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F130" s="8" t="s">
-        <v>180</v>
+        <v>316</v>
+      </c>
+      <c r="F130" s="5">
+        <v>57021</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>346</v>
+        <v>462</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>347</v>
+        <v>179</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F132" s="5">
-        <v>70124</v>
+        <v>10</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>333</v>
+        <v>89</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F133" s="5">
-        <v>20158</v>
+        <v>92</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>308</v>
+        <v>40</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="F134" s="5">
-        <v>12084</v>
+        <v>70124</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>307</v>
+        <v>44</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>34</v>
@@ -5224,182 +5230,182 @@
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F135" s="5" t="s">
-        <v>61</v>
+      <c r="F135" s="5">
+        <v>20158</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>227</v>
+        <v>357</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>228</v>
+        <v>358</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F136" s="5" t="s">
-        <v>37</v>
+        <v>359</v>
+      </c>
+      <c r="F136" s="5">
+        <v>12084</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>457</v>
+        <v>194</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>458</v>
+        <v>195</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F137" s="8" t="s">
-        <v>459</v>
+        <v>36</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>108</v>
+        <v>227</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F139" s="5">
-        <v>12100</v>
+        <v>10</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>459</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>395</v>
+        <v>108</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F140" s="5">
-        <v>40127</v>
+        <v>111</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>355</v>
+        <v>431</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>356</v>
+        <v>432</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>36</v>
+        <v>433</v>
       </c>
       <c r="F141" s="5">
-        <v>20121</v>
+        <v>12100</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>556</v>
+        <v>395</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>525</v>
+        <v>23</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F142" s="5">
-        <v>20154</v>
+        <v>40127</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>526</v>
+        <v>355</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>34</v>
@@ -5408,21 +5414,21 @@
         <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>525</v>
+        <v>356</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F143" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>524</v>
+        <v>556</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>34</v>
@@ -5445,99 +5451,99 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F145" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>232</v>
+        <v>524</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F146" s="5">
+        <v>20154</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>143</v>
+        <v>515</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="F147" s="5">
+        <v>39100</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>441</v>
+        <v>143</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>34</v>
@@ -5546,136 +5552,136 @@
         <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>442</v>
+        <v>144</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="F149" s="5">
-        <v>20038</v>
+        <v>36</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>426</v>
+        <v>56</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F150" s="5">
-        <v>10121</v>
+        <v>36</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>95</v>
+        <v>441</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>97</v>
+        <v>442</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>99</v>
+        <v>443</v>
+      </c>
+      <c r="F151" s="5">
+        <v>20038</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>377</v>
+        <v>426</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>379</v>
+        <v>236</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>380</v>
+        <v>81</v>
       </c>
       <c r="F152" s="5">
-        <v>64020</v>
+        <v>10121</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>410</v>
+        <v>95</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>211</v>
+        <v>97</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F153" s="5">
-        <v>20121</v>
+        <v>98</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>133</v>
+        <v>377</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>34</v>
+        <v>378</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>134</v>
+        <v>379</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>135</v>
+        <v>380</v>
+      </c>
+      <c r="F154" s="5">
+        <v>64020</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>257</v>
+        <v>410</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>34</v>
@@ -5684,13 +5690,13 @@
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="E155" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F155" s="5" t="s">
-        <v>58</v>
+      <c r="F155" s="5">
+        <v>20121</v>
       </c>
       <c r="G155" s="4" t="s">
         <v>38</v>
@@ -5698,30 +5704,30 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>340</v>
+        <v>133</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>342</v>
+        <v>134</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="F156" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>343</v>
+        <v>136</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>34</v>
@@ -5730,44 +5736,44 @@
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>167</v>
+        <v>258</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>529</v>
+        <v>340</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>167</v>
+        <v>342</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>36</v>
+        <v>528</v>
       </c>
       <c r="F158" s="5">
-        <v>20126</v>
+        <v>37045</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>159</v>
+        <v>343</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>471</v>
+        <v>166</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>34</v>
@@ -5776,21 +5782,21 @@
         <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E159" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F159" s="5">
-        <v>20135</v>
+      <c r="F159" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>405</v>
+        <v>529</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>34</v>
@@ -5799,44 +5805,44 @@
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E160" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F160" s="5">
-        <v>20135</v>
+        <v>20126</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>204</v>
+        <v>471</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F161" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F161" s="5">
+        <v>20135</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>453</v>
+        <v>405</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>34</v>
@@ -5845,412 +5851,412 @@
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>454</v>
+        <v>260</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F162" s="5">
-        <v>20144</v>
+        <v>20135</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>36</v>
+        <v>186</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>136</v>
+        <v>319</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>285</v>
+        <v>453</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>317</v>
+        <v>454</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F164" s="5">
-        <v>40026</v>
+        <v>20144</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>286</v>
+        <v>223</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>320</v>
+        <v>224</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>323</v>
+        <v>135</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>533</v>
+        <v>285</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>29</v>
+        <v>317</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>30</v>
+        <v>318</v>
       </c>
       <c r="F166" s="5">
-        <v>39100</v>
+        <v>40026</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>367</v>
+        <v>286</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>368</v>
+        <v>320</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F167" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>287</v>
+        <v>533</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>321</v>
+        <v>29</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>322</v>
+        <v>30</v>
       </c>
       <c r="F168" s="5">
-        <v>12020</v>
+        <v>39100</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>307</v>
+        <v>32</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>39</v>
+        <v>367</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>41</v>
+        <v>368</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
+      </c>
+      <c r="F169" s="5">
+        <v>20123</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>421</v>
+        <v>287</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>422</v>
+        <v>308</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>423</v>
+        <v>321</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>424</v>
+        <v>322</v>
       </c>
       <c r="F170" s="5">
-        <v>28053</v>
+        <v>12020</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>136</v>
+        <v>307</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>172</v>
+        <v>39</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>198</v>
+        <v>421</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>22</v>
+        <v>422</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>199</v>
+        <v>423</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>200</v>
+        <v>424</v>
+      </c>
+      <c r="F172" s="5">
+        <v>28053</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>534</v>
+        <v>207</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F175" s="5">
-        <v>20121</v>
+        <v>71</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>445</v>
+        <v>244</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>447</v>
+        <v>177</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="F176" s="5">
-        <v>53048</v>
+        <v>36</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>449</v>
+        <v>38</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>509</v>
+        <v>34</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>517</v>
+        <v>177</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>518</v>
+        <v>36</v>
       </c>
       <c r="F177" s="5">
-        <v>35011</v>
+        <v>20121</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>505</v>
+        <v>38</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>243</v>
+        <v>445</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>34</v>
+        <v>446</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>177</v>
+        <v>447</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>58</v>
+        <v>448</v>
+      </c>
+      <c r="F178" s="5">
+        <v>53048</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>38</v>
+        <v>449</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>131</v>
+        <v>516</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>28</v>
+        <v>509</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>132</v>
+        <v>517</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>31</v>
+        <v>518</v>
+      </c>
+      <c r="F179" s="5">
+        <v>35011</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>32</v>
+        <v>505</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>531</v>
+        <v>243</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>34</v>
@@ -6259,13 +6265,13 @@
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>532</v>
+        <v>177</v>
       </c>
       <c r="E180" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F180" s="5">
-        <v>20121</v>
+      <c r="F180" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G180" s="4" t="s">
         <v>38</v>
@@ -6273,30 +6279,30 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>381</v>
+        <v>531</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>34</v>
@@ -6305,13 +6311,13 @@
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>382</v>
+        <v>532</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>383</v>
+        <v>36</v>
       </c>
       <c r="F182" s="5">
-        <v>20089</v>
+        <v>20121</v>
       </c>
       <c r="G182" s="4" t="s">
         <v>38</v>
@@ -6319,99 +6325,99 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>476</v>
+        <v>23</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F183" s="8" t="s">
-        <v>477</v>
+        <v>24</v>
+      </c>
+      <c r="F183" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>212</v>
+        <v>381</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>202</v>
+        <v>382</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>203</v>
+        <v>383</v>
+      </c>
+      <c r="F184" s="5">
+        <v>20089</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>214</v>
+        <v>475</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>215</v>
+        <v>476</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F185" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>438</v>
+        <v>212</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F186" s="5">
-        <v>20124</v>
+        <v>24</v>
+      </c>
+      <c r="F186" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>34</v>
@@ -6420,21 +6426,21 @@
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>256</v>
+        <v>438</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>34</v>
@@ -6443,21 +6449,21 @@
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F188" s="5" t="s">
-        <v>231</v>
+      <c r="F188" s="5">
+        <v>20124</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>472</v>
+        <v>229</v>
       </c>
       <c r="B189" s="9" t="s">
         <v>34</v>
@@ -6466,21 +6472,21 @@
         <v>8</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F189" s="10">
-        <v>20129</v>
+      <c r="F189" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>463</v>
+        <v>256</v>
       </c>
       <c r="B190" s="9" t="s">
         <v>34</v>
@@ -6489,21 +6495,21 @@
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E190" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F190" s="10">
-        <v>20129</v>
+      <c r="F190" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B191" s="9" t="s">
         <v>34</v>
@@ -6526,7 +6532,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="B192" s="9" t="s">
         <v>34</v>
@@ -6549,7 +6555,7 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>176</v>
+        <v>473</v>
       </c>
       <c r="B193" s="9" t="s">
         <v>34</v>
@@ -6558,59 +6564,59 @@
         <v>8</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F193" s="10" t="s">
-        <v>58</v>
+      <c r="F193" s="10">
+        <v>20129</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>331</v>
+        <v>474</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C194" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>332</v>
+        <v>464</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F194" s="10">
-        <v>40026</v>
+        <v>20129</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>288</v>
+        <v>176</v>
       </c>
       <c r="B195" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C195" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>324</v>
+        <v>177</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F195" s="10">
-        <v>20124</v>
+      <c r="F195" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G195" s="9" t="s">
         <v>38</v>
@@ -6618,145 +6624,145 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>450</v>
+        <v>331</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="C196" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>451</v>
+        <v>332</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>452</v>
+        <v>318</v>
       </c>
       <c r="F196" s="10">
-        <v>12011</v>
+        <v>40026</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>307</v>
+        <v>26</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>151</v>
+        <v>288</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>153</v>
+        <v>324</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F197" s="10" t="s">
-        <v>155</v>
+        <v>36</v>
+      </c>
+      <c r="F197" s="10">
+        <v>20124</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>419</v>
+        <v>450</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C198" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>36</v>
+        <v>452</v>
       </c>
       <c r="F198" s="10">
-        <v>20123</v>
+        <v>12011</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>491</v>
+        <v>151</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C199" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>492</v>
+        <v>153</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F199" s="10">
-        <v>90141</v>
+        <v>154</v>
+      </c>
+      <c r="F199" s="10" t="s">
+        <v>155</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>480</v>
+        <v>419</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C200" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F200" s="12" t="s">
-        <v>390</v>
+        <v>36</v>
+      </c>
+      <c r="F200" s="10">
+        <v>20123</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A201" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="B201" s="3" t="s">
-        <v>9</v>
+      <c r="A201" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="C201" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D201" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E201" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F201" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="G201" s="3" t="s">
-        <v>11</v>
+      <c r="D201" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="E201" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F201" s="10">
+        <v>90141</v>
+      </c>
+      <c r="G201" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>387</v>
+        <v>480</v>
       </c>
       <c r="B202" s="9" t="s">
         <v>9</v>
@@ -6770,7 +6776,7 @@
       <c r="E202" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F202" s="10" t="s">
+      <c r="F202" s="12" t="s">
         <v>390</v>
       </c>
       <c r="G202" s="9" t="s">
@@ -6778,261 +6784,261 @@
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A203" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="B203" s="9" t="s">
-        <v>264</v>
+      <c r="A203" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C203" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D203" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="E203" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="F203" s="10">
-        <v>38055</v>
-      </c>
-      <c r="G203" s="9" t="s">
-        <v>268</v>
+      <c r="D203" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F203" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="C204" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="E204" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="F204" s="10">
-        <v>25010</v>
+        <v>10</v>
+      </c>
+      <c r="F204" s="10" t="s">
+        <v>390</v>
       </c>
       <c r="G204" s="9" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
-        <v>393</v>
+        <v>465</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C205" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>394</v>
+        <v>466</v>
       </c>
       <c r="E205" s="9" t="s">
-        <v>36</v>
+        <v>467</v>
       </c>
       <c r="F205" s="10">
-        <v>20123</v>
+        <v>38055</v>
       </c>
       <c r="G205" s="9" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C206" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="E206" s="9" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="F206" s="10">
-        <v>71016</v>
+        <v>25010</v>
       </c>
       <c r="G206" s="9" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
-        <v>16</v>
+        <v>393</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C207" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>18</v>
+        <v>394</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F207" s="10" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F207" s="10">
+        <v>20123</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
-        <v>325</v>
+        <v>416</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="C208" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>327</v>
+        <v>417</v>
       </c>
       <c r="E208" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="F208" s="10" t="s">
-        <v>329</v>
+        <v>418</v>
+      </c>
+      <c r="F208" s="10">
+        <v>71016</v>
       </c>
       <c r="G208" s="9" t="s">
-        <v>330</v>
+        <v>44</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C209" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="E209" s="9" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F209" s="10" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G209" s="9" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
-        <v>478</v>
+        <v>325</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="C210" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D210" s="9" t="s">
-        <v>479</v>
+        <v>327</v>
       </c>
       <c r="E210" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F210" s="10">
-        <v>20123</v>
+        <v>328</v>
+      </c>
+      <c r="F210" s="10" t="s">
+        <v>329</v>
       </c>
       <c r="G210" s="9" t="s">
-        <v>38</v>
+        <v>330</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
-        <v>396</v>
+        <v>277</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C211" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F211" s="10" t="s">
-        <v>218</v>
+        <v>37</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
-        <v>216</v>
+        <v>478</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C212" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>217</v>
+        <v>479</v>
       </c>
       <c r="E212" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F212" s="10" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F212" s="10">
+        <v>20123</v>
       </c>
       <c r="G212" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
-        <v>160</v>
+        <v>396</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="C213" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D213" s="9" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="F213" s="10" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="G213" s="9" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
-        <v>434</v>
+        <v>216</v>
       </c>
       <c r="B214" s="9" t="s">
         <v>9</v>
@@ -7055,54 +7061,100 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="C215" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D215" s="9" t="s">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="F215" s="10" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B216" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C216" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D216" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E216" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F216" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G216" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A217" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B217" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C217" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D217" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E217" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F217" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G217" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A218" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B216" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C216" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D216" s="9" t="s">
+      <c r="B218" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C218" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D218" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E216" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F216" s="10" t="s">
+      <c r="E218" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F218" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G216" s="9" t="s">
+      <c r="G218" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G146" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G216">
-      <sortCondition ref="A1:A146"/>
+  <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
+    <sortState ref="A2:G218">
+      <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
   <sortState ref="A2:G107">
@@ -7114,11 +7166,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7355,27 +7408,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7400,9 +7443,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{B5CF236B-803A-4DF5-A97A-DA942647C97A}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{C6C492CB-1D35-4570-989C-0A9A57CD9305}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="564">
   <si>
     <t>Nome account</t>
   </si>
@@ -1700,6 +1700,21 @@
   </si>
   <si>
     <t>DS ITALIA 44 SRL</t>
+  </si>
+  <si>
+    <t>CHIRON ENERGY SPV 10 SRL</t>
+  </si>
+  <si>
+    <t>SICILY MON P1 DEV SRL</t>
+  </si>
+  <si>
+    <t>PIAZZA WALTHER VON DER VOGELWEIDE 22</t>
+  </si>
+  <si>
+    <t>VERBUND GREEN POWER ITALIA SRL</t>
+  </si>
+  <si>
+    <t>VIA DELL'UNIONE 1</t>
   </si>
 </sst>
 </file>
@@ -2124,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G218"/>
+  <dimension ref="A1:G221"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -3151,53 +3166,53 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>499</v>
+        <v>559</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C45" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>500</v>
+        <v>542</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F45" s="5">
-        <v>10143</v>
+        <v>20121</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>389</v>
+        <v>499</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C46" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F46" s="5">
-        <v>20123</v>
+        <v>10143</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>437</v>
+        <v>389</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>34</v>
@@ -3220,7 +3235,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>397</v>
+        <v>437</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>34</v>
@@ -3243,7 +3258,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>269</v>
+        <v>397</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>34</v>
@@ -3257,8 +3272,8 @@
       <c r="E49" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>61</v>
+      <c r="F49" s="5">
+        <v>20123</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>38</v>
@@ -3266,7 +3281,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>34</v>
@@ -3275,13 +3290,13 @@
         <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>38</v>
@@ -3289,7 +3304,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>409</v>
+        <v>137</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>34</v>
@@ -3303,8 +3318,8 @@
       <c r="E51" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F51" s="5">
-        <v>20121</v>
+      <c r="F51" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>38</v>
@@ -3312,191 +3327,191 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>138</v>
+        <v>409</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>142</v>
+        <v>36</v>
+      </c>
+      <c r="F52" s="5">
+        <v>20121</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>444</v>
+        <v>125</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F54" s="5">
-        <v>20158</v>
+        <v>19</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>225</v>
+        <v>444</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F55" s="5">
+        <v>20158</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>544</v>
+        <v>84</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>545</v>
+        <v>86</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>180</v>
+        <v>87</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>487</v>
+        <v>544</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>488</v>
+        <v>9</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>489</v>
+        <v>545</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="F58" s="5">
-        <v>26015</v>
+        <v>10</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>558</v>
+        <v>487</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>9</v>
+        <v>488</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>335</v>
+        <v>489</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>218</v>
+        <v>490</v>
+      </c>
+      <c r="F59" s="5">
+        <v>26015</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>334</v>
+        <v>558</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>9</v>
@@ -3510,7 +3525,7 @@
       <c r="E60" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="F60" s="8" t="s">
         <v>218</v>
       </c>
       <c r="G60" s="4" t="s">
@@ -3519,122 +3534,122 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="F61" s="5">
-        <v>56025</v>
+        <v>10</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>9</v>
+        <v>296</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>273</v>
+        <v>302</v>
+      </c>
+      <c r="F62" s="5">
+        <v>56025</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>375</v>
+        <v>271</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>376</v>
+        <v>272</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F63" s="5">
-        <v>20121</v>
+        <v>10</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>280</v>
+        <v>375</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>303</v>
+        <v>376</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>304</v>
+        <v>36</v>
       </c>
       <c r="F64" s="5">
-        <v>24060</v>
+        <v>20121</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>481</v>
+        <v>280</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="F65" s="5">
-        <v>20121</v>
+        <v>24060</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>175</v>
+        <v>481</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>34</v>
@@ -3643,21 +3658,21 @@
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F66" s="5" t="s">
-        <v>158</v>
+      <c r="F66" s="5">
+        <v>20121</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>34</v>
@@ -3680,7 +3695,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>253</v>
+        <v>156</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>34</v>
@@ -3689,21 +3704,21 @@
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>439</v>
+        <v>253</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>34</v>
@@ -3712,228 +3727,228 @@
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>440</v>
+        <v>230</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="5">
-        <v>20122</v>
+      <c r="F69" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>245</v>
+        <v>439</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>247</v>
+        <v>440</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>249</v>
+        <v>36</v>
+      </c>
+      <c r="F70" s="5">
+        <v>20122</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>83</v>
+        <v>250</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>362</v>
+        <v>251</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>364</v>
+        <v>252</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="F72" s="5">
-        <v>76123</v>
+        <v>81</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>425</v>
+        <v>362</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>132</v>
+        <v>364</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="F73" s="5">
-        <v>39100</v>
+        <v>76123</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>551</v>
+        <v>425</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>552</v>
+        <v>28</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>553</v>
+        <v>132</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>555</v>
+        <v>30</v>
+      </c>
+      <c r="F74" s="5">
+        <v>39100</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>391</v>
+        <v>551</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>40</v>
+        <v>552</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>392</v>
+        <v>553</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F75" s="5">
-        <v>70043</v>
+        <v>554</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>555</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>219</v>
+        <v>391</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>220</v>
+        <v>392</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="F76" s="5">
+        <v>70043</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>34</v>
@@ -3942,13 +3957,13 @@
         <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>38</v>
@@ -3956,7 +3971,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>34</v>
@@ -3979,7 +3994,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>34</v>
@@ -4002,191 +4017,191 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>371</v>
+        <v>130</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>372</v>
+        <v>34</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>373</v>
+        <v>122</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="F82" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>201</v>
+        <v>371</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>34</v>
+        <v>372</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>189</v>
+        <v>373</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>190</v>
+        <v>374</v>
+      </c>
+      <c r="F83" s="5">
+        <v>61121</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>506</v>
+        <v>201</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="C84" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>508</v>
+        <v>189</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="F84" s="5">
-        <v>35010</v>
+        <v>36</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>505</v>
+        <v>159</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>281</v>
+        <v>506</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C85" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>305</v>
+        <v>508</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>36</v>
+        <v>507</v>
       </c>
       <c r="F85" s="5">
-        <v>20123</v>
+        <v>35010</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>351</v>
+        <v>281</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>353</v>
+        <v>305</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>354</v>
+        <v>36</v>
       </c>
       <c r="F86" s="5">
-        <v>15033</v>
+        <v>20123</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>535</v>
+        <v>351</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>117</v>
+        <v>352</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>536</v>
+        <v>353</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>119</v>
+        <v>354</v>
       </c>
       <c r="F87" s="5">
-        <v>65127</v>
+        <v>15033</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>59</v>
+        <v>535</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>60</v>
+        <v>536</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>61</v>
+        <v>119</v>
+      </c>
+      <c r="F88" s="5">
+        <v>65127</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F89" s="5">
-        <v>10153</v>
+        <v>36</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>430</v>
+        <v>336</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>79</v>
@@ -4209,53 +4224,53 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>282</v>
+        <v>430</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="F91" s="5">
-        <v>183</v>
+        <v>10153</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>211</v>
+        <v>306</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>58</v>
+        <v>10</v>
+      </c>
+      <c r="F92" s="5">
+        <v>183</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>549</v>
+        <v>210</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>34</v>
@@ -4264,21 +4279,21 @@
         <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>550</v>
+        <v>211</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F93" s="5">
-        <v>20154</v>
+      <c r="F93" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>275</v>
+        <v>549</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>34</v>
@@ -4287,13 +4302,13 @@
         <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>276</v>
+        <v>550</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F94" s="5" t="s">
-        <v>158</v>
+      <c r="F94" s="5">
+        <v>20154</v>
       </c>
       <c r="G94" s="4" t="s">
         <v>159</v>
@@ -4301,30 +4316,30 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>128</v>
+        <v>275</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>28</v>
@@ -4347,145 +4362,145 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>414</v>
+        <v>242</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>415</v>
+        <v>129</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>274</v>
+        <v>414</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>29</v>
+        <v>415</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>241</v>
+        <v>31</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>537</v>
+        <v>238</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>538</v>
+        <v>146</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>539</v>
+        <v>239</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="F100" s="5">
-        <v>34133</v>
+        <v>240</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>514</v>
+        <v>150</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>435</v>
+        <v>537</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>28</v>
+        <v>538</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>129</v>
+        <v>539</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>30</v>
+        <v>540</v>
       </c>
       <c r="F101" s="5">
-        <v>39100</v>
+        <v>34133</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>32</v>
+        <v>514</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>206</v>
+        <v>435</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>61</v>
+        <v>30</v>
+      </c>
+      <c r="F102" s="5">
+        <v>39100</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>366</v>
+        <v>206</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>34</v>
@@ -4499,8 +4514,8 @@
       <c r="E103" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F103" s="5">
-        <v>20123</v>
+      <c r="F103" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>38</v>
@@ -4508,7 +4523,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>101</v>
+        <v>366</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>34</v>
@@ -4522,8 +4537,8 @@
       <c r="E104" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F104" s="5" t="s">
-        <v>61</v>
+      <c r="F104" s="5">
+        <v>20123</v>
       </c>
       <c r="G104" s="4" t="s">
         <v>38</v>
@@ -4531,237 +4546,237 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>493</v>
+        <v>101</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>494</v>
+        <v>60</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F106" s="5">
-        <v>80121</v>
+        <v>10</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>406</v>
+        <v>519</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>264</v>
+        <v>69</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>408</v>
+        <v>71</v>
       </c>
       <c r="F107" s="5">
-        <v>38121</v>
+        <v>80121</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>268</v>
+        <v>73</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>36</v>
+        <v>408</v>
       </c>
       <c r="F108" s="5">
-        <v>20123</v>
+        <v>38121</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F109" s="5">
-        <v>90139</v>
+        <v>20123</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>195</v>
+        <v>361</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F110" s="5">
-        <v>20123</v>
+        <v>90139</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>455</v>
+        <v>345</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>456</v>
+        <v>195</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F111" s="8" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F111" s="5">
+        <v>20123</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>283</v>
+        <v>455</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>309</v>
+        <v>456</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="F112" s="5">
-        <v>12037</v>
+        <v>10</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>13</v>
+        <v>283</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>14</v>
+        <v>309</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>15</v>
+        <v>310</v>
+      </c>
+      <c r="F113" s="5">
+        <v>12037</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>11</v>
+        <v>307</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>28</v>
@@ -4784,58 +4799,58 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>498</v>
+        <v>27</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
@@ -4844,8 +4859,8 @@
       <c r="E118" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F118" s="5">
-        <v>39100</v>
+      <c r="F118" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G118" s="4" t="s">
         <v>32</v>
@@ -4853,191 +4868,191 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>233</v>
+        <v>498</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C119" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F119" s="5" t="s">
-        <v>218</v>
+        <v>30</v>
+      </c>
+      <c r="F119" s="5">
+        <v>39100</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>188</v>
+        <v>233</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>483</v>
+        <v>188</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>484</v>
+        <v>34</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>485</v>
+        <v>189</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="F121" s="5">
-        <v>66020</v>
+        <v>36</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>411</v>
+        <v>483</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>341</v>
+        <v>484</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>412</v>
+        <v>485</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>413</v>
+        <v>486</v>
       </c>
       <c r="F122" s="5">
-        <v>37137</v>
+        <v>66020</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>343</v>
+        <v>77</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>460</v>
+        <v>411</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>9</v>
+        <v>341</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>461</v>
+        <v>412</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F123" s="8" t="s">
-        <v>218</v>
+        <v>413</v>
+      </c>
+      <c r="F123" s="5">
+        <v>37137</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>11</v>
+        <v>343</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>295</v>
+        <v>460</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>297</v>
+        <v>461</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="F124" s="5">
-        <v>56010</v>
+        <v>10</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="F125" s="5">
-        <v>40060</v>
+        <v>56010</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>26</v>
+        <v>299</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>384</v>
+        <v>311</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>385</v>
+        <v>312</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>36</v>
+        <v>313</v>
       </c>
       <c r="F126" s="5">
-        <v>20121</v>
+        <v>40060</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>34</v>
@@ -5051,8 +5066,8 @@
       <c r="E127" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F127" s="5" t="s">
-        <v>58</v>
+      <c r="F127" s="5">
+        <v>20121</v>
       </c>
       <c r="G127" s="4" t="s">
         <v>38</v>
@@ -5060,99 +5075,99 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>213</v>
+        <v>386</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>179</v>
+        <v>385</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>180</v>
+        <v>58</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>68</v>
+        <v>213</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>284</v>
+        <v>68</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>314</v>
+        <v>69</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>315</v>
+        <v>70</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="F130" s="5">
-        <v>57021</v>
+        <v>71</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>299</v>
+        <v>73</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>184</v>
+        <v>284</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>180</v>
+        <v>316</v>
+      </c>
+      <c r="F131" s="5">
+        <v>57021</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>462</v>
+        <v>184</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>9</v>
@@ -5166,7 +5181,7 @@
       <c r="E132" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F132" s="8" t="s">
+      <c r="F132" s="5" t="s">
         <v>180</v>
       </c>
       <c r="G132" s="4" t="s">
@@ -5175,122 +5190,122 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>89</v>
+        <v>462</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F133" s="5" t="s">
-        <v>93</v>
+        <v>10</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>346</v>
+        <v>89</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>347</v>
+        <v>91</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F134" s="5">
-        <v>70124</v>
+        <v>92</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>189</v>
+        <v>347</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>36</v>
+        <v>348</v>
       </c>
       <c r="F135" s="5">
-        <v>20158</v>
+        <v>70124</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>358</v>
+        <v>189</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>359</v>
+        <v>36</v>
       </c>
       <c r="F136" s="5">
-        <v>12084</v>
+        <v>20158</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>307</v>
+        <v>159</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>194</v>
+        <v>357</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>195</v>
+        <v>358</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>61</v>
+        <v>359</v>
+      </c>
+      <c r="F137" s="5">
+        <v>12084</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>34</v>
@@ -5299,13 +5314,13 @@
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="G138" s="4" t="s">
         <v>38</v>
@@ -5313,122 +5328,122 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>457</v>
+        <v>227</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>458</v>
+        <v>228</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F139" s="8" t="s">
-        <v>459</v>
+        <v>36</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>108</v>
+        <v>457</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>110</v>
+        <v>458</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>112</v>
+        <v>10</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>459</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>431</v>
+        <v>108</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>308</v>
+        <v>109</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>432</v>
+        <v>110</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F141" s="5">
-        <v>12100</v>
+        <v>111</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>307</v>
+        <v>113</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>395</v>
+        <v>431</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>22</v>
+        <v>308</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>23</v>
+        <v>432</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>24</v>
+        <v>433</v>
       </c>
       <c r="F142" s="5">
-        <v>40127</v>
+        <v>12100</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>26</v>
+        <v>307</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>355</v>
+        <v>395</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>356</v>
+        <v>23</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F143" s="5">
-        <v>20121</v>
+        <v>40127</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>556</v>
+        <v>355</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>34</v>
@@ -5437,21 +5452,21 @@
         <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>525</v>
+        <v>356</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F144" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>34</v>
@@ -5474,7 +5489,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>34</v>
@@ -5497,30 +5512,30 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F147" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>232</v>
+        <v>515</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>28</v>
@@ -5534,8 +5549,8 @@
       <c r="E148" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F148" s="5" t="s">
-        <v>31</v>
+      <c r="F148" s="5">
+        <v>39100</v>
       </c>
       <c r="G148" s="4" t="s">
         <v>32</v>
@@ -5543,30 +5558,30 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>34</v>
@@ -5575,13 +5590,13 @@
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G150" s="4" t="s">
         <v>38</v>
@@ -5589,7 +5604,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>441</v>
+        <v>56</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>34</v>
@@ -5598,113 +5613,113 @@
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>442</v>
+        <v>57</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="F151" s="5">
-        <v>20038</v>
+        <v>36</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>236</v>
+        <v>442</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>81</v>
+        <v>443</v>
       </c>
       <c r="F152" s="5">
-        <v>10121</v>
+        <v>20038</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>95</v>
+        <v>426</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F153" s="5" t="s">
-        <v>99</v>
+        <v>81</v>
+      </c>
+      <c r="F153" s="5">
+        <v>10121</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>377</v>
+        <v>95</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>378</v>
+        <v>96</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>379</v>
+        <v>97</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="F154" s="5">
-        <v>64020</v>
+        <v>98</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>34</v>
+        <v>378</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>211</v>
+        <v>379</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>36</v>
+        <v>380</v>
       </c>
       <c r="F155" s="5">
-        <v>20121</v>
+        <v>64020</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>133</v>
+        <v>410</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>34</v>
@@ -5713,21 +5728,21 @@
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="E156" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F156" s="5" t="s">
-        <v>135</v>
+      <c r="F156" s="5">
+        <v>20121</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>34</v>
@@ -5736,67 +5751,67 @@
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>258</v>
+        <v>134</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>340</v>
+        <v>257</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>342</v>
+        <v>258</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="F158" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>343</v>
+        <v>38</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>166</v>
+        <v>340</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>167</v>
+        <v>342</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>168</v>
+        <v>528</v>
+      </c>
+      <c r="F159" s="5">
+        <v>37045</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>159</v>
+        <v>343</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>529</v>
+        <v>166</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>34</v>
@@ -5810,8 +5825,8 @@
       <c r="E160" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F160" s="5">
-        <v>20126</v>
+      <c r="F160" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G160" s="4" t="s">
         <v>159</v>
@@ -5819,7 +5834,7 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>471</v>
+        <v>529</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>34</v>
@@ -5828,21 +5843,21 @@
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E161" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F161" s="5">
-        <v>20135</v>
+        <v>20126</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>405</v>
+        <v>471</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>34</v>
@@ -5865,53 +5880,53 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>204</v>
+        <v>405</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F163" s="5">
+        <v>20135</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>453</v>
+        <v>204</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>454</v>
+        <v>205</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F164" s="5">
-        <v>20144</v>
+        <v>186</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>38</v>
+        <v>319</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>223</v>
+        <v>453</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>34</v>
@@ -5920,389 +5935,389 @@
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>224</v>
+        <v>454</v>
       </c>
       <c r="E165" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F165" s="5" t="s">
-        <v>135</v>
+      <c r="F165" s="5">
+        <v>20144</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>285</v>
+        <v>223</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>317</v>
+        <v>224</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F166" s="5">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>323</v>
+        <v>318</v>
+      </c>
+      <c r="F167" s="5">
+        <v>40026</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>533</v>
+        <v>286</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>29</v>
+        <v>320</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F168" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>367</v>
+        <v>533</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>368</v>
+        <v>29</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F169" s="5">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>321</v>
+        <v>368</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>322</v>
+        <v>36</v>
       </c>
       <c r="F170" s="5">
-        <v>12020</v>
+        <v>20123</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>39</v>
+        <v>287</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>41</v>
+        <v>321</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>43</v>
+        <v>322</v>
+      </c>
+      <c r="F171" s="5">
+        <v>12020</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>421</v>
+        <v>39</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>422</v>
+        <v>40</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>423</v>
+        <v>41</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="F172" s="5">
-        <v>28053</v>
+        <v>42</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>136</v>
+        <v>44</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>172</v>
+        <v>421</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>34</v>
+        <v>422</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>169</v>
+        <v>423</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>171</v>
+        <v>424</v>
+      </c>
+      <c r="F173" s="5">
+        <v>28053</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>24</v>
+        <v>170</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>207</v>
+        <v>560</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>208</v>
+        <v>561</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>209</v>
+        <v>30</v>
+      </c>
+      <c r="F175" s="5">
+        <v>39100</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>534</v>
+        <v>207</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F177" s="5">
-        <v>20121</v>
+        <v>71</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>445</v>
+        <v>244</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>447</v>
+        <v>177</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="F178" s="5">
-        <v>53048</v>
+        <v>36</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>449</v>
+        <v>38</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>509</v>
+        <v>34</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>517</v>
+        <v>177</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>518</v>
+        <v>36</v>
       </c>
       <c r="F179" s="5">
-        <v>35011</v>
+        <v>20121</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>505</v>
+        <v>38</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>243</v>
+        <v>445</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>34</v>
+        <v>446</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>177</v>
+        <v>447</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>58</v>
+        <v>448</v>
+      </c>
+      <c r="F180" s="5">
+        <v>53048</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>38</v>
+        <v>449</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>131</v>
+        <v>516</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>28</v>
+        <v>509</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>132</v>
+        <v>517</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F181" s="5" t="s">
-        <v>31</v>
+        <v>518</v>
+      </c>
+      <c r="F181" s="5">
+        <v>35011</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>32</v>
+        <v>505</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>531</v>
+        <v>243</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>34</v>
@@ -6311,13 +6326,13 @@
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>532</v>
+        <v>177</v>
       </c>
       <c r="E182" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F182" s="5">
-        <v>20121</v>
+      <c r="F182" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G182" s="4" t="s">
         <v>38</v>
@@ -6325,30 +6340,30 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>381</v>
+        <v>531</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>34</v>
@@ -6357,13 +6372,13 @@
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>382</v>
+        <v>532</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>383</v>
+        <v>36</v>
       </c>
       <c r="F184" s="5">
-        <v>20089</v>
+        <v>20121</v>
       </c>
       <c r="G184" s="4" t="s">
         <v>38</v>
@@ -6371,99 +6386,99 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>476</v>
+        <v>23</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F185" s="8" t="s">
-        <v>477</v>
+        <v>24</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>212</v>
+        <v>381</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>202</v>
+        <v>382</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>203</v>
+        <v>383</v>
+      </c>
+      <c r="F186" s="5">
+        <v>20089</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>214</v>
+        <v>475</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>215</v>
+        <v>476</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F187" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>438</v>
+        <v>212</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F188" s="5">
-        <v>20124</v>
+        <v>24</v>
+      </c>
+      <c r="F188" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B189" s="9" t="s">
         <v>34</v>
@@ -6472,21 +6487,21 @@
         <v>8</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F189" s="10" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>256</v>
+        <v>438</v>
       </c>
       <c r="B190" s="9" t="s">
         <v>34</v>
@@ -6495,21 +6510,21 @@
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E190" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F190" s="10" t="s">
-        <v>231</v>
+      <c r="F190" s="10">
+        <v>20124</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>472</v>
+        <v>229</v>
       </c>
       <c r="B191" s="9" t="s">
         <v>34</v>
@@ -6518,21 +6533,21 @@
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F191" s="10">
-        <v>20129</v>
+      <c r="F191" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>463</v>
+        <v>256</v>
       </c>
       <c r="B192" s="9" t="s">
         <v>34</v>
@@ -6541,21 +6556,21 @@
         <v>8</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E192" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F192" s="10">
-        <v>20129</v>
+      <c r="F192" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B193" s="9" t="s">
         <v>34</v>
@@ -6578,7 +6593,7 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="B194" s="9" t="s">
         <v>34</v>
@@ -6601,7 +6616,7 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>176</v>
+        <v>473</v>
       </c>
       <c r="B195" s="9" t="s">
         <v>34</v>
@@ -6610,59 +6625,59 @@
         <v>8</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F195" s="10" t="s">
-        <v>58</v>
+      <c r="F195" s="10">
+        <v>20129</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>331</v>
+        <v>474</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C196" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>332</v>
+        <v>464</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F196" s="10">
-        <v>40026</v>
+        <v>20129</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>288</v>
+        <v>176</v>
       </c>
       <c r="B197" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>324</v>
+        <v>177</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F197" s="10">
-        <v>20124</v>
+      <c r="F197" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G197" s="9" t="s">
         <v>38</v>
@@ -6670,145 +6685,145 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>450</v>
+        <v>331</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="C198" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>451</v>
+        <v>332</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>452</v>
+        <v>318</v>
       </c>
       <c r="F198" s="10">
-        <v>12011</v>
+        <v>40026</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>307</v>
+        <v>26</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>151</v>
+        <v>288</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="C199" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>153</v>
+        <v>324</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F199" s="10" t="s">
-        <v>155</v>
+        <v>36</v>
+      </c>
+      <c r="F199" s="10">
+        <v>20124</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>419</v>
+        <v>450</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C200" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>36</v>
+        <v>452</v>
       </c>
       <c r="F200" s="10">
-        <v>20123</v>
+        <v>12011</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>491</v>
+        <v>151</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="C201" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>492</v>
+        <v>153</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F201" s="10">
-        <v>90141</v>
+        <v>154</v>
+      </c>
+      <c r="F201" s="10" t="s">
+        <v>155</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>480</v>
+        <v>419</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C202" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F202" s="12" t="s">
-        <v>390</v>
+        <v>36</v>
+      </c>
+      <c r="F202" s="10">
+        <v>20123</v>
       </c>
       <c r="G202" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A203" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="B203" s="3" t="s">
-        <v>9</v>
+      <c r="A203" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="B203" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="C203" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D203" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E203" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F203" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="G203" s="3" t="s">
-        <v>11</v>
+      <c r="D203" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="E203" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F203" s="10">
+        <v>90141</v>
+      </c>
+      <c r="G203" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>387</v>
+        <v>480</v>
       </c>
       <c r="B204" s="9" t="s">
         <v>9</v>
@@ -6822,7 +6837,7 @@
       <c r="E204" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F204" s="10" t="s">
+      <c r="F204" s="12" t="s">
         <v>390</v>
       </c>
       <c r="G204" s="9" t="s">
@@ -6830,261 +6845,261 @@
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A205" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="B205" s="9" t="s">
-        <v>264</v>
+      <c r="A205" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C205" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D205" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="E205" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="F205" s="10">
-        <v>38055</v>
-      </c>
-      <c r="G205" s="9" t="s">
-        <v>268</v>
+      <c r="D205" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F205" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="C206" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="E206" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="F206" s="10">
-        <v>25010</v>
+        <v>10</v>
+      </c>
+      <c r="F206" s="10" t="s">
+        <v>390</v>
       </c>
       <c r="G206" s="9" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
-        <v>393</v>
+        <v>465</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C207" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>394</v>
+        <v>466</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>36</v>
+        <v>467</v>
       </c>
       <c r="F207" s="10">
-        <v>20123</v>
+        <v>38055</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C208" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="E208" s="9" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="F208" s="10">
-        <v>71016</v>
+        <v>25010</v>
       </c>
       <c r="G208" s="9" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
-        <v>16</v>
+        <v>393</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C209" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>18</v>
+        <v>394</v>
       </c>
       <c r="E209" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F209" s="10" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F209" s="10">
+        <v>20123</v>
       </c>
       <c r="G209" s="9" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
-        <v>325</v>
+        <v>416</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="C210" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D210" s="9" t="s">
-        <v>327</v>
+        <v>417</v>
       </c>
       <c r="E210" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="F210" s="10" t="s">
-        <v>329</v>
+        <v>418</v>
+      </c>
+      <c r="F210" s="10">
+        <v>71016</v>
       </c>
       <c r="G210" s="9" t="s">
-        <v>330</v>
+        <v>44</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C211" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F211" s="10" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
-        <v>478</v>
+        <v>325</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="C212" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>479</v>
+        <v>327</v>
       </c>
       <c r="E212" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F212" s="10">
-        <v>20123</v>
+        <v>328</v>
+      </c>
+      <c r="F212" s="10" t="s">
+        <v>329</v>
       </c>
       <c r="G212" s="9" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A213" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F213" s="7">
+        <v>20122</v>
+      </c>
+      <c r="G213" s="3" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A213" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="B213" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C213" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D213" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="E213" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F213" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="G213" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
-        <v>216</v>
+        <v>277</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C214" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D214" s="9" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="E214" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F214" s="10" t="s">
-        <v>218</v>
+        <v>37</v>
       </c>
       <c r="G214" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
-        <v>160</v>
+        <v>478</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>161</v>
+        <v>34</v>
       </c>
       <c r="C215" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D215" s="9" t="s">
-        <v>162</v>
+        <v>479</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F215" s="10" t="s">
-        <v>164</v>
+        <v>36</v>
+      </c>
+      <c r="F215" s="10">
+        <v>20123</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
-        <v>434</v>
+        <v>396</v>
       </c>
       <c r="B216" s="9" t="s">
         <v>9</v>
@@ -7107,7 +7122,7 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
-        <v>255</v>
+        <v>216</v>
       </c>
       <c r="B217" s="9" t="s">
         <v>9</v>
@@ -7130,30 +7145,99 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B218" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C218" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D218" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E218" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F218" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G218" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A219" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B219" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C219" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D219" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E219" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F219" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G219" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A220" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B220" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C220" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D220" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E220" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F220" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G220" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A221" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B218" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C218" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D218" s="9" t="s">
+      <c r="B221" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C221" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D221" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E218" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F218" s="10" t="s">
+      <c r="E221" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F221" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G218" s="9" t="s">
+      <c r="G221" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G218">
+    <sortState ref="A2:G221">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -7166,12 +7250,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7408,17 +7491,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7443,18 +7536,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{C6C492CB-1D35-4570-989C-0A9A57CD9305}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{C0564ACE-C930-474F-ABDF-C54E170C4732}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="566">
   <si>
     <t>Nome account</t>
   </si>
@@ -1715,6 +1715,12 @@
   </si>
   <si>
     <t>VIA DELL'UNIONE 1</t>
+  </si>
+  <si>
+    <t>LARGO ARTURO TOSCANINI 1</t>
+  </si>
+  <si>
+    <t>FERRARA SOLAR SRL</t>
   </si>
 </sst>
 </file>
@@ -2139,7 +2145,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G221"/>
+  <dimension ref="A1:G222"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -4132,99 +4138,99 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>351</v>
+        <v>565</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>353</v>
+        <v>564</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>354</v>
+        <v>36</v>
       </c>
       <c r="F87" s="5">
-        <v>15033</v>
+        <v>20122</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>535</v>
+        <v>351</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>117</v>
+        <v>352</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>536</v>
+        <v>353</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>119</v>
+        <v>354</v>
       </c>
       <c r="F88" s="5">
-        <v>65127</v>
+        <v>15033</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>59</v>
+        <v>535</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>60</v>
+        <v>536</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>61</v>
+        <v>119</v>
+      </c>
+      <c r="F89" s="5">
+        <v>65127</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F90" s="5">
-        <v>10153</v>
+        <v>36</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>430</v>
+        <v>336</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>79</v>
@@ -4247,53 +4253,53 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>282</v>
+        <v>430</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="F92" s="5">
-        <v>183</v>
+        <v>10153</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>211</v>
+        <v>306</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>58</v>
+        <v>10</v>
+      </c>
+      <c r="F93" s="5">
+        <v>183</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>549</v>
+        <v>210</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>34</v>
@@ -4302,21 +4308,21 @@
         <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>550</v>
+        <v>211</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F94" s="5">
-        <v>20154</v>
+      <c r="F94" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>275</v>
+        <v>549</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>34</v>
@@ -4325,13 +4331,13 @@
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>276</v>
+        <v>550</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F95" s="5" t="s">
-        <v>158</v>
+      <c r="F95" s="5">
+        <v>20154</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>159</v>
@@ -4339,30 +4345,30 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>128</v>
+        <v>275</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>28</v>
@@ -4385,145 +4391,145 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>414</v>
+        <v>242</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>415</v>
+        <v>129</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>274</v>
+        <v>414</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>29</v>
+        <v>415</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>241</v>
+        <v>31</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>537</v>
+        <v>238</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>538</v>
+        <v>146</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>539</v>
+        <v>239</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="F101" s="5">
-        <v>34133</v>
+        <v>240</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>514</v>
+        <v>150</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>435</v>
+        <v>537</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>28</v>
+        <v>538</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>129</v>
+        <v>539</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>30</v>
+        <v>540</v>
       </c>
       <c r="F102" s="5">
-        <v>39100</v>
+        <v>34133</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>32</v>
+        <v>514</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>206</v>
+        <v>435</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>61</v>
+        <v>30</v>
+      </c>
+      <c r="F103" s="5">
+        <v>39100</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>366</v>
+        <v>206</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>34</v>
@@ -4537,8 +4543,8 @@
       <c r="E104" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F104" s="5">
-        <v>20123</v>
+      <c r="F104" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G104" s="4" t="s">
         <v>38</v>
@@ -4546,7 +4552,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>101</v>
+        <v>366</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>34</v>
@@ -4560,8 +4566,8 @@
       <c r="E105" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F105" s="5" t="s">
-        <v>61</v>
+      <c r="F105" s="5">
+        <v>20123</v>
       </c>
       <c r="G105" s="4" t="s">
         <v>38</v>
@@ -4569,237 +4575,237 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>493</v>
+        <v>101</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>494</v>
+        <v>60</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F106" s="8" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F107" s="5">
-        <v>80121</v>
+        <v>10</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>406</v>
+        <v>519</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>264</v>
+        <v>69</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>408</v>
+        <v>71</v>
       </c>
       <c r="F108" s="5">
-        <v>38121</v>
+        <v>80121</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>268</v>
+        <v>73</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>36</v>
+        <v>408</v>
       </c>
       <c r="F109" s="5">
-        <v>20123</v>
+        <v>38121</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F110" s="5">
-        <v>90139</v>
+        <v>20123</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>195</v>
+        <v>361</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F111" s="5">
-        <v>20123</v>
+        <v>90139</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>455</v>
+        <v>345</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>456</v>
+        <v>195</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F112" s="8" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F112" s="5">
+        <v>20123</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>283</v>
+        <v>455</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>309</v>
+        <v>456</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="F113" s="5">
-        <v>12037</v>
+        <v>10</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>13</v>
+        <v>283</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>14</v>
+        <v>309</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>15</v>
+        <v>310</v>
+      </c>
+      <c r="F114" s="5">
+        <v>12037</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>11</v>
+        <v>307</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>28</v>
@@ -4822,58 +4828,58 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>498</v>
+        <v>27</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C119" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
@@ -4882,8 +4888,8 @@
       <c r="E119" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F119" s="5">
-        <v>39100</v>
+      <c r="F119" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G119" s="4" t="s">
         <v>32</v>
@@ -4891,191 +4897,191 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>233</v>
+        <v>498</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C120" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F120" s="5" t="s">
-        <v>218</v>
+        <v>30</v>
+      </c>
+      <c r="F120" s="5">
+        <v>39100</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>188</v>
+        <v>233</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>483</v>
+        <v>188</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>484</v>
+        <v>34</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>485</v>
+        <v>189</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="F122" s="5">
-        <v>66020</v>
+        <v>36</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>411</v>
+        <v>483</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>341</v>
+        <v>484</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>412</v>
+        <v>485</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>413</v>
+        <v>486</v>
       </c>
       <c r="F123" s="5">
-        <v>37137</v>
+        <v>66020</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>343</v>
+        <v>77</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>460</v>
+        <v>411</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>9</v>
+        <v>341</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>461</v>
+        <v>412</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F124" s="8" t="s">
-        <v>218</v>
+        <v>413</v>
+      </c>
+      <c r="F124" s="5">
+        <v>37137</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>11</v>
+        <v>343</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>295</v>
+        <v>460</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>297</v>
+        <v>461</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="F125" s="5">
-        <v>56010</v>
+        <v>10</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="F126" s="5">
-        <v>40060</v>
+        <v>56010</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>26</v>
+        <v>299</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>384</v>
+        <v>311</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>385</v>
+        <v>312</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>36</v>
+        <v>313</v>
       </c>
       <c r="F127" s="5">
-        <v>20121</v>
+        <v>40060</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>34</v>
@@ -5089,8 +5095,8 @@
       <c r="E128" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F128" s="5" t="s">
-        <v>58</v>
+      <c r="F128" s="5">
+        <v>20121</v>
       </c>
       <c r="G128" s="4" t="s">
         <v>38</v>
@@ -5098,99 +5104,99 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>213</v>
+        <v>386</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>179</v>
+        <v>385</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>180</v>
+        <v>58</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>68</v>
+        <v>213</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>284</v>
+        <v>68</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>314</v>
+        <v>69</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>315</v>
+        <v>70</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="F131" s="5">
-        <v>57021</v>
+        <v>71</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>299</v>
+        <v>73</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>184</v>
+        <v>284</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F132" s="5" t="s">
-        <v>180</v>
+        <v>316</v>
+      </c>
+      <c r="F132" s="5">
+        <v>57021</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>462</v>
+        <v>184</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>9</v>
@@ -5204,7 +5210,7 @@
       <c r="E133" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F133" s="8" t="s">
+      <c r="F133" s="5" t="s">
         <v>180</v>
       </c>
       <c r="G133" s="4" t="s">
@@ -5213,122 +5219,122 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>89</v>
+        <v>462</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F134" s="5" t="s">
-        <v>93</v>
+        <v>10</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>346</v>
+        <v>89</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>347</v>
+        <v>91</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F135" s="5">
-        <v>70124</v>
+        <v>92</v>
+      </c>
+      <c r="F135" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>189</v>
+        <v>347</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>36</v>
+        <v>348</v>
       </c>
       <c r="F136" s="5">
-        <v>20158</v>
+        <v>70124</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>358</v>
+        <v>189</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>359</v>
+        <v>36</v>
       </c>
       <c r="F137" s="5">
-        <v>12084</v>
+        <v>20158</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>307</v>
+        <v>159</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>194</v>
+        <v>357</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>195</v>
+        <v>358</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>61</v>
+        <v>359</v>
+      </c>
+      <c r="F138" s="5">
+        <v>12084</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>34</v>
@@ -5337,13 +5343,13 @@
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="G139" s="4" t="s">
         <v>38</v>
@@ -5351,122 +5357,122 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>457</v>
+        <v>227</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>458</v>
+        <v>228</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F140" s="8" t="s">
-        <v>459</v>
+        <v>36</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>108</v>
+        <v>457</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>110</v>
+        <v>458</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>112</v>
+        <v>10</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>459</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>431</v>
+        <v>108</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>308</v>
+        <v>109</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>432</v>
+        <v>110</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F142" s="5">
-        <v>12100</v>
+        <v>111</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>307</v>
+        <v>113</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>395</v>
+        <v>431</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>22</v>
+        <v>308</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>23</v>
+        <v>432</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>24</v>
+        <v>433</v>
       </c>
       <c r="F143" s="5">
-        <v>40127</v>
+        <v>12100</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>26</v>
+        <v>307</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>355</v>
+        <v>395</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>356</v>
+        <v>23</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F144" s="5">
-        <v>20121</v>
+        <v>40127</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>556</v>
+        <v>355</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>34</v>
@@ -5475,21 +5481,21 @@
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>525</v>
+        <v>356</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F145" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>34</v>
@@ -5512,7 +5518,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>34</v>
@@ -5535,30 +5541,30 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F148" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>232</v>
+        <v>515</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>28</v>
@@ -5572,8 +5578,8 @@
       <c r="E149" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F149" s="5" t="s">
-        <v>31</v>
+      <c r="F149" s="5">
+        <v>39100</v>
       </c>
       <c r="G149" s="4" t="s">
         <v>32</v>
@@ -5581,30 +5587,30 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>34</v>
@@ -5613,13 +5619,13 @@
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G151" s="4" t="s">
         <v>38</v>
@@ -5627,7 +5633,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>441</v>
+        <v>56</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>34</v>
@@ -5636,113 +5642,113 @@
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>442</v>
+        <v>57</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="F152" s="5">
-        <v>20038</v>
+        <v>36</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>236</v>
+        <v>442</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>81</v>
+        <v>443</v>
       </c>
       <c r="F153" s="5">
-        <v>10121</v>
+        <v>20038</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>95</v>
+        <v>426</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>99</v>
+        <v>81</v>
+      </c>
+      <c r="F154" s="5">
+        <v>10121</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>377</v>
+        <v>95</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>378</v>
+        <v>96</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>379</v>
+        <v>97</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="F155" s="5">
-        <v>64020</v>
+        <v>98</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>34</v>
+        <v>378</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>211</v>
+        <v>379</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>36</v>
+        <v>380</v>
       </c>
       <c r="F156" s="5">
-        <v>20121</v>
+        <v>64020</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>133</v>
+        <v>410</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>34</v>
@@ -5751,21 +5757,21 @@
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F157" s="5" t="s">
-        <v>135</v>
+      <c r="F157" s="5">
+        <v>20121</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>34</v>
@@ -5774,67 +5780,67 @@
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>258</v>
+        <v>134</v>
       </c>
       <c r="E158" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>340</v>
+        <v>257</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>342</v>
+        <v>258</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="F159" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>343</v>
+        <v>38</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>166</v>
+        <v>340</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>167</v>
+        <v>342</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F160" s="5" t="s">
-        <v>168</v>
+        <v>528</v>
+      </c>
+      <c r="F160" s="5">
+        <v>37045</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>159</v>
+        <v>343</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>529</v>
+        <v>166</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>34</v>
@@ -5848,8 +5854,8 @@
       <c r="E161" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F161" s="5">
-        <v>20126</v>
+      <c r="F161" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>159</v>
@@ -5857,7 +5863,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>471</v>
+        <v>529</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>34</v>
@@ -5866,21 +5872,21 @@
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F162" s="5">
-        <v>20135</v>
+        <v>20126</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>405</v>
+        <v>471</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>34</v>
@@ -5903,53 +5909,53 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>204</v>
+        <v>405</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F164" s="5">
+        <v>20135</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>453</v>
+        <v>204</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>454</v>
+        <v>205</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F165" s="5">
-        <v>20144</v>
+        <v>186</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>38</v>
+        <v>319</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>223</v>
+        <v>453</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>34</v>
@@ -5958,297 +5964,297 @@
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>224</v>
+        <v>454</v>
       </c>
       <c r="E166" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F166" s="5" t="s">
-        <v>135</v>
+      <c r="F166" s="5">
+        <v>20144</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>285</v>
+        <v>223</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>317</v>
+        <v>224</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F167" s="5">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>323</v>
+        <v>318</v>
+      </c>
+      <c r="F168" s="5">
+        <v>40026</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>533</v>
+        <v>286</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>29</v>
+        <v>320</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F169" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>367</v>
+        <v>533</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>368</v>
+        <v>29</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F170" s="5">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>321</v>
+        <v>368</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>322</v>
+        <v>36</v>
       </c>
       <c r="F171" s="5">
-        <v>12020</v>
+        <v>20123</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>39</v>
+        <v>287</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>41</v>
+        <v>321</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>43</v>
+        <v>322</v>
+      </c>
+      <c r="F172" s="5">
+        <v>12020</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>421</v>
+        <v>39</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>422</v>
+        <v>40</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>423</v>
+        <v>41</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="F173" s="5">
-        <v>28053</v>
+        <v>42</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>136</v>
+        <v>44</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>172</v>
+        <v>421</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>34</v>
+        <v>422</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>169</v>
+        <v>423</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>171</v>
+        <v>424</v>
+      </c>
+      <c r="F174" s="5">
+        <v>28053</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>560</v>
+        <v>172</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>561</v>
+        <v>169</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F175" s="5">
-        <v>39100</v>
+        <v>170</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>198</v>
+        <v>560</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>199</v>
+        <v>561</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>200</v>
+        <v>30</v>
+      </c>
+      <c r="F176" s="5">
+        <v>39100</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>534</v>
+        <v>244</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>34</v>
@@ -6262,8 +6268,8 @@
       <c r="E179" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F179" s="5">
-        <v>20121</v>
+      <c r="F179" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>38</v>
@@ -6271,237 +6277,237 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>445</v>
+        <v>534</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>447</v>
+        <v>177</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>448</v>
+        <v>36</v>
       </c>
       <c r="F180" s="5">
-        <v>53048</v>
+        <v>20121</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>449</v>
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>516</v>
+        <v>445</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>509</v>
+        <v>446</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>517</v>
+        <v>447</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>518</v>
+        <v>448</v>
       </c>
       <c r="F181" s="5">
-        <v>35011</v>
+        <v>53048</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>505</v>
+        <v>449</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>243</v>
+        <v>516</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>34</v>
+        <v>509</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>177</v>
+        <v>517</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>58</v>
+        <v>518</v>
+      </c>
+      <c r="F182" s="5">
+        <v>35011</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>131</v>
+        <v>243</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>531</v>
+        <v>131</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>532</v>
+        <v>132</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F184" s="5">
-        <v>20121</v>
+        <v>30</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>21</v>
+        <v>531</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>23</v>
+        <v>532</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F185" s="5" t="s">
-        <v>25</v>
+        <v>36</v>
+      </c>
+      <c r="F185" s="5">
+        <v>20121</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>381</v>
+        <v>21</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>382</v>
+        <v>23</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="F186" s="5">
-        <v>20089</v>
+        <v>24</v>
+      </c>
+      <c r="F186" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>475</v>
+        <v>381</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>476</v>
+        <v>382</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F187" s="8" t="s">
-        <v>477</v>
+        <v>383</v>
+      </c>
+      <c r="F187" s="5">
+        <v>20089</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>212</v>
+        <v>475</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>202</v>
+        <v>476</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F188" s="5" t="s">
-        <v>203</v>
+        <v>10</v>
+      </c>
+      <c r="F188" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F189" s="10" t="s">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>438</v>
+        <v>214</v>
       </c>
       <c r="B190" s="9" t="s">
         <v>34</v>
@@ -6515,8 +6521,8 @@
       <c r="E190" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F190" s="10">
-        <v>20124</v>
+      <c r="F190" s="10" t="s">
+        <v>158</v>
       </c>
       <c r="G190" s="9" t="s">
         <v>159</v>
@@ -6524,7 +6530,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>229</v>
+        <v>438</v>
       </c>
       <c r="B191" s="9" t="s">
         <v>34</v>
@@ -6533,21 +6539,21 @@
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F191" s="10" t="s">
-        <v>231</v>
+      <c r="F191" s="10">
+        <v>20124</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B192" s="9" t="s">
         <v>34</v>
@@ -6570,7 +6576,7 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>472</v>
+        <v>256</v>
       </c>
       <c r="B193" s="9" t="s">
         <v>34</v>
@@ -6579,21 +6585,21 @@
         <v>8</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F193" s="10">
-        <v>20129</v>
+      <c r="F193" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="B194" s="9" t="s">
         <v>34</v>
@@ -6616,7 +6622,7 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="B195" s="9" t="s">
         <v>34</v>
@@ -6639,7 +6645,7 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B196" s="9" t="s">
         <v>34</v>
@@ -6662,7 +6668,7 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>176</v>
+        <v>474</v>
       </c>
       <c r="B197" s="9" t="s">
         <v>34</v>
@@ -6671,412 +6677,412 @@
         <v>8</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F197" s="10" t="s">
-        <v>58</v>
+      <c r="F197" s="10">
+        <v>20129</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>331</v>
+        <v>176</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C198" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>332</v>
+        <v>177</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="F198" s="10">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F198" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C199" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="F199" s="10">
-        <v>20124</v>
+        <v>40026</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>450</v>
+        <v>288</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C200" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>451</v>
+        <v>324</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>452</v>
+        <v>36</v>
       </c>
       <c r="F200" s="10">
-        <v>12011</v>
+        <v>20124</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>151</v>
+        <v>450</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>152</v>
+        <v>308</v>
       </c>
       <c r="C201" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>153</v>
+        <v>451</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F201" s="10" t="s">
-        <v>155</v>
+        <v>452</v>
+      </c>
+      <c r="F201" s="10">
+        <v>12011</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>419</v>
+        <v>151</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="C202" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>420</v>
+        <v>153</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F202" s="10">
-        <v>20123</v>
+        <v>154</v>
+      </c>
+      <c r="F202" s="10" t="s">
+        <v>155</v>
       </c>
       <c r="G202" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>491</v>
+        <v>419</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C203" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>492</v>
+        <v>420</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F203" s="10">
-        <v>90141</v>
+        <v>20123</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="B204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C204" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D204" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="E204" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F204" s="10">
+        <v>90141</v>
+      </c>
+      <c r="G204" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A205" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="B204" s="9" t="s">
+      <c r="B205" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C204" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D204" s="9" t="s">
+      <c r="C205" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D205" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="E204" s="9" t="s">
+      <c r="E205" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F204" s="12" t="s">
+      <c r="F205" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="G204" s="9" t="s">
+      <c r="G205" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A205" s="3" t="s">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A206" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="B205" s="3" t="s">
+      <c r="B206" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C205" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D205" s="3" t="s">
+      <c r="C206" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D206" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="E205" s="3" t="s">
+      <c r="E206" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F205" s="11" t="s">
+      <c r="F206" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="G205" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A206" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="B206" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C206" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D206" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="E206" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F206" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="G206" s="9" t="s">
+      <c r="G206" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
-        <v>465</v>
+        <v>387</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C207" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>466</v>
+        <v>388</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="F207" s="10">
-        <v>38055</v>
+        <v>10</v>
+      </c>
+      <c r="F207" s="10" t="s">
+        <v>390</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
-        <v>427</v>
+        <v>465</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>103</v>
+        <v>264</v>
       </c>
       <c r="C208" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>428</v>
+        <v>466</v>
       </c>
       <c r="E208" s="9" t="s">
-        <v>429</v>
+        <v>467</v>
       </c>
       <c r="F208" s="10">
-        <v>25010</v>
+        <v>38055</v>
       </c>
       <c r="G208" s="9" t="s">
-        <v>107</v>
+        <v>268</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
-        <v>393</v>
+        <v>427</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="C209" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="E209" s="9" t="s">
-        <v>36</v>
+        <v>429</v>
       </c>
       <c r="F209" s="10">
-        <v>20123</v>
+        <v>25010</v>
       </c>
       <c r="G209" s="9" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C210" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D210" s="9" t="s">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="E210" s="9" t="s">
-        <v>418</v>
+        <v>36</v>
       </c>
       <c r="F210" s="10">
-        <v>71016</v>
+        <v>20123</v>
       </c>
       <c r="G210" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
-        <v>16</v>
+        <v>416</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="C211" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>18</v>
+        <v>417</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F211" s="10" t="s">
-        <v>20</v>
+        <v>418</v>
+      </c>
+      <c r="F211" s="10">
+        <v>71016</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B212" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C212" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D212" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E212" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F212" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G212" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A213" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="B212" s="9" t="s">
+      <c r="B213" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="C212" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D212" s="9" t="s">
+      <c r="C213" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D213" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="E212" s="9" t="s">
+      <c r="E213" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="F212" s="10" t="s">
+      <c r="F213" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="G212" s="9" t="s">
+      <c r="G213" s="9" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A213" s="3" t="s">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A214" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="B213" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C213" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D213" s="3" t="s">
+      <c r="B214" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D214" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="E213" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F213" s="7">
+      <c r="E214" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F214" s="7">
         <v>20122</v>
       </c>
-      <c r="G213" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A214" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="B214" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C214" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D214" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="E214" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F214" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="G214" s="9" t="s">
+      <c r="G214" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
-        <v>478</v>
+        <v>277</v>
       </c>
       <c r="B215" s="9" t="s">
         <v>34</v>
@@ -7085,13 +7091,13 @@
         <v>8</v>
       </c>
       <c r="D215" s="9" t="s">
-        <v>479</v>
+        <v>278</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F215" s="10">
-        <v>20123</v>
+      <c r="F215" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="G215" s="9" t="s">
         <v>38</v>
@@ -7099,30 +7105,30 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
-        <v>396</v>
+        <v>478</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C216" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D216" s="9" t="s">
-        <v>217</v>
+        <v>479</v>
       </c>
       <c r="E216" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F216" s="10" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F216" s="10">
+        <v>20123</v>
       </c>
       <c r="G216" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
-        <v>216</v>
+        <v>396</v>
       </c>
       <c r="B217" s="9" t="s">
         <v>9</v>
@@ -7145,53 +7151,53 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="9" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="C218" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D218" s="9" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="E218" s="9" t="s">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="F218" s="10" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="G218" s="9" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
-        <v>434</v>
+        <v>160</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="C219" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="E219" s="9" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="F219" s="10" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
-        <v>255</v>
+        <v>434</v>
       </c>
       <c r="B220" s="9" t="s">
         <v>9</v>
@@ -7214,30 +7220,53 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B221" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C221" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D221" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E221" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F221" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G221" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A222" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B221" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C221" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D221" s="9" t="s">
+      <c r="B222" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C222" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D222" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E221" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F221" s="10" t="s">
+      <c r="E222" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F222" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G221" s="9" t="s">
+      <c r="G222" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G221">
+    <sortState ref="A2:G222">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -7250,11 +7279,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7491,27 +7521,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7536,9 +7556,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{C0564ACE-C930-474F-ABDF-C54E170C4732}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{046FA0C2-5211-438A-ABAC-0F2ADBFCF7E1}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="586">
   <si>
     <t>Nome account</t>
   </si>
@@ -1721,6 +1721,66 @@
   </si>
   <si>
     <t>FERRARA SOLAR SRL</t>
+  </si>
+  <si>
+    <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+  </si>
+  <si>
+    <t>PIAZZA DELL'INDIPENDENZA 23 B/C</t>
+  </si>
+  <si>
+    <t>00185</t>
+  </si>
+  <si>
+    <t>WOOD SOLARE ITALIA SRL</t>
+  </si>
+  <si>
+    <t>VIA SEBASTIANO CABOTO 15</t>
+  </si>
+  <si>
+    <t>CORSICO</t>
+  </si>
+  <si>
+    <t>TOLALP ENERGY SRL</t>
+  </si>
+  <si>
+    <t>FOREARTH SRL</t>
+  </si>
+  <si>
+    <t>PIAZZA SIGMUND FREUD 1</t>
+  </si>
+  <si>
+    <t>LUMINORA SERRAVALLE SRL</t>
+  </si>
+  <si>
+    <t>JUWI DEVELOPMENT 15 SRL</t>
+  </si>
+  <si>
+    <t>VIA GIOVANNI BATTISTA PIRELLI 30</t>
+  </si>
+  <si>
+    <t>SMARTENERGYIT2104 SRL</t>
+  </si>
+  <si>
+    <t>PIAZZA CONTE CAMILLO BENSO DI CAVOUR 1</t>
+  </si>
+  <si>
+    <t>RAI WAY SPA</t>
+  </si>
+  <si>
+    <t>VIALE CASTRENSE 9</t>
+  </si>
+  <si>
+    <t>00182</t>
+  </si>
+  <si>
+    <t>DOLOMITI ENERGIA MERCATO SPA</t>
+  </si>
+  <si>
+    <t>VIA FERSINA 23</t>
+  </si>
+  <si>
+    <t>CEDRO SRL</t>
   </si>
 </sst>
 </file>
@@ -2145,7 +2205,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G222"/>
+  <dimension ref="A1:G233"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -3103,30 +3163,30 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>215</v>
+        <v>118</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="F42" s="5">
-        <v>20124</v>
+        <v>65125</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>34</v>
@@ -3135,21 +3195,21 @@
         <v>8</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>542</v>
+        <v>215</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F43" s="5">
-        <v>20121</v>
+        <v>20124</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>34</v>
@@ -3172,7 +3232,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>34</v>
@@ -3195,53 +3255,53 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>499</v>
+        <v>559</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C46" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>500</v>
+        <v>542</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F46" s="5">
-        <v>10143</v>
+        <v>20121</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>389</v>
+        <v>499</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C47" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F47" s="5">
-        <v>20123</v>
+        <v>10143</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>437</v>
+        <v>389</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>34</v>
@@ -3264,7 +3324,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>397</v>
+        <v>437</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>34</v>
@@ -3287,7 +3347,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>269</v>
+        <v>397</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>34</v>
@@ -3301,8 +3361,8 @@
       <c r="E50" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>61</v>
+      <c r="F50" s="5">
+        <v>20123</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>38</v>
@@ -3310,7 +3370,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>34</v>
@@ -3319,13 +3379,13 @@
         <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>38</v>
@@ -3333,7 +3393,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>409</v>
+        <v>137</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>34</v>
@@ -3347,8 +3407,8 @@
       <c r="E52" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F52" s="5">
-        <v>20121</v>
+      <c r="F52" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>38</v>
@@ -3356,168 +3416,168 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>138</v>
+        <v>409</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>142</v>
+        <v>36</v>
+      </c>
+      <c r="F53" s="5">
+        <v>20121</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>444</v>
+        <v>125</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F55" s="5">
-        <v>20158</v>
+        <v>19</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>225</v>
+        <v>444</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F56" s="5">
+        <v>20158</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>544</v>
+        <v>84</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>545</v>
+        <v>86</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>180</v>
+        <v>87</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>487</v>
+        <v>583</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>488</v>
+        <v>264</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>489</v>
+        <v>584</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>490</v>
+        <v>408</v>
       </c>
       <c r="F59" s="5">
-        <v>26015</v>
+        <v>38123</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>107</v>
+        <v>268</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>9</v>
@@ -3526,67 +3586,67 @@
         <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>335</v>
+        <v>545</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>334</v>
+        <v>487</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>9</v>
+        <v>488</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>335</v>
+        <v>489</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>218</v>
+        <v>490</v>
+      </c>
+      <c r="F61" s="5">
+        <v>26015</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>300</v>
+        <v>558</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="F62" s="5">
-        <v>56025</v>
+        <v>10</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>271</v>
+        <v>334</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>9</v>
@@ -3595,13 +3655,13 @@
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>272</v>
+        <v>335</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>273</v>
+        <v>218</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>11</v>
@@ -3609,53 +3669,53 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>376</v>
+        <v>301</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>36</v>
+        <v>302</v>
       </c>
       <c r="F64" s="5">
-        <v>20121</v>
+        <v>56025</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="F65" s="5">
-        <v>24060</v>
+        <v>10</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>150</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>481</v>
+        <v>375</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>34</v>
@@ -3664,7 +3724,7 @@
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>258</v>
+        <v>376</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>36</v>
@@ -3678,30 +3738,30 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>157</v>
+        <v>303</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>158</v>
+        <v>304</v>
+      </c>
+      <c r="F67" s="5">
+        <v>24060</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>156</v>
+        <v>481</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>34</v>
@@ -3710,21 +3770,21 @@
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F68" s="5" t="s">
-        <v>158</v>
+      <c r="F68" s="5">
+        <v>20121</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>253</v>
+        <v>175</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>34</v>
@@ -3733,21 +3793,21 @@
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>439</v>
+        <v>156</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>34</v>
@@ -3756,205 +3816,205 @@
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>440</v>
+        <v>157</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F70" s="5">
-        <v>20122</v>
+      <c r="F70" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>248</v>
+        <v>36</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>250</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>251</v>
+        <v>439</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>252</v>
+        <v>440</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>237</v>
+        <v>36</v>
+      </c>
+      <c r="F72" s="5">
+        <v>20122</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>362</v>
+        <v>245</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>363</v>
+        <v>246</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>364</v>
+        <v>247</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="F73" s="5">
-        <v>76123</v>
+        <v>248</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>44</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>425</v>
+        <v>251</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>132</v>
+        <v>252</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F74" s="5">
-        <v>39100</v>
+        <v>81</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>551</v>
+        <v>362</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>552</v>
+        <v>363</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>553</v>
+        <v>364</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>555</v>
+        <v>365</v>
+      </c>
+      <c r="F75" s="5">
+        <v>76123</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>392</v>
+        <v>132</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F76" s="5">
-        <v>70043</v>
+        <v>39100</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>219</v>
+        <v>551</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>34</v>
+        <v>552</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>220</v>
+        <v>553</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>37</v>
+        <v>554</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>555</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>50</v>
+        <v>391</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>47</v>
+        <v>392</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
+      </c>
+      <c r="F78" s="5">
+        <v>70043</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>51</v>
+        <v>219</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>34</v>
@@ -3963,13 +4023,13 @@
         <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>52</v>
+        <v>220</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>38</v>
@@ -3977,30 +4037,30 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>34</v>
@@ -4009,13 +4069,13 @@
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G81" s="4" t="s">
         <v>38</v>
@@ -4023,7 +4083,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>34</v>
@@ -4046,30 +4106,30 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>371</v>
+        <v>124</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>372</v>
+        <v>34</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>373</v>
+        <v>122</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="F83" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>201</v>
+        <v>130</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>34</v>
@@ -4078,44 +4138,44 @@
         <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>190</v>
+        <v>58</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>506</v>
+        <v>371</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="C85" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>508</v>
+        <v>373</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>507</v>
+        <v>374</v>
       </c>
       <c r="F85" s="5">
-        <v>35010</v>
+        <v>61121</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>505</v>
+        <v>165</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>281</v>
+        <v>201</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>34</v>
@@ -4124,128 +4184,128 @@
         <v>8</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>305</v>
+        <v>189</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F86" s="5">
-        <v>20123</v>
+      <c r="F86" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>565</v>
+        <v>506</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C87" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>564</v>
+        <v>508</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>36</v>
+        <v>507</v>
       </c>
       <c r="F87" s="5">
-        <v>20122</v>
+        <v>35010</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>351</v>
+        <v>281</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>353</v>
+        <v>305</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>354</v>
+        <v>36</v>
       </c>
       <c r="F88" s="5">
-        <v>15033</v>
+        <v>20123</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>535</v>
+        <v>565</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>117</v>
+        <v>34</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>536</v>
+        <v>564</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="F89" s="5">
-        <v>65127</v>
+        <v>20122</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>59</v>
+        <v>351</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>34</v>
+        <v>352</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>60</v>
+        <v>353</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>61</v>
+        <v>354</v>
+      </c>
+      <c r="F90" s="5">
+        <v>15033</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>81</v>
+        <v>354</v>
       </c>
       <c r="F91" s="5">
-        <v>10153</v>
+        <v>15033</v>
       </c>
       <c r="G91" s="4" t="s">
         <v>83</v>
@@ -4253,99 +4313,99 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>430</v>
+        <v>535</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>337</v>
+        <v>536</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="F92" s="5">
-        <v>10153</v>
+        <v>65127</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>282</v>
+        <v>59</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>306</v>
+        <v>60</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F93" s="5">
-        <v>183</v>
+        <v>36</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>210</v>
+        <v>336</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>211</v>
+        <v>337</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>58</v>
+        <v>81</v>
+      </c>
+      <c r="F94" s="5">
+        <v>10153</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>549</v>
+        <v>430</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>550</v>
+        <v>337</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F95" s="5">
-        <v>20154</v>
+        <v>10153</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>275</v>
+        <v>573</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>34</v>
@@ -4354,13 +4414,13 @@
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>276</v>
+        <v>574</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F96" s="5" t="s">
-        <v>158</v>
+      <c r="F96" s="5">
+        <v>20154</v>
       </c>
       <c r="G96" s="4" t="s">
         <v>159</v>
@@ -4368,306 +4428,306 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>128</v>
+        <v>282</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>129</v>
+        <v>306</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>31</v>
+        <v>10</v>
+      </c>
+      <c r="F97" s="5">
+        <v>183</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>32</v>
+        <v>307</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>129</v>
+        <v>211</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>414</v>
+        <v>549</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>415</v>
+        <v>550</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F99" s="5">
+        <v>20154</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>29</v>
+        <v>276</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>238</v>
+        <v>128</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>239</v>
+        <v>129</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>241</v>
+        <v>31</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>537</v>
+        <v>242</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>538</v>
+        <v>28</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>539</v>
+        <v>129</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="F102" s="5">
-        <v>34133</v>
+        <v>30</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>514</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>435</v>
+        <v>414</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>129</v>
+        <v>415</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F103" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>206</v>
+        <v>274</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>366</v>
+        <v>238</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>60</v>
+        <v>239</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F105" s="5">
-        <v>20123</v>
+        <v>240</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>101</v>
+        <v>537</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>34</v>
+        <v>538</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>60</v>
+        <v>539</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>61</v>
+        <v>540</v>
+      </c>
+      <c r="F106" s="5">
+        <v>34133</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>38</v>
+        <v>514</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>493</v>
+        <v>435</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>494</v>
+        <v>129</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F107" s="8" t="s">
-        <v>273</v>
+        <v>30</v>
+      </c>
+      <c r="F107" s="5">
+        <v>39100</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>519</v>
+        <v>206</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>520</v>
+        <v>60</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F108" s="5">
-        <v>80121</v>
+        <v>36</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>406</v>
+        <v>366</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>264</v>
+        <v>34</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>407</v>
+        <v>60</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>408</v>
+        <v>36</v>
       </c>
       <c r="F109" s="5">
-        <v>38121</v>
+        <v>20123</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>268</v>
+        <v>38</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>369</v>
+        <v>101</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>34</v>
@@ -4676,13 +4736,13 @@
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>370</v>
+        <v>60</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F110" s="5">
-        <v>20123</v>
+      <c r="F110" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G110" s="4" t="s">
         <v>38</v>
@@ -4690,229 +4750,229 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>360</v>
+        <v>493</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>361</v>
+        <v>494</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F111" s="5">
-        <v>90139</v>
+        <v>10</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>345</v>
+        <v>519</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>195</v>
+        <v>520</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F112" s="5">
-        <v>20123</v>
+        <v>80121</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>455</v>
+        <v>406</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>456</v>
+        <v>407</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113" s="8" t="s">
-        <v>180</v>
+        <v>408</v>
+      </c>
+      <c r="F113" s="5">
+        <v>38121</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>77</v>
+        <v>268</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>283</v>
+        <v>369</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>309</v>
+        <v>370</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>310</v>
+        <v>36</v>
       </c>
       <c r="F114" s="5">
-        <v>12037</v>
+        <v>20123</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>13</v>
+        <v>360</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>14</v>
+        <v>361</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F115" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
+      </c>
+      <c r="F115" s="5">
+        <v>90139</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>123</v>
+        <v>345</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F116" s="5">
+        <v>20123</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>54</v>
+        <v>455</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>55</v>
+        <v>456</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F117" s="5" t="s">
-        <v>31</v>
+        <v>10</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>74</v>
+        <v>283</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>75</v>
+        <v>309</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>76</v>
+        <v>310</v>
+      </c>
+      <c r="F118" s="5">
+        <v>12037</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>77</v>
+        <v>307</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>498</v>
+        <v>123</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C120" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E120" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F120" s="5">
-        <v>39100</v>
+      <c r="F120" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G120" s="4" t="s">
         <v>32</v>
@@ -4920,99 +4980,99 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>233</v>
+        <v>54</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>234</v>
+        <v>55</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>218</v>
+        <v>31</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>188</v>
+        <v>74</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>190</v>
+        <v>76</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>483</v>
+        <v>27</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>484</v>
+        <v>28</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>485</v>
+        <v>29</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="F123" s="5">
-        <v>66020</v>
+        <v>30</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>411</v>
+        <v>498</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="C124" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>412</v>
+        <v>29</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>413</v>
+        <v>30</v>
       </c>
       <c r="F124" s="5">
-        <v>37137</v>
+        <v>39100</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>343</v>
+        <v>32</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>460</v>
+        <v>233</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>9</v>
@@ -5021,12 +5081,12 @@
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>461</v>
+        <v>234</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F125" s="8" t="s">
+      <c r="F125" s="5" t="s">
         <v>218</v>
       </c>
       <c r="G125" s="4" t="s">
@@ -5035,53 +5095,53 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>295</v>
+        <v>188</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>296</v>
+        <v>34</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>297</v>
+        <v>189</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="F126" s="5">
-        <v>56010</v>
+        <v>36</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>299</v>
+        <v>159</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>311</v>
+        <v>483</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>22</v>
+        <v>484</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>312</v>
+        <v>485</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>313</v>
+        <v>486</v>
       </c>
       <c r="F127" s="5">
-        <v>40060</v>
+        <v>66020</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>384</v>
+        <v>576</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>34</v>
@@ -5090,44 +5150,44 @@
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>385</v>
+        <v>577</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F128" s="5">
-        <v>20121</v>
+        <v>20124</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>58</v>
+        <v>413</v>
+      </c>
+      <c r="F129" s="5">
+        <v>37137</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>38</v>
+        <v>343</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>213</v>
+        <v>460</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>9</v>
@@ -5136,343 +5196,343 @@
         <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>179</v>
+        <v>461</v>
       </c>
       <c r="E130" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F130" s="5" t="s">
-        <v>180</v>
+      <c r="F130" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>68</v>
+        <v>295</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>69</v>
+        <v>296</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>70</v>
+        <v>297</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>72</v>
+        <v>298</v>
+      </c>
+      <c r="F131" s="5">
+        <v>56010</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>73</v>
+        <v>299</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>314</v>
+        <v>22</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F132" s="5">
-        <v>57021</v>
+        <v>40060</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>299</v>
+        <v>26</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>184</v>
+        <v>384</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>179</v>
+        <v>385</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F133" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F133" s="5">
+        <v>20121</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>462</v>
+        <v>386</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>179</v>
+        <v>385</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F134" s="8" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>89</v>
+        <v>213</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>346</v>
+        <v>575</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>347</v>
+        <v>192</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>348</v>
+        <v>36</v>
       </c>
       <c r="F136" s="5">
-        <v>70124</v>
+        <v>20124</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>44</v>
+        <v>159</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>333</v>
+        <v>68</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>189</v>
+        <v>70</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F137" s="5">
-        <v>20158</v>
+        <v>71</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>159</v>
+        <v>73</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>357</v>
+        <v>284</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>358</v>
+        <v>315</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>359</v>
+        <v>316</v>
       </c>
       <c r="F138" s="5">
-        <v>12084</v>
+        <v>57021</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>61</v>
+        <v>180</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>227</v>
+        <v>462</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>228</v>
+        <v>179</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>37</v>
+        <v>10</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>457</v>
+        <v>89</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>458</v>
+        <v>91</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F141" s="8" t="s">
-        <v>459</v>
+        <v>92</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>108</v>
+        <v>346</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>110</v>
+        <v>347</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>112</v>
+        <v>348</v>
+      </c>
+      <c r="F142" s="5">
+        <v>70124</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>113</v>
+        <v>44</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>431</v>
+        <v>333</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>432</v>
+        <v>189</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>433</v>
+        <v>36</v>
       </c>
       <c r="F143" s="5">
-        <v>12100</v>
+        <v>20158</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>307</v>
+        <v>159</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>395</v>
+        <v>357</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>22</v>
+        <v>308</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>23</v>
+        <v>358</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>24</v>
+        <v>359</v>
       </c>
       <c r="F144" s="5">
-        <v>40127</v>
+        <v>12084</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>26</v>
+        <v>307</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>355</v>
+        <v>194</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>34</v>
@@ -5481,13 +5541,13 @@
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>356</v>
+        <v>195</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F145" s="5">
-        <v>20121</v>
+      <c r="F145" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G145" s="4" t="s">
         <v>38</v>
@@ -5495,7 +5555,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>556</v>
+        <v>227</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>34</v>
@@ -5504,113 +5564,113 @@
         <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>525</v>
+        <v>228</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F146" s="5">
-        <v>20154</v>
+      <c r="F146" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>526</v>
+        <v>457</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>525</v>
+        <v>458</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F147" s="5">
-        <v>20154</v>
+        <v>10</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>459</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>524</v>
+        <v>108</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>525</v>
+        <v>110</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F148" s="5">
-        <v>20154</v>
+        <v>111</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>515</v>
+        <v>431</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>28</v>
+        <v>308</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>29</v>
+        <v>432</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>30</v>
+        <v>433</v>
       </c>
       <c r="F149" s="5">
-        <v>39100</v>
+        <v>12100</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>32</v>
+        <v>307</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>232</v>
+        <v>395</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
+      </c>
+      <c r="F150" s="5">
+        <v>40127</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>143</v>
+        <v>355</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>34</v>
@@ -5619,13 +5679,13 @@
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>144</v>
+        <v>356</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F151" s="5" t="s">
-        <v>37</v>
+      <c r="F151" s="5">
+        <v>20121</v>
       </c>
       <c r="G151" s="4" t="s">
         <v>38</v>
@@ -5633,7 +5693,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>56</v>
+        <v>556</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>34</v>
@@ -5642,21 +5702,21 @@
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>57</v>
+        <v>525</v>
       </c>
       <c r="E152" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F152" s="5" t="s">
-        <v>58</v>
+      <c r="F152" s="5">
+        <v>20154</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>441</v>
+        <v>526</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>34</v>
@@ -5665,90 +5725,90 @@
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>442</v>
+        <v>525</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>443</v>
+        <v>36</v>
       </c>
       <c r="F153" s="5">
-        <v>20038</v>
+        <v>20154</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>426</v>
+        <v>524</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>236</v>
+        <v>525</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F154" s="5">
-        <v>10121</v>
+        <v>20154</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>83</v>
+        <v>159</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>95</v>
+        <v>515</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F155" s="5" t="s">
-        <v>99</v>
+        <v>30</v>
+      </c>
+      <c r="F155" s="5">
+        <v>39100</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>377</v>
+        <v>232</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>378</v>
+        <v>28</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>379</v>
+        <v>29</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="F156" s="5">
-        <v>64020</v>
+        <v>30</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>410</v>
+        <v>143</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>34</v>
@@ -5757,13 +5817,13 @@
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>211</v>
+        <v>144</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F157" s="5">
-        <v>20121</v>
+      <c r="F157" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G157" s="4" t="s">
         <v>38</v>
@@ -5771,7 +5831,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>34</v>
@@ -5780,21 +5840,21 @@
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="E158" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>257</v>
+        <v>441</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>34</v>
@@ -5803,113 +5863,113 @@
         <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>258</v>
+        <v>442</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>58</v>
+        <v>443</v>
+      </c>
+      <c r="F159" s="5">
+        <v>20038</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>340</v>
+        <v>426</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>341</v>
+        <v>79</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>342</v>
+        <v>236</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>528</v>
+        <v>81</v>
       </c>
       <c r="F160" s="5">
-        <v>37045</v>
+        <v>10121</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>343</v>
+        <v>83</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>167</v>
+        <v>97</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>168</v>
+        <v>99</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>159</v>
+        <v>100</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>529</v>
+        <v>377</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>34</v>
+        <v>378</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>167</v>
+        <v>379</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>36</v>
+        <v>380</v>
       </c>
       <c r="F162" s="5">
-        <v>20126</v>
+        <v>64020</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>471</v>
+        <v>580</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>260</v>
+        <v>581</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F163" s="5">
-        <v>20135</v>
+        <v>10</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>582</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>262</v>
+        <v>11</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>34</v>
@@ -5918,44 +5978,44 @@
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>260</v>
+        <v>211</v>
       </c>
       <c r="E164" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F164" s="5">
-        <v>20135</v>
+        <v>20121</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>262</v>
+        <v>38</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>205</v>
+        <v>134</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>186</v>
+        <v>36</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>319</v>
+        <v>136</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>453</v>
+        <v>257</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>34</v>
@@ -5964,13 +6024,13 @@
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>454</v>
+        <v>258</v>
       </c>
       <c r="E166" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F166" s="5">
-        <v>20144</v>
+      <c r="F166" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G166" s="4" t="s">
         <v>38</v>
@@ -5978,99 +6038,99 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>223</v>
+        <v>340</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>224</v>
+        <v>342</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>135</v>
+        <v>528</v>
+      </c>
+      <c r="F167" s="5">
+        <v>37045</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>136</v>
+        <v>343</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>285</v>
+        <v>166</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>317</v>
+        <v>167</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F168" s="5">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>286</v>
+        <v>529</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>320</v>
+        <v>167</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>323</v>
+        <v>36</v>
+      </c>
+      <c r="F169" s="5">
+        <v>20126</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>533</v>
+        <v>471</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>29</v>
+        <v>260</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F170" s="5">
-        <v>39100</v>
+        <v>20135</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>32</v>
+        <v>262</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>367</v>
+        <v>405</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>34</v>
@@ -6079,82 +6139,82 @@
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>368</v>
+        <v>260</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F171" s="5">
-        <v>20123</v>
+        <v>20135</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>287</v>
+        <v>204</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>308</v>
+        <v>185</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>321</v>
+        <v>205</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F172" s="5">
-        <v>12020</v>
+        <v>186</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>39</v>
+        <v>453</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>41</v>
+        <v>454</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
+      </c>
+      <c r="F173" s="5">
+        <v>20144</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>421</v>
+        <v>223</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>422</v>
+        <v>34</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>423</v>
+        <v>224</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="F174" s="5">
-        <v>28053</v>
+        <v>36</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G174" s="4" t="s">
         <v>136</v>
@@ -6162,283 +6222,283 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>172</v>
+        <v>285</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>169</v>
+        <v>317</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>171</v>
+        <v>318</v>
+      </c>
+      <c r="F175" s="5">
+        <v>40026</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>560</v>
+        <v>286</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>561</v>
+        <v>320</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F176" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>198</v>
+        <v>533</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>199</v>
+        <v>29</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>200</v>
+        <v>30</v>
+      </c>
+      <c r="F177" s="5">
+        <v>39100</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>207</v>
+        <v>367</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>208</v>
+        <v>368</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>209</v>
+        <v>36</v>
+      </c>
+      <c r="F178" s="5">
+        <v>20123</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>244</v>
+        <v>287</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>177</v>
+        <v>321</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>58</v>
+        <v>322</v>
+      </c>
+      <c r="F179" s="5">
+        <v>12020</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>534</v>
+        <v>39</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>177</v>
+        <v>41</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F180" s="5">
-        <v>20121</v>
+        <v>42</v>
+      </c>
+      <c r="F180" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>447</v>
+        <v>423</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="F181" s="5">
-        <v>53048</v>
+        <v>28053</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>449</v>
+        <v>136</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>516</v>
+        <v>172</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>509</v>
+        <v>34</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>517</v>
+        <v>169</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="F182" s="5">
-        <v>35011</v>
+        <v>170</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>505</v>
+        <v>159</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>243</v>
+        <v>560</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>177</v>
+        <v>561</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>58</v>
+        <v>30</v>
+      </c>
+      <c r="F183" s="5">
+        <v>39100</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>131</v>
+        <v>198</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>132</v>
+        <v>199</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>31</v>
+        <v>200</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>531</v>
+        <v>207</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>532</v>
+        <v>208</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F185" s="5">
-        <v>20121</v>
+        <v>71</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>21</v>
+        <v>244</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>381</v>
+        <v>534</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>34</v>
@@ -6447,13 +6507,13 @@
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>382</v>
+        <v>177</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>383</v>
+        <v>36</v>
       </c>
       <c r="F187" s="5">
-        <v>20089</v>
+        <v>20121</v>
       </c>
       <c r="G187" s="4" t="s">
         <v>38</v>
@@ -6461,76 +6521,76 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>475</v>
+        <v>578</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>476</v>
+        <v>579</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F188" s="8" t="s">
-        <v>477</v>
+        <v>36</v>
+      </c>
+      <c r="F188" s="5">
+        <v>20121</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>212</v>
+        <v>445</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>22</v>
+        <v>446</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>202</v>
+        <v>447</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F189" s="10" t="s">
-        <v>203</v>
+        <v>448</v>
+      </c>
+      <c r="F189" s="10">
+        <v>53048</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>26</v>
+        <v>449</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>214</v>
+        <v>516</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>34</v>
+        <v>509</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>215</v>
+        <v>517</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F190" s="10" t="s">
-        <v>158</v>
+        <v>518</v>
+      </c>
+      <c r="F190" s="10">
+        <v>35011</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>159</v>
+        <v>505</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>438</v>
+        <v>243</v>
       </c>
       <c r="B191" s="9" t="s">
         <v>34</v>
@@ -6539,44 +6599,44 @@
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F191" s="10">
-        <v>20124</v>
+      <c r="F191" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>229</v>
+        <v>131</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>230</v>
+        <v>132</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>231</v>
+        <v>31</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>256</v>
+        <v>531</v>
       </c>
       <c r="B193" s="9" t="s">
         <v>34</v>
@@ -6585,67 +6645,67 @@
         <v>8</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>230</v>
+        <v>532</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F193" s="10" t="s">
-        <v>231</v>
+      <c r="F193" s="10">
+        <v>20121</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>472</v>
+        <v>21</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C194" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>464</v>
+        <v>23</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F194" s="10">
-        <v>20129</v>
+        <v>24</v>
+      </c>
+      <c r="F194" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>262</v>
+        <v>26</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A195" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="B195" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C195" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D195" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="E195" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F195" s="10">
-        <v>20129</v>
-      </c>
-      <c r="G195" s="9" t="s">
-        <v>262</v>
+      <c r="A195" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F195" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>473</v>
+        <v>381</v>
       </c>
       <c r="B196" s="9" t="s">
         <v>34</v>
@@ -6654,99 +6714,99 @@
         <v>8</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>464</v>
+        <v>382</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>36</v>
+        <v>383</v>
       </c>
       <c r="F196" s="10">
-        <v>20129</v>
+        <v>20089</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>262</v>
+        <v>38</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C197" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F197" s="10">
-        <v>20129</v>
+        <v>10</v>
+      </c>
+      <c r="F197" s="12" t="s">
+        <v>477</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>262</v>
+        <v>11</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>176</v>
+        <v>212</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C198" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F198" s="10" t="s">
-        <v>58</v>
+        <v>203</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>331</v>
+        <v>214</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C199" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>332</v>
+        <v>215</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="F199" s="10">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F199" s="10" t="s">
+        <v>158</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>288</v>
+        <v>438</v>
       </c>
       <c r="B200" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C200" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>324</v>
+        <v>215</v>
       </c>
       <c r="E200" s="9" t="s">
         <v>36</v>
@@ -6755,58 +6815,58 @@
         <v>20124</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>450</v>
+        <v>229</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C201" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>451</v>
+        <v>230</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="F201" s="10">
-        <v>12011</v>
+        <v>36</v>
+      </c>
+      <c r="F201" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>307</v>
+        <v>136</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>151</v>
+        <v>256</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="C202" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>153</v>
+        <v>230</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>154</v>
+        <v>36</v>
       </c>
       <c r="F202" s="10" t="s">
-        <v>155</v>
+        <v>231</v>
       </c>
       <c r="G202" s="9" t="s">
-        <v>44</v>
+        <v>136</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>419</v>
+        <v>472</v>
       </c>
       <c r="B203" s="9" t="s">
         <v>34</v>
@@ -6815,197 +6875,197 @@
         <v>8</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>420</v>
+        <v>464</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F203" s="10">
-        <v>20123</v>
+        <v>20129</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>491</v>
+        <v>463</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C204" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>492</v>
+        <v>464</v>
       </c>
       <c r="E204" s="9" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F204" s="10">
-        <v>90141</v>
+        <v>20129</v>
       </c>
       <c r="G204" s="9" t="s">
-        <v>12</v>
+        <v>262</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C205" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>388</v>
+        <v>464</v>
       </c>
       <c r="E205" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F205" s="12" t="s">
-        <v>390</v>
+        <v>36</v>
+      </c>
+      <c r="F205" s="10">
+        <v>20129</v>
       </c>
       <c r="G205" s="9" t="s">
-        <v>11</v>
+        <v>262</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A206" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>9</v>
+      <c r="A206" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="B206" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="C206" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D206" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E206" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F206" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="G206" s="3" t="s">
-        <v>11</v>
+      <c r="D206" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="E206" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F206" s="10">
+        <v>20129</v>
+      </c>
+      <c r="G206" s="9" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
-        <v>387</v>
+        <v>176</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C207" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>388</v>
+        <v>177</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F207" s="10" t="s">
-        <v>390</v>
+        <v>58</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
-        <v>465</v>
+        <v>331</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>264</v>
+        <v>22</v>
       </c>
       <c r="C208" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>466</v>
+        <v>332</v>
       </c>
       <c r="E208" s="9" t="s">
-        <v>467</v>
+        <v>318</v>
       </c>
       <c r="F208" s="10">
-        <v>38055</v>
+        <v>40026</v>
       </c>
       <c r="G208" s="9" t="s">
-        <v>268</v>
+        <v>26</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
-        <v>427</v>
+        <v>288</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="C209" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>428</v>
+        <v>324</v>
       </c>
       <c r="E209" s="9" t="s">
-        <v>429</v>
+        <v>36</v>
       </c>
       <c r="F209" s="10">
-        <v>25010</v>
+        <v>20124</v>
       </c>
       <c r="G209" s="9" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
-        <v>393</v>
+        <v>450</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C210" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D210" s="9" t="s">
-        <v>394</v>
+        <v>451</v>
       </c>
       <c r="E210" s="9" t="s">
-        <v>36</v>
+        <v>452</v>
       </c>
       <c r="F210" s="10">
-        <v>20123</v>
+        <v>12011</v>
       </c>
       <c r="G210" s="9" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
-        <v>416</v>
+        <v>151</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>85</v>
+        <v>152</v>
       </c>
       <c r="C211" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>417</v>
+        <v>153</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="F211" s="10">
-        <v>71016</v>
+        <v>154</v>
+      </c>
+      <c r="F211" s="10" t="s">
+        <v>155</v>
       </c>
       <c r="G211" s="9" t="s">
         <v>44</v>
@@ -7013,260 +7073,513 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
-        <v>16</v>
+        <v>419</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C212" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>18</v>
+        <v>420</v>
       </c>
       <c r="E212" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F212" s="10" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F212" s="10">
+        <v>20123</v>
       </c>
       <c r="G212" s="9" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
-        <v>325</v>
+        <v>491</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>326</v>
+        <v>17</v>
       </c>
       <c r="C213" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D213" s="9" t="s">
-        <v>327</v>
+        <v>492</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="F213" s="10" t="s">
-        <v>329</v>
+        <v>19</v>
+      </c>
+      <c r="F213" s="10">
+        <v>90141</v>
       </c>
       <c r="G213" s="9" t="s">
-        <v>330</v>
+        <v>12</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A214" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="B214" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C214" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D214" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="E214" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F214" s="7">
-        <v>20122</v>
-      </c>
-      <c r="G214" s="3" t="s">
-        <v>38</v>
+      <c r="A214" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="B214" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C214" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D214" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="E214" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F214" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="G214" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A215" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="B215" s="9" t="s">
-        <v>34</v>
+      <c r="A215" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C215" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D215" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="E215" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F215" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="G215" s="9" t="s">
-        <v>38</v>
+      <c r="D215" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F215" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
-        <v>478</v>
+        <v>387</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C216" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D216" s="9" t="s">
-        <v>479</v>
+        <v>388</v>
       </c>
       <c r="E216" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F216" s="10">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F216" s="10" t="s">
+        <v>390</v>
       </c>
       <c r="G216" s="9" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
-        <v>396</v>
+        <v>465</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
       <c r="C217" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D217" s="9" t="s">
-        <v>217</v>
+        <v>466</v>
       </c>
       <c r="E217" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F217" s="10" t="s">
-        <v>218</v>
+        <v>467</v>
+      </c>
+      <c r="F217" s="10">
+        <v>38055</v>
       </c>
       <c r="G217" s="9" t="s">
-        <v>11</v>
+        <v>268</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A218" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="B218" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C218" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D218" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="E218" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F218" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="G218" s="9" t="s">
-        <v>11</v>
+      <c r="A218" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F218" s="7">
+        <v>20145</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
-        <v>160</v>
+        <v>427</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="C219" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>162</v>
+        <v>428</v>
       </c>
       <c r="E219" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F219" s="10" t="s">
-        <v>164</v>
+        <v>429</v>
+      </c>
+      <c r="F219" s="10">
+        <v>25010</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
-        <v>434</v>
+        <v>393</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C220" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D220" s="9" t="s">
-        <v>217</v>
+        <v>394</v>
       </c>
       <c r="E220" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F220" s="10" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F220" s="10">
+        <v>20123</v>
       </c>
       <c r="G220" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
-        <v>255</v>
+        <v>416</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="C221" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D221" s="9" t="s">
-        <v>217</v>
+        <v>417</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F221" s="10" t="s">
-        <v>218</v>
+        <v>418</v>
+      </c>
+      <c r="F221" s="10">
+        <v>71016</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C222" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D222" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E222" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F222" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G222" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A223" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B223" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C223" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D223" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E223" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="F223" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="G223" s="9" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A224" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F224" s="7">
+        <v>20122</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A225" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="B225" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C225" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D225" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="E225" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F225" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G225" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A226" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="B226" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C226" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D226" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="E226" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F226" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G226" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A227" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="F227" s="7">
+        <v>20094</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A228" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="B228" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C228" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D228" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E228" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F228" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G228" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A229" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C229" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D229" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E229" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F229" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G229" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A230" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B230" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C230" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D230" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E230" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F230" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G230" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A231" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B231" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C231" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D231" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E231" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F231" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G231" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A232" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B232" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C232" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D232" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E232" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F232" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G232" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A233" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B222" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C222" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D222" s="9" t="s">
+      <c r="B233" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C233" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D233" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E222" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F222" s="10" t="s">
+      <c r="E233" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F233" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G222" s="9" t="s">
+      <c r="G233" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G222">
+    <sortState ref="A2:G233">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -7279,12 +7592,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7521,17 +7833,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7556,18 +7878,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{046FA0C2-5211-438A-ABAC-0F2ADBFCF7E1}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{7741F810-8AF0-4F93-810C-470C461E06E7}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="589">
   <si>
     <t>Nome account</t>
   </si>
@@ -1781,6 +1781,15 @@
   </si>
   <si>
     <t>CEDRO SRL</t>
+  </si>
+  <si>
+    <t>ACEA SOLAR SRL</t>
+  </si>
+  <si>
+    <t>PIAZZALE OSTIENSE 2</t>
+  </si>
+  <si>
+    <t>00154</t>
   </si>
 </sst>
 </file>
@@ -2205,7 +2214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G233"/>
+  <dimension ref="A1:G234"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -2312,183 +2321,183 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>501</v>
+        <v>586</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>503</v>
+        <v>587</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="F5" s="5">
-        <v>45100</v>
+        <v>10</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>588</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>505</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>402</v>
+        <v>503</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>36</v>
+        <v>504</v>
       </c>
       <c r="F6" s="5">
-        <v>20123</v>
+        <v>45100</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>181</v>
+        <v>401</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>182</v>
+        <v>402</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F7" s="5">
+        <v>20123</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>259</v>
+        <v>181</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>260</v>
+        <v>182</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>262</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>510</v>
+        <v>259</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>511</v>
+        <v>34</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>512</v>
+        <v>260</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="F9" s="5">
-        <v>33050</v>
+        <v>36</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>261</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>514</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>263</v>
+        <v>510</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>264</v>
+        <v>511</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>265</v>
+        <v>512</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>267</v>
+        <v>513</v>
+      </c>
+      <c r="F10" s="5">
+        <v>33050</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>268</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>83</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>495</v>
+        <v>235</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>496</v>
+        <v>236</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="F12" s="5">
-        <v>10098</v>
+        <v>81</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>83</v>
@@ -2496,76 +2505,76 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>45</v>
+        <v>495</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>47</v>
+        <v>496</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>49</v>
+        <v>497</v>
+      </c>
+      <c r="F13" s="5">
+        <v>10098</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>9</v>
@@ -2588,7 +2597,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>9</v>
@@ -2611,7 +2620,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>482</v>
+        <v>196</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>9</v>
@@ -2625,7 +2634,7 @@
       <c r="E18" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="5" t="s">
         <v>180</v>
       </c>
       <c r="G18" s="4" t="s">
@@ -2634,7 +2643,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>197</v>
+        <v>482</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>9</v>
@@ -2648,7 +2657,7 @@
       <c r="E19" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="8" t="s">
         <v>180</v>
       </c>
       <c r="G19" s="4" t="s">
@@ -2657,7 +2666,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>9</v>
@@ -2680,99 +2689,99 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>403</v>
+        <v>183</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>404</v>
+        <v>179</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F22" s="5">
-        <v>20124</v>
+        <v>39100</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>468</v>
+        <v>399</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>469</v>
+        <v>400</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>470</v>
+        <v>36</v>
+      </c>
+      <c r="F23" s="5">
+        <v>20124</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>305</v>
+        <v>469</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>470</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>349</v>
+        <v>436</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>34</v>
@@ -2781,13 +2790,13 @@
         <v>8</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>350</v>
+        <v>305</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F25" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>38</v>
@@ -2795,53 +2804,53 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>67</v>
+        <v>349</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>18</v>
+        <v>350</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F26" s="5">
+        <v>20122</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>398</v>
+        <v>67</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27" s="5">
-        <v>10123</v>
+        <v>19</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>78</v>
+        <v>398</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>79</v>
@@ -2855,8 +2864,8 @@
       <c r="E28" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>82</v>
+      <c r="F28" s="5">
+        <v>10123</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>83</v>
@@ -2864,76 +2873,76 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>546</v>
+        <v>78</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>511</v>
+        <v>79</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>547</v>
+        <v>80</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="F29" s="5">
-        <v>33100</v>
+        <v>81</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>514</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>279</v>
+        <v>546</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>28</v>
+        <v>511</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>289</v>
+        <v>547</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>290</v>
+        <v>548</v>
       </c>
       <c r="F30" s="5">
-        <v>39042</v>
+        <v>33100</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>32</v>
+        <v>514</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>523</v>
+        <v>279</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>339</v>
+        <v>289</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>36</v>
+        <v>290</v>
       </c>
       <c r="F31" s="5">
-        <v>20121</v>
+        <v>39042</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>338</v>
+        <v>523</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>34</v>
@@ -2956,7 +2965,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>33</v>
+        <v>338</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>34</v>
@@ -2965,13 +2974,13 @@
         <v>8</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>35</v>
+        <v>339</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F33" s="5" t="s">
-        <v>37</v>
+      <c r="F33" s="5">
+        <v>20121</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>38</v>
@@ -2979,45 +2988,45 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>221</v>
+        <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>116</v>
+        <v>221</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>118</v>
+        <v>222</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>77</v>
@@ -3025,7 +3034,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>527</v>
+        <v>116</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>117</v>
@@ -3039,8 +3048,8 @@
       <c r="E36" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F36" s="5">
-        <v>65125</v>
+      <c r="F36" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>77</v>
@@ -3048,7 +3057,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>254</v>
+        <v>527</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>117</v>
@@ -3062,8 +3071,8 @@
       <c r="E37" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F37" s="5" t="s">
-        <v>120</v>
+      <c r="F37" s="5">
+        <v>65125</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>77</v>
@@ -3071,145 +3080,145 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>62</v>
+        <v>254</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>521</v>
+        <v>145</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>522</v>
+        <v>147</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F40" s="5">
-        <v>20033</v>
+        <v>148</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>291</v>
+        <v>521</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>292</v>
+        <v>34</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>293</v>
+        <v>522</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>294</v>
+        <v>36</v>
       </c>
       <c r="F41" s="5">
-        <v>60035</v>
+        <v>20033</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>585</v>
+        <v>291</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>117</v>
+        <v>292</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>118</v>
+        <v>293</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>119</v>
+        <v>294</v>
       </c>
       <c r="F42" s="5">
-        <v>65125</v>
+        <v>60035</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>77</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>215</v>
+        <v>118</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="F43" s="5">
-        <v>20124</v>
+        <v>65125</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>34</v>
@@ -3218,21 +3227,21 @@
         <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>542</v>
+        <v>215</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F44" s="5">
-        <v>20121</v>
+        <v>20124</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>34</v>
@@ -3255,7 +3264,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>34</v>
@@ -3278,53 +3287,53 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>499</v>
+        <v>559</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C47" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>500</v>
+        <v>542</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F47" s="5">
-        <v>10143</v>
+        <v>20121</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>389</v>
+        <v>499</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C48" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F48" s="5">
-        <v>20123</v>
+        <v>10143</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>437</v>
+        <v>389</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>34</v>
@@ -3347,7 +3356,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>397</v>
+        <v>437</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>34</v>
@@ -3370,7 +3379,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>269</v>
+        <v>397</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>34</v>
@@ -3384,8 +3393,8 @@
       <c r="E51" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F51" s="5" t="s">
-        <v>61</v>
+      <c r="F51" s="5">
+        <v>20123</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>38</v>
@@ -3393,7 +3402,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>34</v>
@@ -3402,13 +3411,13 @@
         <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>38</v>
@@ -3416,7 +3425,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>409</v>
+        <v>137</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>34</v>
@@ -3430,8 +3439,8 @@
       <c r="E53" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F53" s="5">
-        <v>20121</v>
+      <c r="F53" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>38</v>
@@ -3439,214 +3448,214 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>138</v>
+        <v>409</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>142</v>
+        <v>36</v>
+      </c>
+      <c r="F54" s="5">
+        <v>20121</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>444</v>
+        <v>125</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F56" s="5">
-        <v>20158</v>
+        <v>19</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>225</v>
+        <v>444</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F57" s="5">
+        <v>20158</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>583</v>
+        <v>84</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>264</v>
+        <v>85</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>584</v>
+        <v>86</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="F59" s="5">
-        <v>38123</v>
+        <v>87</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>268</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>544</v>
+        <v>583</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>545</v>
+        <v>584</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>180</v>
+        <v>408</v>
+      </c>
+      <c r="F60" s="5">
+        <v>38123</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>77</v>
+        <v>268</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>487</v>
+        <v>544</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>488</v>
+        <v>9</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>489</v>
+        <v>545</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="F61" s="5">
-        <v>26015</v>
+        <v>10</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>558</v>
+        <v>487</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>9</v>
+        <v>488</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>335</v>
+        <v>489</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>218</v>
+        <v>490</v>
+      </c>
+      <c r="F62" s="5">
+        <v>26015</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>334</v>
+        <v>558</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>9</v>
@@ -3660,7 +3669,7 @@
       <c r="E63" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="F63" s="8" t="s">
         <v>218</v>
       </c>
       <c r="G63" s="4" t="s">
@@ -3669,122 +3678,122 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="F64" s="5">
-        <v>56025</v>
+        <v>10</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>9</v>
+        <v>296</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>273</v>
+        <v>302</v>
+      </c>
+      <c r="F65" s="5">
+        <v>56025</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>375</v>
+        <v>271</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>376</v>
+        <v>272</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F66" s="5">
-        <v>20121</v>
+        <v>10</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>280</v>
+        <v>375</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>303</v>
+        <v>376</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>304</v>
+        <v>36</v>
       </c>
       <c r="F67" s="5">
-        <v>24060</v>
+        <v>20121</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>481</v>
+        <v>280</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="F68" s="5">
-        <v>20121</v>
+        <v>24060</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>175</v>
+        <v>481</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>34</v>
@@ -3793,21 +3802,21 @@
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="5" t="s">
-        <v>158</v>
+      <c r="F69" s="5">
+        <v>20121</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>34</v>
@@ -3830,7 +3839,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>253</v>
+        <v>156</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>34</v>
@@ -3839,21 +3848,21 @@
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>439</v>
+        <v>253</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>34</v>
@@ -3862,228 +3871,228 @@
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>440</v>
+        <v>230</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F72" s="5">
-        <v>20122</v>
+      <c r="F72" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>245</v>
+        <v>439</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>247</v>
+        <v>440</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>249</v>
+        <v>36</v>
+      </c>
+      <c r="F73" s="5">
+        <v>20122</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>83</v>
+        <v>250</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>362</v>
+        <v>251</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>364</v>
+        <v>252</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="F75" s="5">
-        <v>76123</v>
+        <v>81</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>425</v>
+        <v>362</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>132</v>
+        <v>364</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="F76" s="5">
-        <v>39100</v>
+        <v>76123</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>551</v>
+        <v>425</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>552</v>
+        <v>28</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>553</v>
+        <v>132</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>555</v>
+        <v>30</v>
+      </c>
+      <c r="F77" s="5">
+        <v>39100</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>391</v>
+        <v>551</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>40</v>
+        <v>552</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>392</v>
+        <v>553</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F78" s="5">
-        <v>70043</v>
+        <v>554</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>555</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>219</v>
+        <v>391</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>220</v>
+        <v>392</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="F79" s="5">
+        <v>70043</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>34</v>
@@ -4092,13 +4101,13 @@
         <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>38</v>
@@ -4106,7 +4115,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>34</v>
@@ -4129,7 +4138,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>34</v>
@@ -4152,99 +4161,99 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>371</v>
+        <v>130</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>372</v>
+        <v>34</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>373</v>
+        <v>122</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="F85" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>201</v>
+        <v>371</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>34</v>
+        <v>372</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>189</v>
+        <v>373</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>190</v>
+        <v>374</v>
+      </c>
+      <c r="F86" s="5">
+        <v>61121</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>506</v>
+        <v>201</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="C87" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>508</v>
+        <v>189</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="F87" s="5">
-        <v>35010</v>
+        <v>36</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>505</v>
+        <v>159</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>281</v>
+        <v>506</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C88" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>305</v>
+        <v>508</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>36</v>
+        <v>507</v>
       </c>
       <c r="F88" s="5">
-        <v>20123</v>
+        <v>35010</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>565</v>
+        <v>281</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>34</v>
@@ -4253,13 +4262,13 @@
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>564</v>
+        <v>305</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F89" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>38</v>
@@ -4267,25 +4276,25 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>351</v>
+        <v>565</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>353</v>
+        <v>564</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>354</v>
+        <v>36</v>
       </c>
       <c r="F90" s="5">
-        <v>15033</v>
+        <v>20122</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
@@ -4313,76 +4322,76 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>535</v>
+        <v>351</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>117</v>
+        <v>352</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>536</v>
+        <v>353</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>119</v>
+        <v>354</v>
       </c>
       <c r="F92" s="5">
-        <v>65127</v>
+        <v>15033</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>59</v>
+        <v>535</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>60</v>
+        <v>536</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>61</v>
+        <v>119</v>
+      </c>
+      <c r="F93" s="5">
+        <v>65127</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F94" s="5">
-        <v>10153</v>
+        <v>36</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>430</v>
+        <v>336</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>79</v>
@@ -4405,76 +4414,76 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>573</v>
+        <v>430</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>574</v>
+        <v>337</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F96" s="5">
-        <v>20154</v>
+        <v>10153</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>282</v>
+        <v>573</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>306</v>
+        <v>574</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F97" s="5">
-        <v>183</v>
+        <v>20154</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>307</v>
+        <v>159</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>211</v>
+        <v>306</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>58</v>
+        <v>10</v>
+      </c>
+      <c r="F98" s="5">
+        <v>183</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>549</v>
+        <v>210</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>34</v>
@@ -4483,21 +4492,21 @@
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>550</v>
+        <v>211</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F99" s="5">
-        <v>20154</v>
+      <c r="F99" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>275</v>
+        <v>549</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>34</v>
@@ -4506,13 +4515,13 @@
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>276</v>
+        <v>550</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F100" s="5" t="s">
-        <v>158</v>
+      <c r="F100" s="5">
+        <v>20154</v>
       </c>
       <c r="G100" s="4" t="s">
         <v>159</v>
@@ -4520,30 +4529,30 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>128</v>
+        <v>275</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>28</v>
@@ -4566,145 +4575,145 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>414</v>
+        <v>242</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>415</v>
+        <v>129</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>274</v>
+        <v>414</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>29</v>
+        <v>415</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>241</v>
+        <v>31</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>537</v>
+        <v>238</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>538</v>
+        <v>146</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>539</v>
+        <v>239</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="F106" s="5">
-        <v>34133</v>
+        <v>240</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>514</v>
+        <v>150</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>435</v>
+        <v>537</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>28</v>
+        <v>538</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>129</v>
+        <v>539</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>30</v>
+        <v>540</v>
       </c>
       <c r="F107" s="5">
-        <v>39100</v>
+        <v>34133</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>32</v>
+        <v>514</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>206</v>
+        <v>435</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>61</v>
+        <v>30</v>
+      </c>
+      <c r="F108" s="5">
+        <v>39100</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>366</v>
+        <v>206</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>34</v>
@@ -4718,8 +4727,8 @@
       <c r="E109" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F109" s="5">
-        <v>20123</v>
+      <c r="F109" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G109" s="4" t="s">
         <v>38</v>
@@ -4727,7 +4736,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>101</v>
+        <v>366</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>34</v>
@@ -4741,8 +4750,8 @@
       <c r="E110" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F110" s="5" t="s">
-        <v>61</v>
+      <c r="F110" s="5">
+        <v>20123</v>
       </c>
       <c r="G110" s="4" t="s">
         <v>38</v>
@@ -4750,237 +4759,237 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>493</v>
+        <v>101</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>494</v>
+        <v>60</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F111" s="8" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F112" s="5">
-        <v>80121</v>
+        <v>10</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>406</v>
+        <v>519</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>264</v>
+        <v>69</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>408</v>
+        <v>71</v>
       </c>
       <c r="F113" s="5">
-        <v>38121</v>
+        <v>80121</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>268</v>
+        <v>73</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>36</v>
+        <v>408</v>
       </c>
       <c r="F114" s="5">
-        <v>20123</v>
+        <v>38121</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F115" s="5">
-        <v>90139</v>
+        <v>20123</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>195</v>
+        <v>361</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F116" s="5">
-        <v>20123</v>
+        <v>90139</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>455</v>
+        <v>345</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>456</v>
+        <v>195</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F117" s="8" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F117" s="5">
+        <v>20123</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>283</v>
+        <v>455</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>309</v>
+        <v>456</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="F118" s="5">
-        <v>12037</v>
+        <v>10</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>13</v>
+        <v>283</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>14</v>
+        <v>309</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F119" s="5" t="s">
-        <v>15</v>
+        <v>310</v>
+      </c>
+      <c r="F119" s="5">
+        <v>12037</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>11</v>
+        <v>307</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>28</v>
@@ -5003,58 +5012,58 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>498</v>
+        <v>27</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C124" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
@@ -5063,8 +5072,8 @@
       <c r="E124" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F124" s="5">
-        <v>39100</v>
+      <c r="F124" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G124" s="4" t="s">
         <v>32</v>
@@ -5072,214 +5081,214 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>233</v>
+        <v>498</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C125" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C125" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F125" s="5" t="s">
-        <v>218</v>
+        <v>30</v>
+      </c>
+      <c r="F125" s="5">
+        <v>39100</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>188</v>
+        <v>233</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>483</v>
+        <v>188</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>484</v>
+        <v>34</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>485</v>
+        <v>189</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="F127" s="5">
-        <v>66020</v>
+        <v>36</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>576</v>
+        <v>483</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>34</v>
+        <v>484</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>577</v>
+        <v>485</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>36</v>
+        <v>486</v>
       </c>
       <c r="F128" s="5">
-        <v>20124</v>
+        <v>66020</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>411</v>
+        <v>576</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>412</v>
+        <v>577</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>413</v>
+        <v>36</v>
       </c>
       <c r="F129" s="5">
-        <v>37137</v>
+        <v>20124</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>343</v>
+        <v>159</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>460</v>
+        <v>411</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>9</v>
+        <v>341</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>461</v>
+        <v>412</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F130" s="8" t="s">
-        <v>218</v>
+        <v>413</v>
+      </c>
+      <c r="F130" s="5">
+        <v>37137</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>11</v>
+        <v>343</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>295</v>
+        <v>460</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>297</v>
+        <v>461</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="F131" s="5">
-        <v>56010</v>
+        <v>10</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="F132" s="5">
-        <v>40060</v>
+        <v>56010</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>26</v>
+        <v>299</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>384</v>
+        <v>311</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>385</v>
+        <v>312</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>36</v>
+        <v>313</v>
       </c>
       <c r="F133" s="5">
-        <v>20121</v>
+        <v>40060</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>34</v>
@@ -5293,8 +5302,8 @@
       <c r="E134" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F134" s="5" t="s">
-        <v>58</v>
+      <c r="F134" s="5">
+        <v>20121</v>
       </c>
       <c r="G134" s="4" t="s">
         <v>38</v>
@@ -5302,122 +5311,122 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>213</v>
+        <v>386</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>179</v>
+        <v>385</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>180</v>
+        <v>58</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>575</v>
+        <v>213</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F136" s="5">
-        <v>20124</v>
+        <v>10</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>68</v>
+        <v>575</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>72</v>
+        <v>36</v>
+      </c>
+      <c r="F137" s="5">
+        <v>20124</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>284</v>
+        <v>68</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>314</v>
+        <v>69</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>315</v>
+        <v>70</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="F138" s="5">
-        <v>57021</v>
+        <v>71</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>299</v>
+        <v>73</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>184</v>
+        <v>284</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>180</v>
+        <v>316</v>
+      </c>
+      <c r="F139" s="5">
+        <v>57021</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>462</v>
+        <v>184</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>9</v>
@@ -5431,7 +5440,7 @@
       <c r="E140" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F140" s="8" t="s">
+      <c r="F140" s="5" t="s">
         <v>180</v>
       </c>
       <c r="G140" s="4" t="s">
@@ -5440,122 +5449,122 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>89</v>
+        <v>462</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>93</v>
+        <v>10</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>346</v>
+        <v>89</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>347</v>
+        <v>91</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F142" s="5">
-        <v>70124</v>
+        <v>92</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>189</v>
+        <v>347</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>36</v>
+        <v>348</v>
       </c>
       <c r="F143" s="5">
-        <v>20158</v>
+        <v>70124</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>358</v>
+        <v>189</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>359</v>
+        <v>36</v>
       </c>
       <c r="F144" s="5">
-        <v>12084</v>
+        <v>20158</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>307</v>
+        <v>159</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>194</v>
+        <v>357</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>195</v>
+        <v>358</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>61</v>
+        <v>359</v>
+      </c>
+      <c r="F145" s="5">
+        <v>12084</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>34</v>
@@ -5564,13 +5573,13 @@
         <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="G146" s="4" t="s">
         <v>38</v>
@@ -5578,122 +5587,122 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>457</v>
+        <v>227</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>458</v>
+        <v>228</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F147" s="8" t="s">
-        <v>459</v>
+        <v>36</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>108</v>
+        <v>457</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>110</v>
+        <v>458</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>112</v>
+        <v>10</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>459</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>431</v>
+        <v>108</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>308</v>
+        <v>109</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>432</v>
+        <v>110</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F149" s="5">
-        <v>12100</v>
+        <v>111</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>307</v>
+        <v>113</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>395</v>
+        <v>431</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>22</v>
+        <v>308</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>23</v>
+        <v>432</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>24</v>
+        <v>433</v>
       </c>
       <c r="F150" s="5">
-        <v>40127</v>
+        <v>12100</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>26</v>
+        <v>307</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>355</v>
+        <v>395</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>356</v>
+        <v>23</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F151" s="5">
-        <v>20121</v>
+        <v>40127</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>556</v>
+        <v>355</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>34</v>
@@ -5702,21 +5711,21 @@
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>525</v>
+        <v>356</v>
       </c>
       <c r="E152" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F152" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>34</v>
@@ -5739,7 +5748,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>34</v>
@@ -5762,30 +5771,30 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F155" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>232</v>
+        <v>515</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>28</v>
@@ -5799,8 +5808,8 @@
       <c r="E156" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F156" s="5" t="s">
-        <v>31</v>
+      <c r="F156" s="5">
+        <v>39100</v>
       </c>
       <c r="G156" s="4" t="s">
         <v>32</v>
@@ -5808,30 +5817,30 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>34</v>
@@ -5840,13 +5849,13 @@
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="E158" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G158" s="4" t="s">
         <v>38</v>
@@ -5854,7 +5863,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>441</v>
+        <v>56</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>34</v>
@@ -5863,136 +5872,136 @@
         <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>442</v>
+        <v>57</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="F159" s="5">
-        <v>20038</v>
+        <v>36</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>236</v>
+        <v>442</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>81</v>
+        <v>443</v>
       </c>
       <c r="F160" s="5">
-        <v>10121</v>
+        <v>20038</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>95</v>
+        <v>426</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F161" s="5" t="s">
-        <v>99</v>
+        <v>81</v>
+      </c>
+      <c r="F161" s="5">
+        <v>10121</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>377</v>
+        <v>95</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>378</v>
+        <v>96</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>379</v>
+        <v>97</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="F162" s="5">
-        <v>64020</v>
+        <v>98</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>580</v>
+        <v>377</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>9</v>
+        <v>378</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>581</v>
+        <v>379</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F163" s="8" t="s">
-        <v>582</v>
+        <v>380</v>
+      </c>
+      <c r="F163" s="5">
+        <v>64020</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>410</v>
+        <v>580</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>211</v>
+        <v>581</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F164" s="5">
-        <v>20121</v>
+        <v>10</v>
+      </c>
+      <c r="F164" s="8" t="s">
+        <v>582</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>133</v>
+        <v>410</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>34</v>
@@ -6001,21 +6010,21 @@
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="E165" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F165" s="5" t="s">
-        <v>135</v>
+      <c r="F165" s="5">
+        <v>20121</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>34</v>
@@ -6024,67 +6033,67 @@
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>258</v>
+        <v>134</v>
       </c>
       <c r="E166" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>340</v>
+        <v>257</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>342</v>
+        <v>258</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="F167" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>343</v>
+        <v>38</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>166</v>
+        <v>340</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>167</v>
+        <v>342</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>168</v>
+        <v>528</v>
+      </c>
+      <c r="F168" s="5">
+        <v>37045</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>159</v>
+        <v>343</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>529</v>
+        <v>166</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>34</v>
@@ -6098,8 +6107,8 @@
       <c r="E169" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F169" s="5">
-        <v>20126</v>
+      <c r="F169" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G169" s="4" t="s">
         <v>159</v>
@@ -6107,7 +6116,7 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>471</v>
+        <v>529</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>34</v>
@@ -6116,21 +6125,21 @@
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F170" s="5">
-        <v>20135</v>
+        <v>20126</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>405</v>
+        <v>471</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>34</v>
@@ -6153,53 +6162,53 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>204</v>
+        <v>405</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F172" s="5">
+        <v>20135</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>453</v>
+        <v>204</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>454</v>
+        <v>205</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F173" s="5">
-        <v>20144</v>
+        <v>186</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>38</v>
+        <v>319</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>223</v>
+        <v>453</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>34</v>
@@ -6208,297 +6217,297 @@
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>224</v>
+        <v>454</v>
       </c>
       <c r="E174" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F174" s="5" t="s">
-        <v>135</v>
+      <c r="F174" s="5">
+        <v>20144</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>285</v>
+        <v>223</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>317</v>
+        <v>224</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F175" s="5">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>323</v>
+        <v>318</v>
+      </c>
+      <c r="F176" s="5">
+        <v>40026</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>533</v>
+        <v>286</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>29</v>
+        <v>320</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F177" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>367</v>
+        <v>533</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>368</v>
+        <v>29</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F178" s="5">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>321</v>
+        <v>368</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>322</v>
+        <v>36</v>
       </c>
       <c r="F179" s="5">
-        <v>12020</v>
+        <v>20123</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>39</v>
+        <v>287</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>41</v>
+        <v>321</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>43</v>
+        <v>322</v>
+      </c>
+      <c r="F180" s="5">
+        <v>12020</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>421</v>
+        <v>39</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>422</v>
+        <v>40</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>423</v>
+        <v>41</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="F181" s="5">
-        <v>28053</v>
+        <v>42</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>136</v>
+        <v>44</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>172</v>
+        <v>421</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>34</v>
+        <v>422</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>169</v>
+        <v>423</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>171</v>
+        <v>424</v>
+      </c>
+      <c r="F182" s="5">
+        <v>28053</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>560</v>
+        <v>172</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>561</v>
+        <v>169</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F183" s="5">
-        <v>39100</v>
+        <v>170</v>
+      </c>
+      <c r="F183" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>198</v>
+        <v>560</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>199</v>
+        <v>561</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>200</v>
+        <v>30</v>
+      </c>
+      <c r="F184" s="5">
+        <v>39100</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>534</v>
+        <v>244</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>34</v>
@@ -6512,8 +6521,8 @@
       <c r="E187" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F187" s="5">
-        <v>20121</v>
+      <c r="F187" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G187" s="4" t="s">
         <v>38</v>
@@ -6521,7 +6530,7 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>578</v>
+        <v>534</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>34</v>
@@ -6530,7 +6539,7 @@
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>579</v>
+        <v>177</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>36</v>
@@ -6544,260 +6553,260 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>447</v>
+        <v>579</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>448</v>
+        <v>36</v>
       </c>
       <c r="F189" s="10">
-        <v>53048</v>
+        <v>20121</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>449</v>
+        <v>38</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>516</v>
+        <v>445</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>509</v>
+        <v>446</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>517</v>
+        <v>447</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>518</v>
+        <v>448</v>
       </c>
       <c r="F190" s="10">
-        <v>35011</v>
+        <v>53048</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>505</v>
+        <v>449</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>243</v>
+        <v>516</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>34</v>
+        <v>509</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>177</v>
+        <v>517</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F191" s="10" t="s">
-        <v>58</v>
+        <v>518</v>
+      </c>
+      <c r="F191" s="10">
+        <v>35011</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>131</v>
+        <v>243</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>531</v>
+        <v>131</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>532</v>
+        <v>132</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F193" s="10">
-        <v>20121</v>
+        <v>30</v>
+      </c>
+      <c r="F193" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B194" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C194" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D194" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="E194" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F194" s="10">
+        <v>20121</v>
+      </c>
+      <c r="G194" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A195" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B194" s="9" t="s">
+      <c r="B195" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C194" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D194" s="9" t="s">
+      <c r="C195" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D195" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E194" s="9" t="s">
+      <c r="E195" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F194" s="10" t="s">
+      <c r="F195" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G194" s="9" t="s">
+      <c r="G195" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A195" s="3" t="s">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A196" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="B195" s="3" t="s">
+      <c r="B196" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C195" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D195" s="3" t="s">
+      <c r="C196" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D196" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="E195" s="3" t="s">
+      <c r="E196" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F195" s="11" t="s">
+      <c r="F196" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="G195" s="3" t="s">
+      <c r="G196" s="3" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A196" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="B196" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C196" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D196" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="E196" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="F196" s="10">
-        <v>20089</v>
-      </c>
-      <c r="G196" s="9" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>475</v>
+        <v>381</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C197" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>476</v>
+        <v>382</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F197" s="12" t="s">
-        <v>477</v>
+        <v>383</v>
+      </c>
+      <c r="F197" s="10">
+        <v>20089</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>212</v>
+        <v>475</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C198" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>202</v>
+        <v>476</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F198" s="10" t="s">
-        <v>203</v>
+        <v>10</v>
+      </c>
+      <c r="F198" s="12" t="s">
+        <v>477</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C199" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F199" s="10" t="s">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>438</v>
+        <v>214</v>
       </c>
       <c r="B200" s="9" t="s">
         <v>34</v>
@@ -6811,8 +6820,8 @@
       <c r="E200" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F200" s="10">
-        <v>20124</v>
+      <c r="F200" s="10" t="s">
+        <v>158</v>
       </c>
       <c r="G200" s="9" t="s">
         <v>159</v>
@@ -6820,7 +6829,7 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>229</v>
+        <v>438</v>
       </c>
       <c r="B201" s="9" t="s">
         <v>34</v>
@@ -6829,21 +6838,21 @@
         <v>8</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F201" s="10" t="s">
-        <v>231</v>
+      <c r="F201" s="10">
+        <v>20124</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B202" s="9" t="s">
         <v>34</v>
@@ -6866,7 +6875,7 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>472</v>
+        <v>256</v>
       </c>
       <c r="B203" s="9" t="s">
         <v>34</v>
@@ -6875,21 +6884,21 @@
         <v>8</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F203" s="10">
-        <v>20129</v>
+      <c r="F203" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="B204" s="9" t="s">
         <v>34</v>
@@ -6912,7 +6921,7 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="B205" s="9" t="s">
         <v>34</v>
@@ -6935,7 +6944,7 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B206" s="9" t="s">
         <v>34</v>
@@ -6958,7 +6967,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
-        <v>176</v>
+        <v>474</v>
       </c>
       <c r="B207" s="9" t="s">
         <v>34</v>
@@ -6967,435 +6976,435 @@
         <v>8</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F207" s="10" t="s">
-        <v>58</v>
+      <c r="F207" s="10">
+        <v>20129</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
-        <v>331</v>
+        <v>176</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C208" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>332</v>
+        <v>177</v>
       </c>
       <c r="E208" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="F208" s="10">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F208" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G208" s="9" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C209" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="E209" s="9" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="F209" s="10">
-        <v>20124</v>
+        <v>40026</v>
       </c>
       <c r="G209" s="9" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
-        <v>450</v>
+        <v>288</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C210" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D210" s="9" t="s">
-        <v>451</v>
+        <v>324</v>
       </c>
       <c r="E210" s="9" t="s">
-        <v>452</v>
+        <v>36</v>
       </c>
       <c r="F210" s="10">
-        <v>12011</v>
+        <v>20124</v>
       </c>
       <c r="G210" s="9" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
-        <v>151</v>
+        <v>450</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>152</v>
+        <v>308</v>
       </c>
       <c r="C211" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>153</v>
+        <v>451</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F211" s="10" t="s">
-        <v>155</v>
+        <v>452</v>
+      </c>
+      <c r="F211" s="10">
+        <v>12011</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
-        <v>419</v>
+        <v>151</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="C212" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>420</v>
+        <v>153</v>
       </c>
       <c r="E212" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F212" s="10">
-        <v>20123</v>
+        <v>154</v>
+      </c>
+      <c r="F212" s="10" t="s">
+        <v>155</v>
       </c>
       <c r="G212" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
-        <v>491</v>
+        <v>419</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C213" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D213" s="9" t="s">
-        <v>492</v>
+        <v>420</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F213" s="10">
-        <v>90141</v>
+        <v>20123</v>
       </c>
       <c r="G213" s="9" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="B214" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C214" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D214" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="E214" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F214" s="10">
+        <v>90141</v>
+      </c>
+      <c r="G214" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A215" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="B214" s="9" t="s">
+      <c r="B215" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C214" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D214" s="9" t="s">
+      <c r="C215" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D215" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="E214" s="9" t="s">
+      <c r="E215" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F214" s="12" t="s">
+      <c r="F215" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="G214" s="9" t="s">
+      <c r="G215" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A215" s="3" t="s">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A216" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="B215" s="3" t="s">
+      <c r="B216" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C215" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D215" s="3" t="s">
+      <c r="C216" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D216" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="E215" s="3" t="s">
+      <c r="E216" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F215" s="11" t="s">
+      <c r="F216" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="G215" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A216" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="B216" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C216" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D216" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="E216" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F216" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="G216" s="9" t="s">
+      <c r="G216" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="B217" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C217" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D217" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="E217" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F217" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="G217" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A218" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="B217" s="9" t="s">
+      <c r="B218" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C217" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D217" s="9" t="s">
+      <c r="C218" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D218" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="E217" s="9" t="s">
+      <c r="E218" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="F217" s="10">
+      <c r="F218" s="10">
         <v>38055</v>
       </c>
-      <c r="G217" s="9" t="s">
+      <c r="G218" s="9" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A218" s="3" t="s">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A219" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="B218" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C218" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D218" s="3" t="s">
+      <c r="B219" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D219" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E218" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F218" s="7">
+      <c r="E219" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F219" s="7">
         <v>20145</v>
       </c>
-      <c r="G218" s="3" t="s">
+      <c r="G219" s="3" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A219" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="B219" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C219" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D219" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="E219" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="F219" s="10">
-        <v>25010</v>
-      </c>
-      <c r="G219" s="9" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
-        <v>393</v>
+        <v>427</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="C220" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D220" s="9" t="s">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="E220" s="9" t="s">
-        <v>36</v>
+        <v>429</v>
       </c>
       <c r="F220" s="10">
-        <v>20123</v>
+        <v>25010</v>
       </c>
       <c r="G220" s="9" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C221" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D221" s="9" t="s">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>418</v>
+        <v>36</v>
       </c>
       <c r="F221" s="10">
-        <v>71016</v>
+        <v>20123</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="9" t="s">
-        <v>16</v>
+        <v>416</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="C222" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>18</v>
+        <v>417</v>
       </c>
       <c r="E222" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F222" s="10" t="s">
-        <v>20</v>
+        <v>418</v>
+      </c>
+      <c r="F222" s="10">
+        <v>71016</v>
       </c>
       <c r="G222" s="9" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B223" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C223" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D223" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E223" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F223" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G223" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A224" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="B223" s="9" t="s">
+      <c r="B224" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="C223" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D223" s="9" t="s">
+      <c r="C224" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D224" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="E223" s="9" t="s">
+      <c r="E224" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="F223" s="10" t="s">
+      <c r="F224" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="G223" s="9" t="s">
+      <c r="G224" s="9" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A224" s="3" t="s">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A225" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="B224" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D224" s="3" t="s">
+      <c r="B225" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D225" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="E224" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F224" s="7">
+      <c r="E225" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F225" s="7">
         <v>20122</v>
       </c>
-      <c r="G224" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A225" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="B225" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C225" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D225" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="E225" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F225" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="G225" s="9" t="s">
+      <c r="G225" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="9" t="s">
-        <v>478</v>
+        <v>277</v>
       </c>
       <c r="B226" s="9" t="s">
         <v>34</v>
@@ -7404,67 +7413,67 @@
         <v>8</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>479</v>
+        <v>278</v>
       </c>
       <c r="E226" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F226" s="10">
-        <v>20123</v>
+      <c r="F226" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="G226" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A227" s="3" t="s">
+      <c r="A227" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="B227" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C227" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D227" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="E227" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F227" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G227" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A228" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="B227" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C227" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D227" s="3" t="s">
+      <c r="B228" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D228" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="E227" s="3" t="s">
+      <c r="E228" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="F227" s="7">
+      <c r="F228" s="7">
         <v>20094</v>
       </c>
-      <c r="G227" s="3" t="s">
+      <c r="G228" s="3" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A228" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="B228" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C228" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D228" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="E228" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F228" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="G228" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="9" t="s">
-        <v>216</v>
+        <v>396</v>
       </c>
       <c r="B229" s="9" t="s">
         <v>9</v>
@@ -7487,53 +7496,53 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="9" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="C230" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D230" s="9" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="E230" s="9" t="s">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="F230" s="10" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="G230" s="9" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="9" t="s">
-        <v>434</v>
+        <v>160</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="C231" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D231" s="9" t="s">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="E231" s="9" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="F231" s="10" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="G231" s="9" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="9" t="s">
-        <v>255</v>
+        <v>434</v>
       </c>
       <c r="B232" s="9" t="s">
         <v>9</v>
@@ -7556,30 +7565,53 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B233" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C233" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D233" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E233" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F233" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G233" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A234" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B233" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C233" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D233" s="9" t="s">
+      <c r="B234" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C234" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D234" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E233" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F233" s="10" t="s">
+      <c r="E234" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F234" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G233" s="9" t="s">
+      <c r="G234" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G233">
+    <sortState ref="A2:G234">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -7592,11 +7624,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7833,27 +7866,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7878,9 +7901,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{7741F810-8AF0-4F93-810C-470C461E06E7}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{919956C8-C0A4-4BA2-B048-2D24D323037F}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="590">
   <si>
     <t>Nome account</t>
   </si>
@@ -1790,6 +1790,9 @@
   </si>
   <si>
     <t>00154</t>
+  </si>
+  <si>
+    <t>LUMINORA SPARPAGLIATA SRL</t>
   </si>
 </sst>
 </file>
@@ -2214,7 +2217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G234"/>
+  <dimension ref="A1:G235"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -5380,76 +5383,76 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>68</v>
+        <v>589</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>72</v>
+        <v>36</v>
+      </c>
+      <c r="F138" s="5">
+        <v>20124</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>284</v>
+        <v>68</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>314</v>
+        <v>69</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>315</v>
+        <v>70</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="F139" s="5">
-        <v>57021</v>
+        <v>71</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>299</v>
+        <v>73</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>184</v>
+        <v>284</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>180</v>
+        <v>316</v>
+      </c>
+      <c r="F140" s="5">
+        <v>57021</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>462</v>
+        <v>184</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>9</v>
@@ -5463,7 +5466,7 @@
       <c r="E141" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F141" s="8" t="s">
+      <c r="F141" s="5" t="s">
         <v>180</v>
       </c>
       <c r="G141" s="4" t="s">
@@ -5472,122 +5475,122 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>89</v>
+        <v>462</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>93</v>
+        <v>10</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>346</v>
+        <v>89</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>347</v>
+        <v>91</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F143" s="5">
-        <v>70124</v>
+        <v>92</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>189</v>
+        <v>347</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>36</v>
+        <v>348</v>
       </c>
       <c r="F144" s="5">
-        <v>20158</v>
+        <v>70124</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>358</v>
+        <v>189</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>359</v>
+        <v>36</v>
       </c>
       <c r="F145" s="5">
-        <v>12084</v>
+        <v>20158</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>307</v>
+        <v>159</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>194</v>
+        <v>357</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>195</v>
+        <v>358</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>61</v>
+        <v>359</v>
+      </c>
+      <c r="F146" s="5">
+        <v>12084</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>34</v>
@@ -5596,13 +5599,13 @@
         <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="G147" s="4" t="s">
         <v>38</v>
@@ -5610,122 +5613,122 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>457</v>
+        <v>227</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>458</v>
+        <v>228</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F148" s="8" t="s">
-        <v>459</v>
+        <v>36</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>108</v>
+        <v>457</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>110</v>
+        <v>458</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>112</v>
+        <v>10</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>459</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>431</v>
+        <v>108</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>308</v>
+        <v>109</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>432</v>
+        <v>110</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F150" s="5">
-        <v>12100</v>
+        <v>111</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>307</v>
+        <v>113</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>395</v>
+        <v>431</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>22</v>
+        <v>308</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>23</v>
+        <v>432</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>24</v>
+        <v>433</v>
       </c>
       <c r="F151" s="5">
-        <v>40127</v>
+        <v>12100</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>26</v>
+        <v>307</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>355</v>
+        <v>395</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>356</v>
+        <v>23</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F152" s="5">
-        <v>20121</v>
+        <v>40127</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>556</v>
+        <v>355</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>34</v>
@@ -5734,21 +5737,21 @@
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>525</v>
+        <v>356</v>
       </c>
       <c r="E153" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F153" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>34</v>
@@ -5771,7 +5774,7 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>34</v>
@@ -5794,30 +5797,30 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F156" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>232</v>
+        <v>515</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>28</v>
@@ -5831,8 +5834,8 @@
       <c r="E157" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F157" s="5" t="s">
-        <v>31</v>
+      <c r="F157" s="5">
+        <v>39100</v>
       </c>
       <c r="G157" s="4" t="s">
         <v>32</v>
@@ -5840,30 +5843,30 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>34</v>
@@ -5872,13 +5875,13 @@
         <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="E159" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>38</v>
@@ -5886,7 +5889,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>441</v>
+        <v>56</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>34</v>
@@ -5895,136 +5898,136 @@
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>442</v>
+        <v>57</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="F160" s="5">
-        <v>20038</v>
+        <v>36</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>236</v>
+        <v>442</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>81</v>
+        <v>443</v>
       </c>
       <c r="F161" s="5">
-        <v>10121</v>
+        <v>20038</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>95</v>
+        <v>426</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F162" s="5" t="s">
-        <v>99</v>
+        <v>81</v>
+      </c>
+      <c r="F162" s="5">
+        <v>10121</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>377</v>
+        <v>95</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>378</v>
+        <v>96</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>379</v>
+        <v>97</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="F163" s="5">
-        <v>64020</v>
+        <v>98</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>580</v>
+        <v>377</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>9</v>
+        <v>378</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>581</v>
+        <v>379</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F164" s="8" t="s">
-        <v>582</v>
+        <v>380</v>
+      </c>
+      <c r="F164" s="5">
+        <v>64020</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>410</v>
+        <v>580</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>211</v>
+        <v>581</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F165" s="5">
-        <v>20121</v>
+        <v>10</v>
+      </c>
+      <c r="F165" s="8" t="s">
+        <v>582</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>133</v>
+        <v>410</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>34</v>
@@ -6033,21 +6036,21 @@
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="E166" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F166" s="5" t="s">
-        <v>135</v>
+      <c r="F166" s="5">
+        <v>20121</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>34</v>
@@ -6056,67 +6059,67 @@
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>258</v>
+        <v>134</v>
       </c>
       <c r="E167" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>340</v>
+        <v>257</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>342</v>
+        <v>258</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="F168" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>343</v>
+        <v>38</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>166</v>
+        <v>340</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>167</v>
+        <v>342</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>168</v>
+        <v>528</v>
+      </c>
+      <c r="F169" s="5">
+        <v>37045</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>159</v>
+        <v>343</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>529</v>
+        <v>166</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>34</v>
@@ -6130,8 +6133,8 @@
       <c r="E170" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F170" s="5">
-        <v>20126</v>
+      <c r="F170" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G170" s="4" t="s">
         <v>159</v>
@@ -6139,7 +6142,7 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>471</v>
+        <v>529</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>34</v>
@@ -6148,21 +6151,21 @@
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F171" s="5">
-        <v>20135</v>
+        <v>20126</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>405</v>
+        <v>471</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>34</v>
@@ -6185,53 +6188,53 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>204</v>
+        <v>405</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F173" s="5">
+        <v>20135</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>453</v>
+        <v>204</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>454</v>
+        <v>205</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F174" s="5">
-        <v>20144</v>
+        <v>186</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>38</v>
+        <v>319</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>223</v>
+        <v>453</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>34</v>
@@ -6240,297 +6243,297 @@
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>224</v>
+        <v>454</v>
       </c>
       <c r="E175" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F175" s="5" t="s">
-        <v>135</v>
+      <c r="F175" s="5">
+        <v>20144</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>285</v>
+        <v>223</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>317</v>
+        <v>224</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F176" s="5">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>323</v>
+        <v>318</v>
+      </c>
+      <c r="F177" s="5">
+        <v>40026</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>533</v>
+        <v>286</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>29</v>
+        <v>320</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F178" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>367</v>
+        <v>533</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>368</v>
+        <v>29</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F179" s="5">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>321</v>
+        <v>368</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>322</v>
+        <v>36</v>
       </c>
       <c r="F180" s="5">
-        <v>12020</v>
+        <v>20123</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>39</v>
+        <v>287</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>41</v>
+        <v>321</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F181" s="5" t="s">
-        <v>43</v>
+        <v>322</v>
+      </c>
+      <c r="F181" s="5">
+        <v>12020</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>421</v>
+        <v>39</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>422</v>
+        <v>40</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>423</v>
+        <v>41</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="F182" s="5">
-        <v>28053</v>
+        <v>42</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>136</v>
+        <v>44</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>172</v>
+        <v>421</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>34</v>
+        <v>422</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>169</v>
+        <v>423</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>171</v>
+        <v>424</v>
+      </c>
+      <c r="F183" s="5">
+        <v>28053</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>560</v>
+        <v>172</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>561</v>
+        <v>169</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F184" s="5">
-        <v>39100</v>
+        <v>170</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>198</v>
+        <v>560</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>199</v>
+        <v>561</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F185" s="5" t="s">
-        <v>200</v>
+        <v>30</v>
+      </c>
+      <c r="F185" s="5">
+        <v>39100</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>534</v>
+        <v>244</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>34</v>
@@ -6544,8 +6547,8 @@
       <c r="E188" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F188" s="5">
-        <v>20121</v>
+      <c r="F188" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G188" s="4" t="s">
         <v>38</v>
@@ -6553,7 +6556,7 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>578</v>
+        <v>534</v>
       </c>
       <c r="B189" s="9" t="s">
         <v>34</v>
@@ -6562,7 +6565,7 @@
         <v>8</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>579</v>
+        <v>177</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>36</v>
@@ -6576,260 +6579,260 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>447</v>
+        <v>579</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>448</v>
+        <v>36</v>
       </c>
       <c r="F190" s="10">
-        <v>53048</v>
+        <v>20121</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>449</v>
+        <v>38</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>516</v>
+        <v>445</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>509</v>
+        <v>446</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>517</v>
+        <v>447</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>518</v>
+        <v>448</v>
       </c>
       <c r="F191" s="10">
-        <v>35011</v>
+        <v>53048</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>505</v>
+        <v>449</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>243</v>
+        <v>516</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>34</v>
+        <v>509</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>177</v>
+        <v>517</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F192" s="10" t="s">
-        <v>58</v>
+        <v>518</v>
+      </c>
+      <c r="F192" s="10">
+        <v>35011</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>131</v>
+        <v>243</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F193" s="10" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>531</v>
+        <v>131</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C194" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>532</v>
+        <v>132</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F194" s="10">
-        <v>20121</v>
+        <v>30</v>
+      </c>
+      <c r="F194" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B195" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C195" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D195" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="E195" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F195" s="10">
+        <v>20121</v>
+      </c>
+      <c r="G195" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A196" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B195" s="9" t="s">
+      <c r="B196" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C195" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D195" s="9" t="s">
+      <c r="C196" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D196" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E195" s="9" t="s">
+      <c r="E196" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F195" s="10" t="s">
+      <c r="F196" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G195" s="9" t="s">
+      <c r="G196" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A196" s="3" t="s">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A197" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="B196" s="3" t="s">
+      <c r="B197" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C196" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D196" s="3" t="s">
+      <c r="C197" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D197" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="E196" s="3" t="s">
+      <c r="E197" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F196" s="11" t="s">
+      <c r="F197" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="G196" s="3" t="s">
+      <c r="G197" s="3" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A197" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="B197" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C197" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D197" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="E197" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="F197" s="10">
-        <v>20089</v>
-      </c>
-      <c r="G197" s="9" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>475</v>
+        <v>381</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C198" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>476</v>
+        <v>382</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F198" s="12" t="s">
-        <v>477</v>
+        <v>383</v>
+      </c>
+      <c r="F198" s="10">
+        <v>20089</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>212</v>
+        <v>475</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C199" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>202</v>
+        <v>476</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F199" s="10" t="s">
-        <v>203</v>
+        <v>10</v>
+      </c>
+      <c r="F199" s="12" t="s">
+        <v>477</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C200" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F200" s="10" t="s">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>438</v>
+        <v>214</v>
       </c>
       <c r="B201" s="9" t="s">
         <v>34</v>
@@ -6843,8 +6846,8 @@
       <c r="E201" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F201" s="10">
-        <v>20124</v>
+      <c r="F201" s="10" t="s">
+        <v>158</v>
       </c>
       <c r="G201" s="9" t="s">
         <v>159</v>
@@ -6852,7 +6855,7 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>229</v>
+        <v>438</v>
       </c>
       <c r="B202" s="9" t="s">
         <v>34</v>
@@ -6861,21 +6864,21 @@
         <v>8</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E202" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F202" s="10" t="s">
-        <v>231</v>
+      <c r="F202" s="10">
+        <v>20124</v>
       </c>
       <c r="G202" s="9" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B203" s="9" t="s">
         <v>34</v>
@@ -6898,7 +6901,7 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>472</v>
+        <v>256</v>
       </c>
       <c r="B204" s="9" t="s">
         <v>34</v>
@@ -6907,21 +6910,21 @@
         <v>8</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E204" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F204" s="10">
-        <v>20129</v>
+      <c r="F204" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G204" s="9" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="B205" s="9" t="s">
         <v>34</v>
@@ -6944,7 +6947,7 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="B206" s="9" t="s">
         <v>34</v>
@@ -6967,7 +6970,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B207" s="9" t="s">
         <v>34</v>
@@ -6990,7 +6993,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
-        <v>176</v>
+        <v>474</v>
       </c>
       <c r="B208" s="9" t="s">
         <v>34</v>
@@ -6999,435 +7002,435 @@
         <v>8</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="E208" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F208" s="10" t="s">
-        <v>58</v>
+      <c r="F208" s="10">
+        <v>20129</v>
       </c>
       <c r="G208" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
-        <v>331</v>
+        <v>176</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C209" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>332</v>
+        <v>177</v>
       </c>
       <c r="E209" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="F209" s="10">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F209" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G209" s="9" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C210" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D210" s="9" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="E210" s="9" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="F210" s="10">
-        <v>20124</v>
+        <v>40026</v>
       </c>
       <c r="G210" s="9" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
-        <v>450</v>
+        <v>288</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C211" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>451</v>
+        <v>324</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>452</v>
+        <v>36</v>
       </c>
       <c r="F211" s="10">
-        <v>12011</v>
+        <v>20124</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
-        <v>151</v>
+        <v>450</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>152</v>
+        <v>308</v>
       </c>
       <c r="C212" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>153</v>
+        <v>451</v>
       </c>
       <c r="E212" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F212" s="10" t="s">
-        <v>155</v>
+        <v>452</v>
+      </c>
+      <c r="F212" s="10">
+        <v>12011</v>
       </c>
       <c r="G212" s="9" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
-        <v>419</v>
+        <v>151</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="C213" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D213" s="9" t="s">
-        <v>420</v>
+        <v>153</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F213" s="10">
-        <v>20123</v>
+        <v>154</v>
+      </c>
+      <c r="F213" s="10" t="s">
+        <v>155</v>
       </c>
       <c r="G213" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
-        <v>491</v>
+        <v>419</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C214" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D214" s="9" t="s">
-        <v>492</v>
+        <v>420</v>
       </c>
       <c r="E214" s="9" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F214" s="10">
-        <v>90141</v>
+        <v>20123</v>
       </c>
       <c r="G214" s="9" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C215" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D215" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="E215" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F215" s="10">
+        <v>90141</v>
+      </c>
+      <c r="G215" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A216" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="B215" s="9" t="s">
+      <c r="B216" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C215" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D215" s="9" t="s">
+      <c r="C216" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D216" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="E215" s="9" t="s">
+      <c r="E216" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F215" s="12" t="s">
+      <c r="F216" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="G215" s="9" t="s">
+      <c r="G216" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A216" s="3" t="s">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A217" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="B216" s="3" t="s">
+      <c r="B217" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C216" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D216" s="3" t="s">
+      <c r="C217" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D217" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="E216" s="3" t="s">
+      <c r="E217" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F216" s="11" t="s">
+      <c r="F217" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="G216" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A217" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="B217" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C217" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D217" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="E217" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F217" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="G217" s="9" t="s">
+      <c r="G217" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="B218" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C218" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D218" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="E218" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F218" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="G218" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A219" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="B218" s="9" t="s">
+      <c r="B219" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C218" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D218" s="9" t="s">
+      <c r="C219" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D219" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="E218" s="9" t="s">
+      <c r="E219" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="F218" s="10">
+      <c r="F219" s="10">
         <v>38055</v>
       </c>
-      <c r="G218" s="9" t="s">
+      <c r="G219" s="9" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A219" s="3" t="s">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A220" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="B219" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C219" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D219" s="3" t="s">
+      <c r="B220" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D220" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E219" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F219" s="7">
+      <c r="E220" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F220" s="7">
         <v>20145</v>
       </c>
-      <c r="G219" s="3" t="s">
+      <c r="G220" s="3" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A220" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="B220" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C220" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D220" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="E220" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="F220" s="10">
-        <v>25010</v>
-      </c>
-      <c r="G220" s="9" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
-        <v>393</v>
+        <v>427</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="C221" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D221" s="9" t="s">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>36</v>
+        <v>429</v>
       </c>
       <c r="F221" s="10">
-        <v>20123</v>
+        <v>25010</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="9" t="s">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C222" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="E222" s="9" t="s">
-        <v>418</v>
+        <v>36</v>
       </c>
       <c r="F222" s="10">
-        <v>71016</v>
+        <v>20123</v>
       </c>
       <c r="G222" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="9" t="s">
-        <v>16</v>
+        <v>416</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="C223" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>18</v>
+        <v>417</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F223" s="10" t="s">
-        <v>20</v>
+        <v>418</v>
+      </c>
+      <c r="F223" s="10">
+        <v>71016</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B224" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C224" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D224" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E224" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F224" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G224" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A225" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="B224" s="9" t="s">
+      <c r="B225" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="C224" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D224" s="9" t="s">
+      <c r="C225" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D225" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="E224" s="9" t="s">
+      <c r="E225" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="F224" s="10" t="s">
+      <c r="F225" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="G224" s="9" t="s">
+      <c r="G225" s="9" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A225" s="3" t="s">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A226" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="B225" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C225" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D225" s="3" t="s">
+      <c r="B226" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D226" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="E225" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F225" s="7">
+      <c r="E226" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F226" s="7">
         <v>20122</v>
       </c>
-      <c r="G225" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A226" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="B226" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C226" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D226" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="E226" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F226" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="G226" s="9" t="s">
+      <c r="G226" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="9" t="s">
-        <v>478</v>
+        <v>277</v>
       </c>
       <c r="B227" s="9" t="s">
         <v>34</v>
@@ -7436,67 +7439,67 @@
         <v>8</v>
       </c>
       <c r="D227" s="9" t="s">
-        <v>479</v>
+        <v>278</v>
       </c>
       <c r="E227" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F227" s="10">
-        <v>20123</v>
+      <c r="F227" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="G227" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A228" s="3" t="s">
+      <c r="A228" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="B228" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C228" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D228" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="E228" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F228" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G228" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A229" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="B228" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D228" s="3" t="s">
+      <c r="B229" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D229" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="E228" s="3" t="s">
+      <c r="E229" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="F228" s="7">
+      <c r="F229" s="7">
         <v>20094</v>
       </c>
-      <c r="G228" s="3" t="s">
+      <c r="G229" s="3" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A229" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="B229" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C229" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D229" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="E229" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F229" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="G229" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="9" t="s">
-        <v>216</v>
+        <v>396</v>
       </c>
       <c r="B230" s="9" t="s">
         <v>9</v>
@@ -7519,53 +7522,53 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="9" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="C231" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D231" s="9" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="E231" s="9" t="s">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="F231" s="10" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="G231" s="9" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="9" t="s">
-        <v>434</v>
+        <v>160</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="C232" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D232" s="9" t="s">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="E232" s="9" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="F232" s="10" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="G232" s="9" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="9" t="s">
-        <v>255</v>
+        <v>434</v>
       </c>
       <c r="B233" s="9" t="s">
         <v>9</v>
@@ -7588,30 +7591,53 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B234" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C234" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D234" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E234" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F234" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G234" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A235" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B234" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C234" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D234" s="9" t="s">
+      <c r="B235" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C235" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D235" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E234" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F234" s="10" t="s">
+      <c r="E235" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F235" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G234" s="9" t="s">
+      <c r="G235" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G234">
+    <sortState ref="A2:G235">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -7624,12 +7650,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7866,17 +7891,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7901,18 +7936,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{919956C8-C0A4-4BA2-B048-2D24D323037F}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{ECA58198-9EC6-48F7-8BE0-30F431221322}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="595">
   <si>
     <t>Nome account</t>
   </si>
@@ -1793,6 +1793,21 @@
   </si>
   <si>
     <t>LUMINORA SPARPAGLIATA SRL</t>
+  </si>
+  <si>
+    <t>INNOVAZIONE AGRISOLARE SRL</t>
+  </si>
+  <si>
+    <t>VIA CHIARAVALLE 7/9</t>
+  </si>
+  <si>
+    <t>E24E SRL</t>
+  </si>
+  <si>
+    <t>CORSO DI PORTA VITTORIA 28</t>
+  </si>
+  <si>
+    <t>RERE 62 SRL</t>
   </si>
 </sst>
 </file>
@@ -2217,7 +2232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G235"/>
+  <dimension ref="A1:G238"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -3704,122 +3719,122 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>300</v>
+        <v>592</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>296</v>
+        <v>34</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>301</v>
+        <v>593</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>302</v>
+        <v>36</v>
       </c>
       <c r="F65" s="5">
-        <v>56025</v>
+        <v>20122</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>299</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>9</v>
+        <v>296</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>273</v>
+        <v>302</v>
+      </c>
+      <c r="F66" s="5">
+        <v>56025</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>375</v>
+        <v>271</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>376</v>
+        <v>272</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F67" s="5">
-        <v>20121</v>
+        <v>10</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>280</v>
+        <v>375</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>303</v>
+        <v>376</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>304</v>
+        <v>36</v>
       </c>
       <c r="F68" s="5">
-        <v>24060</v>
+        <v>20121</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>481</v>
+        <v>280</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="F69" s="5">
-        <v>20121</v>
+        <v>24060</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>175</v>
+        <v>481</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>34</v>
@@ -3828,21 +3843,21 @@
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F70" s="5" t="s">
-        <v>158</v>
+      <c r="F70" s="5">
+        <v>20121</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>34</v>
@@ -3865,7 +3880,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>253</v>
+        <v>156</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>34</v>
@@ -3874,21 +3889,21 @@
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>439</v>
+        <v>253</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>34</v>
@@ -3897,228 +3912,228 @@
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>440</v>
+        <v>230</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F73" s="5">
-        <v>20122</v>
+      <c r="F73" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>439</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>247</v>
+        <v>440</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>249</v>
+        <v>36</v>
+      </c>
+      <c r="F74" s="5">
+        <v>20122</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>83</v>
+        <v>250</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>362</v>
+        <v>251</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>364</v>
+        <v>252</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="F76" s="5">
-        <v>76123</v>
+        <v>81</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>425</v>
+        <v>362</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>132</v>
+        <v>364</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="F77" s="5">
-        <v>39100</v>
+        <v>76123</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>551</v>
+        <v>425</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>552</v>
+        <v>28</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>553</v>
+        <v>132</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>555</v>
+        <v>30</v>
+      </c>
+      <c r="F78" s="5">
+        <v>39100</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>391</v>
+        <v>551</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>40</v>
+        <v>552</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>392</v>
+        <v>553</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F79" s="5">
-        <v>70043</v>
+        <v>554</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>555</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>219</v>
+        <v>391</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>220</v>
+        <v>392</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="F80" s="5">
+        <v>70043</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>34</v>
@@ -4127,13 +4142,13 @@
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G83" s="4" t="s">
         <v>38</v>
@@ -4141,7 +4156,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>34</v>
@@ -4164,7 +4179,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>34</v>
@@ -4187,99 +4202,99 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>371</v>
+        <v>130</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>372</v>
+        <v>34</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>373</v>
+        <v>122</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="F86" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>201</v>
+        <v>371</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>34</v>
+        <v>372</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>189</v>
+        <v>373</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>190</v>
+        <v>374</v>
+      </c>
+      <c r="F87" s="5">
+        <v>61121</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>506</v>
+        <v>201</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="C88" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>508</v>
+        <v>189</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="F88" s="5">
-        <v>35010</v>
+        <v>36</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>505</v>
+        <v>159</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>281</v>
+        <v>506</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C89" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>305</v>
+        <v>508</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>36</v>
+        <v>507</v>
       </c>
       <c r="F89" s="5">
-        <v>20123</v>
+        <v>35010</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>565</v>
+        <v>281</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>34</v>
@@ -4288,13 +4303,13 @@
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>564</v>
+        <v>305</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F90" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G90" s="4" t="s">
         <v>38</v>
@@ -4302,25 +4317,25 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>351</v>
+        <v>565</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>353</v>
+        <v>564</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>354</v>
+        <v>36</v>
       </c>
       <c r="F91" s="5">
-        <v>15033</v>
+        <v>20122</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
@@ -4348,76 +4363,76 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>535</v>
+        <v>351</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>117</v>
+        <v>352</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>536</v>
+        <v>353</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>119</v>
+        <v>354</v>
       </c>
       <c r="F93" s="5">
-        <v>65127</v>
+        <v>15033</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>59</v>
+        <v>535</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>60</v>
+        <v>536</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>61</v>
+        <v>119</v>
+      </c>
+      <c r="F94" s="5">
+        <v>65127</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F95" s="5">
-        <v>10153</v>
+        <v>36</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>430</v>
+        <v>336</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>79</v>
@@ -4440,76 +4455,76 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>573</v>
+        <v>430</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>574</v>
+        <v>337</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F97" s="5">
-        <v>20154</v>
+        <v>10153</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>282</v>
+        <v>573</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>306</v>
+        <v>574</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F98" s="5">
-        <v>183</v>
+        <v>20154</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>307</v>
+        <v>159</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>211</v>
+        <v>306</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>58</v>
+        <v>10</v>
+      </c>
+      <c r="F99" s="5">
+        <v>183</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>549</v>
+        <v>210</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>34</v>
@@ -4518,21 +4533,21 @@
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>550</v>
+        <v>211</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F100" s="5">
-        <v>20154</v>
+      <c r="F100" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>275</v>
+        <v>549</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>34</v>
@@ -4541,13 +4556,13 @@
         <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>276</v>
+        <v>550</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F101" s="5" t="s">
-        <v>158</v>
+      <c r="F101" s="5">
+        <v>20154</v>
       </c>
       <c r="G101" s="4" t="s">
         <v>159</v>
@@ -4555,30 +4570,30 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>128</v>
+        <v>275</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>28</v>
@@ -4601,145 +4616,145 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>414</v>
+        <v>242</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>415</v>
+        <v>129</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>274</v>
+        <v>414</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>29</v>
+        <v>415</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>241</v>
+        <v>31</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>537</v>
+        <v>238</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>538</v>
+        <v>146</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>539</v>
+        <v>239</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="F107" s="5">
-        <v>34133</v>
+        <v>240</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>514</v>
+        <v>150</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>435</v>
+        <v>537</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>28</v>
+        <v>538</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>129</v>
+        <v>539</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>30</v>
+        <v>540</v>
       </c>
       <c r="F108" s="5">
-        <v>39100</v>
+        <v>34133</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>32</v>
+        <v>514</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>206</v>
+        <v>435</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F109" s="5" t="s">
-        <v>61</v>
+        <v>30</v>
+      </c>
+      <c r="F109" s="5">
+        <v>39100</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>366</v>
+        <v>206</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>34</v>
@@ -4753,8 +4768,8 @@
       <c r="E110" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F110" s="5">
-        <v>20123</v>
+      <c r="F110" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G110" s="4" t="s">
         <v>38</v>
@@ -4762,7 +4777,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>101</v>
+        <v>366</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>34</v>
@@ -4776,8 +4791,8 @@
       <c r="E111" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F111" s="5" t="s">
-        <v>61</v>
+      <c r="F111" s="5">
+        <v>20123</v>
       </c>
       <c r="G111" s="4" t="s">
         <v>38</v>
@@ -4785,237 +4800,237 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>493</v>
+        <v>101</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>494</v>
+        <v>60</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F112" s="8" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F113" s="5">
-        <v>80121</v>
+        <v>10</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>406</v>
+        <v>519</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>264</v>
+        <v>69</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>408</v>
+        <v>71</v>
       </c>
       <c r="F114" s="5">
-        <v>38121</v>
+        <v>80121</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>268</v>
+        <v>73</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>36</v>
+        <v>408</v>
       </c>
       <c r="F115" s="5">
-        <v>20123</v>
+        <v>38121</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F116" s="5">
-        <v>90139</v>
+        <v>20123</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>195</v>
+        <v>361</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F117" s="5">
-        <v>20123</v>
+        <v>90139</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>455</v>
+        <v>345</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>456</v>
+        <v>195</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F118" s="8" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F118" s="5">
+        <v>20123</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>283</v>
+        <v>455</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>309</v>
+        <v>456</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="F119" s="5">
-        <v>12037</v>
+        <v>10</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>13</v>
+        <v>283</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>14</v>
+        <v>309</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F120" s="5" t="s">
-        <v>15</v>
+        <v>310</v>
+      </c>
+      <c r="F120" s="5">
+        <v>12037</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>11</v>
+        <v>307</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>28</v>
@@ -5038,58 +5053,58 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>498</v>
+        <v>27</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C125" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
@@ -5098,8 +5113,8 @@
       <c r="E125" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F125" s="5">
-        <v>39100</v>
+      <c r="F125" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G125" s="4" t="s">
         <v>32</v>
@@ -5107,76 +5122,76 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>233</v>
+        <v>498</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C126" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F126" s="5" t="s">
-        <v>218</v>
+        <v>30</v>
+      </c>
+      <c r="F126" s="5">
+        <v>39100</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>188</v>
+        <v>233</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>483</v>
+        <v>590</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>484</v>
+        <v>34</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>485</v>
+        <v>591</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>486</v>
+        <v>36</v>
       </c>
       <c r="F128" s="5">
-        <v>66020</v>
+        <v>20122</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>576</v>
+        <v>188</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>34</v>
@@ -5185,13 +5200,13 @@
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>577</v>
+        <v>189</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F129" s="5">
-        <v>20124</v>
+      <c r="F129" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G129" s="4" t="s">
         <v>159</v>
@@ -5199,168 +5214,168 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>411</v>
+        <v>483</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>341</v>
+        <v>484</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>412</v>
+        <v>485</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>413</v>
+        <v>486</v>
       </c>
       <c r="F130" s="5">
-        <v>37137</v>
+        <v>66020</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>343</v>
+        <v>77</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>460</v>
+        <v>576</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>461</v>
+        <v>577</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F131" s="8" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F131" s="5">
+        <v>20124</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>295</v>
+        <v>411</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>296</v>
+        <v>341</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>297</v>
+        <v>412</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>298</v>
+        <v>413</v>
       </c>
       <c r="F132" s="5">
-        <v>56010</v>
+        <v>37137</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>299</v>
+        <v>343</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>311</v>
+        <v>460</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>312</v>
+        <v>461</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="F133" s="5">
-        <v>40060</v>
+        <v>10</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>384</v>
+        <v>295</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>36</v>
+        <v>298</v>
       </c>
       <c r="F134" s="5">
-        <v>20121</v>
+        <v>56010</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>386</v>
+        <v>311</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>385</v>
+        <v>312</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F135" s="5" t="s">
-        <v>58</v>
+        <v>313</v>
+      </c>
+      <c r="F135" s="5">
+        <v>40060</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>213</v>
+        <v>384</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>179</v>
+        <v>385</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F136" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F136" s="5">
+        <v>20121</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>575</v>
+        <v>386</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>34</v>
@@ -5369,228 +5384,228 @@
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>192</v>
+        <v>385</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F137" s="5">
-        <v>20124</v>
+      <c r="F137" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>589</v>
+        <v>213</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F138" s="5">
-        <v>20124</v>
+        <v>10</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>68</v>
+        <v>575</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>72</v>
+        <v>36</v>
+      </c>
+      <c r="F139" s="5">
+        <v>20124</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>284</v>
+        <v>589</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>314</v>
+        <v>34</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>315</v>
+        <v>192</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>316</v>
+        <v>36</v>
       </c>
       <c r="F140" s="5">
-        <v>57021</v>
+        <v>20124</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>299</v>
+        <v>159</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>179</v>
+        <v>70</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>462</v>
+        <v>284</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F142" s="8" t="s">
-        <v>180</v>
+        <v>316</v>
+      </c>
+      <c r="F142" s="5">
+        <v>57021</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>346</v>
+        <v>462</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>347</v>
+        <v>179</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F144" s="5">
-        <v>70124</v>
+        <v>10</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>333</v>
+        <v>89</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F145" s="5">
-        <v>20158</v>
+        <v>92</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>308</v>
+        <v>40</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="F146" s="5">
-        <v>12084</v>
+        <v>70124</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>307</v>
+        <v>44</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>34</v>
@@ -5599,182 +5614,182 @@
         <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F147" s="5" t="s">
-        <v>61</v>
+      <c r="F147" s="5">
+        <v>20158</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>227</v>
+        <v>357</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>228</v>
+        <v>358</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>37</v>
+        <v>359</v>
+      </c>
+      <c r="F148" s="5">
+        <v>12084</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>457</v>
+        <v>194</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>458</v>
+        <v>195</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F149" s="8" t="s">
-        <v>459</v>
+        <v>36</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>108</v>
+        <v>227</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F151" s="5">
-        <v>12100</v>
+        <v>10</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>459</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>395</v>
+        <v>108</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F152" s="5">
-        <v>40127</v>
+        <v>111</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>355</v>
+        <v>431</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>356</v>
+        <v>432</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>36</v>
+        <v>433</v>
       </c>
       <c r="F153" s="5">
-        <v>20121</v>
+        <v>12100</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>556</v>
+        <v>395</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>525</v>
+        <v>23</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F154" s="5">
-        <v>20154</v>
+        <v>40127</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>526</v>
+        <v>355</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>34</v>
@@ -5783,21 +5798,21 @@
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>525</v>
+        <v>356</v>
       </c>
       <c r="E155" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F155" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>524</v>
+        <v>556</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>34</v>
@@ -5820,99 +5835,99 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F157" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>232</v>
+        <v>524</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F158" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F158" s="5">
+        <v>20154</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>143</v>
+        <v>515</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="F159" s="5">
+        <v>39100</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>441</v>
+        <v>143</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>34</v>
@@ -5921,159 +5936,159 @@
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>442</v>
+        <v>144</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="F161" s="5">
-        <v>20038</v>
+        <v>36</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>426</v>
+        <v>56</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F162" s="5">
-        <v>10121</v>
+        <v>36</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>95</v>
+        <v>441</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>97</v>
+        <v>442</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>99</v>
+        <v>443</v>
+      </c>
+      <c r="F163" s="5">
+        <v>20038</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>377</v>
+        <v>426</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>379</v>
+        <v>236</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>380</v>
+        <v>81</v>
       </c>
       <c r="F164" s="5">
-        <v>64020</v>
+        <v>10121</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>580</v>
+        <v>95</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>581</v>
+        <v>97</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F165" s="8" t="s">
-        <v>582</v>
+        <v>98</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>11</v>
+        <v>100</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>34</v>
+        <v>378</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>211</v>
+        <v>379</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>36</v>
+        <v>380</v>
       </c>
       <c r="F166" s="5">
-        <v>20121</v>
+        <v>64020</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>133</v>
+        <v>580</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>134</v>
+        <v>581</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>135</v>
+        <v>10</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>582</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>257</v>
+        <v>410</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>34</v>
@@ -6082,13 +6097,13 @@
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="E168" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F168" s="5" t="s">
-        <v>58</v>
+      <c r="F168" s="5">
+        <v>20121</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>38</v>
@@ -6096,30 +6111,30 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>340</v>
+        <v>133</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>342</v>
+        <v>134</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="F169" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>343</v>
+        <v>136</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>34</v>
@@ -6128,44 +6143,44 @@
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>167</v>
+        <v>258</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>529</v>
+        <v>340</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>167</v>
+        <v>342</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>36</v>
+        <v>528</v>
       </c>
       <c r="F171" s="5">
-        <v>20126</v>
+        <v>37045</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>159</v>
+        <v>343</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>471</v>
+        <v>166</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>34</v>
@@ -6174,21 +6189,21 @@
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E172" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F172" s="5">
-        <v>20135</v>
+      <c r="F172" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>405</v>
+        <v>529</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>34</v>
@@ -6197,44 +6212,44 @@
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E173" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F173" s="5">
-        <v>20135</v>
+        <v>20126</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>204</v>
+        <v>594</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>205</v>
+        <v>394</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F174" s="5">
+        <v>20123</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>319</v>
+        <v>38</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>34</v>
@@ -6243,21 +6258,21 @@
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>454</v>
+        <v>260</v>
       </c>
       <c r="E175" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F175" s="5">
-        <v>20144</v>
+        <v>20135</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>223</v>
+        <v>405</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>34</v>
@@ -6266,389 +6281,389 @@
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="E176" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F176" s="5" t="s">
-        <v>135</v>
+      <c r="F176" s="5">
+        <v>20135</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>136</v>
+        <v>262</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>285</v>
+        <v>204</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>22</v>
+        <v>185</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F177" s="5">
-        <v>40026</v>
+        <v>186</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>26</v>
+        <v>319</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>286</v>
+        <v>453</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>320</v>
+        <v>454</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>323</v>
+        <v>36</v>
+      </c>
+      <c r="F178" s="5">
+        <v>20144</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>533</v>
+        <v>223</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F179" s="5">
-        <v>39100</v>
+        <v>36</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>367</v>
+        <v>285</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>368</v>
+        <v>317</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="F180" s="5">
-        <v>20123</v>
+        <v>40026</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F181" s="5">
-        <v>12020</v>
+        <v>10</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>307</v>
+        <v>11</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>39</v>
+        <v>533</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
+      </c>
+      <c r="F182" s="5">
+        <v>39100</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>422</v>
+        <v>34</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>423</v>
+        <v>368</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>424</v>
+        <v>36</v>
       </c>
       <c r="F183" s="5">
-        <v>28053</v>
+        <v>20123</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>172</v>
+        <v>287</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>169</v>
+        <v>321</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>171</v>
+        <v>322</v>
+      </c>
+      <c r="F184" s="5">
+        <v>12020</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>159</v>
+        <v>307</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>560</v>
+        <v>39</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>561</v>
+        <v>41</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F185" s="5">
-        <v>39100</v>
+        <v>42</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>198</v>
+        <v>421</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>22</v>
+        <v>422</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>199</v>
+        <v>423</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>200</v>
+        <v>424</v>
+      </c>
+      <c r="F186" s="5">
+        <v>28053</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>244</v>
+        <v>560</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>177</v>
+        <v>561</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F188" s="5" t="s">
-        <v>58</v>
+        <v>30</v>
+      </c>
+      <c r="F188" s="5">
+        <v>39100</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>534</v>
+        <v>198</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F189" s="10">
-        <v>20121</v>
+        <v>24</v>
+      </c>
+      <c r="F189" s="10" t="s">
+        <v>200</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>578</v>
+        <v>207</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>579</v>
+        <v>208</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F190" s="10">
-        <v>20121</v>
+        <v>71</v>
+      </c>
+      <c r="F190" s="10" t="s">
+        <v>209</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>445</v>
+        <v>244</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>447</v>
+        <v>177</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="F191" s="10">
-        <v>53048</v>
+        <v>36</v>
+      </c>
+      <c r="F191" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>449</v>
+        <v>38</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>509</v>
+        <v>34</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>517</v>
+        <v>177</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>518</v>
+        <v>36</v>
       </c>
       <c r="F192" s="10">
-        <v>35011</v>
+        <v>20121</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>505</v>
+        <v>38</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>243</v>
+        <v>578</v>
       </c>
       <c r="B193" s="9" t="s">
         <v>34</v>
@@ -6657,13 +6672,13 @@
         <v>8</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>177</v>
+        <v>579</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F193" s="10" t="s">
-        <v>58</v>
+      <c r="F193" s="10">
+        <v>20121</v>
       </c>
       <c r="G193" s="9" t="s">
         <v>38</v>
@@ -6671,99 +6686,99 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>131</v>
+        <v>445</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>28</v>
+        <v>446</v>
       </c>
       <c r="C194" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>132</v>
+        <v>447</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F194" s="10" t="s">
-        <v>31</v>
+        <v>448</v>
+      </c>
+      <c r="F194" s="10">
+        <v>53048</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>32</v>
+        <v>449</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>34</v>
+        <v>509</v>
       </c>
       <c r="C195" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>36</v>
+        <v>518</v>
       </c>
       <c r="F195" s="10">
-        <v>20121</v>
+        <v>35011</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C196" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F196" s="10" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A197" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="B197" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C197" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="E197" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F197" s="11" t="s">
-        <v>568</v>
-      </c>
-      <c r="G197" s="3" t="s">
-        <v>77</v>
+      <c r="A197" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C197" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D197" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E197" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F197" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G197" s="9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>381</v>
+        <v>531</v>
       </c>
       <c r="B198" s="9" t="s">
         <v>34</v>
@@ -6772,13 +6787,13 @@
         <v>8</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>382</v>
+        <v>532</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>383</v>
+        <v>36</v>
       </c>
       <c r="F198" s="10">
-        <v>20089</v>
+        <v>20121</v>
       </c>
       <c r="G198" s="9" t="s">
         <v>38</v>
@@ -6786,53 +6801,53 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="B199" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C199" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D199" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E199" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F199" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G199" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A200" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B200" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C199" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D199" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="E199" s="9" t="s">
+      <c r="C200" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="E200" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F199" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="G199" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A200" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="B200" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C200" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D200" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="E200" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F200" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="G200" s="9" t="s">
-        <v>26</v>
+      <c r="F200" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>214</v>
+        <v>381</v>
       </c>
       <c r="B201" s="9" t="s">
         <v>34</v>
@@ -6841,67 +6856,67 @@
         <v>8</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>215</v>
+        <v>382</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F201" s="10" t="s">
-        <v>158</v>
+        <v>383</v>
+      </c>
+      <c r="F201" s="10">
+        <v>20089</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C202" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>215</v>
+        <v>476</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F202" s="10">
-        <v>20124</v>
+        <v>10</v>
+      </c>
+      <c r="F202" s="12" t="s">
+        <v>477</v>
       </c>
       <c r="G202" s="9" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C203" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F203" s="10" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>136</v>
+        <v>26</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="B204" s="9" t="s">
         <v>34</v>
@@ -6910,21 +6925,21 @@
         <v>8</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E204" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F204" s="10" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G204" s="9" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
-        <v>472</v>
+        <v>438</v>
       </c>
       <c r="B205" s="9" t="s">
         <v>34</v>
@@ -6933,21 +6948,21 @@
         <v>8</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>464</v>
+        <v>215</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F205" s="10">
-        <v>20129</v>
+        <v>20124</v>
       </c>
       <c r="G205" s="9" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
-        <v>463</v>
+        <v>229</v>
       </c>
       <c r="B206" s="9" t="s">
         <v>34</v>
@@ -6956,21 +6971,21 @@
         <v>8</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E206" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F206" s="10">
-        <v>20129</v>
+      <c r="F206" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G206" s="9" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
-        <v>473</v>
+        <v>256</v>
       </c>
       <c r="B207" s="9" t="s">
         <v>34</v>
@@ -6979,21 +6994,21 @@
         <v>8</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F207" s="10">
-        <v>20129</v>
+      <c r="F207" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B208" s="9" t="s">
         <v>34</v>
@@ -7016,7 +7031,7 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
-        <v>176</v>
+        <v>463</v>
       </c>
       <c r="B209" s="9" t="s">
         <v>34</v>
@@ -7025,128 +7040,128 @@
         <v>8</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="E209" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F209" s="10" t="s">
-        <v>58</v>
+      <c r="F209" s="10">
+        <v>20129</v>
       </c>
       <c r="G209" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
-        <v>331</v>
+        <v>473</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C210" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D210" s="9" t="s">
-        <v>332</v>
+        <v>464</v>
       </c>
       <c r="E210" s="9" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F210" s="10">
-        <v>40026</v>
+        <v>20129</v>
       </c>
       <c r="G210" s="9" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
-        <v>288</v>
+        <v>474</v>
       </c>
       <c r="B211" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C211" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>324</v>
+        <v>464</v>
       </c>
       <c r="E211" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F211" s="10">
-        <v>20124</v>
+        <v>20129</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
-        <v>450</v>
+        <v>176</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C212" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>451</v>
+        <v>177</v>
       </c>
       <c r="E212" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="F212" s="10">
-        <v>12011</v>
+        <v>36</v>
+      </c>
+      <c r="F212" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G212" s="9" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
-        <v>151</v>
+        <v>331</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>152</v>
+        <v>22</v>
       </c>
       <c r="C213" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D213" s="9" t="s">
-        <v>153</v>
+        <v>332</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F213" s="10" t="s">
-        <v>155</v>
+        <v>318</v>
+      </c>
+      <c r="F213" s="10">
+        <v>40026</v>
       </c>
       <c r="G213" s="9" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
-        <v>419</v>
+        <v>288</v>
       </c>
       <c r="B214" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C214" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D214" s="9" t="s">
-        <v>420</v>
+        <v>324</v>
       </c>
       <c r="E214" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F214" s="10">
-        <v>20123</v>
+        <v>20124</v>
       </c>
       <c r="G214" s="9" t="s">
         <v>38</v>
@@ -7154,329 +7169,329 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
-        <v>491</v>
+        <v>450</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="C215" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D215" s="9" t="s">
-        <v>492</v>
+        <v>451</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>19</v>
+        <v>452</v>
       </c>
       <c r="F215" s="10">
-        <v>90141</v>
+        <v>12011</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>12</v>
+        <v>307</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
-        <v>480</v>
+        <v>151</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>9</v>
+        <v>152</v>
       </c>
       <c r="C216" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D216" s="9" t="s">
-        <v>388</v>
+        <v>153</v>
       </c>
       <c r="E216" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F216" s="12" t="s">
-        <v>390</v>
+        <v>154</v>
+      </c>
+      <c r="F216" s="10" t="s">
+        <v>155</v>
       </c>
       <c r="G216" s="9" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A217" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="B217" s="3" t="s">
-        <v>9</v>
+      <c r="A217" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="B217" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="C217" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D217" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E217" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F217" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="G217" s="3" t="s">
-        <v>11</v>
+      <c r="D217" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E217" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F217" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G217" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="9" t="s">
-        <v>387</v>
+        <v>491</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C218" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D218" s="9" t="s">
-        <v>388</v>
+        <v>492</v>
       </c>
       <c r="E218" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F218" s="10" t="s">
-        <v>390</v>
+        <v>19</v>
+      </c>
+      <c r="F218" s="10">
+        <v>90141</v>
       </c>
       <c r="G218" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C219" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>466</v>
+        <v>388</v>
       </c>
       <c r="E219" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="F219" s="10">
-        <v>38055</v>
+        <v>10</v>
+      </c>
+      <c r="F219" s="12" t="s">
+        <v>390</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="3" t="s">
-        <v>572</v>
+        <v>530</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C220" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C220" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>134</v>
+        <v>388</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F220" s="7">
-        <v>20145</v>
+        <v>10</v>
+      </c>
+      <c r="F220" s="11" t="s">
+        <v>390</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="C221" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D221" s="9" t="s">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="F221" s="10">
-        <v>25010</v>
+        <v>10</v>
+      </c>
+      <c r="F221" s="10" t="s">
+        <v>390</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="9" t="s">
-        <v>393</v>
+        <v>465</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C222" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>394</v>
+        <v>466</v>
       </c>
       <c r="E222" s="9" t="s">
-        <v>36</v>
+        <v>467</v>
       </c>
       <c r="F222" s="10">
-        <v>20123</v>
+        <v>38055</v>
       </c>
       <c r="G222" s="9" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A223" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="B223" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C223" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D223" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="E223" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="F223" s="10">
-        <v>71016</v>
-      </c>
-      <c r="G223" s="9" t="s">
-        <v>44</v>
+      <c r="A223" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F223" s="7">
+        <v>20145</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="9" t="s">
-        <v>16</v>
+        <v>427</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="C224" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D224" s="9" t="s">
-        <v>18</v>
+        <v>428</v>
       </c>
       <c r="E224" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F224" s="10" t="s">
-        <v>20</v>
+        <v>429</v>
+      </c>
+      <c r="F224" s="10">
+        <v>25010</v>
       </c>
       <c r="G224" s="9" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="9" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="B225" s="9" t="s">
-        <v>326</v>
+        <v>34</v>
       </c>
       <c r="C225" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D225" s="9" t="s">
-        <v>327</v>
+        <v>394</v>
       </c>
       <c r="E225" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="F225" s="10" t="s">
-        <v>329</v>
+        <v>36</v>
+      </c>
+      <c r="F225" s="10">
+        <v>20123</v>
       </c>
       <c r="G225" s="9" t="s">
-        <v>330</v>
+        <v>38</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A226" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="E226" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F226" s="7">
-        <v>20122</v>
-      </c>
-      <c r="G226" s="3" t="s">
-        <v>38</v>
+      <c r="A226" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="B226" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C226" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D226" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="E226" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="F226" s="10">
+        <v>71016</v>
+      </c>
+      <c r="G226" s="9" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="9" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C227" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D227" s="9" t="s">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="E227" s="9" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F227" s="10" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="9" t="s">
-        <v>478</v>
+        <v>325</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="C228" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D228" s="9" t="s">
-        <v>479</v>
+        <v>327</v>
       </c>
       <c r="E228" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F228" s="10">
-        <v>20123</v>
+        <v>328</v>
+      </c>
+      <c r="F228" s="10" t="s">
+        <v>329</v>
       </c>
       <c r="G228" s="9" t="s">
-        <v>38</v>
+        <v>330</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="3" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>34</v>
@@ -7485,13 +7500,13 @@
         <v>8</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>571</v>
+        <v>36</v>
       </c>
       <c r="F229" s="7">
-        <v>20094</v>
+        <v>20122</v>
       </c>
       <c r="G229" s="3" t="s">
         <v>38</v>
@@ -7499,76 +7514,76 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="9" t="s">
-        <v>396</v>
+        <v>277</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C230" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D230" s="9" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="E230" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F230" s="10" t="s">
-        <v>218</v>
+        <v>37</v>
       </c>
       <c r="G230" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="9" t="s">
-        <v>216</v>
+        <v>478</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C231" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D231" s="9" t="s">
-        <v>217</v>
+        <v>479</v>
       </c>
       <c r="E231" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F231" s="10" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F231" s="10">
+        <v>20123</v>
       </c>
       <c r="G231" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A232" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="B232" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C232" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D232" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="E232" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F232" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G232" s="9" t="s">
-        <v>165</v>
+      <c r="A232" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="F232" s="7">
+        <v>20094</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="9" t="s">
-        <v>434</v>
+        <v>396</v>
       </c>
       <c r="B233" s="9" t="s">
         <v>9</v>
@@ -7591,7 +7606,7 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="9" t="s">
-        <v>255</v>
+        <v>216</v>
       </c>
       <c r="B234" s="9" t="s">
         <v>9</v>
@@ -7614,30 +7629,99 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B235" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C235" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D235" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E235" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F235" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G235" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A236" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B236" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C236" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D236" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E236" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F236" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G236" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A237" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B237" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C237" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D237" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E237" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F237" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G237" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A238" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B235" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C235" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D235" s="9" t="s">
+      <c r="B238" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C238" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D238" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E235" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F235" s="10" t="s">
+      <c r="E238" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F238" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G235" s="9" t="s">
+      <c r="G238" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G235">
+    <sortState ref="A2:G238">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -7650,14 +7734,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F040406D9EE34E48977C379A242BB45D" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ab2d492e43f6bec9a26aa4599c840e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="877b7d34-4df7-40bf-9eb1-208952470e96" xmlns:ns4="05fc27dd-4454-4248-9c78-3d72b2b155c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc604e5d4aadf5a992ba83f8d4fb519" ns3:_="" ns4:_="">
     <xsd:import namespace="877b7d34-4df7-40bf-9eb1-208952470e96"/>
@@ -7890,6 +7966,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -7900,23 +7984,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC6436E-C4E7-4E8D-94E8-64DAEC05792B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7935,6 +8002,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
   <ds:schemaRefs>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="14_{71F6E7E0-BB3F-481B-BA34-56C6BE90288E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{ECA58198-9EC6-48F7-8BE0-30F431221322}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="113_{1398BFE9-7F31-4A84-A4C4-391DE17DDF9A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{3402415C-7B21-45D3-8856-1636A6034240}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="596">
   <si>
     <t>Nome account</t>
   </si>
@@ -1808,6 +1808,9 @@
   </si>
   <si>
     <t>RERE 62 SRL</t>
+  </si>
+  <si>
+    <t>APOLLO SAN SEVERO SRL</t>
   </si>
 </sst>
 </file>
@@ -2232,7 +2235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G238"/>
+  <dimension ref="A1:G239"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -2753,76 +2756,76 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>399</v>
+        <v>595</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F23" s="5">
-        <v>20124</v>
+        <v>39100</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>468</v>
+        <v>399</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>469</v>
+        <v>400</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>470</v>
+        <v>36</v>
+      </c>
+      <c r="F24" s="5">
+        <v>20124</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>305</v>
+        <v>469</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>470</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>349</v>
+        <v>436</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>34</v>
@@ -2831,13 +2834,13 @@
         <v>8</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>350</v>
+        <v>305</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F26" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>38</v>
@@ -2845,53 +2848,53 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>67</v>
+        <v>349</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>18</v>
+        <v>350</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F27" s="5">
+        <v>20122</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>398</v>
+        <v>67</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F28" s="5">
-        <v>10123</v>
+        <v>19</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDes